--- a/docassemble/PowerOfAttorneyHealthCare/data/sources/poa_hc_es.xlsx
+++ b/docassemble/PowerOfAttorneyHealthCare/data/sources/poa_hc_es.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnewsted\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC64C83B-1430-44AD-8FCF-CB9C3972A0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F5A3949-6F06-4366-A4CE-A0D8643C3E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="24" yWindow="120" windowWidth="23016" windowHeight="12216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1667" uniqueCount="791">
   <si>
     <t>interview</t>
   </si>
@@ -22755,6 +22755,19 @@
       </rPr>
       <t>% endif</t>
     </r>
+  </si>
+  <si>
+    <t>docassemble.playground3PoAHealthCareSpanish:power_of_attorney_for_health_care.yml</t>
+  </si>
+  <si>
+    <t>64ed875eeb30496e64d73b9be2b5030e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">About the witness
+</t>
+  </si>
+  <si>
+    <t>Acerca del testigo</t>
   </si>
 </sst>
 </file>
@@ -23219,7 +23232,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H237"/>
+  <dimension ref="A1:H238"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="61.109375" customWidth="1"/>
@@ -29391,6 +29404,32 @@
         <v>602</v>
       </c>
     </row>
+    <row r="238" spans="1:8">
+      <c r="A238" t="s">
+        <v>787</v>
+      </c>
+      <c r="B238" t="s">
+        <v>599</v>
+      </c>
+      <c r="C238">
+        <v>1</v>
+      </c>
+      <c r="D238" t="s">
+        <v>788</v>
+      </c>
+      <c r="E238" t="s">
+        <v>11</v>
+      </c>
+      <c r="F238" t="s">
+        <v>12</v>
+      </c>
+      <c r="G238" t="s">
+        <v>789</v>
+      </c>
+      <c r="H238" s="4" t="s">
+        <v>790</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/docassemble/PowerOfAttorneyHealthCare/data/sources/poa_hc_es.xlsx
+++ b/docassemble/PowerOfAttorneyHealthCare/data/sources/poa_hc_es.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnewsted\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F5A3949-6F06-4366-A4CE-A0D8643C3E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5533994-9589-4A66-A80F-83B63FDC31AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="120" windowWidth="23016" windowHeight="12216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16116,118 +16116,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if not user_logged_in():
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[${fa_icon("sign-in-alt", color="#0079d0", size="sm")} **Iniciar sesión**]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${url_of('login', next=interview_url())}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>) o [**crear**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${url_of('register', next=interview_url())}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">) una cuenta de Formularios Guiados de ILAO para guardar tu progreso (opcional).
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${ action_button_html(interview_url(i="docassemble.ILAO:feedback.yml", easy_form_interview=ilao_easy_form_url, easy_form_title=ilao_easy_form_title, easy_form_page=current_context().question_id, easy_form_variable=current_context().variable, local=False,reset=1), label='^^comment^^ ¿Fue útil este programa?', color="#181c36", size="md", new_window=True) }</t>
-    </r>
-  </si>
-  <si>
     <t>Empodérate de tu Futuro - Pérdida de memoria</t>
   </si>
   <si>
@@ -21509,6 +21397,1074 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Tus formularios están listos. Puedes verlos y descargarlos abajo. Haz clic en **Hacer cambios** para corregir cualquier error.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if user_path == "Shirley":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[YOUTUBE NE0faXuz5v4]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif user_path == "Frederico" or user_path == "Federico":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[YOUTUBE g5Vdv0hWJ6g]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif user_path == "Lisa":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[YOUTUBE F2QbdrhcZ0g]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Lee las instrucciones para saber qué hacer después.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ action_button_html(url_action('review_answers'), label=':edit: Hacer cambios', color='success', size="md") }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ al_user_bundle.download_list_html() }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+&amp;nbsp;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ al_user_bundle.send_button_html(show_editable_checkbox=False) }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+**Nota:** El Poder Notarial debe firmarse frente a al menos un testigo para que sea válido.
+¡Gracias por usar los Formularios Guiados de ILAO!</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Bienvenido(a) al Formulario Guiado de Poder Notarial para el Cuidado de la Salud de Illinois Legal Aid Online.
+Este programa te ayuda a crear documentos que le dan a alguien en quien confías el poder legal para tomar decisiones sobre tu atención médica. Esto significa que esa persona podrá tomar decisiones sobre tu atención médica cuando no puedas hacerlo tú mismo(a). También puedes permitir que esa persona tome decisiones sobre tu atención médica antes, si así lo decides.
+Este programa incluye videos con información sobre cómo hacer un Poder Notarial para el Cuidado de la Salud. No tienes que verlos, pero pueden serte útiles.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if user_path == "Shirley":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">[YOUTUBE 7qy101TRdiI]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif user_path == "Frederico" or user_path == "Federico":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">[YOUTUBE GR9t6ygX13g]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif user_path == "Lisa":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">[YOUTUBE h2ZGl568xHo]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Para obtener más información, lee el artículo de ILAO sobre los [**Conceptos Básicos del Poder Notarial para el Cuidado de la Salud**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://es.illinoislegalaid.org/legal-information/setting-power-attorney-healthcare</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Después de descargar tus formularios, tendrás que firmar el documento frente a un testigo. El testigo también tendrá que firmar el documento. No necesitas saber quién será el testigo para usar este programa.
+Después de que el formulario esté firmado, querrás entregar copias del poder notarial a tu agente, así como a tus proveedores de atención médica. Tus formularios incluirán instrucciones con más información.
+Para obtener más información, lee el artículo de ILAO sobre los [**Conceptos Básicos del Poder Notarial para el Cuidado de la Salud**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://es.illinoislegalaid.org/legal-information/setting-power-attorney-healthcare</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).
+Si deseas saber más sobre la planificación en caso de discapacidad o el cuidado al final de la vida, puedes revisar la guía de ILAO y CDEL [**Empodérate de tu Futuro**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ preview.url_for() }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Tu agente es una persona en quien confías y que eliges para tomar decisiones sobre tu atención médica y cuidado de tu salud por ti, si alguna vez necesitas ayuda. 
+Tu agente debe tener al menos 18 años de edad. Tu agente no tiene que ser un familiar, pero debe ser alguien en quien confíes. Tu agente no necesita ser ciudadano de los Estados Unidos. 
+Puedes seleccionar agentes sucesores como respaldo si el primer agente no puede tomar estas decisiones.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">${collapse_template(video_who_agent)}
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+ **Nota:** Si puedes comunicarte y entender tus opciones, tú eres quien toma las decisiones.
+Para obtener más información, lee el artículo de ILAO sobre [**Conceptos Básicos del Poder Notarial para el Cuidado de la Salud**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://es.illinoislegalaid.org/legal-information/setting-power-attorney-healthcare</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>No. Puedes nombrar como agente a alguien que vive fuera de los Estados Unidos. El agente no necesita ser ciudadano de los Estados Unidos. Sin embargo, pueden haber problemas si un banco u otra institución financiera no puede comunicarse con esa persona. Es posible que desees consultar a un abogado para obtener asesoramiento. Usa [**Obtener ayuda legal**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://es.illinoislegalaid.org/get-legal-help</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) para encontrar servicios legales gratuitos o de bajo costo en tu área.
+Para direcciones internacionales, habrá espacio para ingresar la dirección en dos líneas. Debes escribir la dirección internacional usando el alfabeto inglés.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Puedes cambiar de opinión y poner fin a tu Poder Notarial para el Cuidado de la Salud en cualquier momento. Esto se llama revocación.
+La revocación significa que dejas de permitir que </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tome decisiones por ti. Para obtener más información, lee el artículo de ILAO sobre [**poner fin a un Poder Notarial**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://es.illinoislegalaid.org/legal-information/ending-power-attorney-0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).
+Puedes poner fin a un Poder Notarial haciendo una revocación formal. Para hacer una Revocación de Poder Notarial, usa el [**Formulario Guiado de Revocación de Poder Notarial**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://es.illinoislegalaid.org/legal-information/power-attorney-revocation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> puede cambiar de opinión y poner fin a su Poder Notarial para el Cuidado de la Salud en cualquier momento. Esto se llama revocación.
+La revocación significa que </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> deja de permitir que </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tome decisiones en su nombre. Para obtener más información, lee el artículo de ILAO sobre [**poner fin a un Poder Notarial**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://es.illinoislegalaid.org/legal-information/ending-power-attorney-0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> puede poner fin a un Poder Notarial haciendo una revocación formal. Para hacer una Revocación de Poder Notarial, usa el [**Formulario Guiado de Revocación de Poder Notarial**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://es.illinoislegalaid.org/legal-information/power-attorney-revocation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% endif</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>No. Puedes nombrar como agente sucesor a alguien que vive fuera de los Estados Unidos. El agente sucesor no necesita ser ciudadano de los Estados Unidos. Sin embargo, puede haber problemas si un banco u otra institución financiera no puede comunicarse con esa persona. Es posible que desees consultar con un abogado. Usa [**Obtener ayuda legal**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://es.illinoislegalaid.org/get-legal-help</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) para encontrar servicios legales gratuitos o de bajo costo en tu área.
+Para direcciones internacionales, habrá espacio para ingresar la dirección en dos líneas.
+Debes escribir la dirección internacional usando el alfabeto inglés.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Tus formularios están adjuntos.
+¡Gracias por usar los Formularios Guiados de ILAO!
+[Illinois Legal Aid Online](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://es.illinoislegalaid.org</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**Estás haciendo estos formularios para:**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Para mí
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Para otra persona
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% endif</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">**Your treatment instructions:**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if quality_of_life == 'quality':
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">The quality of my life is more important than the length of my life.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+% if quality_of_life == 'longevity':
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">I want my life to be prolonged to the greatest extent possible.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+% if quality_of_life == 'do_not':
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">I do not want to decide this now.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>**Tus instrucciones sobre tratamiento:**</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+% if quality_of_life == 'quality':
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">La calidad de mi vida es más importante que la duración de mi vida.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+% if quality_of_life == 'longevity':
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Quiero que mi vida se prolongue en la mayor medida posible.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+% if quality_of_life == 'do_not':
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">No quiero decidir esto ahora.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% endif</t>
+    </r>
+  </si>
+  <si>
+    <t>docassemble.playground3PoAHealthCareSpanish:power_of_attorney_for_health_care.yml</t>
+  </si>
+  <si>
+    <t>64ed875eeb30496e64d73b9be2b5030e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">About the witness
+</t>
+  </si>
+  <si>
+    <t>Acerca del testigo</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">Your forms are ready. View and download your forms below. Click **Make changes** to fix any mistakes.
 </t>
     </r>
@@ -21711,37 +22667,91 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Tus formularios están listos. Puedes verlos y descargarlos abajo. Haz clic en **Hacer cambios** para corregir cualquier error.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if user_path == "Shirley":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[YOUTUBE NE0faXuz5v4]</t>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if not user_logged_in():
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[${fa_icon("sign-in-alt", color="#0079d0", size="sm")} **Iniciar sesión**]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${url_of('login', next=interview_url())}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) o [**crear**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${url_of('register', next=interview_url())}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) una cuenta de Formularios Guiados de ILAO para guardar tu progreso (opcional).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
     </r>
     <r>
       <rPr>
@@ -21758,1016 +22768,13 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif user_path == "Frederico" or user_path == "Federico":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[YOUTUBE g5Vdv0hWJ6g]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif user_path == "Lisa":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[YOUTUBE F2QbdrhcZ0g]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Lee las instrucciones para saber qué hacer después.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${ action_button_html(url_action('review_answers'), label=':edit: Hacer cambios', color='success', size="md") }</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${ al_user_bundle.download_list_html() }</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-&amp;nbsp;
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${ al_user_bundle.send_button_html(show_editable_checkbox=False) }</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-**Nota:** El Poder Notarial debe firmarse frente a al menos un testigo para que sea válido.
-¡Gracias por usar los Formularios Guiados de ILAO!</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Bienvenido(a) al Formulario Guiado de Poder Notarial para el Cuidado de la Salud de Illinois Legal Aid Online.
-Este programa te ayuda a crear documentos que le dan a alguien en quien confías el poder legal para tomar decisiones sobre tu atención médica. Esto significa que esa persona podrá tomar decisiones sobre tu atención médica cuando no puedas hacerlo tú mismo(a). También puedes permitir que esa persona tome decisiones sobre tu atención médica antes, si así lo decides.
-Este programa incluye videos con información sobre cómo hacer un Poder Notarial para el Cuidado de la Salud. No tienes que verlos, pero pueden serte útiles.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if user_path == "Shirley":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">[YOUTUBE 7qy101TRdiI]
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif user_path == "Frederico" or user_path == "Federico":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">[YOUTUBE GR9t6ygX13g]
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif user_path == "Lisa":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">[YOUTUBE h2ZGl568xHo]
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Para obtener más información, lee el artículo de ILAO sobre los [**Conceptos Básicos del Poder Notarial para el Cuidado de la Salud**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://es.illinoislegalaid.org/legal-information/setting-power-attorney-healthcare</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Después de descargar tus formularios, tendrás que firmar el documento frente a un testigo. El testigo también tendrá que firmar el documento. No necesitas saber quién será el testigo para usar este programa.
-Después de que el formulario esté firmado, querrás entregar copias del poder notarial a tu agente, así como a tus proveedores de atención médica. Tus formularios incluirán instrucciones con más información.
-Para obtener más información, lee el artículo de ILAO sobre los [**Conceptos Básicos del Poder Notarial para el Cuidado de la Salud**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://es.illinoislegalaid.org/legal-information/setting-power-attorney-healthcare</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>).
-Si deseas saber más sobre la planificación en caso de discapacidad o el cuidado al final de la vida, puedes revisar la guía de ILAO y CDEL [**Empodérate de tu Futuro**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${ preview.url_for() }</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Tu agente es una persona en quien confías y que eliges para tomar decisiones sobre tu atención médica y cuidado de tu salud por ti, si alguna vez necesitas ayuda. 
-Tu agente debe tener al menos 18 años de edad. Tu agente no tiene que ser un familiar, pero debe ser alguien en quien confíes. Tu agente no necesita ser ciudadano de los Estados Unidos. 
-Puedes seleccionar agentes sucesores como respaldo si el primer agente no puede tomar estas decisiones.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">${collapse_template(video_who_agent)}
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
- **Nota:** Si puedes comunicarte y entender tus opciones, tú eres quien toma las decisiones.
-Para obtener más información, lee el artículo de ILAO sobre [**Conceptos Básicos del Poder Notarial para el Cuidado de la Salud**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://es.illinoislegalaid.org/legal-information/setting-power-attorney-healthcare</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>No. Puedes nombrar como agente a alguien que vive fuera de los Estados Unidos. El agente no necesita ser ciudadano de los Estados Unidos. Sin embargo, pueden haber problemas si un banco u otra institución financiera no puede comunicarse con esa persona. Es posible que desees consultar a un abogado para obtener asesoramiento. Usa [**Obtener ayuda legal**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://es.illinoislegalaid.org/get-legal-help</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>) para encontrar servicios legales gratuitos o de bajo costo en tu área.
-Para direcciones internacionales, habrá espacio para ingresar la dirección en dos líneas. Debes escribir la dirección internacional usando el alfabeto inglés.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Puedes cambiar de opinión y poner fin a tu Poder Notarial para el Cuidado de la Salud en cualquier momento. Esto se llama revocación.
-La revocación significa que dejas de permitir que </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tome decisiones por ti. Para obtener más información, lee el artículo de ILAO sobre [**poner fin a un Poder Notarial**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://es.illinoislegalaid.org/legal-information/ending-power-attorney-0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>).
-Puedes poner fin a un Poder Notarial haciendo una revocación formal. Para hacer una Revocación de Poder Notarial, usa el [**Formulario Guiado de Revocación de Poder Notarial**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://es.illinoislegalaid.org/legal-information/power-attorney-revocation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">).
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> puede cambiar de opinión y poner fin a su Poder Notarial para el Cuidado de la Salud en cualquier momento. Esto se llama revocación.
-La revocación significa que </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> deja de permitir que </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tome decisiones en su nombre. Para obtener más información, lee el artículo de ILAO sobre [**poner fin a un Poder Notarial**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://es.illinoislegalaid.org/legal-information/ending-power-attorney-0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">). 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> puede poner fin a un Poder Notarial haciendo una revocación formal. Para hacer una Revocación de Poder Notarial, usa el [**Formulario Guiado de Revocación de Poder Notarial**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://es.illinoislegalaid.org/legal-information/power-attorney-revocation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">).
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>No. Puedes nombrar como agente sucesor a alguien que vive fuera de los Estados Unidos. El agente sucesor no necesita ser ciudadano de los Estados Unidos. Sin embargo, puede haber problemas si un banco u otra institución financiera no puede comunicarse con esa persona. Es posible que desees consultar con un abogado. Usa [**Obtener ayuda legal**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://es.illinoislegalaid.org/get-legal-help</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>) para encontrar servicios legales gratuitos o de bajo costo en tu área.
-Para direcciones internacionales, habrá espacio para ingresar la dirección en dos líneas.
-Debes escribir la dirección internacional usando el alfabeto inglés.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Tus formularios están adjuntos.
-¡Gracias por usar los Formularios Guiados de ILAO!
-[Illinois Legal Aid Online](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://es.illinoislegalaid.org</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**Estás haciendo estos formularios para:**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Para mí
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Para otra persona
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">**Your treatment instructions:**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if quality_of_life == 'quality':
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">The quality of my life is more important than the length of my life.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-% if quality_of_life == 'longevity':
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">I want my life to be prolonged to the greatest extent possible.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-% if quality_of_life == 'do_not':
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">I do not want to decide this now.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>**Tus instrucciones sobre tratamiento:**</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-% if quality_of_life == 'quality':
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">La calidad de mi vida es más importante que la duración de mi vida.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-% if quality_of_life == 'longevity':
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Quiero que mi vida se prolongue en la mayor medida posible.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-% if quality_of_life == 'do_not':
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">No quiero decidir esto ahora.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
-    </r>
-  </si>
-  <si>
-    <t>docassemble.playground3PoAHealthCareSpanish:power_of_attorney_for_health_care.yml</t>
-  </si>
-  <si>
-    <t>64ed875eeb30496e64d73b9be2b5030e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">About the witness
-</t>
-  </si>
-  <si>
-    <t>Acerca del testigo</t>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ action_button_html(interview_url(i="docassemble.ILAO:feedback.yml", easy_form_interview=ilao_easy_form_url, easy_form_title=ilao_easy_form_title, easy_form_page=current_context().question_id, easy_form_variable=current_context().variable, local=False,reset=1), label=':comment: ¿Fue útil este programa?', color="#181c36", size="md", new_window=True) }</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -23232,7 +23239,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H238"/>
+  <dimension ref="A1:H240"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="61.109375" customWidth="1"/>
@@ -23317,7 +23324,7 @@
         <v>16</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -23473,7 +23480,7 @@
         <v>33</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="28.8">
@@ -23487,7 +23494,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>11</v>
@@ -23496,7 +23503,7 @@
         <v>12</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>35</v>
@@ -23513,7 +23520,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>11</v>
@@ -23522,7 +23529,7 @@
         <v>12</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>36</v>
@@ -23577,7 +23584,7 @@
         <v>42</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="28.8">
@@ -23681,7 +23688,7 @@
         <v>54</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="28.8">
@@ -23785,7 +23792,7 @@
         <v>66</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="57.6">
@@ -23811,7 +23818,7 @@
         <v>68</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="28.8">
@@ -23967,7 +23974,7 @@
         <v>82</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -24409,7 +24416,7 @@
         <v>125</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -24539,7 +24546,7 @@
         <v>136</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="28.8">
@@ -24565,7 +24572,7 @@
         <v>138</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="28.8">
@@ -24669,7 +24676,7 @@
         <v>149</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="28.8">
@@ -25007,7 +25014,7 @@
         <v>182</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="28.8">
@@ -25033,7 +25040,7 @@
         <v>184</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -25111,7 +25118,7 @@
         <v>190</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -25189,7 +25196,7 @@
         <v>198</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="115.2">
@@ -25241,7 +25248,7 @@
         <v>203</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="28.8">
@@ -25345,7 +25352,7 @@
         <v>213</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -25475,7 +25482,7 @@
         <v>226</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="43.2">
@@ -25527,7 +25534,7 @@
         <v>651</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="72">
@@ -25579,7 +25586,7 @@
         <v>234</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -25735,7 +25742,7 @@
         <v>249</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="129.6">
@@ -25761,7 +25768,7 @@
         <v>251</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="86.4">
@@ -25813,7 +25820,7 @@
         <v>256</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="28.8">
@@ -26096,7 +26103,7 @@
         <v>12</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H110" s="3" t="s">
         <v>663</v>
@@ -26437,7 +26444,7 @@
         <v>313</v>
       </c>
       <c r="H123" s="8" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="28.8">
@@ -26463,7 +26470,7 @@
         <v>315</v>
       </c>
       <c r="H124" s="8" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="28.8">
@@ -26489,7 +26496,7 @@
         <v>317</v>
       </c>
       <c r="H125" s="8" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -26567,7 +26574,7 @@
         <v>324</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -26645,7 +26652,7 @@
         <v>331</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -26711,7 +26718,7 @@
         <v>2</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>11</v>
@@ -26720,10 +26727,10 @@
         <v>12</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="409.6">
@@ -26749,7 +26756,7 @@
         <v>338</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="136" spans="1:8" ht="28.8">
@@ -26983,7 +26990,7 @@
         <v>360</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -27113,7 +27120,7 @@
         <v>374</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="150" spans="1:8" ht="28.8">
@@ -27243,7 +27250,7 @@
         <v>388</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="155" spans="1:8" ht="43.2">
@@ -27347,7 +27354,7 @@
         <v>400</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="100.8">
@@ -27399,7 +27406,7 @@
         <v>405</v>
       </c>
       <c r="H160" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="100.8">
@@ -27555,7 +27562,7 @@
         <v>423</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="57.6">
@@ -27711,7 +27718,7 @@
         <v>708</v>
       </c>
       <c r="H172" s="3" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="28.8">
@@ -27760,10 +27767,10 @@
         <v>12</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>775</v>
+        <v>789</v>
       </c>
       <c r="H174" s="3" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="201.6">
@@ -27789,7 +27796,7 @@
         <v>446</v>
       </c>
       <c r="H175" s="3" t="s">
-        <v>709</v>
+        <v>790</v>
       </c>
     </row>
     <row r="176" spans="1:8" ht="86.4">
@@ -27815,7 +27822,7 @@
         <v>449</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -27867,7 +27874,7 @@
         <v>455</v>
       </c>
       <c r="H178" s="6" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -27893,7 +27900,7 @@
         <v>458</v>
       </c>
       <c r="H179" s="6" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="180" spans="1:8">
@@ -27919,7 +27926,7 @@
         <v>461</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -27945,7 +27952,7 @@
         <v>464</v>
       </c>
       <c r="H181" s="6" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -27971,7 +27978,7 @@
         <v>467</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="183" spans="1:8" ht="144">
@@ -27997,7 +28004,7 @@
         <v>470</v>
       </c>
       <c r="H183" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="28.8">
@@ -28231,7 +28238,7 @@
         <v>496</v>
       </c>
       <c r="H192" s="6" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="193" spans="1:8">
@@ -28309,7 +28316,7 @@
         <v>504</v>
       </c>
       <c r="H195" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="196" spans="1:8">
@@ -28335,7 +28342,7 @@
         <v>506</v>
       </c>
       <c r="H196" s="6" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="197" spans="1:8" ht="100.8">
@@ -28361,7 +28368,7 @@
         <v>508</v>
       </c>
       <c r="H197" s="3" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="198" spans="1:8" ht="158.4">
@@ -28387,7 +28394,7 @@
         <v>510</v>
       </c>
       <c r="H198" s="3" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="43.2">
@@ -28413,7 +28420,7 @@
         <v>512</v>
       </c>
       <c r="H199" s="3" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="200" spans="1:8" ht="100.8">
@@ -28439,7 +28446,7 @@
         <v>514</v>
       </c>
       <c r="H200" s="3" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="201" spans="1:8" ht="43.2">
@@ -28465,7 +28472,7 @@
         <v>516</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="202" spans="1:8" ht="100.8">
@@ -28491,7 +28498,7 @@
         <v>518</v>
       </c>
       <c r="H202" s="3" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="203" spans="1:8" ht="100.8">
@@ -28517,7 +28524,7 @@
         <v>520</v>
       </c>
       <c r="H203" s="3" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="115.2">
@@ -28543,7 +28550,7 @@
         <v>522</v>
       </c>
       <c r="H204" s="3" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="205" spans="1:8" ht="158.4">
@@ -28569,7 +28576,7 @@
         <v>524</v>
       </c>
       <c r="H205" s="3" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="172.8">
@@ -28595,7 +28602,7 @@
         <v>526</v>
       </c>
       <c r="H206" s="3" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="207" spans="1:8" ht="115.2">
@@ -28621,7 +28628,7 @@
         <v>528</v>
       </c>
       <c r="H207" s="3" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="158.4">
@@ -28644,10 +28651,10 @@
         <v>12</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="H208" s="3" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="209" spans="1:8" ht="158.4">
@@ -28673,7 +28680,7 @@
         <v>531</v>
       </c>
       <c r="H209" s="3" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="210" spans="1:8" ht="100.8">
@@ -28699,7 +28706,7 @@
         <v>533</v>
       </c>
       <c r="H210" s="3" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="211" spans="1:8" ht="100.8">
@@ -28725,7 +28732,7 @@
         <v>535</v>
       </c>
       <c r="H211" s="3" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="212" spans="1:8" ht="43.2">
@@ -28751,7 +28758,7 @@
         <v>537</v>
       </c>
       <c r="H212" s="3" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="213" spans="1:8" ht="43.2">
@@ -28803,7 +28810,7 @@
         <v>542</v>
       </c>
       <c r="H214" s="3" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="215" spans="1:8" ht="288">
@@ -28829,7 +28836,7 @@
         <v>544</v>
       </c>
       <c r="H215" s="3" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="216" spans="1:8" ht="115.2">
@@ -28855,7 +28862,7 @@
         <v>546</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="217" spans="1:8" ht="43.2">
@@ -28985,7 +28992,7 @@
         <v>557</v>
       </c>
       <c r="H221" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="222" spans="1:8" ht="43.2">
@@ -29406,7 +29413,7 @@
     </row>
     <row r="238" spans="1:8">
       <c r="A238" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="B238" t="s">
         <v>599</v>
@@ -29415,7 +29422,7 @@
         <v>1</v>
       </c>
       <c r="D238" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="E238" t="s">
         <v>11</v>
@@ -29424,11 +29431,31 @@
         <v>12</v>
       </c>
       <c r="G238" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="H238" s="4" t="s">
-        <v>790</v>
-      </c>
+        <v>788</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8">
+      <c r="A239" s="2"/>
+      <c r="B239" s="2"/>
+      <c r="C239" s="2"/>
+      <c r="D239" s="2"/>
+      <c r="E239" s="2"/>
+      <c r="F239" s="2"/>
+      <c r="G239" s="3"/>
+      <c r="H239" s="3"/>
+    </row>
+    <row r="240" spans="1:8">
+      <c r="A240" s="2"/>
+      <c r="B240" s="2"/>
+      <c r="C240" s="2"/>
+      <c r="D240" s="2"/>
+      <c r="E240" s="2"/>
+      <c r="F240" s="2"/>
+      <c r="G240" s="3"/>
+      <c r="H240" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docassemble/PowerOfAttorneyHealthCare/data/sources/poa_hc_es.xlsx
+++ b/docassemble/PowerOfAttorneyHealthCare/data/sources/poa_hc_es.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnewsted\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF4D47FC-559F-467F-9C85-E42AD8F50C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6134A77E-A56B-4A08-AD08-7A572988C9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34545" yWindow="-1995" windowWidth="30045" windowHeight="19425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-32055" yWindow="645" windowWidth="19530" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22005,214 +22005,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Your forms are ready. View and download your forms below. Click **Make changes** to fix any mistakes.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if user_path == "Shirley":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[YOUTUBE NE0faXuz5v4]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif user_path == "Frederico" or user_path == "Federico":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[YOUTUBE g5Vdv0hWJ6g]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif user_path == "Lisa":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[YOUTUBE F2QbdrhcZ0g]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Read the instructions to learn what to do next.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${ action_button_html(url_action('review_answers'), label='^^edit^^ Make changes', color='success', size="md") }</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${ al_user_bundle.download_list_html() }</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-&amp;nbsp;
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${ al_user_bundle.send_button_html(show_editable_checkbox=False) }</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-**Note:** The Power of Attorney needs to be signed in front of at least one witness to become official.
-Thank you for using ILAO Easy Forms!
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <b/>
         <sz val="11"/>
         <color rgb="FF008000"/>
@@ -22847,6 +22639,206 @@
       <t xml:space="preserve">
 **Nota:** El Poder Notarial debe firmarse frente a al menos un testigo para que sea válido.
 ¡Gracias por usar los Formularios Guiados de ILAO!</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Your forms are ready. View and download your forms below. Click **Make changes** to fix any mistakes.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if user_path == "Shirley":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[YOUTUBE NE0faXuz5v4]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif user_path == "Frederico" or user_path == "Federico":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[YOUTUBE g5Vdv0hWJ6g]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif user_path == "Lisa":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[YOUTUBE F2QbdrhcZ0g]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Read the instructions to learn what to do next.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ action_button_html(url_action('review_answers'), label=':edit: Make changes', color='success', size='md') }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ al_user_bundle.download_list_html(view_label='View', download_label='Download', zip_label='Download all') }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ al_user_bundle.send_button_html(show_editable_checkbox=False, label='Send') }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+**Note:** The Power of Attorney needs to be signed in front of at least one witness to become official.
+Thank you for using ILAO Easy Forms!
+</t>
     </r>
   </si>
 </sst>
@@ -23397,7 +23389,7 @@
         <v>16</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -23709,7 +23701,7 @@
         <v>48</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="28.8">
@@ -23769,13 +23761,13 @@
         <v>781</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C18" s="2">
         <v>0</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>11</v>
@@ -23784,10 +23776,10 @@
         <v>12</v>
       </c>
       <c r="G18" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>791</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="28.8">
@@ -23795,7 +23787,7 @@
         <v>781</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
@@ -26837,13 +26829,13 @@
         <v>781</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C136" s="2">
         <v>0</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>11</v>
@@ -26852,10 +26844,10 @@
         <v>12</v>
       </c>
       <c r="G136" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="H136" s="3" t="s">
         <v>795</v>
-      </c>
-      <c r="H136" s="3" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="137" spans="1:8" ht="409.6">
@@ -27872,7 +27864,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="388.8">
+    <row r="176" spans="1:8" ht="374.4">
       <c r="A176" s="2" t="s">
         <v>8</v>
       </c>
@@ -27892,10 +27884,10 @@
         <v>12</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>785</v>
+        <v>797</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="177" spans="1:8" ht="201.6">
@@ -27921,7 +27913,7 @@
         <v>445</v>
       </c>
       <c r="H177" s="3" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="86.4">

--- a/docassemble/PowerOfAttorneyHealthCare/data/sources/poa_hc_es.xlsx
+++ b/docassemble/PowerOfAttorneyHealthCare/data/sources/poa_hc_es.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnewsted\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6134A77E-A56B-4A08-AD08-7A572988C9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24235661-ED45-4127-BBDE-4E397A8609F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32055" yWindow="645" windowWidth="19530" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -802,122 +802,6 @@
     </r>
   </si>
   <si>
-    <t>6fabd2edf7f0fff29713a1ce0336aac6</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == False:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">The principal is the person who chooses an agent to make decisions about their medical treatment.
-You should enter their legal name on their government-issued identification. 
-You may want to click **They have another name** if:
-* They go by a name other than their legal name, or
-* They have changed their name and also have an old legal name that is not on their identification.
-You can then enter that name in the **Additional name** field.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${collapse_template(changed_name)}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">You should enter your legal name on your government-issued identification. 
-You may want to click **I have another name** if:
-* You go by a name other than your legal name, or
-* You have changed your name and also have an old legal name that is not on your identification.
-You can then enter that name in the **Additional name** field.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${collapse_template(changed_name)}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-  </si>
-  <si>
     <t>7fb55ed0b7a30342ba6da306428cae04</t>
   </si>
   <si>
@@ -3426,40 +3310,6 @@
   </si>
   <si>
     <t>8f9812d6e28e6beea846e8938b5d46e1</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">What life-sustaining treatment instructions do you want </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to follow?
-</t>
-    </r>
   </si>
   <si>
     <t>952d09b3ad225d88593c466cd9a4345f</t>
@@ -12318,29 +12168,6 @@
     <t>Apellido</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${capitalize(i_they)}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tengo otro nombre. / tiene otro nombre.</t>
-    </r>
-  </si>
-  <si>
     <t>¿El nombre adicional corresponde a un nombre legal anterior?</t>
   </si>
   <si>
@@ -12975,128 +12802,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">¿Quieres nominar a </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> como tu tutor legal, si es necesario?
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>¿</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> quiere nominar a </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> como su tutor legal, si es necesario?
 </t>
     </r>
     <r>
@@ -17996,118 +17701,6 @@
   <si>
     <r>
       <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == False:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">El otorgante es la persona que elige a un agente para tomar decisiones sobre su tratamiento médico.
-Debes ingresar su nombre legal tal como aparece en su identificación oficial emitida por el gobierno.
-Es posible que debas hacer clic en **Tiene otro nombre** si:
-* Usa un nombre distinto de su nombre legal, o
-* Ha cambiado su nombre y también tiene un nombre legal anterior que no aparece en su identificación.
-Luego puedes ingresar ese nombre en el campo **Nombre adicional**.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${collapse_template(changed_name)}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Debes ingresar tu nombre legal tal como aparece en tu identificación oficial emitida por el gobierno.
-Es posible que debas hacer clic en **Tengo otro nombre** si:
-* Usas un nombre distinto a tu nombre legal, o
-* Has cambiado tu nombre y también tienes un nombre legal anterior que no aparece en tu identificación.
-Luego puedes ingresar ese nombre en el campo **Nombre adicional**.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${collapse_template(changed_name)}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
@@ -19257,61 +18850,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>% endif</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Hasta ahora nos has dicho lo siguiente sobre </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${fix_punctuation(successors.full_names())}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Si nombras a otro agente sucesor, esa persona solo tendrá poder si tanto </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> como los agentes sucesores que ya ingresaste no están disponibles para actuar.</t>
     </r>
   </si>
   <si>
@@ -20392,168 +19930,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Si no decides si </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> debe enfocarse en la calidad de tu vida o en la duración de tu vida, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tendrá que tomar esa decisión después de hablar con el médico.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Si </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> no decide si </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> debe enfocarse en la calidad de su vida o en la duración de su vida, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tendrá que tomar esa decisión después de hablar con el médico.
 </t>
     </r>
     <r>
@@ -20909,279 +20285,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  Si seleccionas **Sí** y **{revocar}** tu Poder Notarial en el futuro, tendrás un "periodo de reflexión." </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> aún podrá tomar decisiones por ti hasta 30 días después de que revoques el Poder Notarial. Puedes usar esos 30 días para reflexionar sobre tu decisión. Esto puede ser útil cuando las decisiones se toman durante una crisis de salud, un episodio de salud mental, o mientras experimentas confusión o pérdida de memoria. 
-Si seleccionas **No** y revocas tu Poder Notarial en el futuro, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> dejará inmediatamente de poder tomar decisiones por ti.
-**Nota**: Puedes **{revocar}** un Poder Notarial para el Cuidado de la Salud incluso si no tienes **{capacidad legal}**, pero necesitarás capacidad legal para hacer uno nuevo.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  Si seleccionas **Sí** y </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> **{revoca}** su Poder Notarial en el futuro, tendrá un “período de reflexión.” </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> aún podrá tomar decisiones por </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hasta 30 días después de que revoque su Poder Notarial. Puede usar esos 30 días para reflexionar sobre su decisión. Esto puede ser útil cuando las decisiones se toman durante una crisis de salud, un episodio de salud mental, o mientras experimenta confusión o pérdida de memoria.
-  Si seleccionas **No** y </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> revoca el Poder Notarial en el futuro, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> dejará inmediatamente de poder tomar decisiones por </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF3D67FA"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-  **Nota**: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> puede **{revocar}** un Poder Notarial para el Cuidado de la Salud incluso si no tiene **{capacidad legal}**, pero necesitaría capacidad legal para hacer uno nuevo.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${collapse_template(video_cooling)}</t>
-    </r>
-  </si>
-  <si>
     <t>41aa7fa986efe3dfddb426137e8b1038</t>
   </si>
   <si>
@@ -22112,65 +21215,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>${ action_button_html(interview_url(i="docassemble.ILAO:feedback.yml", easy_form_interview=ilao_easy_form_url, easy_form_title=ilao_easy_form_title, easy_form_page=current_context().question_id, easy_form_variable=current_context().variable, local=False,reset=1), label=':comment: ¿Fue útil este programa?', color="#181c36", size="md", new_window=True) }</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Bienvenido(a) al Formulario Guiado de Poder Notarial para el Cuidado de la Salud de Illinois Legal Aid Online.
-Este programa te ayuda a crear documentos que le dan a alguien en quien confías el poder legal para tomar decisiones sobre tu atención médica. Esto significa que esa persona podrá tomar decisiones sobre tu atención médica cuando no puedas hacerlo tú mismo(a). También puedes permitir que esa persona tome decisiones sobre tu atención médica antes, si así lo decides.
-Este programa incluye videos con información sobre cómo hacer un Poder Notarial para el Cuidado de la Salud. No tienes que verlos, pero pueden serte útiles.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">[YOUTUBE ccToVpEse7s]
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Para obtener más información, lee el artículo de ILAO sobre los [**Conceptos Básicos del Poder Notarial para el Cuidado de la Salud**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://es.illinoislegalaid.org/legal-information/setting-power-attorney-healthcare</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>).</t>
     </r>
   </si>
   <si>
@@ -22839,6 +21883,955 @@
 **Note:** The Power of Attorney needs to be signed in front of at least one witness to become official.
 Thank you for using ILAO Easy Forms!
 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Bienvenido(a) al Formulario Guiado de Poder Notarial para el Cuidado de la Salud de Illinois Legal Aid Online.
+Este programa te ayuda a crear documentos que le otorgan a una persona de tu confianza la autoridad legal para tomar decisiones sobre tu atención médica. Esto significa que esa persona podrá tomar decisiones sobre tu atención médica cuando no puedas hacerlo por ti mismo(a). Si así lo deseas, también puedes autorizarla para que tome decisiones sobre tu atención médica antesde que eso ocurra.
+Este programa incluye videos con información sobre cómo hacer un Poder Notarial para el Cuidado de la Salud. No tienes que verlos, pero pueden serte útiles.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">[YOUTUBE ccToVpEse7s]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Para obtener más información, lee el artículo de ILAO sobre los [**Conceptos Básicos del Poder Notarial para el Cuidado de la Salud**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://es.illinoislegalaid.org/legal-information/setting-power-attorney-healthcare</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${capitalize(i_they)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tengo otro nombre.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">What life-sustaining treatment instructions do you want </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to follow?
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Hasta ahora, has nombrado como agente sucesor a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${fix_punctuation(successors.full_names())}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Si nombras a otro agente sucesor, esa persona solo tendrá poder si tanto </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> como los agentes sucesores que ya ingresaste no están disponibles para actuar.</t>
+    </r>
+  </si>
+  <si>
+    <t>aa654d6a29fff7f9a2c2f2fa98ac42e3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == False:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">The principal is the person who chooses an agent to make decisions about their medical treatment.
+You should enter their legal name on their government-issued identification. 
+You may want to click **They have another name** if:
+* They go by a name other than their legal name, or
+* They have changed their name and also have an old legal name that is not on their identification.
+You can then enter that name in the **Additional name** field.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${collapse_template(changed_name_other)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">You should enter your legal name on your government-issued identification. 
+You may want to click **I have another name** if:
+* You go by a name other than your legal name, or
+* You have changed your name and also have an old legal name that is not on your identification.
+You can then enter that name in the **Additional name** field.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${collapse_template(changed_name)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == False:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">El otorgante es la persona que elige a un agente para tomar decisiones sobre su tratamiento médico.
+Debes ingresar su nombre legal tal como aparece en su identificación oficial emitida por el gobierno.
+Es posible que debas hacer clic en **Tiene otro nombre** si:
+* Usa un nombre distinto de su nombre legal, o
+* Ha cambiado su nombre y también tiene un nombre legal anterior que no aparece en su identificación.
+Luego puedes ingresar ese nombre en el campo **Nombre adicional**.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${collapse_template(changed_name_other)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Debes ingresar tu nombre legal tal como aparece en tu identificación oficial emitida por el gobierno.
+Es posible que debas hacer clic en **Tengo otro nombre** si:
+* Usas un nombre distinto a tu nombre legal, o
+* Has cambiado tu nombre y también tienes un nombre legal anterior que no aparece en tu identificación.
+Luego puedes ingresar ese nombre en el campo **Nombre adicional**.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${collapse_template(changed_name)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% endif</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">¿Quieres nominar a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> como tu tutor(a) legal, si es necesario?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">¿Quiere </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nominar a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> como su tutor(a) legal, si es necesario?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% endif</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Si no decides si </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> debe enfocarse en la calidad de tu vida o en la duración de tu vida, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tendrá que tomar esa decisión después de hablar con el médico.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Si </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> no decide si </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> debedar prioridad a su calidad de vida o a prolongar su vida, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tendrá que tomar esa decisión después de hablar con el médico.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% endif</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  Si seleccionas **Sí** y revocas tu Poder Notarial en el futuro, tendrás un "periodo de reflexión." </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> aún podrá tomar decisiones por ti hasta 30 días después de que revoques el Poder Notarial. Puedes usar esos 30 días para reflexionar sobre tu decisión. Esto puede ser útil cuando las decisiones se toman durante una crisis de salud, un episodio de salud mental, o mientras experimentas confusión o pérdida de memoria. 
+Si seleccionas **No** y revocas tu Poder Notarial en el futuro, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dejará inmediatamente de poder tomar decisiones por ti.
+**Nota**: Puedes **{revocar}** un Poder Notarial para el Cuidado de la Salud incluso si no tienes **{capacidad legal}**, pero necesitarás capacidad legal para hacer uno nuevo.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  Si seleccionas **Sí** y </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> revoca su Poder Notarial en el futuro, tendrá un “período de reflexión.” </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> aún podrá tomar decisiones por </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hasta 30 días después de que revoque su Poder Notarial. Puede usar esos 30 días para reflexionar sobre su decisión. Esto puede ser útil cuando las decisiones se toman durante una crisis de salud, un episodio de salud mental, o mientras experimenta confusión o pérdida de memoria.
+  Si seleccionas **No** y </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> revoca el Poder Notarial en el futuro, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dejará inmediatamente de poder tomar decisiones por </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF3D67FA"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+  **Nota**: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> puede **{revocar}** un Poder Notarial para el Cuidado de la Salud incluso si no tiene **{capacidad legal}**, pero necesitaría capacidad legal para hacer uno nuevo.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${collapse_template(video_cooling)}</t>
     </r>
   </si>
 </sst>
@@ -23389,7 +23382,7 @@
         <v>16</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -23441,7 +23434,7 @@
         <v>22</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -23545,7 +23538,7 @@
         <v>33</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="28.8">
@@ -23559,7 +23552,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>766</v>
+        <v>757</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>11</v>
@@ -23568,7 +23561,7 @@
         <v>12</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>35</v>
@@ -23585,7 +23578,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>767</v>
+        <v>758</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>11</v>
@@ -23594,7 +23587,7 @@
         <v>12</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>768</v>
+        <v>759</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>36</v>
@@ -23649,7 +23642,7 @@
         <v>42</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>772</v>
+        <v>763</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="28.8">
@@ -23701,7 +23694,7 @@
         <v>48</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="28.8">
@@ -23753,21 +23746,21 @@
         <v>54</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>773</v>
+        <v>764</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="115.2">
       <c r="A18" s="2" t="s">
-        <v>781</v>
+        <v>772</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>788</v>
+        <v>778</v>
       </c>
       <c r="C18" s="2">
         <v>0</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>789</v>
+        <v>779</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>11</v>
@@ -23776,18 +23769,18 @@
         <v>12</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>790</v>
+        <v>780</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>791</v>
+        <v>781</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="28.8">
       <c r="A19" s="2" t="s">
-        <v>781</v>
+        <v>772</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>788</v>
+        <v>778</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
@@ -23831,7 +23824,7 @@
         <v>60</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -23857,7 +23850,7 @@
         <v>63</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="43.2">
@@ -23883,7 +23876,7 @@
         <v>65</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="57.6">
@@ -23909,7 +23902,7 @@
         <v>67</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>762</v>
+        <v>754</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="28.8">
@@ -23935,7 +23928,7 @@
         <v>69</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="57.6">
@@ -23961,7 +23954,7 @@
         <v>71</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="28.8">
@@ -23987,7 +23980,7 @@
         <v>74</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="244.8">
@@ -24013,7 +24006,7 @@
         <v>76</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="86.4">
@@ -24039,7 +24032,7 @@
         <v>79</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="409.6">
@@ -24053,7 +24046,7 @@
         <v>1</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>80</v>
+        <v>792</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>11</v>
@@ -24062,10 +24055,10 @@
         <v>12</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>81</v>
+        <v>793</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>730</v>
+        <v>794</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -24079,7 +24072,7 @@
         <v>2</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>11</v>
@@ -24088,10 +24081,10 @@
         <v>12</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -24105,7 +24098,7 @@
         <v>3</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>11</v>
@@ -24114,10 +24107,10 @@
         <v>12</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -24131,7 +24124,7 @@
         <v>4</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>11</v>
@@ -24140,10 +24133,10 @@
         <v>12</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -24157,7 +24150,7 @@
         <v>5</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>11</v>
@@ -24166,10 +24159,10 @@
         <v>12</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>613</v>
+        <v>789</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -24183,7 +24176,7 @@
         <v>6</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>11</v>
@@ -24192,10 +24185,10 @@
         <v>12</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -24209,7 +24202,7 @@
         <v>7</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>11</v>
@@ -24218,10 +24211,10 @@
         <v>12</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="100.8">
@@ -24229,13 +24222,13 @@
         <v>8</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C36" s="2">
         <v>0</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>11</v>
@@ -24244,10 +24237,10 @@
         <v>12</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="28.8">
@@ -24255,13 +24248,13 @@
         <v>8</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C37" s="2">
         <v>1</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>11</v>
@@ -24270,10 +24263,10 @@
         <v>12</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="86.4">
@@ -24281,13 +24274,13 @@
         <v>8</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C38" s="2">
         <v>0</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>11</v>
@@ -24296,10 +24289,10 @@
         <v>12</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="28.8">
@@ -24307,13 +24300,13 @@
         <v>8</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C39" s="2">
         <v>0</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>11</v>
@@ -24322,10 +24315,10 @@
         <v>12</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="144">
@@ -24333,13 +24326,13 @@
         <v>8</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C40" s="2">
         <v>1</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>11</v>
@@ -24348,10 +24341,10 @@
         <v>12</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="86.4">
@@ -24359,13 +24352,13 @@
         <v>8</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C41" s="2">
         <v>0</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>11</v>
@@ -24374,10 +24367,10 @@
         <v>12</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="86.4">
@@ -24385,13 +24378,13 @@
         <v>8</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C42" s="2">
         <v>0</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>11</v>
@@ -24400,10 +24393,10 @@
         <v>12</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="374.4">
@@ -24411,13 +24404,13 @@
         <v>8</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C43" s="2">
         <v>1</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>11</v>
@@ -24426,10 +24419,10 @@
         <v>12</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="86.4">
@@ -24437,13 +24430,13 @@
         <v>8</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C44" s="2">
         <v>0</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>11</v>
@@ -24452,10 +24445,10 @@
         <v>12</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="28.8">
@@ -24463,13 +24456,13 @@
         <v>8</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C45" s="2">
         <v>1</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>11</v>
@@ -24478,10 +24471,10 @@
         <v>12</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="28.8">
@@ -24489,13 +24482,13 @@
         <v>8</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C46" s="2">
         <v>0</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>11</v>
@@ -24504,10 +24497,10 @@
         <v>12</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -24515,13 +24508,13 @@
         <v>8</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C47" s="2">
         <v>2</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>11</v>
@@ -24530,10 +24523,10 @@
         <v>12</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="43.2">
@@ -24541,13 +24534,13 @@
         <v>8</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C48" s="2">
         <v>3</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>11</v>
@@ -24556,10 +24549,10 @@
         <v>12</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H48" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -24567,13 +24560,13 @@
         <v>8</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C49" s="2">
         <v>4</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>11</v>
@@ -24582,10 +24575,10 @@
         <v>12</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -24593,13 +24586,13 @@
         <v>8</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C50" s="2">
         <v>5</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>11</v>
@@ -24608,10 +24601,10 @@
         <v>12</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="129.6">
@@ -24619,13 +24612,13 @@
         <v>8</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C51" s="2">
         <v>0</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>11</v>
@@ -24634,10 +24627,10 @@
         <v>12</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>774</v>
+        <v>765</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="28.8">
@@ -24645,13 +24638,13 @@
         <v>8</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C52" s="2">
         <v>1</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>11</v>
@@ -24660,10 +24653,10 @@
         <v>12</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>763</v>
+        <v>755</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="28.8">
@@ -24671,13 +24664,13 @@
         <v>8</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C53" s="2">
         <v>0</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>11</v>
@@ -24686,10 +24679,10 @@
         <v>12</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="100.8">
@@ -24697,13 +24690,13 @@
         <v>8</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C54" s="2">
         <v>1</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>11</v>
@@ -24712,10 +24705,10 @@
         <v>12</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="100.8">
@@ -24723,13 +24716,13 @@
         <v>8</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C55" s="2">
         <v>0</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>11</v>
@@ -24738,10 +24731,10 @@
         <v>12</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>629</v>
+        <v>795</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="288">
@@ -24749,13 +24742,13 @@
         <v>8</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C56" s="2">
         <v>1</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>11</v>
@@ -24764,10 +24757,10 @@
         <v>12</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="28.8">
@@ -24775,13 +24768,13 @@
         <v>8</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C57" s="2">
         <v>1</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>11</v>
@@ -24790,10 +24783,10 @@
         <v>12</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -24801,13 +24794,13 @@
         <v>8</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C58" s="2">
         <v>0</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>11</v>
@@ -24816,10 +24809,10 @@
         <v>12</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="28.8">
@@ -24827,13 +24820,13 @@
         <v>8</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C59" s="2">
         <v>1</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>11</v>
@@ -24842,10 +24835,10 @@
         <v>12</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="28.8">
@@ -24853,13 +24846,13 @@
         <v>8</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C60" s="2">
         <v>2</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>11</v>
@@ -24868,10 +24861,10 @@
         <v>12</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="144">
@@ -24879,13 +24872,13 @@
         <v>8</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C61" s="2">
         <v>3</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>11</v>
@@ -24894,10 +24887,10 @@
         <v>12</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -24905,13 +24898,13 @@
         <v>8</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C62" s="2">
         <v>4</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>11</v>
@@ -24920,10 +24913,10 @@
         <v>12</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="28.8">
@@ -24931,13 +24924,13 @@
         <v>8</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C63" s="2">
         <v>5</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>11</v>
@@ -24946,10 +24939,10 @@
         <v>12</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -24957,13 +24950,13 @@
         <v>8</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C64" s="2">
         <v>6</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>11</v>
@@ -24972,10 +24965,10 @@
         <v>12</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="43.2">
@@ -24983,13 +24976,13 @@
         <v>8</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C65" s="2">
         <v>7</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>11</v>
@@ -24998,10 +24991,10 @@
         <v>12</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="57.6">
@@ -25009,13 +25002,13 @@
         <v>8</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C66" s="2">
         <v>8</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>11</v>
@@ -25024,10 +25017,10 @@
         <v>12</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -25035,13 +25028,13 @@
         <v>8</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C67" s="2">
         <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>11</v>
@@ -25050,10 +25043,10 @@
         <v>12</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="28.8">
@@ -25061,13 +25054,13 @@
         <v>8</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C68" s="2">
         <v>0</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>11</v>
@@ -25076,10 +25069,10 @@
         <v>12</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="172.8">
@@ -25087,13 +25080,13 @@
         <v>8</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C69" s="2">
         <v>1</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>11</v>
@@ -25102,10 +25095,10 @@
         <v>12</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="28.8">
@@ -25113,13 +25106,13 @@
         <v>8</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C70" s="2">
         <v>2</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>11</v>
@@ -25128,10 +25121,10 @@
         <v>12</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -25139,13 +25132,13 @@
         <v>8</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C71" s="2">
         <v>3</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>11</v>
@@ -25154,10 +25147,10 @@
         <v>12</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="43.2">
@@ -25165,13 +25158,13 @@
         <v>8</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C72" s="2">
         <v>4</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>11</v>
@@ -25180,10 +25173,10 @@
         <v>12</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="57.6">
@@ -25191,13 +25184,13 @@
         <v>8</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C73" s="2">
         <v>5</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>11</v>
@@ -25206,10 +25199,10 @@
         <v>12</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -25217,13 +25210,13 @@
         <v>8</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C74" s="2">
         <v>6</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>11</v>
@@ -25232,10 +25225,10 @@
         <v>12</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="28.8">
@@ -25243,13 +25236,13 @@
         <v>8</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C75" s="2">
         <v>0</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>11</v>
@@ -25258,10 +25251,10 @@
         <v>12</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="144">
@@ -25269,13 +25262,13 @@
         <v>8</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C76" s="2">
         <v>1</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>11</v>
@@ -25284,10 +25277,10 @@
         <v>12</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="115.2">
@@ -25295,13 +25288,13 @@
         <v>8</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C77" s="2">
         <v>0</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>11</v>
@@ -25310,10 +25303,10 @@
         <v>12</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="360">
@@ -25321,13 +25314,13 @@
         <v>8</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>11</v>
@@ -25336,10 +25329,10 @@
         <v>12</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="28.8">
@@ -25347,13 +25340,13 @@
         <v>8</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C79" s="2">
         <v>1</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>11</v>
@@ -25362,10 +25355,10 @@
         <v>12</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="28.8">
@@ -25373,13 +25366,13 @@
         <v>8</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C80" s="2">
         <v>0</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>11</v>
@@ -25388,10 +25381,10 @@
         <v>12</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>208</v>
+        <v>790</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="72">
@@ -25399,13 +25392,13 @@
         <v>8</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C81" s="2">
         <v>1</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>11</v>
@@ -25414,10 +25407,10 @@
         <v>12</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="72">
@@ -25425,13 +25418,13 @@
         <v>8</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C82" s="2">
         <v>2</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>11</v>
@@ -25440,10 +25433,10 @@
         <v>12</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -25451,13 +25444,13 @@
         <v>8</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C83" s="2">
         <v>3</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>11</v>
@@ -25466,10 +25459,10 @@
         <v>12</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="43.2">
@@ -25477,13 +25470,13 @@
         <v>8</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C84" s="2">
         <v>4</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>11</v>
@@ -25492,10 +25485,10 @@
         <v>12</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -25503,13 +25496,13 @@
         <v>8</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C85" s="2">
         <v>5</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>11</v>
@@ -25518,10 +25511,10 @@
         <v>12</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -25529,13 +25522,13 @@
         <v>8</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C86" s="2">
         <v>6</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>11</v>
@@ -25544,10 +25537,10 @@
         <v>12</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="172.8">
@@ -25555,13 +25548,13 @@
         <v>8</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C87" s="2">
         <v>0</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>11</v>
@@ -25570,10 +25563,10 @@
         <v>12</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="43.2">
@@ -25581,13 +25574,13 @@
         <v>8</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C88" s="2">
         <v>1</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>11</v>
@@ -25596,10 +25589,10 @@
         <v>12</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="43.2">
@@ -25607,13 +25600,13 @@
         <v>8</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C89" s="2">
         <v>0</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>11</v>
@@ -25622,10 +25615,10 @@
         <v>12</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="72">
@@ -25633,13 +25626,13 @@
         <v>8</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C90" s="2">
         <v>1</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>11</v>
@@ -25648,10 +25641,10 @@
         <v>12</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="72">
@@ -25659,13 +25652,13 @@
         <v>8</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C91" s="2">
         <v>2</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>11</v>
@@ -25674,10 +25667,10 @@
         <v>12</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -25685,13 +25678,13 @@
         <v>8</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C92" s="2">
         <v>3</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>11</v>
@@ -25700,10 +25693,10 @@
         <v>12</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="57.6">
@@ -25711,13 +25704,13 @@
         <v>8</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C93" s="2">
         <v>4</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>11</v>
@@ -25726,10 +25719,10 @@
         <v>12</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -25737,13 +25730,13 @@
         <v>8</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C94" s="2">
         <v>5</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>11</v>
@@ -25752,10 +25745,10 @@
         <v>12</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -25763,13 +25756,13 @@
         <v>8</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C95" s="2">
         <v>6</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>11</v>
@@ -25778,10 +25771,10 @@
         <v>12</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="201.6">
@@ -25789,13 +25782,13 @@
         <v>8</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C96" s="2">
         <v>0</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>11</v>
@@ -25804,10 +25797,10 @@
         <v>12</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="28.8">
@@ -25815,13 +25808,13 @@
         <v>8</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C97" s="2">
         <v>0</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>11</v>
@@ -25830,10 +25823,10 @@
         <v>12</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="129.6">
@@ -25841,13 +25834,13 @@
         <v>8</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C98" s="2">
         <v>1</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>11</v>
@@ -25856,10 +25849,10 @@
         <v>12</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>757</v>
+        <v>796</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="86.4">
@@ -25867,13 +25860,13 @@
         <v>8</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C99" s="2">
         <v>0</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>11</v>
@@ -25882,10 +25875,10 @@
         <v>12</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="302.39999999999998">
@@ -25893,13 +25886,13 @@
         <v>8</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C100" s="2">
         <v>1</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>11</v>
@@ -25908,10 +25901,10 @@
         <v>12</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>764</v>
+        <v>756</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="28.8">
@@ -25919,13 +25912,13 @@
         <v>8</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C101" s="2">
         <v>0</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>11</v>
@@ -25934,10 +25927,10 @@
         <v>12</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
     </row>
     <row r="102" spans="1:8" ht="86.4">
@@ -25945,13 +25938,13 @@
         <v>8</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C102" s="2">
         <v>1</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>11</v>
@@ -25960,10 +25953,10 @@
         <v>12</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -25971,13 +25964,13 @@
         <v>8</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C103" s="2">
         <v>2</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>11</v>
@@ -25986,10 +25979,10 @@
         <v>12</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -25997,13 +25990,13 @@
         <v>8</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C104" s="2">
         <v>3</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>11</v>
@@ -26012,10 +26005,10 @@
         <v>12</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -26023,13 +26016,13 @@
         <v>8</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C105" s="2">
         <v>4</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>11</v>
@@ -26038,10 +26031,10 @@
         <v>12</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -26049,13 +26042,13 @@
         <v>8</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C106" s="2">
         <v>5</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>11</v>
@@ -26064,10 +26057,10 @@
         <v>12</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -26075,13 +26068,13 @@
         <v>8</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C107" s="2">
         <v>6</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>11</v>
@@ -26090,10 +26083,10 @@
         <v>12</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -26101,13 +26094,13 @@
         <v>8</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C108" s="2">
         <v>7</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>11</v>
@@ -26116,10 +26109,10 @@
         <v>12</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -26127,13 +26120,13 @@
         <v>8</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C109" s="2">
         <v>8</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>11</v>
@@ -26142,10 +26135,10 @@
         <v>12</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
     </row>
     <row r="110" spans="1:8" ht="43.2">
@@ -26153,13 +26146,13 @@
         <v>8</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C110" s="2">
         <v>0</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>11</v>
@@ -26168,10 +26161,10 @@
         <v>12</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="86.4">
@@ -26179,13 +26172,13 @@
         <v>8</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C111" s="2">
         <v>1</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>11</v>
@@ -26194,10 +26187,10 @@
         <v>12</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -26205,13 +26198,13 @@
         <v>8</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C112" s="2">
         <v>2</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>11</v>
@@ -26220,10 +26213,10 @@
         <v>12</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H112" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -26231,13 +26224,13 @@
         <v>8</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C113" s="2">
         <v>3</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>11</v>
@@ -26246,10 +26239,10 @@
         <v>12</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H113" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -26257,13 +26250,13 @@
         <v>8</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C114" s="2">
         <v>4</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>11</v>
@@ -26272,10 +26265,10 @@
         <v>12</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H114" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -26283,13 +26276,13 @@
         <v>8</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C115" s="2">
         <v>5</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>11</v>
@@ -26298,10 +26291,10 @@
         <v>12</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H115" s="6" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
     </row>
     <row r="116" spans="1:8" ht="43.2">
@@ -26309,13 +26302,13 @@
         <v>8</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C116" s="2">
         <v>6</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>11</v>
@@ -26324,10 +26317,10 @@
         <v>12</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="28.8">
@@ -26335,13 +26328,13 @@
         <v>8</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C117" s="2">
         <v>0</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>11</v>
@@ -26350,10 +26343,10 @@
         <v>12</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H117" s="6" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -26361,13 +26354,13 @@
         <v>8</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C118" s="2">
         <v>1</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>11</v>
@@ -26376,10 +26369,10 @@
         <v>12</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -26387,13 +26380,13 @@
         <v>8</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C119" s="2">
         <v>2</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>11</v>
@@ -26402,10 +26395,10 @@
         <v>12</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="H119" s="6" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
     </row>
     <row r="120" spans="1:8" ht="28.8">
@@ -26413,13 +26406,13 @@
         <v>8</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C120" s="2">
         <v>0</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>11</v>
@@ -26428,10 +26421,10 @@
         <v>12</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -26439,13 +26432,13 @@
         <v>8</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C121" s="2">
         <v>1</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>11</v>
@@ -26454,10 +26447,10 @@
         <v>12</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H121" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="86.4">
@@ -26465,13 +26458,13 @@
         <v>8</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C122" s="2">
         <v>0</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>11</v>
@@ -26480,10 +26473,10 @@
         <v>12</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="28.8">
@@ -26491,13 +26484,13 @@
         <v>8</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C123" s="2">
         <v>1</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>11</v>
@@ -26506,10 +26499,10 @@
         <v>12</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="H123" s="6" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="28.8">
@@ -26517,13 +26510,13 @@
         <v>8</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C124" s="2">
         <v>2</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>11</v>
@@ -26532,10 +26525,10 @@
         <v>12</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="H124" s="8" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="28.8">
@@ -26543,13 +26536,13 @@
         <v>8</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C125" s="2">
         <v>3</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>11</v>
@@ -26558,10 +26551,10 @@
         <v>12</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="H125" s="8" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="28.8">
@@ -26569,13 +26562,13 @@
         <v>8</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C126" s="2">
         <v>4</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>11</v>
@@ -26584,10 +26577,10 @@
         <v>12</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="H126" s="8" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -26595,13 +26588,13 @@
         <v>8</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C127" s="2">
         <v>5</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>11</v>
@@ -26610,10 +26603,10 @@
         <v>12</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="H127" s="8" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -26621,13 +26614,13 @@
         <v>8</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C128" s="2">
         <v>6</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>11</v>
@@ -26636,10 +26629,10 @@
         <v>12</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -26647,13 +26640,13 @@
         <v>8</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C129" s="2">
         <v>7</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>11</v>
@@ -26662,10 +26655,10 @@
         <v>12</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -26673,13 +26666,13 @@
         <v>8</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C130" s="2">
         <v>8</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>11</v>
@@ -26688,10 +26681,10 @@
         <v>12</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
     </row>
     <row r="131" spans="1:8" ht="28.8">
@@ -26699,13 +26692,13 @@
         <v>8</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C131" s="2">
         <v>0</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>11</v>
@@ -26714,10 +26707,10 @@
         <v>12</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H131" s="6" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
     </row>
     <row r="132" spans="1:8" ht="403.2">
@@ -26725,13 +26718,13 @@
         <v>8</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C132" s="2">
         <v>1</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>11</v>
@@ -26740,10 +26733,10 @@
         <v>12</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -26751,13 +26744,13 @@
         <v>8</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C133" s="2">
         <v>0</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>11</v>
@@ -26766,10 +26759,10 @@
         <v>12</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="H133" s="6" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
     </row>
     <row r="134" spans="1:8" ht="43.2">
@@ -26777,13 +26770,13 @@
         <v>8</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C134" s="2">
         <v>1</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>11</v>
@@ -26792,10 +26785,10 @@
         <v>12</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="100.8">
@@ -26803,13 +26796,13 @@
         <v>8</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C135" s="2">
         <v>2</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>11</v>
@@ -26818,24 +26811,24 @@
         <v>12</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>771</v>
+        <v>762</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
     </row>
     <row r="136" spans="1:8" ht="115.2">
       <c r="A136" s="2" t="s">
-        <v>781</v>
+        <v>772</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>792</v>
+        <v>782</v>
       </c>
       <c r="C136" s="2">
         <v>0</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>793</v>
+        <v>783</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>11</v>
@@ -26844,10 +26837,10 @@
         <v>12</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>794</v>
+        <v>784</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>795</v>
+        <v>785</v>
       </c>
     </row>
     <row r="137" spans="1:8" ht="409.6">
@@ -26855,13 +26848,13 @@
         <v>8</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C137" s="2">
         <v>3</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>11</v>
@@ -26870,10 +26863,10 @@
         <v>12</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>765</v>
+        <v>797</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="28.8">
@@ -26881,13 +26874,13 @@
         <v>8</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C138" s="2">
         <v>1</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>11</v>
@@ -26896,10 +26889,10 @@
         <v>12</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -26907,13 +26900,13 @@
         <v>8</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C139" s="2">
         <v>0</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>11</v>
@@ -26922,10 +26915,10 @@
         <v>12</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="H139" s="6" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
     </row>
     <row r="140" spans="1:8" ht="57.6">
@@ -26933,13 +26926,13 @@
         <v>8</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C140" s="2">
         <v>1</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>11</v>
@@ -26948,10 +26941,10 @@
         <v>12</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -26959,13 +26952,13 @@
         <v>8</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C141" s="2">
         <v>2</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>11</v>
@@ -26974,10 +26967,10 @@
         <v>12</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="H141" s="6" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
     </row>
     <row r="142" spans="1:8" ht="43.2">
@@ -26985,13 +26978,13 @@
         <v>8</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C142" s="2">
         <v>3</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>11</v>
@@ -27000,10 +26993,10 @@
         <v>12</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
     </row>
     <row r="143" spans="1:8" ht="86.4">
@@ -27011,13 +27004,13 @@
         <v>8</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C143" s="2">
         <v>4</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>11</v>
@@ -27026,10 +27019,10 @@
         <v>12</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
     </row>
     <row r="144" spans="1:8" ht="216">
@@ -27037,13 +27030,13 @@
         <v>8</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C144" s="2">
         <v>5</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>11</v>
@@ -27052,10 +27045,10 @@
         <v>12</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
     </row>
     <row r="145" spans="1:8" ht="86.4">
@@ -27063,13 +27056,13 @@
         <v>8</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C145" s="2">
         <v>0</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>11</v>
@@ -27078,10 +27071,10 @@
         <v>12</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="146" spans="1:8" ht="86.4">
@@ -27089,13 +27082,13 @@
         <v>8</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C146" s="2">
         <v>1</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>11</v>
@@ -27104,10 +27097,10 @@
         <v>12</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>747</v>
+        <v>791</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -27115,13 +27108,13 @@
         <v>8</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C147" s="2">
         <v>2</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>11</v>
@@ -27130,10 +27123,10 @@
         <v>12</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="H147" s="6" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="148" spans="1:8" ht="86.4">
@@ -27141,13 +27134,13 @@
         <v>8</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C148" s="2">
         <v>0</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>11</v>
@@ -27156,10 +27149,10 @@
         <v>12</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="28.8">
@@ -27167,13 +27160,13 @@
         <v>8</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C149" s="2">
         <v>0</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>11</v>
@@ -27182,10 +27175,10 @@
         <v>12</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -27193,13 +27186,13 @@
         <v>8</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C150" s="2">
         <v>2</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>11</v>
@@ -27208,10 +27201,10 @@
         <v>12</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="129.6">
@@ -27219,13 +27212,13 @@
         <v>8</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C151" s="2">
         <v>0</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>11</v>
@@ -27234,10 +27227,10 @@
         <v>12</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>776</v>
+        <v>767</v>
       </c>
     </row>
     <row r="152" spans="1:8" ht="28.8">
@@ -27245,13 +27238,13 @@
         <v>8</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C152" s="2">
         <v>1</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>11</v>
@@ -27260,10 +27253,10 @@
         <v>12</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="153" spans="1:8" ht="28.8">
@@ -27271,13 +27264,13 @@
         <v>8</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C153" s="2">
         <v>0</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>11</v>
@@ -27286,10 +27279,10 @@
         <v>12</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="H153" s="3" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="154" spans="1:8" ht="115.2">
@@ -27297,13 +27290,13 @@
         <v>8</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C154" s="2">
         <v>1</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>11</v>
@@ -27312,10 +27305,10 @@
         <v>12</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
     </row>
     <row r="155" spans="1:8" ht="28.8">
@@ -27323,13 +27316,13 @@
         <v>8</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C155" s="2">
         <v>0</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>11</v>
@@ -27338,10 +27331,10 @@
         <v>12</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="H155" s="6" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
     </row>
     <row r="156" spans="1:8" ht="409.6">
@@ -27349,13 +27342,13 @@
         <v>8</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C156" s="2">
         <v>1</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>11</v>
@@ -27364,10 +27357,10 @@
         <v>12</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
     </row>
     <row r="157" spans="1:8" ht="43.2">
@@ -27375,13 +27368,13 @@
         <v>8</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C157" s="2">
         <v>0</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>11</v>
@@ -27390,10 +27383,10 @@
         <v>12</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="H157" s="6" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
     </row>
     <row r="158" spans="1:8" ht="86.4">
@@ -27401,13 +27394,13 @@
         <v>8</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C158" s="2">
         <v>1</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>11</v>
@@ -27416,10 +27409,10 @@
         <v>12</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="28.8">
@@ -27427,13 +27420,13 @@
         <v>8</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C159" s="2">
         <v>0</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>11</v>
@@ -27442,10 +27435,10 @@
         <v>12</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="H159" s="6" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="160" spans="1:8" ht="144">
@@ -27453,13 +27446,13 @@
         <v>8</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C160" s="2">
         <v>1</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>11</v>
@@ -27468,10 +27461,10 @@
         <v>12</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="100.8">
@@ -27479,13 +27472,13 @@
         <v>8</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C161" s="2">
         <v>0</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>11</v>
@@ -27494,10 +27487,10 @@
         <v>12</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="144">
@@ -27505,13 +27498,13 @@
         <v>8</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C162" s="2">
         <v>1</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>11</v>
@@ -27520,10 +27513,10 @@
         <v>12</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="100.8">
@@ -27531,13 +27524,13 @@
         <v>8</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C163" s="2">
         <v>0</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>11</v>
@@ -27546,10 +27539,10 @@
         <v>12</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
     </row>
     <row r="164" spans="1:8" ht="43.2">
@@ -27557,13 +27550,13 @@
         <v>8</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C164" s="2">
         <v>1</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>11</v>
@@ -27572,10 +27565,10 @@
         <v>12</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
     </row>
     <row r="165" spans="1:8" ht="115.2">
@@ -27583,13 +27576,13 @@
         <v>8</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C165" s="2">
         <v>0</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>11</v>
@@ -27598,10 +27591,10 @@
         <v>12</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
     </row>
     <row r="166" spans="1:8" ht="86.4">
@@ -27609,13 +27602,13 @@
         <v>8</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C166" s="2">
         <v>1</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>11</v>
@@ -27624,10 +27617,10 @@
         <v>12</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="86.4">
@@ -27635,13 +27628,13 @@
         <v>8</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C167" s="2">
         <v>0</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>11</v>
@@ -27650,10 +27643,10 @@
         <v>12</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="H167" s="3" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="28.8">
@@ -27661,13 +27654,13 @@
         <v>8</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C168" s="2">
         <v>0</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>11</v>
@@ -27676,10 +27669,10 @@
         <v>12</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
     </row>
     <row r="169" spans="1:8" ht="57.6">
@@ -27687,13 +27680,13 @@
         <v>8</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C169" s="2">
         <v>1</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>11</v>
@@ -27702,10 +27695,10 @@
         <v>12</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="H169" s="3" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="170" spans="1:8">
@@ -27713,13 +27706,13 @@
         <v>8</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C170" s="2">
         <v>2</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>11</v>
@@ -27728,10 +27721,10 @@
         <v>12</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="H170" s="3" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="57.6">
@@ -27739,13 +27732,13 @@
         <v>8</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C171" s="2">
         <v>0</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>11</v>
@@ -27754,10 +27747,10 @@
         <v>12</v>
       </c>
       <c r="G171" s="3" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H171" s="6" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
     </row>
     <row r="172" spans="1:8" ht="28.8">
@@ -27765,13 +27758,13 @@
         <v>8</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C172" s="2">
         <v>1</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>11</v>
@@ -27780,10 +27773,10 @@
         <v>12</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H172" s="6" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="28.8">
@@ -27791,13 +27784,13 @@
         <v>8</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C173" s="2">
         <v>0</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>11</v>
@@ -27806,10 +27799,10 @@
         <v>12</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H173" s="6" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="409.6">
@@ -27817,13 +27810,13 @@
         <v>8</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C174" s="2">
         <v>1</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>11</v>
@@ -27832,10 +27825,10 @@
         <v>12</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="H174" s="3" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="28.8">
@@ -27843,13 +27836,13 @@
         <v>8</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C175" s="2">
         <v>0</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>11</v>
@@ -27858,10 +27851,10 @@
         <v>12</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="H175" s="6" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:8" ht="374.4">
@@ -27869,13 +27862,13 @@
         <v>8</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C176" s="2">
         <v>1</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>11</v>
@@ -27884,10 +27877,10 @@
         <v>12</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>797</v>
+        <v>787</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>796</v>
+        <v>786</v>
       </c>
     </row>
     <row r="177" spans="1:8" ht="201.6">
@@ -27895,13 +27888,13 @@
         <v>8</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C177" s="2">
         <v>2</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>11</v>
@@ -27910,10 +27903,10 @@
         <v>12</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="H177" s="3" t="s">
-        <v>785</v>
+        <v>776</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="86.4">
@@ -27921,13 +27914,13 @@
         <v>8</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C178" s="2">
         <v>0</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>11</v>
@@ -27936,10 +27929,10 @@
         <v>12</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>777</v>
+        <v>768</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -27947,13 +27940,13 @@
         <v>8</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C179" s="2">
         <v>1</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>11</v>
@@ -27962,7 +27955,7 @@
         <v>12</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="H179" s="6" t="s">
         <v>31</v>
@@ -27973,13 +27966,13 @@
         <v>8</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C180" s="2">
         <v>0</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>11</v>
@@ -27988,10 +27981,10 @@
         <v>12</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -27999,13 +27992,13 @@
         <v>8</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C181" s="2">
         <v>0</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>11</v>
@@ -28014,10 +28007,10 @@
         <v>12</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="H181" s="6" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -28025,13 +28018,13 @@
         <v>8</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C182" s="2">
         <v>0</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>11</v>
@@ -28040,10 +28033,10 @@
         <v>12</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -28051,13 +28044,13 @@
         <v>8</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C183" s="2">
         <v>0</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>11</v>
@@ -28066,10 +28059,10 @@
         <v>12</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="H183" s="6" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -28077,13 +28070,13 @@
         <v>8</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C184" s="2">
         <v>0</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>11</v>
@@ -28092,10 +28085,10 @@
         <v>12</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="144">
@@ -28103,13 +28096,13 @@
         <v>8</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C185" s="2">
         <v>0</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>11</v>
@@ -28118,10 +28111,10 @@
         <v>12</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
     </row>
     <row r="186" spans="1:8" ht="28.8">
@@ -28129,13 +28122,13 @@
         <v>8</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C186" s="2">
         <v>14</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>11</v>
@@ -28144,10 +28137,10 @@
         <v>12</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="187" spans="1:8" ht="28.8">
@@ -28155,13 +28148,13 @@
         <v>8</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C187" s="2">
         <v>15</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>11</v>
@@ -28170,10 +28163,10 @@
         <v>12</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H187" s="6" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="188" spans="1:8" ht="57.6">
@@ -28181,13 +28174,13 @@
         <v>8</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C188" s="2">
         <v>16</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>11</v>
@@ -28196,10 +28189,10 @@
         <v>12</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="H188" s="3" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="28.8">
@@ -28207,13 +28200,13 @@
         <v>8</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C189" s="2">
         <v>18</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>11</v>
@@ -28222,10 +28215,10 @@
         <v>12</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="H189" s="6" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="190" spans="1:8" ht="57.6">
@@ -28233,13 +28226,13 @@
         <v>8</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C190" s="2">
         <v>20</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>11</v>
@@ -28248,10 +28241,10 @@
         <v>12</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="43.2">
@@ -28259,13 +28252,13 @@
         <v>8</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C191" s="2">
         <v>21</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>11</v>
@@ -28274,10 +28267,10 @@
         <v>12</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="H191" s="6" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="192" spans="1:8" ht="28.8">
@@ -28285,13 +28278,13 @@
         <v>8</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C192" s="2">
         <v>22</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>11</v>
@@ -28300,10 +28293,10 @@
         <v>12</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="H192" s="6" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="193" spans="1:8" ht="28.8">
@@ -28311,13 +28304,13 @@
         <v>8</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C193" s="2">
         <v>29</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>11</v>
@@ -28326,10 +28319,10 @@
         <v>12</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="H193" s="6" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="194" spans="1:8" ht="244.8">
@@ -28337,13 +28330,13 @@
         <v>8</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C194" s="2">
         <v>30</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>11</v>
@@ -28352,10 +28345,10 @@
         <v>12</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="H194" s="6" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -28363,13 +28356,13 @@
         <v>8</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C195" s="2">
         <v>31</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>11</v>
@@ -28378,7 +28371,7 @@
         <v>12</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="H195" s="6" t="s">
         <v>14</v>
@@ -28389,13 +28382,13 @@
         <v>8</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C196" s="2">
         <v>0</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>11</v>
@@ -28404,10 +28397,10 @@
         <v>12</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="H196" s="6" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="197" spans="1:8" ht="28.8">
@@ -28415,13 +28408,13 @@
         <v>8</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C197" s="2">
         <v>1</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>11</v>
@@ -28430,10 +28423,10 @@
         <v>12</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="H197" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -28441,13 +28434,13 @@
         <v>8</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C198" s="2">
         <v>2</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>11</v>
@@ -28456,10 +28449,10 @@
         <v>12</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="H198" s="6" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="100.8">
@@ -28467,13 +28460,13 @@
         <v>8</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C199" s="2">
         <v>3</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>11</v>
@@ -28482,10 +28475,10 @@
         <v>12</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="H199" s="3" t="s">
-        <v>778</v>
+        <v>769</v>
       </c>
     </row>
     <row r="200" spans="1:8" ht="158.4">
@@ -28493,13 +28486,13 @@
         <v>8</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C200" s="2">
         <v>4</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>11</v>
@@ -28508,10 +28501,10 @@
         <v>12</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="H200" s="3" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
     </row>
     <row r="201" spans="1:8" ht="43.2">
@@ -28519,13 +28512,13 @@
         <v>8</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C201" s="2">
         <v>5</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>11</v>
@@ -28534,10 +28527,10 @@
         <v>12</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
     </row>
     <row r="202" spans="1:8" ht="100.8">
@@ -28545,13 +28538,13 @@
         <v>8</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C202" s="2">
         <v>6</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>11</v>
@@ -28560,10 +28553,10 @@
         <v>12</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="H202" s="3" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
     </row>
     <row r="203" spans="1:8" ht="43.2">
@@ -28571,13 +28564,13 @@
         <v>8</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C203" s="2">
         <v>7</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>11</v>
@@ -28586,10 +28579,10 @@
         <v>12</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="H203" s="3" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="100.8">
@@ -28597,13 +28590,13 @@
         <v>8</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C204" s="2">
         <v>8</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>11</v>
@@ -28612,10 +28605,10 @@
         <v>12</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="H204" s="3" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
     </row>
     <row r="205" spans="1:8" ht="100.8">
@@ -28623,13 +28616,13 @@
         <v>8</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C205" s="2">
         <v>9</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>11</v>
@@ -28638,10 +28631,10 @@
         <v>12</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="H205" s="3" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="115.2">
@@ -28649,13 +28642,13 @@
         <v>8</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C206" s="2">
         <v>10</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>11</v>
@@ -28664,10 +28657,10 @@
         <v>12</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="H206" s="3" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
     </row>
     <row r="207" spans="1:8" ht="158.4">
@@ -28675,13 +28668,13 @@
         <v>8</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C207" s="2">
         <v>11</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>11</v>
@@ -28690,10 +28683,10 @@
         <v>12</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="H207" s="3" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="172.8">
@@ -28701,13 +28694,13 @@
         <v>8</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C208" s="2">
         <v>12</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>11</v>
@@ -28716,10 +28709,10 @@
         <v>12</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="H208" s="3" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
     </row>
     <row r="209" spans="1:8" ht="115.2">
@@ -28727,13 +28720,13 @@
         <v>8</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C209" s="2">
         <v>13</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>11</v>
@@ -28742,10 +28735,10 @@
         <v>12</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H209" s="3" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
     </row>
     <row r="210" spans="1:8" ht="158.4">
@@ -28753,13 +28746,13 @@
         <v>8</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C210" s="2">
         <v>14</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>11</v>
@@ -28768,10 +28761,10 @@
         <v>12</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>779</v>
+        <v>770</v>
       </c>
       <c r="H210" s="3" t="s">
-        <v>780</v>
+        <v>771</v>
       </c>
     </row>
     <row r="211" spans="1:8" ht="158.4">
@@ -28779,13 +28772,13 @@
         <v>8</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C211" s="2">
         <v>15</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>11</v>
@@ -28794,10 +28787,10 @@
         <v>12</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="H211" s="3" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
     </row>
     <row r="212" spans="1:8" ht="100.8">
@@ -28805,13 +28798,13 @@
         <v>8</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C212" s="2">
         <v>16</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>11</v>
@@ -28820,10 +28813,10 @@
         <v>12</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="H212" s="3" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
     </row>
     <row r="213" spans="1:8" ht="100.8">
@@ -28831,13 +28824,13 @@
         <v>8</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C213" s="2">
         <v>17</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>11</v>
@@ -28846,10 +28839,10 @@
         <v>12</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="H213" s="3" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
     </row>
     <row r="214" spans="1:8" ht="43.2">
@@ -28857,13 +28850,13 @@
         <v>8</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C214" s="2">
         <v>18</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>11</v>
@@ -28872,10 +28865,10 @@
         <v>12</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="H214" s="3" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
     </row>
     <row r="215" spans="1:8" ht="43.2">
@@ -28883,13 +28876,13 @@
         <v>8</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C215" s="2">
         <v>19</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>11</v>
@@ -28898,10 +28891,10 @@
         <v>12</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="H215" s="3" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="216" spans="1:8" ht="43.2">
@@ -28909,13 +28902,13 @@
         <v>8</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C216" s="2">
         <v>20</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>11</v>
@@ -28924,10 +28917,10 @@
         <v>12</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
     </row>
     <row r="217" spans="1:8" ht="288">
@@ -28935,13 +28928,13 @@
         <v>8</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C217" s="2">
         <v>21</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>11</v>
@@ -28950,10 +28943,10 @@
         <v>12</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="H217" s="3" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
     </row>
     <row r="218" spans="1:8" ht="115.2">
@@ -28961,13 +28954,13 @@
         <v>8</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C218" s="2">
         <v>22</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>11</v>
@@ -28976,10 +28969,10 @@
         <v>12</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="H218" s="3" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
     </row>
     <row r="219" spans="1:8" ht="43.2">
@@ -28987,13 +28980,13 @@
         <v>8</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C219" s="2">
         <v>23</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>11</v>
@@ -29002,10 +28995,10 @@
         <v>12</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="H219" s="3" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="220" spans="1:8" ht="86.4">
@@ -29013,13 +29006,13 @@
         <v>8</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C220" s="2">
         <v>24</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>11</v>
@@ -29028,10 +29021,10 @@
         <v>12</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="H220" s="3" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
     </row>
     <row r="221" spans="1:8" ht="115.2">
@@ -29039,13 +29032,13 @@
         <v>8</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C221" s="2">
         <v>25</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>11</v>
@@ -29054,10 +29047,10 @@
         <v>12</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="H221" s="3" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
     </row>
     <row r="222" spans="1:8" ht="43.2">
@@ -29065,13 +29058,13 @@
         <v>8</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C222" s="2">
         <v>26</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>11</v>
@@ -29080,10 +29073,10 @@
         <v>12</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="H222" s="3" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
     </row>
     <row r="223" spans="1:8" ht="100.8">
@@ -29091,13 +29084,13 @@
         <v>8</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C223" s="2">
         <v>27</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>11</v>
@@ -29106,10 +29099,10 @@
         <v>12</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="H223" s="3" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
     </row>
     <row r="224" spans="1:8" ht="43.2">
@@ -29117,13 +29110,13 @@
         <v>8</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C224" s="2">
         <v>28</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>11</v>
@@ -29132,10 +29125,10 @@
         <v>12</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="H224" s="3" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="225" spans="1:8" ht="43.2">
@@ -29143,13 +29136,13 @@
         <v>8</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C225" s="2">
         <v>29</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>11</v>
@@ -29158,10 +29151,10 @@
         <v>12</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="H225" s="3" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
     </row>
     <row r="226" spans="1:8" ht="100.8">
@@ -29169,13 +29162,13 @@
         <v>8</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C226" s="2">
         <v>30</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>11</v>
@@ -29184,10 +29177,10 @@
         <v>12</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="H226" s="3" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
     </row>
     <row r="227" spans="1:8" ht="28.8">
@@ -29195,13 +29188,13 @@
         <v>8</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="C227" s="2">
         <v>0</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>11</v>
@@ -29210,10 +29203,10 @@
         <v>12</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="H227" s="6" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
     </row>
     <row r="228" spans="1:8" ht="28.8">
@@ -29221,13 +29214,13 @@
         <v>8</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C228" s="2">
         <v>0</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>11</v>
@@ -29236,10 +29229,10 @@
         <v>12</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="229" spans="1:8" ht="43.2">
@@ -29247,13 +29240,13 @@
         <v>8</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C229" s="2">
         <v>1</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>11</v>
@@ -29262,10 +29255,10 @@
         <v>12</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="H229" s="3" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
     </row>
     <row r="230" spans="1:8" ht="100.8">
@@ -29273,13 +29266,13 @@
         <v>8</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C230" s="2">
         <v>2</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>11</v>
@@ -29288,10 +29281,10 @@
         <v>12</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="H230" s="3" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
     </row>
     <row r="231" spans="1:8" ht="43.2">
@@ -29299,13 +29292,13 @@
         <v>8</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C231" s="2">
         <v>3</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>11</v>
@@ -29314,10 +29307,10 @@
         <v>12</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="H231" s="3" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
     </row>
     <row r="232" spans="1:8">
@@ -29325,13 +29318,13 @@
         <v>8</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="C232" s="2">
         <v>0</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>11</v>
@@ -29340,10 +29333,10 @@
         <v>12</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="H232" s="6" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="233" spans="1:8">
@@ -29351,13 +29344,13 @@
         <v>8</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C233" s="2">
         <v>0</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>11</v>
@@ -29366,10 +29359,10 @@
         <v>12</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="H233" s="6" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="234" spans="1:8" ht="28.8">
@@ -29377,13 +29370,13 @@
         <v>8</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C234" s="2">
         <v>1</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>11</v>
@@ -29392,10 +29385,10 @@
         <v>12</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="H234" s="6" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
     </row>
     <row r="235" spans="1:8">
@@ -29403,13 +29396,13 @@
         <v>8</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="C235" s="2">
         <v>0</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>11</v>
@@ -29418,10 +29411,10 @@
         <v>12</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="H235" s="6" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="236" spans="1:8" ht="28.8">
@@ -29429,13 +29422,13 @@
         <v>8</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="C236" s="2">
         <v>1</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>11</v>
@@ -29444,10 +29437,10 @@
         <v>12</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="H236" s="4" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="237" spans="1:8">
@@ -29455,13 +29448,13 @@
         <v>8</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="C237" s="2">
         <v>0</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>11</v>
@@ -29470,7 +29463,7 @@
         <v>12</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="H237" s="4" t="s">
         <v>25</v>
@@ -29481,13 +29474,13 @@
         <v>8</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="C238" s="2">
         <v>1</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>11</v>
@@ -29496,10 +29489,10 @@
         <v>12</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="H238" s="4" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -29507,13 +29500,13 @@
         <v>8</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C239" s="2">
         <v>0</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>11</v>
@@ -29522,24 +29515,24 @@
         <v>12</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="H239" s="4" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="240" spans="1:8">
       <c r="A240" t="s">
-        <v>781</v>
+        <v>772</v>
       </c>
       <c r="B240" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C240">
         <v>1</v>
       </c>
       <c r="D240" t="s">
-        <v>782</v>
+        <v>773</v>
       </c>
       <c r="E240" t="s">
         <v>11</v>
@@ -29548,10 +29541,10 @@
         <v>12</v>
       </c>
       <c r="G240" t="s">
-        <v>783</v>
+        <v>774</v>
       </c>
       <c r="H240" s="4" t="s">
-        <v>784</v>
+        <v>775</v>
       </c>
     </row>
     <row r="241" spans="1:8">

--- a/docassemble/PowerOfAttorneyHealthCare/data/sources/poa_hc_es.xlsx
+++ b/docassemble/PowerOfAttorneyHealthCare/data/sources/poa_hc_es.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnewsted\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24235661-ED45-4127-BBDE-4E397A8609F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB43FF36-A6FE-43D2-B494-EFFC05E36C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5340" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20391,63 +20391,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Después de descargar tus formularios, tendrás que firmar el documento frente a un testigo. El testigo también tendrá que firmar el documento. No necesitas saber quién será el testigo para usar este programa.
-Después de que el formulario esté firmado, querrás entregar copias del poder notarial a tu agente, así como a tus proveedores de atención médica. Tus formularios incluirán instrucciones con más información.
-Para obtener más información, lee el artículo de ILAO sobre los [**Conceptos Básicos del Poder Notarial para el Cuidado de la Salud**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://es.illinoislegalaid.org/legal-information/setting-power-attorney-healthcare</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>).
-Si deseas saber más sobre la planificación en caso de discapacidad o el cuidado al final de la vida, puedes revisar la guía de ILAO y CDEL [**Empodérate de tu Futuro**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${ preview.url_for() }</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">Tu agente es una persona en quien confías y que eliges para tomar decisiones sobre tu atención médica y cuidado de tu salud por ti, si alguna vez necesitas ayuda. 
 Tu agente debe tener al menos 18 años de edad. Tu agente no tiene que ser un familiar, pero debe ser alguien en quien confíes. Tu agente no necesita ser ciudadano de los Estados Unidos. 
 Puedes seleccionar agentes sucesores como respaldo si el primer agente no puede tomar estas decisiones.
@@ -22832,6 +22775,63 @@
         <scheme val="minor"/>
       </rPr>
       <t>${collapse_template(video_cooling)}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Después de descargar tus formularios, tendrás que firmar el documento frente a un testigo. El testigo también tendrá que firmar el documento. No necesitas saber quién será el testigo para usar este programa.
+Después de que el formulario esté firmado, querrás entregar copias del poder notarial a tu agente, así como a tus proveedores de atención médica. Tus formularios incluirán instrucciones con más información.
+Para obtener más información, lee el artículo de ILAO sobre los [**Conceptos Básicos del Poder Notarial para el Cuidado de la Salud**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://es.illinoislegalaid.org/legal-information/setting-power-attorney-healthcare</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).
+Si deseas saber más sobre la planificación en caso de discapacidad o el cuidado al final de la vida, puedes revisar la guía de ILAO y CDEL [**Empodérate de tu Futuro**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ preview_es.url_for() }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
     </r>
   </si>
 </sst>
@@ -23382,7 +23382,7 @@
         <v>16</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -23642,7 +23642,7 @@
         <v>42</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>763</v>
+        <v>797</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="28.8">
@@ -23694,7 +23694,7 @@
         <v>48</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="28.8">
@@ -23746,21 +23746,21 @@
         <v>54</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="115.2">
       <c r="A18" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C18" s="2">
         <v>0</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>11</v>
@@ -23769,18 +23769,18 @@
         <v>12</v>
       </c>
       <c r="G18" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>780</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="28.8">
       <c r="A19" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
@@ -24046,7 +24046,7 @@
         <v>1</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>11</v>
@@ -24055,10 +24055,10 @@
         <v>12</v>
       </c>
       <c r="G29" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="H29" s="3" t="s">
         <v>793</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -24162,7 +24162,7 @@
         <v>87</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -24630,7 +24630,7 @@
         <v>133</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="28.8">
@@ -24734,7 +24734,7 @@
         <v>144</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="288">
@@ -25381,7 +25381,7 @@
         <v>12</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>639</v>
@@ -25852,7 +25852,7 @@
         <v>247</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="86.4">
@@ -26736,7 +26736,7 @@
         <v>327</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -26819,16 +26819,16 @@
     </row>
     <row r="136" spans="1:8" ht="115.2">
       <c r="A136" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C136" s="2">
         <v>0</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>11</v>
@@ -26837,10 +26837,10 @@
         <v>12</v>
       </c>
       <c r="G136" s="3" t="s">
+        <v>783</v>
+      </c>
+      <c r="H136" s="3" t="s">
         <v>784</v>
-      </c>
-      <c r="H136" s="3" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="137" spans="1:8" ht="409.6">
@@ -26866,7 +26866,7 @@
         <v>334</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="28.8">
@@ -27100,7 +27100,7 @@
         <v>356</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -27230,7 +27230,7 @@
         <v>370</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="152" spans="1:8" ht="28.8">
@@ -27877,10 +27877,10 @@
         <v>12</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="177" spans="1:8" ht="201.6">
@@ -27906,7 +27906,7 @@
         <v>442</v>
       </c>
       <c r="H177" s="3" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="86.4">
@@ -27932,7 +27932,7 @@
         <v>445</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -28478,7 +28478,7 @@
         <v>504</v>
       </c>
       <c r="H199" s="3" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="200" spans="1:8" ht="158.4">
@@ -28761,10 +28761,10 @@
         <v>12</v>
       </c>
       <c r="G210" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="H210" s="3" t="s">
         <v>770</v>
-      </c>
-      <c r="H210" s="3" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="211" spans="1:8" ht="158.4">
@@ -29523,7 +29523,7 @@
     </row>
     <row r="240" spans="1:8">
       <c r="A240" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B240" t="s">
         <v>595</v>
@@ -29532,7 +29532,7 @@
         <v>1</v>
       </c>
       <c r="D240" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="E240" t="s">
         <v>11</v>
@@ -29541,10 +29541,10 @@
         <v>12</v>
       </c>
       <c r="G240" t="s">
+        <v>773</v>
+      </c>
+      <c r="H240" s="4" t="s">
         <v>774</v>
-      </c>
-      <c r="H240" s="4" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="241" spans="1:8">

--- a/docassemble/PowerOfAttorneyHealthCare/data/sources/poa_hc_es.xlsx
+++ b/docassemble/PowerOfAttorneyHealthCare/data/sources/poa_hc_es.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnewsted\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB43FF36-A6FE-43D2-B494-EFFC05E36C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD8239A-22B3-4E79-9362-9091D3D53A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5340" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-34695" yWindow="-2895" windowWidth="31785" windowHeight="17910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -10524,386 +10524,6 @@
     </r>
   </si>
   <si>
-    <t>4df62dd05d59a5e95853014f178b6ac4</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**Limits for </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">:**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if limit_checkboxes['no_autopsy']:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">* </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${subject_do_does}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> not authorize an autopsy.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if limit_checkboxes['no_science']:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">* </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${subject_do_does}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> not authorize donation of </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${my_their}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> remains to science.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if limit_checkboxes['no_start']:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">* </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${subject_do_does}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> not authorize starting these treatments: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${fix_punctuation(no_start_text)}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if limit_checkboxes['no_end']:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">* </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${subject_do_does}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> not authorize ending these treatments: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${fix_punctuation(no_end_text)}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if limit_checkboxes['other']:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">* </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${fix_punctuation(other_limits)}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-  </si>
-  <si>
     <t>53f4eea875cd986be67631969353d829</t>
   </si>
   <si>
@@ -17277,338 +16897,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**Límites para </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">:**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if limit_checkboxes['no_autopsy']:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">* </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${subject_do_does}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> no autoriza una autopsia.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-% if limit_checkboxes['no_science']:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">* </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${subject_do_does}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> no autoriza la donación de </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${my_their}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> restos a la ciencia.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-% if limit_checkboxes['no_start']:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">* </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${subject_do_does}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> no autoriza iniciar estos tratamientos: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${fix_punctuation(no_start_text)}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-% if limit_checkboxes['no_end']:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">* </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${subject_do_does}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> no autoriza suspender estos tratamientos: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${fix_punctuation(no_end_text)}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-% if limit_checkboxes['other']:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">* </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${fix_punctuation(other_limits)}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <b/>
         <sz val="11"/>
         <color rgb="FF008000"/>
@@ -22832,6 +22120,990 @@
         <scheme val="minor"/>
       </rPr>
       <t>).</t>
+    </r>
+  </si>
+  <si>
+    <t>98dc4f5f71b807757f3e798f7c664c92</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**Limits for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if limit_checkboxes['no_autopsy'] and for_yourself:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">* I do not authorize an autopsy.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if limit_checkboxes['no_science'] and for_yourself:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">* I do not authorize donation of my remains to science.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if limit_checkboxes['no_start'] and for_yourself:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">* I do not authorize starting these treatments: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${fix_punctuation(no_start_text)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if limit_checkboxes['no_end'] and for_yourself:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">* I do not authorize ending these treatments: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${fix_punctuation(no_end_text)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if limit_checkboxes['no_autopsy'] and not for_yourself:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">* </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> does not authorize an autopsy.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if limit_checkboxes['no_science'] and not for_yourself:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">* </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> does not authorize donation of their remains to science.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if limit_checkboxes['no_start'] and not for_yourself:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">* </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> does not authorize starting these treatments: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${fix_punctuation(no_start_text)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if limit_checkboxes['no_end'] and not for_yourself:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">* </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> does not authorize ending these treatments: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${fix_punctuation(no_end_text)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if limit_checkboxes['other']:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">* </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${fix_punctuation(other_limits)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">**Límites para </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if limit_checkboxes['no_autopsy'] and for_yourself:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">* Yo no autorizo una autopsia.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+% if limit_checkboxes['no_science'] and for_yourself:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">* Yo no autorizo la donación de mi restos a la ciencia.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+% if limit_checkboxes['no_start'] and for_yourself:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">* Yo no autorizo iniciar estos tratamientos: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${fix_punctuation(no_start_text)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+% if limit_checkboxes['no_end'] and for_yourself:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">* Yo no autorizo suspender estos tratamientos: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${fix_punctuation(no_end_text)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+% if limit_checkboxes['no_autopsy'] and not for_yourself:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">* </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> no autoriza una autopsia.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+% if limit_checkboxes['no_science'] and not for_yourself:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">* </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> no autoriza la donación de sus restos a la ciencia.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+% if limit_checkboxes['no_start'] and not for_yourself:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">* </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> no autoriza iniciar estos tratamientos: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${fix_punctuation(no_start_text)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+% if limit_checkboxes['no_end'] and not for_yourself:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">* </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> no autoriza suspender estos tratamientos: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${fix_punctuation(no_end_text)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+% if limit_checkboxes['other']:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">* </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${fix_punctuation(other_limits)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
     </r>
   </si>
 </sst>
@@ -23297,7 +23569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H242"/>
+  <dimension ref="A1:I242"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="61.109375" customWidth="1"/>
@@ -23305,6 +23577,7 @@
     <col min="3" max="3" width="12.6640625" customWidth="1"/>
     <col min="4" max="4" width="32.5546875" customWidth="1"/>
     <col min="7" max="8" width="75.6640625" customWidth="1"/>
+    <col min="9" max="9" width="15.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -23382,7 +23655,7 @@
         <v>16</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -23434,7 +23707,7 @@
         <v>22</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -23538,7 +23811,7 @@
         <v>33</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="28.8">
@@ -23552,7 +23825,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>11</v>
@@ -23561,7 +23834,7 @@
         <v>12</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>35</v>
@@ -23578,7 +23851,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>11</v>
@@ -23587,7 +23860,7 @@
         <v>12</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>36</v>
@@ -23642,7 +23915,7 @@
         <v>42</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="28.8">
@@ -23694,7 +23967,7 @@
         <v>48</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="28.8">
@@ -23746,21 +24019,21 @@
         <v>54</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="115.2">
       <c r="A18" s="2" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="C18" s="2">
         <v>0</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>11</v>
@@ -23769,18 +24042,18 @@
         <v>12</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="28.8">
       <c r="A19" s="2" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
@@ -23824,7 +24097,7 @@
         <v>60</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -23850,7 +24123,7 @@
         <v>63</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="43.2">
@@ -23876,7 +24149,7 @@
         <v>65</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="57.6">
@@ -23902,7 +24175,7 @@
         <v>67</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="28.8">
@@ -23928,7 +24201,7 @@
         <v>69</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="57.6">
@@ -23954,7 +24227,7 @@
         <v>71</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="28.8">
@@ -23980,7 +24253,7 @@
         <v>74</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="244.8">
@@ -24006,7 +24279,7 @@
         <v>76</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="86.4">
@@ -24032,7 +24305,7 @@
         <v>79</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="409.6">
@@ -24046,7 +24319,7 @@
         <v>1</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>11</v>
@@ -24055,10 +24328,10 @@
         <v>12</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -24084,7 +24357,7 @@
         <v>81</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -24110,7 +24383,7 @@
         <v>83</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -24136,7 +24409,7 @@
         <v>85</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -24162,7 +24435,7 @@
         <v>87</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -24214,7 +24487,7 @@
         <v>92</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="100.8">
@@ -24240,7 +24513,7 @@
         <v>95</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="28.8">
@@ -24266,7 +24539,7 @@
         <v>97</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="86.4">
@@ -24292,7 +24565,7 @@
         <v>100</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="28.8">
@@ -24318,7 +24591,7 @@
         <v>103</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="144">
@@ -24344,7 +24617,7 @@
         <v>105</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="86.4">
@@ -24396,7 +24669,7 @@
         <v>112</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="374.4">
@@ -24422,7 +24695,7 @@
         <v>114</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="86.4">
@@ -24448,7 +24721,7 @@
         <v>117</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="28.8">
@@ -24474,7 +24747,7 @@
         <v>119</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="28.8">
@@ -24500,7 +24773,7 @@
         <v>122</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -24526,7 +24799,7 @@
         <v>124</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="43.2">
@@ -24552,7 +24825,7 @@
         <v>126</v>
       </c>
       <c r="H48" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -24578,7 +24851,7 @@
         <v>128</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -24604,7 +24877,7 @@
         <v>130</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="129.6">
@@ -24630,7 +24903,7 @@
         <v>133</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="28.8">
@@ -24656,7 +24929,7 @@
         <v>135</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="28.8">
@@ -24708,7 +24981,7 @@
         <v>141</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="100.8">
@@ -24734,7 +25007,7 @@
         <v>144</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="288">
@@ -24760,7 +25033,7 @@
         <v>146</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="28.8">
@@ -24786,7 +25059,7 @@
         <v>149</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -24838,7 +25111,7 @@
         <v>155</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="28.8">
@@ -24864,7 +25137,7 @@
         <v>157</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="144">
@@ -24890,7 +25163,7 @@
         <v>159</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -24968,7 +25241,7 @@
         <v>167</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="43.2">
@@ -24994,7 +25267,7 @@
         <v>169</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="57.6">
@@ -25020,7 +25293,7 @@
         <v>171</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -25072,7 +25345,7 @@
         <v>177</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="172.8">
@@ -25098,7 +25371,7 @@
         <v>179</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="28.8">
@@ -25124,7 +25397,7 @@
         <v>181</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -25150,7 +25423,7 @@
         <v>183</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="43.2">
@@ -25176,7 +25449,7 @@
         <v>185</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="57.6">
@@ -25202,7 +25475,7 @@
         <v>187</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -25228,7 +25501,7 @@
         <v>189</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="28.8">
@@ -25280,7 +25553,7 @@
         <v>195</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="115.2">
@@ -25306,7 +25579,7 @@
         <v>198</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="360">
@@ -25332,7 +25605,7 @@
         <v>200</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="28.8">
@@ -25358,7 +25631,7 @@
         <v>203</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="28.8">
@@ -25381,10 +25654,10 @@
         <v>12</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="72">
@@ -25410,7 +25683,7 @@
         <v>207</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="72">
@@ -25436,7 +25709,7 @@
         <v>209</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -25488,7 +25761,7 @@
         <v>214</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -25514,7 +25787,7 @@
         <v>216</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -25566,7 +25839,7 @@
         <v>222</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="43.2">
@@ -25592,7 +25865,7 @@
         <v>224</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="43.2">
@@ -25615,10 +25888,10 @@
         <v>12</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="72">
@@ -25644,7 +25917,7 @@
         <v>228</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="72">
@@ -25670,7 +25943,7 @@
         <v>230</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -25722,7 +25995,7 @@
         <v>235</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -25748,7 +26021,7 @@
         <v>237</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -25774,7 +26047,7 @@
         <v>239</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="201.6">
@@ -25800,7 +26073,7 @@
         <v>242</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="28.8">
@@ -25826,7 +26099,7 @@
         <v>245</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="129.6">
@@ -25852,7 +26125,7 @@
         <v>247</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="86.4">
@@ -25878,7 +26151,7 @@
         <v>250</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="302.39999999999998">
@@ -25904,7 +26177,7 @@
         <v>252</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="28.8">
@@ -25930,7 +26203,7 @@
         <v>255</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="102" spans="1:8" ht="86.4">
@@ -25956,7 +26229,7 @@
         <v>257</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -26008,7 +26281,7 @@
         <v>262</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -26060,7 +26333,7 @@
         <v>267</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -26138,7 +26411,7 @@
         <v>275</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="110" spans="1:8" ht="43.2">
@@ -26164,7 +26437,7 @@
         <v>278</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="86.4">
@@ -26187,10 +26460,10 @@
         <v>12</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -26216,7 +26489,7 @@
         <v>281</v>
       </c>
       <c r="H112" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -26242,7 +26515,7 @@
         <v>283</v>
       </c>
       <c r="H113" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -26268,7 +26541,7 @@
         <v>285</v>
       </c>
       <c r="H114" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -26294,7 +26567,7 @@
         <v>287</v>
       </c>
       <c r="H115" s="6" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="116" spans="1:8" ht="43.2">
@@ -26320,7 +26593,7 @@
         <v>289</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="28.8">
@@ -26398,7 +26671,7 @@
         <v>297</v>
       </c>
       <c r="H119" s="6" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="120" spans="1:8" ht="28.8">
@@ -26424,7 +26697,7 @@
         <v>300</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -26450,7 +26723,7 @@
         <v>302</v>
       </c>
       <c r="H121" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="86.4">
@@ -26476,7 +26749,7 @@
         <v>305</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="28.8">
@@ -26502,7 +26775,7 @@
         <v>307</v>
       </c>
       <c r="H123" s="6" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="28.8">
@@ -26528,7 +26801,7 @@
         <v>309</v>
       </c>
       <c r="H124" s="8" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="28.8">
@@ -26554,7 +26827,7 @@
         <v>311</v>
       </c>
       <c r="H125" s="8" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="28.8">
@@ -26580,7 +26853,7 @@
         <v>313</v>
       </c>
       <c r="H126" s="8" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -26606,7 +26879,7 @@
         <v>315</v>
       </c>
       <c r="H127" s="8" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -26658,7 +26931,7 @@
         <v>320</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -26684,7 +26957,7 @@
         <v>322</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="131" spans="1:8" ht="28.8">
@@ -26710,7 +26983,7 @@
         <v>325</v>
       </c>
       <c r="H131" s="6" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="132" spans="1:8" ht="403.2">
@@ -26736,7 +27009,7 @@
         <v>327</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -26762,7 +27035,7 @@
         <v>330</v>
       </c>
       <c r="H133" s="6" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="134" spans="1:8" ht="43.2">
@@ -26788,7 +27061,7 @@
         <v>332</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="100.8">
@@ -26802,7 +27075,7 @@
         <v>2</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>11</v>
@@ -26811,24 +27084,24 @@
         <v>12</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
     </row>
     <row r="136" spans="1:8" ht="115.2">
       <c r="A136" s="2" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="C136" s="2">
         <v>0</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>11</v>
@@ -26837,10 +27110,10 @@
         <v>12</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
     </row>
     <row r="137" spans="1:8" ht="409.6">
@@ -26866,7 +27139,7 @@
         <v>334</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="28.8">
@@ -26892,7 +27165,7 @@
         <v>337</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -26918,7 +27191,7 @@
         <v>340</v>
       </c>
       <c r="H139" s="6" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="140" spans="1:8" ht="57.6">
@@ -26944,7 +27217,7 @@
         <v>342</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -26970,7 +27243,7 @@
         <v>344</v>
       </c>
       <c r="H141" s="6" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="142" spans="1:8" ht="43.2">
@@ -26996,7 +27269,7 @@
         <v>346</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="143" spans="1:8" ht="86.4">
@@ -27022,7 +27295,7 @@
         <v>348</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="144" spans="1:8" ht="216">
@@ -27048,7 +27321,7 @@
         <v>350</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="145" spans="1:8" ht="86.4">
@@ -27100,7 +27373,7 @@
         <v>356</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -27152,7 +27425,7 @@
         <v>362</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="28.8">
@@ -27178,7 +27451,7 @@
         <v>365</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -27204,7 +27477,7 @@
         <v>367</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="129.6">
@@ -27230,7 +27503,7 @@
         <v>370</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
     </row>
     <row r="152" spans="1:8" ht="28.8">
@@ -27308,7 +27581,7 @@
         <v>379</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="155" spans="1:8" ht="28.8">
@@ -27334,7 +27607,7 @@
         <v>382</v>
       </c>
       <c r="H155" s="6" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="156" spans="1:8" ht="409.6">
@@ -27360,7 +27633,7 @@
         <v>384</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
     </row>
     <row r="157" spans="1:8" ht="43.2">
@@ -27386,7 +27659,7 @@
         <v>387</v>
       </c>
       <c r="H157" s="6" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="158" spans="1:8" ht="86.4">
@@ -27464,7 +27737,7 @@
         <v>396</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="100.8">
@@ -27490,7 +27763,7 @@
         <v>399</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="144">
@@ -27516,7 +27789,7 @@
         <v>401</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="100.8">
@@ -27542,7 +27815,7 @@
         <v>404</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="164" spans="1:8" ht="43.2">
@@ -27568,7 +27841,7 @@
         <v>406</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="165" spans="1:8" ht="115.2">
@@ -27594,7 +27867,7 @@
         <v>409</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="166" spans="1:8" ht="86.4">
@@ -27672,7 +27945,7 @@
         <v>419</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
     </row>
     <row r="169" spans="1:8" ht="57.6">
@@ -27724,7 +27997,7 @@
         <v>424</v>
       </c>
       <c r="H170" s="3" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="57.6">
@@ -27750,7 +28023,7 @@
         <v>427</v>
       </c>
       <c r="H171" s="6" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="172" spans="1:8" ht="28.8">
@@ -27825,10 +28098,10 @@
         <v>12</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H174" s="3" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="28.8">
@@ -27877,10 +28150,10 @@
         <v>12</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
     </row>
     <row r="177" spans="1:8" ht="201.6">
@@ -27906,7 +28179,7 @@
         <v>442</v>
       </c>
       <c r="H177" s="3" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="86.4">
@@ -27932,7 +28205,7 @@
         <v>445</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -27984,7 +28257,7 @@
         <v>451</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -28010,7 +28283,7 @@
         <v>454</v>
       </c>
       <c r="H181" s="6" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -28036,7 +28309,7 @@
         <v>457</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -28062,7 +28335,7 @@
         <v>460</v>
       </c>
       <c r="H183" s="6" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -28088,7 +28361,7 @@
         <v>463</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="144">
@@ -28114,7 +28387,7 @@
         <v>466</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="186" spans="1:8" ht="28.8">
@@ -28348,7 +28621,7 @@
         <v>492</v>
       </c>
       <c r="H194" s="6" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -28426,7 +28699,7 @@
         <v>500</v>
       </c>
       <c r="H197" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -28452,7 +28725,7 @@
         <v>502</v>
       </c>
       <c r="H198" s="6" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="100.8">
@@ -28478,7 +28751,7 @@
         <v>504</v>
       </c>
       <c r="H199" s="3" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
     </row>
     <row r="200" spans="1:8" ht="158.4">
@@ -28504,7 +28777,7 @@
         <v>506</v>
       </c>
       <c r="H200" s="3" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
     </row>
     <row r="201" spans="1:8" ht="43.2">
@@ -28530,7 +28803,7 @@
         <v>508</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="202" spans="1:8" ht="100.8">
@@ -28556,7 +28829,7 @@
         <v>510</v>
       </c>
       <c r="H202" s="3" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
     </row>
     <row r="203" spans="1:8" ht="43.2">
@@ -28582,7 +28855,7 @@
         <v>512</v>
       </c>
       <c r="H203" s="3" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="100.8">
@@ -28608,7 +28881,7 @@
         <v>514</v>
       </c>
       <c r="H204" s="3" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
     </row>
     <row r="205" spans="1:8" ht="100.8">
@@ -28634,7 +28907,7 @@
         <v>516</v>
       </c>
       <c r="H205" s="3" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="115.2">
@@ -28660,7 +28933,7 @@
         <v>518</v>
       </c>
       <c r="H206" s="3" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="207" spans="1:8" ht="158.4">
@@ -28686,7 +28959,7 @@
         <v>520</v>
       </c>
       <c r="H207" s="3" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="172.8">
@@ -28712,10 +28985,10 @@
         <v>522</v>
       </c>
       <c r="H208" s="3" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
-    <row r="209" spans="1:8" ht="115.2">
+    <row r="209" spans="1:9" ht="115.2">
       <c r="A209" s="2" t="s">
         <v>8</v>
       </c>
@@ -28738,10 +29011,10 @@
         <v>524</v>
       </c>
       <c r="H209" s="3" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
     </row>
-    <row r="210" spans="1:8" ht="158.4">
+    <row r="210" spans="1:9" ht="158.4">
       <c r="A210" s="2" t="s">
         <v>8</v>
       </c>
@@ -28761,13 +29034,13 @@
         <v>12</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="H210" s="3" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
     </row>
-    <row r="211" spans="1:8" ht="158.4">
+    <row r="211" spans="1:9" ht="158.4">
       <c r="A211" s="2" t="s">
         <v>8</v>
       </c>
@@ -28790,10 +29063,10 @@
         <v>527</v>
       </c>
       <c r="H211" s="3" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
-    <row r="212" spans="1:8" ht="100.8">
+    <row r="212" spans="1:9" ht="100.8">
       <c r="A212" s="2" t="s">
         <v>8</v>
       </c>
@@ -28816,10 +29089,10 @@
         <v>529</v>
       </c>
       <c r="H212" s="3" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
     </row>
-    <row r="213" spans="1:8" ht="100.8">
+    <row r="213" spans="1:9" ht="100.8">
       <c r="A213" s="2" t="s">
         <v>8</v>
       </c>
@@ -28842,10 +29115,10 @@
         <v>531</v>
       </c>
       <c r="H213" s="3" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
-    <row r="214" spans="1:8" ht="43.2">
+    <row r="214" spans="1:9" ht="43.2">
       <c r="A214" s="2" t="s">
         <v>8</v>
       </c>
@@ -28868,10 +29141,10 @@
         <v>533</v>
       </c>
       <c r="H214" s="3" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
     </row>
-    <row r="215" spans="1:8" ht="43.2">
+    <row r="215" spans="1:9" ht="43.2">
       <c r="A215" s="2" t="s">
         <v>8</v>
       </c>
@@ -28897,7 +29170,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="216" spans="1:8" ht="43.2">
+    <row r="216" spans="1:9" ht="43.2">
       <c r="A216" s="2" t="s">
         <v>8</v>
       </c>
@@ -28920,10 +29193,10 @@
         <v>538</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
-    <row r="217" spans="1:8" ht="288">
+    <row r="217" spans="1:9" ht="409.6">
       <c r="A217" s="2" t="s">
         <v>8</v>
       </c>
@@ -28934,7 +29207,7 @@
         <v>21</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>539</v>
+        <v>795</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>11</v>
@@ -28943,13 +29216,14 @@
         <v>12</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>540</v>
+        <v>796</v>
       </c>
       <c r="H217" s="3" t="s">
-        <v>723</v>
-      </c>
+        <v>797</v>
+      </c>
+      <c r="I217" s="3"/>
     </row>
-    <row r="218" spans="1:8" ht="115.2">
+    <row r="218" spans="1:9" ht="115.2">
       <c r="A218" s="2" t="s">
         <v>8</v>
       </c>
@@ -28960,7 +29234,7 @@
         <v>22</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>11</v>
@@ -28969,13 +29243,13 @@
         <v>12</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H218" s="3" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
     </row>
-    <row r="219" spans="1:8" ht="43.2">
+    <row r="219" spans="1:9" ht="43.2">
       <c r="A219" s="2" t="s">
         <v>8</v>
       </c>
@@ -28986,7 +29260,7 @@
         <v>23</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>11</v>
@@ -28995,13 +29269,13 @@
         <v>12</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="H219" s="3" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
-    <row r="220" spans="1:8" ht="86.4">
+    <row r="220" spans="1:9" ht="86.4">
       <c r="A220" s="2" t="s">
         <v>8</v>
       </c>
@@ -29012,7 +29286,7 @@
         <v>24</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>11</v>
@@ -29021,13 +29295,13 @@
         <v>12</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="H220" s="3" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
-    <row r="221" spans="1:8" ht="115.2">
+    <row r="221" spans="1:9" ht="115.2">
       <c r="A221" s="2" t="s">
         <v>8</v>
       </c>
@@ -29038,7 +29312,7 @@
         <v>25</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>11</v>
@@ -29047,13 +29321,13 @@
         <v>12</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="H221" s="3" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
-    <row r="222" spans="1:8" ht="43.2">
+    <row r="222" spans="1:9" ht="43.2">
       <c r="A222" s="2" t="s">
         <v>8</v>
       </c>
@@ -29064,7 +29338,7 @@
         <v>26</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>11</v>
@@ -29073,13 +29347,13 @@
         <v>12</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="H222" s="3" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
-    <row r="223" spans="1:8" ht="100.8">
+    <row r="223" spans="1:9" ht="100.8">
       <c r="A223" s="2" t="s">
         <v>8</v>
       </c>
@@ -29090,7 +29364,7 @@
         <v>27</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>11</v>
@@ -29099,13 +29373,13 @@
         <v>12</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="H223" s="3" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
     </row>
-    <row r="224" spans="1:8" ht="43.2">
+    <row r="224" spans="1:9" ht="43.2">
       <c r="A224" s="2" t="s">
         <v>8</v>
       </c>
@@ -29116,7 +29390,7 @@
         <v>28</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>11</v>
@@ -29125,10 +29399,10 @@
         <v>12</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="H224" s="3" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="225" spans="1:8" ht="43.2">
@@ -29142,7 +29416,7 @@
         <v>29</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>11</v>
@@ -29151,10 +29425,10 @@
         <v>12</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="H225" s="3" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="226" spans="1:8" ht="100.8">
@@ -29168,7 +29442,7 @@
         <v>30</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>11</v>
@@ -29177,10 +29451,10 @@
         <v>12</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H226" s="3" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="227" spans="1:8" ht="28.8">
@@ -29188,13 +29462,13 @@
         <v>8</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C227" s="2">
         <v>0</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>11</v>
@@ -29203,10 +29477,10 @@
         <v>12</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H227" s="6" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="228" spans="1:8" ht="28.8">
@@ -29214,13 +29488,13 @@
         <v>8</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C228" s="2">
         <v>0</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>11</v>
@@ -29229,10 +29503,10 @@
         <v>12</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="229" spans="1:8" ht="43.2">
@@ -29240,13 +29514,13 @@
         <v>8</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C229" s="2">
         <v>1</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>11</v>
@@ -29255,10 +29529,10 @@
         <v>12</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="H229" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="230" spans="1:8" ht="100.8">
@@ -29266,13 +29540,13 @@
         <v>8</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C230" s="2">
         <v>2</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>11</v>
@@ -29281,10 +29555,10 @@
         <v>12</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="H230" s="3" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="231" spans="1:8" ht="43.2">
@@ -29292,13 +29566,13 @@
         <v>8</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C231" s="2">
         <v>3</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>11</v>
@@ -29307,10 +29581,10 @@
         <v>12</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H231" s="3" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="232" spans="1:8">
@@ -29318,13 +29592,13 @@
         <v>8</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C232" s="2">
         <v>0</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>11</v>
@@ -29333,10 +29607,10 @@
         <v>12</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="H232" s="6" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="233" spans="1:8">
@@ -29344,13 +29618,13 @@
         <v>8</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C233" s="2">
         <v>0</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>11</v>
@@ -29359,10 +29633,10 @@
         <v>12</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H233" s="6" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="234" spans="1:8" ht="28.8">
@@ -29370,13 +29644,13 @@
         <v>8</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C234" s="2">
         <v>1</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>11</v>
@@ -29385,10 +29659,10 @@
         <v>12</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H234" s="6" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="235" spans="1:8">
@@ -29396,13 +29670,13 @@
         <v>8</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C235" s="2">
         <v>0</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>11</v>
@@ -29411,10 +29685,10 @@
         <v>12</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="H235" s="6" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="236" spans="1:8" ht="28.8">
@@ -29422,13 +29696,13 @@
         <v>8</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C236" s="2">
         <v>1</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>11</v>
@@ -29437,10 +29711,10 @@
         <v>12</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="H236" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="237" spans="1:8">
@@ -29448,13 +29722,13 @@
         <v>8</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C237" s="2">
         <v>0</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>11</v>
@@ -29463,7 +29737,7 @@
         <v>12</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="H237" s="4" t="s">
         <v>25</v>
@@ -29474,13 +29748,13 @@
         <v>8</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C238" s="2">
         <v>1</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>11</v>
@@ -29489,10 +29763,10 @@
         <v>12</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="H238" s="4" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -29500,13 +29774,13 @@
         <v>8</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C239" s="2">
         <v>0</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>11</v>
@@ -29515,24 +29789,24 @@
         <v>12</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H239" s="4" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="240" spans="1:8">
       <c r="A240" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="B240" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C240">
         <v>1</v>
       </c>
       <c r="D240" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="E240" t="s">
         <v>11</v>
@@ -29541,10 +29815,10 @@
         <v>12</v>
       </c>
       <c r="G240" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="H240" s="4" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
     </row>
     <row r="241" spans="1:8">

--- a/docassemble/PowerOfAttorneyHealthCare/data/sources/poa_hc_es.xlsx
+++ b/docassemble/PowerOfAttorneyHealthCare/data/sources/poa_hc_es.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnewsted\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD8239A-22B3-4E79-9362-9091D3D53A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6216AE60-B8D2-4472-A453-4D0A62E5BC07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34695" yWindow="-2895" windowWidth="31785" windowHeight="17910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-31905" yWindow="-3210" windowWidth="26445" windowHeight="16770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -84,141 +84,6 @@
     <t>Poder Notarial para el Cuidado de la Salud</t>
   </si>
   <si>
-    <t>80b04da1b3097b769fbc55dc4f8a6d71</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Welcome to Illinois Legal Aid Online's **Power of Attorney for Health Care** Easy Form.
-This program helps you make documents that give someone you trust power of attorney to make decisions about your health care. This means they can make choices about your health care when you cannot. You can also let them make choices about your health care earlier, if you choose.
-This program has videos with information about making a Power of Attorney for Health Care. You do not have to watch them, but you may find them helpful.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if user_path == "Shirley":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">[YOUTUBE 7qy101TRdiI]
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif user_path == "Frederico" or user_path == "Federico":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">[YOUTUBE GR9t6ygX13g]
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif user_path == "Lisa":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">[YOUTUBE h2ZGl568xHo]
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-To learn more, read ILAO's article about [**Power of Attorney for Health Care basics**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://www.illinoislegalaid.org/legal-information/setting-power-attorney-healthcare</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">).
-</t>
-    </r>
-  </si>
-  <si>
     <t>instructions</t>
   </si>
   <si>
@@ -7893,9 +7758,6 @@
     <t>Descargar</t>
   </si>
   <si>
-    <t>407b707f02944bd25ed6abc4bb23fe2f</t>
-  </si>
-  <si>
     <t>ff460440eb211ebc6cc5d39426b9fa08</t>
   </si>
   <si>
@@ -20814,370 +20676,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Tus formularios están listos. Puedes verlos y descargarlos abajo. Haz clic en **Hacer cambios** para corregir cualquier error.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">[YOUTUBE vuN6YBYEh6k]
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Lee las instrucciones para saber qué hacer después.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${ action_button_html(url_action('review_answers'), label=':edit: Hacer cambios', color='success', size="md") }</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${ al_user_bundle.download_list_html() }</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-&amp;nbsp;
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${ al_user_bundle.send_button_html(show_editable_checkbox=False) }</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-**Nota:** El Poder Notarial debe firmarse frente a al menos un testigo para que sea válido.
-¡Gracias por usar los Formularios Guiados de ILAO!</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Your forms are ready. View and download your forms below. Click **Make changes** to fix any mistakes.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if user_path == "Shirley":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[YOUTUBE NE0faXuz5v4]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif user_path == "Frederico" or user_path == "Federico":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[YOUTUBE g5Vdv0hWJ6g]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif user_path == "Lisa":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[YOUTUBE F2QbdrhcZ0g]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Read the instructions to learn what to do next.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${ action_button_html(url_action('review_answers'), label=':edit: Make changes', color='success', size='md') }</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${ al_user_bundle.download_list_html(view_label='View', download_label='Download', zip_label='Download all') }</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${ al_user_bundle.send_button_html(show_editable_checkbox=False, label='Send') }</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-**Note:** The Power of Attorney needs to be signed in front of at least one witness to become official.
-Thank you for using ILAO Easy Forms!
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Bienvenido(a) al Formulario Guiado de Poder Notarial para el Cuidado de la Salud de Illinois Legal Aid Online.
-Este programa te ayuda a crear documentos que le otorgan a una persona de tu confianza la autoridad legal para tomar decisiones sobre tu atención médica. Esto significa que esa persona podrá tomar decisiones sobre tu atención médica cuando no puedas hacerlo por ti mismo(a). Si así lo deseas, también puedes autorizarla para que tome decisiones sobre tu atención médica antesde que eso ocurra.
-Este programa incluye videos con información sobre cómo hacer un Poder Notarial para el Cuidado de la Salud. No tienes que verlos, pero pueden serte útiles.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">[YOUTUBE ccToVpEse7s]
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Para obtener más información, lee el artículo de ILAO sobre los [**Conceptos Básicos del Poder Notarial para el Cuidado de la Salud**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://es.illinoislegalaid.org/legal-information/setting-power-attorney-healthcare</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <b/>
         <sz val="11"/>
         <color rgb="FF0000FF"/>
@@ -22664,6 +22162,243 @@
     </r>
   </si>
   <si>
+    <t>31a3791a34401744a473ea590edf5be1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ get_language_list(lang_codes=al_interview_languages, current=al_user_language) }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Welcome to Illinois Legal Aid Online's **Power of Attorney for Health Care** Easy Form.
+This program helps you make documents that give someone you trust power of attorney to make decisions about your health care. This means they can make choices about your health care when you cannot. You can also let them make choices about your health care earlier, if you choose.
+This program has videos with information about making a Power of Attorney for Health Care. You do not have to watch them, but you may find them helpful.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if user_path == "Shirley":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[YOUTUBE 7qy101TRdiI]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif user_path == "Frederico" or user_path == "Federico":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[YOUTUBE GR9t6ygX13g]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif user_path == "Lisa":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[YOUTUBE h2ZGl568xHo]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+To learn more, read ILAO's article about [**Power of Attorney for Health Care basics**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://www.illinoislegalaid.org/legal-information/setting-power-attorney-healthcare</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">).
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">${ get_language_list(lang_codes=al_interview_languages, current=al_user_language) }
+Bienvenido(a) al Formulario Guiado de Poder Notarial para el Cuidado de la Salud de Illinois Legal Aid Online.
+Este programa te ayuda a crear documentos que le otorgan a una persona de tu confianza la autoridad legal para tomar decisiones sobre tu atención médica. Esto significa que esa persona podrá tomar decisiones sobre tu atención médica cuando no puedas hacerlo por ti mismo(a). Si así lo deseas, también puedes autorizarla para que tome decisiones sobre tu atención médica antesde que eso ocurra.
+Este programa incluye videos con información sobre cómo hacer un Poder Notarial para el Cuidado de la Salud. No tienes que verlos, pero pueden serte útiles.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">[YOUTUBE ccToVpEse7s]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Para obtener más información, lee el artículo de ILAO sobre los [**Conceptos Básicos del Poder Notarial para el Cuidado de la Salud**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://es.illinoislegalaid.org/legal-information/setting-power-attorney-healthcare</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">**Límites para </t>
     </r>
@@ -22686,7 +22421,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">:**
+      <t xml:space="preserve">: (En inglés)**
 </t>
     </r>
     <r>
@@ -23104,6 +22839,344 @@
       </rPr>
       <t xml:space="preserve">% endif
 </t>
+    </r>
+  </si>
+  <si>
+    <t>2f06b33dff4925dc1eff398c5c52e0fb</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Your forms are ready. View and download your forms below. Click **Make changes** to fix any mistakes.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if user_path == "Shirley":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[YOUTUBE NE0faXuz5v4]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif user_path == "Frederico" or user_path == "Federico":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[YOUTUBE g5Vdv0hWJ6g]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif user_path == "Lisa":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[YOUTUBE F2QbdrhcZ0g]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Read the instructions to learn what to do next.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ action_button_html(url_action('review_answers'), label='^^edit^^ Make changes', color='success', size='md') }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+**Note:** These forms and instructions are in English. To get bilingual English and Spanish forms, select **Español** from the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:globe:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> language picker in the menu.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ al_user_bundle.download_list_html(view_label='View', download_label='Download', zip_label='Download all') }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ al_user_bundle.send_button_html(show_editable_checkbox=False, label='Send') }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+**Note:** The Power of Attorney needs to be signed in front of at least one witness to become official.
+Thank you for using ILAO Easy Forms!
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Tus formularios están listos. Puedes verlos y descargarlos abajo. Haz clic en **Hacer cambios** para corregir cualquier error.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">[YOUTUBE vuN6YBYEh6k]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Lee las instrucciones para saber qué hacer después.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ action_button_html(url_action('review_answers'), label=':edit: Hacer cambios', color='success', size="md") }
+**Nota:** Estos son formularios e instrucciones bilingües en inglés y español. Para obtener formularios solo en inglés, seleccione **English** en el selector de idioma :globe: del menú.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ al_user_bundle.download_list_html() }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+&amp;nbsp;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ al_user_bundle.send_button_html(show_editable_checkbox=False) }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+**Nota:** El Poder Notarial debe firmarse frente a al menos un testigo para que sea válido.
+¡Gracias por usar los Formularios Guiados de ILAO!</t>
     </r>
   </si>
 </sst>
@@ -23632,7 +23705,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="316.8">
+    <row r="3" spans="1:8" ht="345.6">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -23643,7 +23716,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>15</v>
+        <v>791</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>11</v>
@@ -23652,10 +23725,10 @@
         <v>12</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>16</v>
+        <v>792</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>784</v>
+        <v>793</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -23663,13 +23736,13 @@
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" s="2">
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>11</v>
@@ -23678,10 +23751,10 @@
         <v>12</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="72">
@@ -23689,13 +23762,13 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>11</v>
@@ -23704,10 +23777,10 @@
         <v>12</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -23715,13 +23788,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" s="2">
         <v>2</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>11</v>
@@ -23730,10 +23803,10 @@
         <v>12</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="43.2">
@@ -23741,13 +23814,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C7" s="2">
         <v>3</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>11</v>
@@ -23756,10 +23829,10 @@
         <v>12</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="28.8">
@@ -23767,13 +23840,13 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C8" s="2">
         <v>4</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>11</v>
@@ -23782,10 +23855,10 @@
         <v>12</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="288">
@@ -23793,13 +23866,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" s="2">
         <v>5</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>11</v>
@@ -23808,10 +23881,10 @@
         <v>12</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="28.8">
@@ -23819,13 +23892,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C10" s="2">
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>11</v>
@@ -23834,10 +23907,10 @@
         <v>12</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="28.8">
@@ -23845,13 +23918,13 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C11" s="2">
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>11</v>
@@ -23860,10 +23933,10 @@
         <v>12</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="28.8">
@@ -23871,13 +23944,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C12" s="2">
         <v>0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>11</v>
@@ -23886,10 +23959,10 @@
         <v>12</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="216">
@@ -23897,13 +23970,13 @@
         <v>8</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C13" s="2">
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>11</v>
@@ -23912,10 +23985,10 @@
         <v>12</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="28.8">
@@ -23923,13 +23996,13 @@
         <v>8</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C14" s="2">
         <v>0</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>11</v>
@@ -23938,10 +24011,10 @@
         <v>12</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="331.2">
@@ -23949,13 +24022,13 @@
         <v>8</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C15" s="2">
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>11</v>
@@ -23964,10 +24037,10 @@
         <v>12</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="28.8">
@@ -23975,13 +24048,13 @@
         <v>8</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C16" s="2">
         <v>0</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>11</v>
@@ -23990,10 +24063,10 @@
         <v>12</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="273.60000000000002">
@@ -24001,13 +24074,13 @@
         <v>8</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C17" s="2">
         <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>11</v>
@@ -24016,24 +24089,24 @@
         <v>12</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="115.2">
       <c r="A18" s="2" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="C18" s="2">
         <v>0</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>11</v>
@@ -24042,24 +24115,24 @@
         <v>12</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="28.8">
       <c r="A19" s="2" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>11</v>
@@ -24068,10 +24141,10 @@
         <v>12</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="187.2">
@@ -24079,13 +24152,13 @@
         <v>8</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C20" s="2">
         <v>0</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>11</v>
@@ -24094,10 +24167,10 @@
         <v>12</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -24105,13 +24178,13 @@
         <v>8</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C21" s="2">
         <v>0</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>11</v>
@@ -24120,10 +24193,10 @@
         <v>12</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="43.2">
@@ -24131,13 +24204,13 @@
         <v>8</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C22" s="2">
         <v>1</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>11</v>
@@ -24146,10 +24219,10 @@
         <v>12</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="57.6">
@@ -24157,13 +24230,13 @@
         <v>8</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C23" s="2">
         <v>2</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>11</v>
@@ -24172,10 +24245,10 @@
         <v>12</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="28.8">
@@ -24183,13 +24256,13 @@
         <v>8</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C24" s="2">
         <v>3</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>11</v>
@@ -24198,10 +24271,10 @@
         <v>12</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="57.6">
@@ -24209,13 +24282,13 @@
         <v>8</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C25" s="2">
         <v>4</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>11</v>
@@ -24224,10 +24297,10 @@
         <v>12</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="28.8">
@@ -24235,13 +24308,13 @@
         <v>8</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C26" s="2">
         <v>0</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>11</v>
@@ -24250,10 +24323,10 @@
         <v>12</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="244.8">
@@ -24261,13 +24334,13 @@
         <v>8</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C27" s="2">
         <v>1</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>11</v>
@@ -24276,10 +24349,10 @@
         <v>12</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="86.4">
@@ -24287,13 +24360,13 @@
         <v>8</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C28" s="2">
         <v>0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>11</v>
@@ -24302,10 +24375,10 @@
         <v>12</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="409.6">
@@ -24313,13 +24386,13 @@
         <v>8</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C29" s="2">
         <v>1</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>11</v>
@@ -24328,10 +24401,10 @@
         <v>12</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -24339,13 +24412,13 @@
         <v>8</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C30" s="2">
         <v>2</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>11</v>
@@ -24354,10 +24427,10 @@
         <v>12</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -24365,13 +24438,13 @@
         <v>8</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C31" s="2">
         <v>3</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>11</v>
@@ -24380,10 +24453,10 @@
         <v>12</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -24391,13 +24464,13 @@
         <v>8</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C32" s="2">
         <v>4</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>11</v>
@@ -24406,10 +24479,10 @@
         <v>12</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -24417,13 +24490,13 @@
         <v>8</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C33" s="2">
         <v>5</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>11</v>
@@ -24432,10 +24505,10 @@
         <v>12</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -24443,13 +24516,13 @@
         <v>8</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C34" s="2">
         <v>6</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>11</v>
@@ -24458,10 +24531,10 @@
         <v>12</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -24469,13 +24542,13 @@
         <v>8</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C35" s="2">
         <v>7</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>11</v>
@@ -24484,10 +24557,10 @@
         <v>12</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="100.8">
@@ -24495,13 +24568,13 @@
         <v>8</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C36" s="2">
         <v>0</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>11</v>
@@ -24510,10 +24583,10 @@
         <v>12</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="28.8">
@@ -24521,13 +24594,13 @@
         <v>8</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C37" s="2">
         <v>1</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>11</v>
@@ -24536,10 +24609,10 @@
         <v>12</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="86.4">
@@ -24547,13 +24620,13 @@
         <v>8</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C38" s="2">
         <v>0</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>11</v>
@@ -24562,10 +24635,10 @@
         <v>12</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="28.8">
@@ -24573,13 +24646,13 @@
         <v>8</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C39" s="2">
         <v>0</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>11</v>
@@ -24588,10 +24661,10 @@
         <v>12</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="144">
@@ -24599,13 +24672,13 @@
         <v>8</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C40" s="2">
         <v>1</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>11</v>
@@ -24614,10 +24687,10 @@
         <v>12</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="86.4">
@@ -24625,13 +24698,13 @@
         <v>8</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C41" s="2">
         <v>0</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>11</v>
@@ -24640,10 +24713,10 @@
         <v>12</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="86.4">
@@ -24651,13 +24724,13 @@
         <v>8</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C42" s="2">
         <v>0</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>11</v>
@@ -24666,10 +24739,10 @@
         <v>12</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="374.4">
@@ -24677,13 +24750,13 @@
         <v>8</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C43" s="2">
         <v>1</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>11</v>
@@ -24692,10 +24765,10 @@
         <v>12</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="86.4">
@@ -24703,13 +24776,13 @@
         <v>8</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C44" s="2">
         <v>0</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>11</v>
@@ -24718,10 +24791,10 @@
         <v>12</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="28.8">
@@ -24729,13 +24802,13 @@
         <v>8</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C45" s="2">
         <v>1</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>11</v>
@@ -24744,10 +24817,10 @@
         <v>12</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="28.8">
@@ -24755,13 +24828,13 @@
         <v>8</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C46" s="2">
         <v>0</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>11</v>
@@ -24770,10 +24843,10 @@
         <v>12</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -24781,13 +24854,13 @@
         <v>8</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C47" s="2">
         <v>2</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>11</v>
@@ -24796,10 +24869,10 @@
         <v>12</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="43.2">
@@ -24807,13 +24880,13 @@
         <v>8</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C48" s="2">
         <v>3</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>11</v>
@@ -24822,10 +24895,10 @@
         <v>12</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H48" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -24833,13 +24906,13 @@
         <v>8</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C49" s="2">
         <v>4</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>11</v>
@@ -24848,10 +24921,10 @@
         <v>12</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -24859,13 +24932,13 @@
         <v>8</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C50" s="2">
         <v>5</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>11</v>
@@ -24874,10 +24947,10 @@
         <v>12</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="129.6">
@@ -24885,13 +24958,13 @@
         <v>8</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C51" s="2">
         <v>0</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>11</v>
@@ -24900,10 +24973,10 @@
         <v>12</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="28.8">
@@ -24911,13 +24984,13 @@
         <v>8</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C52" s="2">
         <v>1</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>11</v>
@@ -24926,10 +24999,10 @@
         <v>12</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="28.8">
@@ -24937,13 +25010,13 @@
         <v>8</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C53" s="2">
         <v>0</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>11</v>
@@ -24952,10 +25025,10 @@
         <v>12</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="100.8">
@@ -24963,13 +25036,13 @@
         <v>8</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C54" s="2">
         <v>1</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>11</v>
@@ -24978,10 +25051,10 @@
         <v>12</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="100.8">
@@ -24989,13 +25062,13 @@
         <v>8</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C55" s="2">
         <v>0</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>11</v>
@@ -25004,10 +25077,10 @@
         <v>12</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="288">
@@ -25015,13 +25088,13 @@
         <v>8</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C56" s="2">
         <v>1</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>11</v>
@@ -25030,10 +25103,10 @@
         <v>12</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="28.8">
@@ -25041,13 +25114,13 @@
         <v>8</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C57" s="2">
         <v>1</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>11</v>
@@ -25056,10 +25129,10 @@
         <v>12</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -25067,13 +25140,13 @@
         <v>8</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C58" s="2">
         <v>0</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>11</v>
@@ -25082,10 +25155,10 @@
         <v>12</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="28.8">
@@ -25093,13 +25166,13 @@
         <v>8</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C59" s="2">
         <v>1</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>11</v>
@@ -25108,10 +25181,10 @@
         <v>12</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="28.8">
@@ -25119,13 +25192,13 @@
         <v>8</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C60" s="2">
         <v>2</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>11</v>
@@ -25134,10 +25207,10 @@
         <v>12</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="144">
@@ -25145,13 +25218,13 @@
         <v>8</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C61" s="2">
         <v>3</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>11</v>
@@ -25160,10 +25233,10 @@
         <v>12</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -25171,13 +25244,13 @@
         <v>8</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C62" s="2">
         <v>4</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>11</v>
@@ -25186,10 +25259,10 @@
         <v>12</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="28.8">
@@ -25197,13 +25270,13 @@
         <v>8</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C63" s="2">
         <v>5</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>11</v>
@@ -25212,10 +25285,10 @@
         <v>12</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -25223,13 +25296,13 @@
         <v>8</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C64" s="2">
         <v>6</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>11</v>
@@ -25238,10 +25311,10 @@
         <v>12</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="43.2">
@@ -25249,13 +25322,13 @@
         <v>8</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C65" s="2">
         <v>7</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>11</v>
@@ -25264,10 +25337,10 @@
         <v>12</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="57.6">
@@ -25275,13 +25348,13 @@
         <v>8</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C66" s="2">
         <v>8</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>11</v>
@@ -25290,10 +25363,10 @@
         <v>12</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -25301,13 +25374,13 @@
         <v>8</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C67" s="2">
         <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>11</v>
@@ -25316,10 +25389,10 @@
         <v>12</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="28.8">
@@ -25327,13 +25400,13 @@
         <v>8</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C68" s="2">
         <v>0</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>11</v>
@@ -25342,10 +25415,10 @@
         <v>12</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="172.8">
@@ -25353,13 +25426,13 @@
         <v>8</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C69" s="2">
         <v>1</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>11</v>
@@ -25368,10 +25441,10 @@
         <v>12</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="28.8">
@@ -25379,13 +25452,13 @@
         <v>8</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C70" s="2">
         <v>2</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>11</v>
@@ -25394,10 +25467,10 @@
         <v>12</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -25405,13 +25478,13 @@
         <v>8</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C71" s="2">
         <v>3</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>11</v>
@@ -25420,10 +25493,10 @@
         <v>12</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="43.2">
@@ -25431,13 +25504,13 @@
         <v>8</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C72" s="2">
         <v>4</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>11</v>
@@ -25446,10 +25519,10 @@
         <v>12</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="57.6">
@@ -25457,13 +25530,13 @@
         <v>8</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C73" s="2">
         <v>5</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>11</v>
@@ -25472,10 +25545,10 @@
         <v>12</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -25483,13 +25556,13 @@
         <v>8</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C74" s="2">
         <v>6</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>11</v>
@@ -25498,10 +25571,10 @@
         <v>12</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="28.8">
@@ -25509,13 +25582,13 @@
         <v>8</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C75" s="2">
         <v>0</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>11</v>
@@ -25524,10 +25597,10 @@
         <v>12</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="144">
@@ -25535,13 +25608,13 @@
         <v>8</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C76" s="2">
         <v>1</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>11</v>
@@ -25550,10 +25623,10 @@
         <v>12</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="115.2">
@@ -25561,13 +25634,13 @@
         <v>8</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C77" s="2">
         <v>0</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>11</v>
@@ -25576,10 +25649,10 @@
         <v>12</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="360">
@@ -25587,13 +25660,13 @@
         <v>8</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>11</v>
@@ -25602,10 +25675,10 @@
         <v>12</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="28.8">
@@ -25613,13 +25686,13 @@
         <v>8</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C79" s="2">
         <v>1</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>11</v>
@@ -25628,10 +25701,10 @@
         <v>12</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="28.8">
@@ -25639,13 +25712,13 @@
         <v>8</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C80" s="2">
         <v>0</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>11</v>
@@ -25654,10 +25727,10 @@
         <v>12</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="72">
@@ -25665,13 +25738,13 @@
         <v>8</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C81" s="2">
         <v>1</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>11</v>
@@ -25680,10 +25753,10 @@
         <v>12</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="72">
@@ -25691,13 +25764,13 @@
         <v>8</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C82" s="2">
         <v>2</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>11</v>
@@ -25706,10 +25779,10 @@
         <v>12</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -25717,13 +25790,13 @@
         <v>8</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C83" s="2">
         <v>3</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>11</v>
@@ -25732,10 +25805,10 @@
         <v>12</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="43.2">
@@ -25743,13 +25816,13 @@
         <v>8</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C84" s="2">
         <v>4</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>11</v>
@@ -25758,10 +25831,10 @@
         <v>12</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -25769,13 +25842,13 @@
         <v>8</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C85" s="2">
         <v>5</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>11</v>
@@ -25784,10 +25857,10 @@
         <v>12</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -25795,13 +25868,13 @@
         <v>8</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C86" s="2">
         <v>6</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>11</v>
@@ -25810,10 +25883,10 @@
         <v>12</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="172.8">
@@ -25821,13 +25894,13 @@
         <v>8</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C87" s="2">
         <v>0</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>11</v>
@@ -25836,10 +25909,10 @@
         <v>12</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="43.2">
@@ -25847,13 +25920,13 @@
         <v>8</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C88" s="2">
         <v>1</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>11</v>
@@ -25862,10 +25935,10 @@
         <v>12</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="43.2">
@@ -25873,13 +25946,13 @@
         <v>8</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C89" s="2">
         <v>0</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>11</v>
@@ -25888,10 +25961,10 @@
         <v>12</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="72">
@@ -25899,13 +25972,13 @@
         <v>8</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C90" s="2">
         <v>1</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>11</v>
@@ -25914,10 +25987,10 @@
         <v>12</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="72">
@@ -25925,13 +25998,13 @@
         <v>8</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C91" s="2">
         <v>2</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>11</v>
@@ -25940,10 +26013,10 @@
         <v>12</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -25951,13 +26024,13 @@
         <v>8</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C92" s="2">
         <v>3</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>11</v>
@@ -25966,10 +26039,10 @@
         <v>12</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="57.6">
@@ -25977,13 +26050,13 @@
         <v>8</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C93" s="2">
         <v>4</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>11</v>
@@ -25992,10 +26065,10 @@
         <v>12</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -26003,13 +26076,13 @@
         <v>8</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C94" s="2">
         <v>5</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>11</v>
@@ -26018,10 +26091,10 @@
         <v>12</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -26029,13 +26102,13 @@
         <v>8</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C95" s="2">
         <v>6</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>11</v>
@@ -26044,10 +26117,10 @@
         <v>12</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="201.6">
@@ -26055,13 +26128,13 @@
         <v>8</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C96" s="2">
         <v>0</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>11</v>
@@ -26070,10 +26143,10 @@
         <v>12</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="28.8">
@@ -26081,13 +26154,13 @@
         <v>8</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C97" s="2">
         <v>0</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>11</v>
@@ -26096,10 +26169,10 @@
         <v>12</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="129.6">
@@ -26107,13 +26180,13 @@
         <v>8</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C98" s="2">
         <v>1</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>11</v>
@@ -26122,10 +26195,10 @@
         <v>12</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="86.4">
@@ -26133,13 +26206,13 @@
         <v>8</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C99" s="2">
         <v>0</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>11</v>
@@ -26148,10 +26221,10 @@
         <v>12</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="302.39999999999998">
@@ -26159,13 +26232,13 @@
         <v>8</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C100" s="2">
         <v>1</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>11</v>
@@ -26174,10 +26247,10 @@
         <v>12</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="28.8">
@@ -26185,13 +26258,13 @@
         <v>8</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C101" s="2">
         <v>0</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>11</v>
@@ -26200,10 +26273,10 @@
         <v>12</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
     </row>
     <row r="102" spans="1:8" ht="86.4">
@@ -26211,13 +26284,13 @@
         <v>8</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C102" s="2">
         <v>1</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>11</v>
@@ -26226,10 +26299,10 @@
         <v>12</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -26237,13 +26310,13 @@
         <v>8</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C103" s="2">
         <v>2</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>11</v>
@@ -26252,10 +26325,10 @@
         <v>12</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -26263,13 +26336,13 @@
         <v>8</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C104" s="2">
         <v>3</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>11</v>
@@ -26278,10 +26351,10 @@
         <v>12</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -26289,13 +26362,13 @@
         <v>8</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C105" s="2">
         <v>4</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>11</v>
@@ -26304,10 +26377,10 @@
         <v>12</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -26315,13 +26388,13 @@
         <v>8</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C106" s="2">
         <v>5</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>11</v>
@@ -26330,10 +26403,10 @@
         <v>12</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -26341,13 +26414,13 @@
         <v>8</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C107" s="2">
         <v>6</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>11</v>
@@ -26356,10 +26429,10 @@
         <v>12</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -26367,13 +26440,13 @@
         <v>8</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C108" s="2">
         <v>7</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>11</v>
@@ -26382,10 +26455,10 @@
         <v>12</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -26393,13 +26466,13 @@
         <v>8</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C109" s="2">
         <v>8</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>11</v>
@@ -26408,10 +26481,10 @@
         <v>12</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
     </row>
     <row r="110" spans="1:8" ht="43.2">
@@ -26419,13 +26492,13 @@
         <v>8</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C110" s="2">
         <v>0</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>11</v>
@@ -26434,10 +26507,10 @@
         <v>12</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="86.4">
@@ -26445,13 +26518,13 @@
         <v>8</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C111" s="2">
         <v>1</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>11</v>
@@ -26460,10 +26533,10 @@
         <v>12</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -26471,13 +26544,13 @@
         <v>8</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C112" s="2">
         <v>2</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>11</v>
@@ -26486,10 +26559,10 @@
         <v>12</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="H112" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -26497,13 +26570,13 @@
         <v>8</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C113" s="2">
         <v>3</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>11</v>
@@ -26512,10 +26585,10 @@
         <v>12</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="H113" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -26523,13 +26596,13 @@
         <v>8</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C114" s="2">
         <v>4</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>11</v>
@@ -26538,10 +26611,10 @@
         <v>12</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H114" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -26549,13 +26622,13 @@
         <v>8</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C115" s="2">
         <v>5</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>11</v>
@@ -26564,10 +26637,10 @@
         <v>12</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H115" s="6" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="116" spans="1:8" ht="43.2">
@@ -26575,13 +26648,13 @@
         <v>8</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C116" s="2">
         <v>6</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>11</v>
@@ -26590,10 +26663,10 @@
         <v>12</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="28.8">
@@ -26601,13 +26674,13 @@
         <v>8</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C117" s="2">
         <v>0</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>11</v>
@@ -26616,10 +26689,10 @@
         <v>12</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H117" s="6" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -26627,13 +26700,13 @@
         <v>8</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C118" s="2">
         <v>1</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>11</v>
@@ -26642,10 +26715,10 @@
         <v>12</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -26653,13 +26726,13 @@
         <v>8</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C119" s="2">
         <v>2</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>11</v>
@@ -26668,10 +26741,10 @@
         <v>12</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H119" s="6" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
     </row>
     <row r="120" spans="1:8" ht="28.8">
@@ -26679,13 +26752,13 @@
         <v>8</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C120" s="2">
         <v>0</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>11</v>
@@ -26694,10 +26767,10 @@
         <v>12</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -26705,13 +26778,13 @@
         <v>8</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C121" s="2">
         <v>1</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>11</v>
@@ -26720,10 +26793,10 @@
         <v>12</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H121" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="86.4">
@@ -26731,13 +26804,13 @@
         <v>8</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C122" s="2">
         <v>0</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>11</v>
@@ -26746,10 +26819,10 @@
         <v>12</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="28.8">
@@ -26757,13 +26830,13 @@
         <v>8</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C123" s="2">
         <v>1</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>11</v>
@@ -26772,10 +26845,10 @@
         <v>12</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H123" s="6" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="28.8">
@@ -26783,13 +26856,13 @@
         <v>8</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C124" s="2">
         <v>2</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>11</v>
@@ -26798,10 +26871,10 @@
         <v>12</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H124" s="8" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="28.8">
@@ -26809,13 +26882,13 @@
         <v>8</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C125" s="2">
         <v>3</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>11</v>
@@ -26824,10 +26897,10 @@
         <v>12</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H125" s="8" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="28.8">
@@ -26835,13 +26908,13 @@
         <v>8</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C126" s="2">
         <v>4</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>11</v>
@@ -26850,10 +26923,10 @@
         <v>12</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H126" s="8" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -26861,13 +26934,13 @@
         <v>8</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C127" s="2">
         <v>5</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>11</v>
@@ -26876,10 +26949,10 @@
         <v>12</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H127" s="8" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -26887,13 +26960,13 @@
         <v>8</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C128" s="2">
         <v>6</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>11</v>
@@ -26902,10 +26975,10 @@
         <v>12</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -26913,13 +26986,13 @@
         <v>8</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C129" s="2">
         <v>7</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>11</v>
@@ -26928,10 +27001,10 @@
         <v>12</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -26939,13 +27012,13 @@
         <v>8</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C130" s="2">
         <v>8</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>11</v>
@@ -26954,10 +27027,10 @@
         <v>12</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
     </row>
     <row r="131" spans="1:8" ht="28.8">
@@ -26965,13 +27038,13 @@
         <v>8</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C131" s="2">
         <v>0</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>11</v>
@@ -26980,10 +27053,10 @@
         <v>12</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H131" s="6" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
     </row>
     <row r="132" spans="1:8" ht="403.2">
@@ -26991,13 +27064,13 @@
         <v>8</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C132" s="2">
         <v>1</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>11</v>
@@ -27006,10 +27079,10 @@
         <v>12</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -27017,13 +27090,13 @@
         <v>8</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C133" s="2">
         <v>0</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>11</v>
@@ -27032,10 +27105,10 @@
         <v>12</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="H133" s="6" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="134" spans="1:8" ht="43.2">
@@ -27043,13 +27116,13 @@
         <v>8</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C134" s="2">
         <v>1</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>11</v>
@@ -27058,10 +27131,10 @@
         <v>12</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="100.8">
@@ -27069,13 +27142,13 @@
         <v>8</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C135" s="2">
         <v>2</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>11</v>
@@ -27084,24 +27157,24 @@
         <v>12</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
     </row>
     <row r="136" spans="1:8" ht="115.2">
       <c r="A136" s="2" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="C136" s="2">
         <v>0</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>11</v>
@@ -27110,10 +27183,10 @@
         <v>12</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
     </row>
     <row r="137" spans="1:8" ht="409.6">
@@ -27121,13 +27194,13 @@
         <v>8</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C137" s="2">
         <v>3</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>11</v>
@@ -27136,10 +27209,10 @@
         <v>12</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="28.8">
@@ -27147,13 +27220,13 @@
         <v>8</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C138" s="2">
         <v>1</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>11</v>
@@ -27162,10 +27235,10 @@
         <v>12</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -27173,13 +27246,13 @@
         <v>8</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C139" s="2">
         <v>0</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>11</v>
@@ -27188,10 +27261,10 @@
         <v>12</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H139" s="6" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
     </row>
     <row r="140" spans="1:8" ht="57.6">
@@ -27199,13 +27272,13 @@
         <v>8</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C140" s="2">
         <v>1</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>11</v>
@@ -27214,10 +27287,10 @@
         <v>12</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -27225,13 +27298,13 @@
         <v>8</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C141" s="2">
         <v>2</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>11</v>
@@ -27240,10 +27313,10 @@
         <v>12</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H141" s="6" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
     </row>
     <row r="142" spans="1:8" ht="43.2">
@@ -27251,13 +27324,13 @@
         <v>8</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C142" s="2">
         <v>3</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>11</v>
@@ -27266,10 +27339,10 @@
         <v>12</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
     </row>
     <row r="143" spans="1:8" ht="86.4">
@@ -27277,13 +27350,13 @@
         <v>8</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C143" s="2">
         <v>4</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>11</v>
@@ -27292,10 +27365,10 @@
         <v>12</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
     </row>
     <row r="144" spans="1:8" ht="216">
@@ -27303,13 +27376,13 @@
         <v>8</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C144" s="2">
         <v>5</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>11</v>
@@ -27318,10 +27391,10 @@
         <v>12</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
     </row>
     <row r="145" spans="1:8" ht="86.4">
@@ -27329,13 +27402,13 @@
         <v>8</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C145" s="2">
         <v>0</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>11</v>
@@ -27344,10 +27417,10 @@
         <v>12</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="146" spans="1:8" ht="86.4">
@@ -27355,13 +27428,13 @@
         <v>8</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C146" s="2">
         <v>1</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>11</v>
@@ -27370,10 +27443,10 @@
         <v>12</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -27381,13 +27454,13 @@
         <v>8</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C147" s="2">
         <v>2</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>11</v>
@@ -27396,10 +27469,10 @@
         <v>12</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H147" s="6" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="148" spans="1:8" ht="86.4">
@@ -27407,13 +27480,13 @@
         <v>8</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C148" s="2">
         <v>0</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>11</v>
@@ -27422,10 +27495,10 @@
         <v>12</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="28.8">
@@ -27433,13 +27506,13 @@
         <v>8</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C149" s="2">
         <v>0</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>11</v>
@@ -27448,10 +27521,10 @@
         <v>12</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -27459,13 +27532,13 @@
         <v>8</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C150" s="2">
         <v>2</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>11</v>
@@ -27474,10 +27547,10 @@
         <v>12</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="129.6">
@@ -27485,13 +27558,13 @@
         <v>8</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C151" s="2">
         <v>0</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>11</v>
@@ -27500,10 +27573,10 @@
         <v>12</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
     </row>
     <row r="152" spans="1:8" ht="28.8">
@@ -27511,13 +27584,13 @@
         <v>8</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C152" s="2">
         <v>1</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>11</v>
@@ -27526,10 +27599,10 @@
         <v>12</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="153" spans="1:8" ht="28.8">
@@ -27537,13 +27610,13 @@
         <v>8</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C153" s="2">
         <v>0</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>11</v>
@@ -27552,10 +27625,10 @@
         <v>12</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H153" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="154" spans="1:8" ht="115.2">
@@ -27563,13 +27636,13 @@
         <v>8</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C154" s="2">
         <v>1</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>11</v>
@@ -27578,10 +27651,10 @@
         <v>12</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="155" spans="1:8" ht="28.8">
@@ -27589,13 +27662,13 @@
         <v>8</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C155" s="2">
         <v>0</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>11</v>
@@ -27604,10 +27677,10 @@
         <v>12</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="H155" s="6" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="156" spans="1:8" ht="409.6">
@@ -27615,13 +27688,13 @@
         <v>8</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C156" s="2">
         <v>1</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>11</v>
@@ -27630,10 +27703,10 @@
         <v>12</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
     </row>
     <row r="157" spans="1:8" ht="43.2">
@@ -27641,13 +27714,13 @@
         <v>8</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C157" s="2">
         <v>0</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>11</v>
@@ -27656,10 +27729,10 @@
         <v>12</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H157" s="6" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
     </row>
     <row r="158" spans="1:8" ht="86.4">
@@ -27667,13 +27740,13 @@
         <v>8</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C158" s="2">
         <v>1</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>11</v>
@@ -27682,10 +27755,10 @@
         <v>12</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="28.8">
@@ -27693,13 +27766,13 @@
         <v>8</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C159" s="2">
         <v>0</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>11</v>
@@ -27708,10 +27781,10 @@
         <v>12</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H159" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="160" spans="1:8" ht="144">
@@ -27719,13 +27792,13 @@
         <v>8</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C160" s="2">
         <v>1</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>11</v>
@@ -27734,10 +27807,10 @@
         <v>12</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="100.8">
@@ -27745,13 +27818,13 @@
         <v>8</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C161" s="2">
         <v>0</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>11</v>
@@ -27760,10 +27833,10 @@
         <v>12</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="144">
@@ -27771,13 +27844,13 @@
         <v>8</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C162" s="2">
         <v>1</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>11</v>
@@ -27786,10 +27859,10 @@
         <v>12</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="100.8">
@@ -27797,13 +27870,13 @@
         <v>8</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C163" s="2">
         <v>0</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>11</v>
@@ -27812,10 +27885,10 @@
         <v>12</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
     </row>
     <row r="164" spans="1:8" ht="43.2">
@@ -27823,13 +27896,13 @@
         <v>8</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C164" s="2">
         <v>1</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>11</v>
@@ -27838,10 +27911,10 @@
         <v>12</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
     </row>
     <row r="165" spans="1:8" ht="115.2">
@@ -27849,13 +27922,13 @@
         <v>8</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C165" s="2">
         <v>0</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>11</v>
@@ -27864,10 +27937,10 @@
         <v>12</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
     </row>
     <row r="166" spans="1:8" ht="86.4">
@@ -27875,13 +27948,13 @@
         <v>8</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C166" s="2">
         <v>1</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>11</v>
@@ -27890,10 +27963,10 @@
         <v>12</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="86.4">
@@ -27901,13 +27974,13 @@
         <v>8</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C167" s="2">
         <v>0</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>11</v>
@@ -27916,10 +27989,10 @@
         <v>12</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H167" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="28.8">
@@ -27927,13 +28000,13 @@
         <v>8</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C168" s="2">
         <v>0</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>11</v>
@@ -27942,10 +28015,10 @@
         <v>12</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
     </row>
     <row r="169" spans="1:8" ht="57.6">
@@ -27953,13 +28026,13 @@
         <v>8</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C169" s="2">
         <v>1</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>11</v>
@@ -27968,10 +28041,10 @@
         <v>12</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="H169" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="170" spans="1:8">
@@ -27979,13 +28052,13 @@
         <v>8</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C170" s="2">
         <v>2</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>11</v>
@@ -27994,10 +28067,10 @@
         <v>12</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H170" s="3" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="57.6">
@@ -28005,13 +28078,13 @@
         <v>8</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C171" s="2">
         <v>0</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>11</v>
@@ -28020,10 +28093,10 @@
         <v>12</v>
       </c>
       <c r="G171" s="3" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="H171" s="6" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
     </row>
     <row r="172" spans="1:8" ht="28.8">
@@ -28031,13 +28104,13 @@
         <v>8</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C172" s="2">
         <v>1</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>11</v>
@@ -28046,10 +28119,10 @@
         <v>12</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H172" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="28.8">
@@ -28057,13 +28130,13 @@
         <v>8</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C173" s="2">
         <v>0</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>11</v>
@@ -28072,10 +28145,10 @@
         <v>12</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="H173" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="409.6">
@@ -28083,13 +28156,13 @@
         <v>8</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C174" s="2">
         <v>1</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>11</v>
@@ -28098,10 +28171,10 @@
         <v>12</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="H174" s="3" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="28.8">
@@ -28109,13 +28182,13 @@
         <v>8</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C175" s="2">
         <v>0</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>11</v>
@@ -28124,24 +28197,24 @@
         <v>12</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="H175" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="374.4">
+    <row r="176" spans="1:8" ht="409.6">
       <c r="A176" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C176" s="2">
         <v>1</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>440</v>
+        <v>795</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>11</v>
@@ -28150,10 +28223,10 @@
         <v>12</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>783</v>
+        <v>796</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>782</v>
+        <v>797</v>
       </c>
     </row>
     <row r="177" spans="1:8" ht="201.6">
@@ -28161,13 +28234,13 @@
         <v>8</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C177" s="2">
         <v>2</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>11</v>
@@ -28176,10 +28249,10 @@
         <v>12</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="H177" s="3" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="86.4">
@@ -28187,13 +28260,13 @@
         <v>8</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C178" s="2">
         <v>0</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>11</v>
@@ -28202,10 +28275,10 @@
         <v>12</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -28213,13 +28286,13 @@
         <v>8</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C179" s="2">
         <v>1</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>11</v>
@@ -28228,10 +28301,10 @@
         <v>12</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="H179" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="180" spans="1:8">
@@ -28239,13 +28312,13 @@
         <v>8</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C180" s="2">
         <v>0</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>11</v>
@@ -28254,10 +28327,10 @@
         <v>12</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -28265,13 +28338,13 @@
         <v>8</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C181" s="2">
         <v>0</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>11</v>
@@ -28280,10 +28353,10 @@
         <v>12</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="H181" s="6" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -28291,13 +28364,13 @@
         <v>8</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C182" s="2">
         <v>0</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>11</v>
@@ -28306,10 +28379,10 @@
         <v>12</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -28317,13 +28390,13 @@
         <v>8</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C183" s="2">
         <v>0</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>11</v>
@@ -28332,10 +28405,10 @@
         <v>12</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="H183" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -28343,13 +28416,13 @@
         <v>8</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C184" s="2">
         <v>0</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>11</v>
@@ -28358,10 +28431,10 @@
         <v>12</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="144">
@@ -28369,13 +28442,13 @@
         <v>8</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C185" s="2">
         <v>0</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>11</v>
@@ -28384,10 +28457,10 @@
         <v>12</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
     </row>
     <row r="186" spans="1:8" ht="28.8">
@@ -28395,13 +28468,13 @@
         <v>8</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C186" s="2">
         <v>14</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>11</v>
@@ -28410,10 +28483,10 @@
         <v>12</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="187" spans="1:8" ht="28.8">
@@ -28421,13 +28494,13 @@
         <v>8</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C187" s="2">
         <v>15</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>11</v>
@@ -28436,10 +28509,10 @@
         <v>12</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="H187" s="6" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="188" spans="1:8" ht="57.6">
@@ -28447,13 +28520,13 @@
         <v>8</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C188" s="2">
         <v>16</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>11</v>
@@ -28462,10 +28535,10 @@
         <v>12</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H188" s="3" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="28.8">
@@ -28473,13 +28546,13 @@
         <v>8</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C189" s="2">
         <v>18</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>11</v>
@@ -28488,10 +28561,10 @@
         <v>12</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="H189" s="6" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="190" spans="1:8" ht="57.6">
@@ -28499,13 +28572,13 @@
         <v>8</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C190" s="2">
         <v>20</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>11</v>
@@ -28514,10 +28587,10 @@
         <v>12</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="43.2">
@@ -28525,13 +28598,13 @@
         <v>8</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C191" s="2">
         <v>21</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>11</v>
@@ -28540,10 +28613,10 @@
         <v>12</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="H191" s="6" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="192" spans="1:8" ht="28.8">
@@ -28551,13 +28624,13 @@
         <v>8</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C192" s="2">
         <v>22</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>11</v>
@@ -28566,10 +28639,10 @@
         <v>12</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="H192" s="6" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="193" spans="1:8" ht="28.8">
@@ -28577,13 +28650,13 @@
         <v>8</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C193" s="2">
         <v>29</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>11</v>
@@ -28592,10 +28665,10 @@
         <v>12</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="H193" s="6" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="194" spans="1:8" ht="244.8">
@@ -28603,13 +28676,13 @@
         <v>8</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C194" s="2">
         <v>30</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>11</v>
@@ -28618,10 +28691,10 @@
         <v>12</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="H194" s="6" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -28629,13 +28702,13 @@
         <v>8</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C195" s="2">
         <v>31</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>11</v>
@@ -28644,7 +28717,7 @@
         <v>12</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="H195" s="6" t="s">
         <v>14</v>
@@ -28655,13 +28728,13 @@
         <v>8</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C196" s="2">
         <v>0</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>11</v>
@@ -28670,10 +28743,10 @@
         <v>12</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="H196" s="6" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="197" spans="1:8" ht="28.8">
@@ -28681,13 +28754,13 @@
         <v>8</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C197" s="2">
         <v>1</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>11</v>
@@ -28696,10 +28769,10 @@
         <v>12</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="H197" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -28707,13 +28780,13 @@
         <v>8</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C198" s="2">
         <v>2</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>11</v>
@@ -28722,10 +28795,10 @@
         <v>12</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="H198" s="6" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="100.8">
@@ -28733,13 +28806,13 @@
         <v>8</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C199" s="2">
         <v>3</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>11</v>
@@ -28748,10 +28821,10 @@
         <v>12</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="H199" s="3" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
     </row>
     <row r="200" spans="1:8" ht="158.4">
@@ -28759,13 +28832,13 @@
         <v>8</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C200" s="2">
         <v>4</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>11</v>
@@ -28774,10 +28847,10 @@
         <v>12</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="H200" s="3" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
     </row>
     <row r="201" spans="1:8" ht="43.2">
@@ -28785,13 +28858,13 @@
         <v>8</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C201" s="2">
         <v>5</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>11</v>
@@ -28800,10 +28873,10 @@
         <v>12</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
     </row>
     <row r="202" spans="1:8" ht="100.8">
@@ -28811,13 +28884,13 @@
         <v>8</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C202" s="2">
         <v>6</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>11</v>
@@ -28826,10 +28899,10 @@
         <v>12</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="H202" s="3" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
     </row>
     <row r="203" spans="1:8" ht="43.2">
@@ -28837,13 +28910,13 @@
         <v>8</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C203" s="2">
         <v>7</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>11</v>
@@ -28852,10 +28925,10 @@
         <v>12</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="H203" s="3" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="100.8">
@@ -28863,13 +28936,13 @@
         <v>8</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C204" s="2">
         <v>8</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>11</v>
@@ -28878,10 +28951,10 @@
         <v>12</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="H204" s="3" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
     </row>
     <row r="205" spans="1:8" ht="100.8">
@@ -28889,13 +28962,13 @@
         <v>8</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C205" s="2">
         <v>9</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>11</v>
@@ -28904,10 +28977,10 @@
         <v>12</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="H205" s="3" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="115.2">
@@ -28915,13 +28988,13 @@
         <v>8</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C206" s="2">
         <v>10</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>11</v>
@@ -28930,10 +29003,10 @@
         <v>12</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="H206" s="3" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
     </row>
     <row r="207" spans="1:8" ht="158.4">
@@ -28941,13 +29014,13 @@
         <v>8</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C207" s="2">
         <v>11</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>11</v>
@@ -28956,10 +29029,10 @@
         <v>12</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="H207" s="3" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="172.8">
@@ -28967,13 +29040,13 @@
         <v>8</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C208" s="2">
         <v>12</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>11</v>
@@ -28982,10 +29055,10 @@
         <v>12</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="H208" s="3" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
     </row>
     <row r="209" spans="1:9" ht="115.2">
@@ -28993,13 +29066,13 @@
         <v>8</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C209" s="2">
         <v>13</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>11</v>
@@ -29008,10 +29081,10 @@
         <v>12</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="H209" s="3" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
     </row>
     <row r="210" spans="1:9" ht="158.4">
@@ -29019,13 +29092,13 @@
         <v>8</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C210" s="2">
         <v>14</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>11</v>
@@ -29034,10 +29107,10 @@
         <v>12</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="H210" s="3" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
     </row>
     <row r="211" spans="1:9" ht="158.4">
@@ -29045,13 +29118,13 @@
         <v>8</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C211" s="2">
         <v>15</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>11</v>
@@ -29060,10 +29133,10 @@
         <v>12</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H211" s="3" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
     </row>
     <row r="212" spans="1:9" ht="100.8">
@@ -29071,13 +29144,13 @@
         <v>8</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C212" s="2">
         <v>16</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>11</v>
@@ -29086,10 +29159,10 @@
         <v>12</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="H212" s="3" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
     </row>
     <row r="213" spans="1:9" ht="100.8">
@@ -29097,13 +29170,13 @@
         <v>8</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C213" s="2">
         <v>17</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>11</v>
@@ -29112,10 +29185,10 @@
         <v>12</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="H213" s="3" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
     </row>
     <row r="214" spans="1:9" ht="43.2">
@@ -29123,13 +29196,13 @@
         <v>8</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C214" s="2">
         <v>18</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>11</v>
@@ -29138,10 +29211,10 @@
         <v>12</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="H214" s="3" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
     </row>
     <row r="215" spans="1:9" ht="43.2">
@@ -29149,13 +29222,13 @@
         <v>8</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C215" s="2">
         <v>19</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>11</v>
@@ -29164,10 +29237,10 @@
         <v>12</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="H215" s="3" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="216" spans="1:9" ht="43.2">
@@ -29175,13 +29248,13 @@
         <v>8</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C216" s="2">
         <v>20</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>11</v>
@@ -29190,10 +29263,10 @@
         <v>12</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
     </row>
     <row r="217" spans="1:9" ht="409.6">
@@ -29201,13 +29274,13 @@
         <v>8</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C217" s="2">
         <v>21</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>11</v>
@@ -29216,10 +29289,10 @@
         <v>12</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="H217" s="3" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="I217" s="3"/>
     </row>
@@ -29228,13 +29301,13 @@
         <v>8</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C218" s="2">
         <v>22</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>11</v>
@@ -29243,10 +29316,10 @@
         <v>12</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="H218" s="3" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
     </row>
     <row r="219" spans="1:9" ht="43.2">
@@ -29254,13 +29327,13 @@
         <v>8</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C219" s="2">
         <v>23</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>11</v>
@@ -29269,10 +29342,10 @@
         <v>12</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="H219" s="3" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="220" spans="1:9" ht="86.4">
@@ -29280,13 +29353,13 @@
         <v>8</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C220" s="2">
         <v>24</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>11</v>
@@ -29295,10 +29368,10 @@
         <v>12</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="H220" s="3" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
     </row>
     <row r="221" spans="1:9" ht="115.2">
@@ -29306,13 +29379,13 @@
         <v>8</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C221" s="2">
         <v>25</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>11</v>
@@ -29321,10 +29394,10 @@
         <v>12</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="H221" s="3" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
     </row>
     <row r="222" spans="1:9" ht="43.2">
@@ -29332,13 +29405,13 @@
         <v>8</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C222" s="2">
         <v>26</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>11</v>
@@ -29347,10 +29420,10 @@
         <v>12</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="H222" s="3" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="223" spans="1:9" ht="100.8">
@@ -29358,13 +29431,13 @@
         <v>8</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C223" s="2">
         <v>27</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>11</v>
@@ -29373,10 +29446,10 @@
         <v>12</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="H223" s="3" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="224" spans="1:9" ht="43.2">
@@ -29384,13 +29457,13 @@
         <v>8</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C224" s="2">
         <v>28</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>11</v>
@@ -29399,10 +29472,10 @@
         <v>12</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="H224" s="3" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="225" spans="1:8" ht="43.2">
@@ -29410,13 +29483,13 @@
         <v>8</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C225" s="2">
         <v>29</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>11</v>
@@ -29425,10 +29498,10 @@
         <v>12</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="H225" s="3" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="226" spans="1:8" ht="100.8">
@@ -29436,13 +29509,13 @@
         <v>8</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C226" s="2">
         <v>30</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>11</v>
@@ -29451,10 +29524,10 @@
         <v>12</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="H226" s="3" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
     </row>
     <row r="227" spans="1:8" ht="28.8">
@@ -29462,13 +29535,13 @@
         <v>8</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C227" s="2">
         <v>0</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>11</v>
@@ -29477,10 +29550,10 @@
         <v>12</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="H227" s="6" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="228" spans="1:8" ht="28.8">
@@ -29488,13 +29561,13 @@
         <v>8</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="C228" s="2">
         <v>0</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>11</v>
@@ -29503,10 +29576,10 @@
         <v>12</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
     </row>
     <row r="229" spans="1:8" ht="43.2">
@@ -29514,13 +29587,13 @@
         <v>8</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="C229" s="2">
         <v>1</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>11</v>
@@ -29529,10 +29602,10 @@
         <v>12</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="H229" s="3" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
     </row>
     <row r="230" spans="1:8" ht="100.8">
@@ -29540,13 +29613,13 @@
         <v>8</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="C230" s="2">
         <v>2</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>11</v>
@@ -29555,10 +29628,10 @@
         <v>12</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="H230" s="3" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
     <row r="231" spans="1:8" ht="43.2">
@@ -29566,13 +29639,13 @@
         <v>8</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="C231" s="2">
         <v>3</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>11</v>
@@ -29581,10 +29654,10 @@
         <v>12</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="H231" s="3" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
     </row>
     <row r="232" spans="1:8">
@@ -29592,13 +29665,13 @@
         <v>8</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C232" s="2">
         <v>0</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>11</v>
@@ -29607,10 +29680,10 @@
         <v>12</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="H232" s="6" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="233" spans="1:8">
@@ -29618,13 +29691,13 @@
         <v>8</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="C233" s="2">
         <v>0</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>11</v>
@@ -29633,10 +29706,10 @@
         <v>12</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="H233" s="6" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="234" spans="1:8" ht="28.8">
@@ -29644,13 +29717,13 @@
         <v>8</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="C234" s="2">
         <v>1</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>11</v>
@@ -29659,10 +29732,10 @@
         <v>12</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="H234" s="6" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="235" spans="1:8">
@@ -29670,13 +29743,13 @@
         <v>8</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C235" s="2">
         <v>0</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>11</v>
@@ -29685,10 +29758,10 @@
         <v>12</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="H235" s="6" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="236" spans="1:8" ht="28.8">
@@ -29696,13 +29769,13 @@
         <v>8</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C236" s="2">
         <v>1</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>11</v>
@@ -29711,10 +29784,10 @@
         <v>12</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="H236" s="4" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="237" spans="1:8">
@@ -29722,13 +29795,13 @@
         <v>8</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C237" s="2">
         <v>0</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>11</v>
@@ -29737,10 +29810,10 @@
         <v>12</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="H237" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="238" spans="1:8" ht="28.8">
@@ -29748,13 +29821,13 @@
         <v>8</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C238" s="2">
         <v>1</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>11</v>
@@ -29763,10 +29836,10 @@
         <v>12</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="H238" s="4" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -29774,13 +29847,13 @@
         <v>8</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="C239" s="2">
         <v>0</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>11</v>
@@ -29789,24 +29862,24 @@
         <v>12</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="H239" s="4" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="240" spans="1:8">
       <c r="A240" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="B240" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="C240">
         <v>1</v>
       </c>
       <c r="D240" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="E240" t="s">
         <v>11</v>
@@ -29815,10 +29888,10 @@
         <v>12</v>
       </c>
       <c r="G240" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="H240" s="4" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
     </row>
     <row r="241" spans="1:8">

--- a/docassemble/PowerOfAttorneyHealthCare/data/sources/poa_hc_es.xlsx
+++ b/docassemble/PowerOfAttorneyHealthCare/data/sources/poa_hc_es.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnewsted\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6216AE60-B8D2-4472-A453-4D0A62E5BC07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{270D9FCB-92ED-4F26-8FEB-ACFC17602995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31905" yWindow="-3210" windowWidth="26445" windowHeight="16770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-34950" yWindow="3765" windowWidth="26445" windowHeight="16770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22162,243 +22162,6 @@
     </r>
   </si>
   <si>
-    <t>31a3791a34401744a473ea590edf5be1</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${ get_language_list(lang_codes=al_interview_languages, current=al_user_language) }</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Welcome to Illinois Legal Aid Online's **Power of Attorney for Health Care** Easy Form.
-This program helps you make documents that give someone you trust power of attorney to make decisions about your health care. This means they can make choices about your health care when you cannot. You can also let them make choices about your health care earlier, if you choose.
-This program has videos with information about making a Power of Attorney for Health Care. You do not have to watch them, but you may find them helpful.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if user_path == "Shirley":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[YOUTUBE 7qy101TRdiI]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif user_path == "Frederico" or user_path == "Federico":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[YOUTUBE GR9t6ygX13g]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif user_path == "Lisa":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[YOUTUBE h2ZGl568xHo]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-To learn more, read ILAO's article about [**Power of Attorney for Health Care basics**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://www.illinoislegalaid.org/legal-information/setting-power-attorney-healthcare</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">).
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">${ get_language_list(lang_codes=al_interview_languages, current=al_user_language) }
-Bienvenido(a) al Formulario Guiado de Poder Notarial para el Cuidado de la Salud de Illinois Legal Aid Online.
-Este programa te ayuda a crear documentos que le otorgan a una persona de tu confianza la autoridad legal para tomar decisiones sobre tu atención médica. Esto significa que esa persona podrá tomar decisiones sobre tu atención médica cuando no puedas hacerlo por ti mismo(a). Si así lo deseas, también puedes autorizarla para que tome decisiones sobre tu atención médica antesde que eso ocurra.
-Este programa incluye videos con información sobre cómo hacer un Poder Notarial para el Cuidado de la Salud. No tienes que verlos, pero pueden serte útiles.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">[YOUTUBE ccToVpEse7s]
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Para obtener más información, lee el artículo de ILAO sobre los [**Conceptos Básicos del Poder Notarial para el Cuidado de la Salud**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://es.illinoislegalaid.org/legal-information/setting-power-attorney-healthcare</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>).</t>
-    </r>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">**Límites para </t>
     </r>
@@ -23177,6 +22940,250 @@
       <t xml:space="preserve">
 **Nota:** El Poder Notarial debe firmarse frente a al menos un testigo para que sea válido.
 ¡Gracias por usar los Formularios Guiados de ILAO!</t>
+    </r>
+  </si>
+  <si>
+    <t>80b04da1b3097b769fbc55dc4f8a6d71</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Welcome to Illinois Legal Aid Online's **Power of Attorney for Health Care** Easy Form.
+This program helps you make documents that give someone you trust power of attorney to make decisions about your health care. This means they can make choices about your health care when you cannot. You can also let them make choices about your health care earlier, if you choose.
+This program has videos with information about making a Power of Attorney for Health Care. You do not have to watch them, but you may find them helpful.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if user_path == "Shirley":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[YOUTUBE 7qy101TRdiI]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif user_path == "Frederico" or user_path == "Federico":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[YOUTUBE GR9t6ygX13g]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif user_path == "Lisa":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[YOUTUBE h2ZGl568xHo]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+To learn more, read ILAO's article about </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[**Power of Attorney for Health Care basics**]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://www.illinoislegalaid.org/legal-information/setting-power-attorney-healthcare</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">).
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Bienvenido(a) al Formulario Guiado de Poder Notarial para el Cuidado de la Salud de Illinois Legal Aid Online.
+Este programa te ayuda a crear documentos que le otorgan a una persona de tu confianza la autoridad legal para tomar decisiones sobre tu atención médica. Esto significa que esa persona podrá tomar decisiones sobre tu atención médica cuando no puedas hacerlo por ti mismo(a). Si así lo deseas, también puedes autorizarla para que tome decisiones sobre tu atención médica antesde que eso ocurra.
+Este programa incluye videos con información sobre cómo hacer un Poder Notarial para el Cuidado de la Salud. No tienes que verlos, pero pueden serte útiles.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">[YOUTUBE ccToVpEse7s]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Para obtener más información, lee el artículo de ILAO sobre los [**Conceptos Básicos del Poder Notarial para el Cuidado de la Salud**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://es.illinoislegalaid.org/legal-information/setting-power-attorney-healthcare</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
     </r>
   </si>
 </sst>
@@ -23705,7 +23712,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="345.6">
+    <row r="3" spans="1:8" ht="316.8">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -23716,7 +23723,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>11</v>
@@ -23725,10 +23732,10 @@
         <v>12</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -28214,7 +28221,7 @@
         <v>1</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>11</v>
@@ -28223,10 +28230,10 @@
         <v>12</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
     </row>
     <row r="177" spans="1:8" ht="201.6">
@@ -29292,7 +29299,7 @@
         <v>790</v>
       </c>
       <c r="H217" s="3" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="I217" s="3"/>
     </row>

--- a/docassemble/PowerOfAttorneyHealthCare/data/sources/poa_hc_es.xlsx
+++ b/docassemble/PowerOfAttorneyHealthCare/data/sources/poa_hc_es.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnewsted\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{270D9FCB-92ED-4F26-8FEB-ACFC17602995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81486406-1880-4DF9-B9C7-20B763325E4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34950" yWindow="3765" windowWidth="26445" windowHeight="16770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1164" yWindow="936" windowWidth="21156" windowHeight="13416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22943,18 +22943,30 @@
     </r>
   </si>
   <si>
-    <t>80b04da1b3097b769fbc55dc4f8a6d71</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Welcome to Illinois Legal Aid Online's **Power of Attorney for Health Care** Easy Form.
+    <t>7ae3790d22f601b38af6ba8ae684093e</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ get_language_list(lang_codes=al_interview_languages, current=get_language()) }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Welcome to Illinois Legal Aid Online's **Power of Attorney for Health Care** Easy Form.
 This program helps you make documents that give someone you trust power of attorney to make decisions about your health care. This means they can make choices about your health care when you cannot. You can also let them make choices about your health care earlier, if you choose.
 This program has videos with information about making a Power of Attorney for Health Care. You do not have to watch them, but you may find them helpful.
 </t>
@@ -23136,7 +23148,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Bienvenido(a) al Formulario Guiado de Poder Notarial para el Cuidado de la Salud de Illinois Legal Aid Online.
+      <t xml:space="preserve">${ get_language_list(lang_codes=al_interview_languages, current=get_language()) }
+Bienvenido(a) al Formulario Guiado de Poder Notarial para el Cuidado de la Salud de Illinois Legal Aid Online.
 Este programa te ayuda a crear documentos que le otorgan a una persona de tu confianza la autoridad legal para tomar decisiones sobre tu atención médica. Esto significa que esa persona podrá tomar decisiones sobre tu atención médica cuando no puedas hacerlo por ti mismo(a). Si así lo deseas, también puedes autorizarla para que tome decisiones sobre tu atención médica antesde que eso ocurra.
 Este programa incluye videos con información sobre cómo hacer un Poder Notarial para el Cuidado de la Salud. No tienes que verlos, pero pueden serte útiles.
 </t>
@@ -23712,7 +23725,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="316.8">
+    <row r="3" spans="1:8" ht="345.6">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>

--- a/docassemble/PowerOfAttorneyHealthCare/data/sources/poa_hc_es.xlsx
+++ b/docassemble/PowerOfAttorneyHealthCare/data/sources/poa_hc_es.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnewsted\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81486406-1880-4DF9-B9C7-20B763325E4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD69830-080F-4232-A12C-AFFA3E5058E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1164" yWindow="936" windowWidth="21156" windowHeight="13416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-35400" yWindow="-3195" windowWidth="30840" windowHeight="16845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16491,211 +16491,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">**Instrucciones sobre la disposición de tus restos:** 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if self_remains_preference != "specific":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${self_remains_preference}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${self_specific_burial_preference}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**Instrucciones sobre la disposición de los restos de </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if other_remains_preference != "specific":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${other_remains_preference}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${other_specific_burial_preference}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">**¿Quisieras donar tus órganos?**  
 </t>
     </r>
@@ -22943,30 +22738,77 @@
     </r>
   </si>
   <si>
-    <t>7ae3790d22f601b38af6ba8ae684093e</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${ get_language_list(lang_codes=al_interview_languages, current=get_language()) }</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Bienvenido(a) al Formulario Guiado de Poder Notarial para el Cuidado de la Salud de Illinois Legal Aid Online.
+Este programa te ayuda a crear documentos que le otorgan a una persona de tu confianza la autoridad legal para tomar decisiones sobre tu atención médica. Esto significa que esa persona podrá tomar decisiones sobre tu atención médica cuando no puedas hacerlo por ti mismo(a). Si así lo deseas, también puedes autorizarla para que tome decisiones sobre tu atención médica antesde que eso ocurra.
+Este programa incluye videos con información sobre cómo hacer un Poder Notarial para el Cuidado de la Salud. No tienes que verlos, pero pueden serte útiles.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">[YOUTUBE ccToVpEse7s]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-Welcome to Illinois Legal Aid Online's **Power of Attorney for Health Care** Easy Form.
+Para obtener más información, lee el artículo de ILAO sobre los [**Conceptos Básicos del Poder Notarial para el Cuidado de la Salud**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://es.illinoislegalaid.org/legal-information/setting-power-attorney-healthcare</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <t>80b04da1b3097b769fbc55dc4f8a6d71</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Welcome to Illinois Legal Aid Online's **Power of Attorney for Health Care** Easy Form.
 This program helps you make documents that give someone you trust power of attorney to make decisions about your health care. This means they can make choices about your health care when you cannot. You can also let them make choices about your health care earlier, if you choose.
 This program has videos with information about making a Power of Attorney for Health Care. You do not have to watch them, but you may find them helpful.
 </t>
@@ -23148,23 +22990,31 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">${ get_language_list(lang_codes=al_interview_languages, current=get_language()) }
-Bienvenido(a) al Formulario Guiado de Poder Notarial para el Cuidado de la Salud de Illinois Legal Aid Online.
-Este programa te ayuda a crear documentos que le otorgan a una persona de tu confianza la autoridad legal para tomar decisiones sobre tu atención médica. Esto significa que esa persona podrá tomar decisiones sobre tu atención médica cuando no puedas hacerlo por ti mismo(a). Si así lo deseas, también puedes autorizarla para que tome decisiones sobre tu atención médica antesde que eso ocurra.
-Este programa incluye videos con información sobre cómo hacer un Poder Notarial para el Cuidado de la Salud. No tienes que verlos, pero pueden serte útiles.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">[YOUTUBE ccToVpEse7s]
-</t>
+      <t xml:space="preserve">**Instrucciones sobre la disposición de tus restos: (En inglés)** 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if self_remains_preference != "specific":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${self_remains_preference}</t>
     </r>
     <r>
       <rPr>
@@ -23175,28 +23025,165 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-Para obtener más información, lee el artículo de ILAO sobre los [**Conceptos Básicos del Poder Notarial para el Cuidado de la Salud**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://es.illinoislegalaid.org/legal-information/setting-power-attorney-healthcare</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>).</t>
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${self_specific_burial_preference}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% endif</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**Instrucciones sobre la disposición de los restos de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()} (En inglés)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if other_remains_preference != "specific":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${other_remains_preference}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${other_specific_burial_preference}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% endif</t>
     </r>
   </si>
 </sst>
@@ -23323,7 +23310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -23348,6 +23335,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -23725,30 +23718,30 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="345.6">
+    <row r="3" spans="1:8" ht="316.8">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="10">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="10" t="s">
+        <v>794</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="11" t="s">
         <v>795</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>796</v>
-      </c>
       <c r="H3" s="7" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -23904,7 +23897,7 @@
         <v>31</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="28.8">
@@ -23918,7 +23911,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>11</v>
@@ -23927,7 +23920,7 @@
         <v>12</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>33</v>
@@ -23944,7 +23937,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>11</v>
@@ -23953,7 +23946,7 @@
         <v>12</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>34</v>
@@ -24008,7 +24001,7 @@
         <v>40</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="28.8">
@@ -24060,7 +24053,7 @@
         <v>46</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="28.8">
@@ -24112,21 +24105,21 @@
         <v>52</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="115.2">
       <c r="A18" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C18" s="2">
         <v>0</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>11</v>
@@ -24135,18 +24128,18 @@
         <v>12</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="28.8">
       <c r="A19" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
@@ -24242,7 +24235,7 @@
         <v>63</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="57.6">
@@ -24268,7 +24261,7 @@
         <v>65</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="28.8">
@@ -24412,7 +24405,7 @@
         <v>1</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>11</v>
@@ -24421,10 +24414,10 @@
         <v>12</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -24528,7 +24521,7 @@
         <v>85</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -24866,7 +24859,7 @@
         <v>120</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -24996,7 +24989,7 @@
         <v>131</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="28.8">
@@ -25022,7 +25015,7 @@
         <v>133</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="28.8">
@@ -25100,7 +25093,7 @@
         <v>142</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="288">
@@ -25126,7 +25119,7 @@
         <v>144</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="28.8">
@@ -25464,7 +25457,7 @@
         <v>177</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="28.8">
@@ -25490,7 +25483,7 @@
         <v>179</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -25568,7 +25561,7 @@
         <v>185</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -25646,7 +25639,7 @@
         <v>193</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="115.2">
@@ -25698,7 +25691,7 @@
         <v>198</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="28.8">
@@ -25747,7 +25740,7 @@
         <v>12</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>634</v>
@@ -25802,7 +25795,7 @@
         <v>207</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -25932,7 +25925,7 @@
         <v>220</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="43.2">
@@ -25984,7 +25977,7 @@
         <v>639</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="72">
@@ -26036,7 +26029,7 @@
         <v>228</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -26192,7 +26185,7 @@
         <v>243</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="129.6">
@@ -26218,7 +26211,7 @@
         <v>245</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="86.4">
@@ -26270,7 +26263,7 @@
         <v>250</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="28.8">
@@ -26553,7 +26546,7 @@
         <v>12</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="H111" s="3" t="s">
         <v>651</v>
@@ -26894,7 +26887,7 @@
         <v>307</v>
       </c>
       <c r="H124" s="8" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="28.8">
@@ -26920,7 +26913,7 @@
         <v>309</v>
       </c>
       <c r="H125" s="8" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="28.8">
@@ -26946,7 +26939,7 @@
         <v>311</v>
       </c>
       <c r="H126" s="8" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -27024,7 +27017,7 @@
         <v>318</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -27102,7 +27095,7 @@
         <v>325</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -27168,7 +27161,7 @@
         <v>2</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>11</v>
@@ -27177,24 +27170,24 @@
         <v>12</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="136" spans="1:8" ht="115.2">
       <c r="A136" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C136" s="2">
         <v>0</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>11</v>
@@ -27203,10 +27196,10 @@
         <v>12</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
     </row>
     <row r="137" spans="1:8" ht="409.6">
@@ -27232,7 +27225,7 @@
         <v>332</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="28.8">
@@ -27466,7 +27459,7 @@
         <v>354</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -27596,7 +27589,7 @@
         <v>368</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="152" spans="1:8" ht="28.8">
@@ -27726,7 +27719,7 @@
         <v>382</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
     <row r="157" spans="1:8" ht="43.2">
@@ -27830,7 +27823,7 @@
         <v>394</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="100.8">
@@ -27882,7 +27875,7 @@
         <v>399</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="100.8">
@@ -28038,7 +28031,7 @@
         <v>417</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="169" spans="1:8" ht="57.6">
@@ -28194,7 +28187,7 @@
         <v>696</v>
       </c>
       <c r="H174" s="3" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="28.8">
@@ -28234,7 +28227,7 @@
         <v>1</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>11</v>
@@ -28243,10 +28236,10 @@
         <v>12</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="177" spans="1:8" ht="201.6">
@@ -28272,7 +28265,7 @@
         <v>439</v>
       </c>
       <c r="H177" s="3" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="86.4">
@@ -28298,7 +28291,7 @@
         <v>442</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -28792,7 +28785,7 @@
         <v>497</v>
       </c>
       <c r="H197" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -28818,7 +28811,7 @@
         <v>499</v>
       </c>
       <c r="H198" s="6" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="100.8">
@@ -28844,7 +28837,7 @@
         <v>501</v>
       </c>
       <c r="H199" s="3" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="200" spans="1:8" ht="158.4">
@@ -29000,7 +28993,7 @@
         <v>513</v>
       </c>
       <c r="H205" s="3" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="115.2">
@@ -29127,10 +29120,10 @@
         <v>12</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="H210" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="211" spans="1:9" ht="158.4">
@@ -29182,7 +29175,7 @@
         <v>526</v>
       </c>
       <c r="H212" s="3" t="s">
-        <v>714</v>
+        <v>796</v>
       </c>
     </row>
     <row r="213" spans="1:9" ht="100.8">
@@ -29208,7 +29201,7 @@
         <v>528</v>
       </c>
       <c r="H213" s="3" t="s">
-        <v>715</v>
+        <v>797</v>
       </c>
     </row>
     <row r="214" spans="1:9" ht="43.2">
@@ -29234,7 +29227,7 @@
         <v>530</v>
       </c>
       <c r="H214" s="3" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="215" spans="1:9" ht="43.2">
@@ -29286,7 +29279,7 @@
         <v>535</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
     </row>
     <row r="217" spans="1:9" ht="409.6">
@@ -29300,7 +29293,7 @@
         <v>21</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>11</v>
@@ -29309,10 +29302,10 @@
         <v>12</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="H217" s="3" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="I217" s="3"/>
     </row>
@@ -29339,7 +29332,7 @@
         <v>537</v>
       </c>
       <c r="H218" s="3" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="219" spans="1:9" ht="43.2">
@@ -29469,7 +29462,7 @@
         <v>548</v>
       </c>
       <c r="H223" s="3" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
     </row>
     <row r="224" spans="1:9" ht="43.2">
@@ -29890,7 +29883,7 @@
     </row>
     <row r="240" spans="1:8">
       <c r="A240" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="B240" t="s">
         <v>590</v>
@@ -29899,7 +29892,7 @@
         <v>1</v>
       </c>
       <c r="D240" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="E240" t="s">
         <v>11</v>
@@ -29908,10 +29901,10 @@
         <v>12</v>
       </c>
       <c r="G240" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="H240" s="4" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="241" spans="1:8">

--- a/docassemble/PowerOfAttorneyHealthCare/data/sources/poa_hc_es.xlsx
+++ b/docassemble/PowerOfAttorneyHealthCare/data/sources/poa_hc_es.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnewsted\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD69830-080F-4232-A12C-AFFA3E5058E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{726B4E2B-DC62-4DF1-8113-8FB901BCE7A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35400" yWindow="-3195" windowWidth="30840" windowHeight="16845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-36045" yWindow="-3345" windowWidth="30840" windowHeight="16845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5111,13 +5111,6 @@
     <t>legal capacity</t>
   </si>
   <si>
-    <t>eae54beffdc63e0f44821e6670d5495b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">You have the **legal capacity** to revoke a Power of Attorney for Health Care if you understand what you are signing and what it means for your future.
-</t>
-  </si>
-  <si>
     <t>58ca2de59caab479fb537acf8b4b6f5c</t>
   </si>
   <si>
@@ -13622,9 +13615,6 @@
     <t>Capacidad legal</t>
   </si>
   <si>
-    <t>Tienes capacidad legal para revocar un Poder Notarial para el Cuidado de la Salud si entiendes lo que estás firmando y lo que significa para tu futuro.</t>
-  </si>
-  <si>
     <t>**Video: ¿Qué es este periodo de reflexión de 30 días?**</t>
   </si>
   <si>
@@ -23185,6 +23175,16 @@
       </rPr>
       <t>% endif</t>
     </r>
+  </si>
+  <si>
+    <t>La **capacidad legal** significa que una persona puede entender lo que está firmando y lo que esto implica para su futuro.</t>
+  </si>
+  <si>
+    <t>758dbe9f10315dbb11909fb009a7a357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**Legal capacity** means a person is mentally able to understand what they are signing and understand what it means for their future.
+</t>
   </si>
 </sst>
 </file>
@@ -23725,23 +23725,23 @@
       <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="2">
         <v>1</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>794</v>
-      </c>
-      <c r="E3" s="10" t="s">
+      <c r="D3" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="11" t="s">
-        <v>795</v>
+      <c r="G3" s="3" t="s">
+        <v>792</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -23793,7 +23793,7 @@
         <v>20</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -23897,7 +23897,7 @@
         <v>31</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="28.8">
@@ -23911,7 +23911,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>11</v>
@@ -23920,7 +23920,7 @@
         <v>12</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>33</v>
@@ -23937,7 +23937,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>11</v>
@@ -23946,7 +23946,7 @@
         <v>12</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>34</v>
@@ -24001,7 +24001,7 @@
         <v>40</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="28.8">
@@ -24053,7 +24053,7 @@
         <v>46</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="28.8">
@@ -24105,21 +24105,21 @@
         <v>52</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="115.2">
       <c r="A18" s="2" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="C18" s="2">
         <v>0</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>11</v>
@@ -24128,18 +24128,18 @@
         <v>12</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="28.8">
       <c r="A19" s="2" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
@@ -24183,7 +24183,7 @@
         <v>58</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -24209,7 +24209,7 @@
         <v>61</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="43.2">
@@ -24235,7 +24235,7 @@
         <v>63</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="57.6">
@@ -24261,7 +24261,7 @@
         <v>65</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="28.8">
@@ -24287,7 +24287,7 @@
         <v>67</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="57.6">
@@ -24313,7 +24313,7 @@
         <v>69</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="28.8">
@@ -24339,7 +24339,7 @@
         <v>72</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="244.8">
@@ -24365,7 +24365,7 @@
         <v>74</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="86.4">
@@ -24391,7 +24391,7 @@
         <v>77</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="409.6">
@@ -24405,7 +24405,7 @@
         <v>1</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>11</v>
@@ -24414,10 +24414,10 @@
         <v>12</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -24443,7 +24443,7 @@
         <v>79</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -24469,7 +24469,7 @@
         <v>81</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -24495,7 +24495,7 @@
         <v>83</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -24521,7 +24521,7 @@
         <v>85</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -24573,7 +24573,7 @@
         <v>90</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="100.8">
@@ -24599,7 +24599,7 @@
         <v>93</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="28.8">
@@ -24625,7 +24625,7 @@
         <v>95</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="86.4">
@@ -24651,7 +24651,7 @@
         <v>98</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="28.8">
@@ -24677,7 +24677,7 @@
         <v>101</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="144">
@@ -24703,7 +24703,7 @@
         <v>103</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="86.4">
@@ -24755,7 +24755,7 @@
         <v>110</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="374.4">
@@ -24781,7 +24781,7 @@
         <v>112</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="86.4">
@@ -24807,7 +24807,7 @@
         <v>115</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="28.8">
@@ -24833,7 +24833,7 @@
         <v>117</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="28.8">
@@ -24859,7 +24859,7 @@
         <v>120</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -24885,7 +24885,7 @@
         <v>122</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="43.2">
@@ -24911,7 +24911,7 @@
         <v>124</v>
       </c>
       <c r="H48" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -24937,7 +24937,7 @@
         <v>126</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -24963,7 +24963,7 @@
         <v>128</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="129.6">
@@ -24989,7 +24989,7 @@
         <v>131</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="28.8">
@@ -25015,7 +25015,7 @@
         <v>133</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="28.8">
@@ -25067,7 +25067,7 @@
         <v>139</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="100.8">
@@ -25093,7 +25093,7 @@
         <v>142</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="288">
@@ -25119,7 +25119,7 @@
         <v>144</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="28.8">
@@ -25145,7 +25145,7 @@
         <v>147</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -25197,7 +25197,7 @@
         <v>153</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="28.8">
@@ -25223,7 +25223,7 @@
         <v>155</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="144">
@@ -25249,7 +25249,7 @@
         <v>157</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -25327,7 +25327,7 @@
         <v>165</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="43.2">
@@ -25353,7 +25353,7 @@
         <v>167</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="57.6">
@@ -25379,7 +25379,7 @@
         <v>169</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -25431,7 +25431,7 @@
         <v>175</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="172.8">
@@ -25457,7 +25457,7 @@
         <v>177</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="28.8">
@@ -25483,7 +25483,7 @@
         <v>179</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -25509,7 +25509,7 @@
         <v>181</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="43.2">
@@ -25535,7 +25535,7 @@
         <v>183</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="57.6">
@@ -25561,7 +25561,7 @@
         <v>185</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -25587,7 +25587,7 @@
         <v>187</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="28.8">
@@ -25639,7 +25639,7 @@
         <v>193</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="115.2">
@@ -25665,7 +25665,7 @@
         <v>196</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="360">
@@ -25691,7 +25691,7 @@
         <v>198</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="28.8">
@@ -25717,7 +25717,7 @@
         <v>201</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="28.8">
@@ -25740,10 +25740,10 @@
         <v>12</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="72">
@@ -25769,7 +25769,7 @@
         <v>205</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="72">
@@ -25795,7 +25795,7 @@
         <v>207</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -25847,7 +25847,7 @@
         <v>212</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -25873,7 +25873,7 @@
         <v>214</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -25925,7 +25925,7 @@
         <v>220</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="43.2">
@@ -25951,7 +25951,7 @@
         <v>222</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="43.2">
@@ -25974,10 +25974,10 @@
         <v>12</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="72">
@@ -26003,7 +26003,7 @@
         <v>226</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="72">
@@ -26029,7 +26029,7 @@
         <v>228</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -26081,7 +26081,7 @@
         <v>233</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -26107,7 +26107,7 @@
         <v>235</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -26133,7 +26133,7 @@
         <v>237</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="201.6">
@@ -26159,7 +26159,7 @@
         <v>240</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="28.8">
@@ -26185,7 +26185,7 @@
         <v>243</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="129.6">
@@ -26211,7 +26211,7 @@
         <v>245</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="86.4">
@@ -26237,7 +26237,7 @@
         <v>248</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="302.39999999999998">
@@ -26263,7 +26263,7 @@
         <v>250</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="28.8">
@@ -26289,7 +26289,7 @@
         <v>253</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="102" spans="1:8" ht="86.4">
@@ -26315,7 +26315,7 @@
         <v>255</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -26367,7 +26367,7 @@
         <v>260</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -26419,7 +26419,7 @@
         <v>265</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -26497,7 +26497,7 @@
         <v>273</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="110" spans="1:8" ht="43.2">
@@ -26523,7 +26523,7 @@
         <v>276</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="86.4">
@@ -26546,10 +26546,10 @@
         <v>12</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -26575,7 +26575,7 @@
         <v>279</v>
       </c>
       <c r="H112" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -26601,7 +26601,7 @@
         <v>281</v>
       </c>
       <c r="H113" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -26627,7 +26627,7 @@
         <v>283</v>
       </c>
       <c r="H114" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -26653,7 +26653,7 @@
         <v>285</v>
       </c>
       <c r="H115" s="6" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="116" spans="1:8" ht="43.2">
@@ -26679,7 +26679,7 @@
         <v>287</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="28.8">
@@ -26757,7 +26757,7 @@
         <v>295</v>
       </c>
       <c r="H119" s="6" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="120" spans="1:8" ht="28.8">
@@ -26783,7 +26783,7 @@
         <v>298</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -26809,7 +26809,7 @@
         <v>300</v>
       </c>
       <c r="H121" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="86.4">
@@ -26835,7 +26835,7 @@
         <v>303</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="28.8">
@@ -26861,7 +26861,7 @@
         <v>305</v>
       </c>
       <c r="H123" s="6" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="28.8">
@@ -26887,7 +26887,7 @@
         <v>307</v>
       </c>
       <c r="H124" s="8" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="28.8">
@@ -26913,7 +26913,7 @@
         <v>309</v>
       </c>
       <c r="H125" s="8" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="28.8">
@@ -26939,7 +26939,7 @@
         <v>311</v>
       </c>
       <c r="H126" s="8" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -26965,7 +26965,7 @@
         <v>313</v>
       </c>
       <c r="H127" s="8" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -27017,7 +27017,7 @@
         <v>318</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -27043,7 +27043,7 @@
         <v>320</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="131" spans="1:8" ht="28.8">
@@ -27069,7 +27069,7 @@
         <v>323</v>
       </c>
       <c r="H131" s="6" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="132" spans="1:8" ht="403.2">
@@ -27095,7 +27095,7 @@
         <v>325</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -27121,7 +27121,7 @@
         <v>328</v>
       </c>
       <c r="H133" s="6" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="134" spans="1:8" ht="43.2">
@@ -27131,23 +27131,23 @@
       <c r="B134" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="C134" s="2">
+      <c r="C134" s="10">
         <v>1</v>
       </c>
-      <c r="D134" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="E134" s="2" t="s">
+      <c r="D134" s="10" t="s">
+        <v>796</v>
+      </c>
+      <c r="E134" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F134" s="2" t="s">
+      <c r="F134" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="G134" s="3" t="s">
-        <v>330</v>
+      <c r="G134" s="11" t="s">
+        <v>797</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>667</v>
+        <v>795</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="100.8">
@@ -27161,7 +27161,7 @@
         <v>2</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>11</v>
@@ -27170,24 +27170,24 @@
         <v>12</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
     </row>
     <row r="136" spans="1:8" ht="115.2">
       <c r="A136" s="2" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C136" s="2">
         <v>0</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>11</v>
@@ -27196,10 +27196,10 @@
         <v>12</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
     </row>
     <row r="137" spans="1:8" ht="409.6">
@@ -27213,7 +27213,7 @@
         <v>3</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>11</v>
@@ -27222,10 +27222,10 @@
         <v>12</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="28.8">
@@ -27233,13 +27233,13 @@
         <v>8</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C138" s="2">
         <v>1</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>11</v>
@@ -27248,10 +27248,10 @@
         <v>12</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -27259,13 +27259,13 @@
         <v>8</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C139" s="2">
         <v>0</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>11</v>
@@ -27274,10 +27274,10 @@
         <v>12</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H139" s="6" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="140" spans="1:8" ht="57.6">
@@ -27285,13 +27285,13 @@
         <v>8</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C140" s="2">
         <v>1</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>11</v>
@@ -27300,10 +27300,10 @@
         <v>12</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -27311,13 +27311,13 @@
         <v>8</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C141" s="2">
         <v>2</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>11</v>
@@ -27326,10 +27326,10 @@
         <v>12</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="H141" s="6" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
     </row>
     <row r="142" spans="1:8" ht="43.2">
@@ -27337,13 +27337,13 @@
         <v>8</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C142" s="2">
         <v>3</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>11</v>
@@ -27352,10 +27352,10 @@
         <v>12</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
     </row>
     <row r="143" spans="1:8" ht="86.4">
@@ -27363,13 +27363,13 @@
         <v>8</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C143" s="2">
         <v>4</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>11</v>
@@ -27378,10 +27378,10 @@
         <v>12</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
     </row>
     <row r="144" spans="1:8" ht="216">
@@ -27389,13 +27389,13 @@
         <v>8</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C144" s="2">
         <v>5</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>11</v>
@@ -27404,10 +27404,10 @@
         <v>12</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
     </row>
     <row r="145" spans="1:8" ht="86.4">
@@ -27415,13 +27415,13 @@
         <v>8</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C145" s="2">
         <v>0</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>11</v>
@@ -27430,10 +27430,10 @@
         <v>12</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="146" spans="1:8" ht="86.4">
@@ -27441,13 +27441,13 @@
         <v>8</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C146" s="2">
         <v>1</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>11</v>
@@ -27456,10 +27456,10 @@
         <v>12</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -27467,13 +27467,13 @@
         <v>8</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C147" s="2">
         <v>2</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>11</v>
@@ -27482,10 +27482,10 @@
         <v>12</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="H147" s="6" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="148" spans="1:8" ht="86.4">
@@ -27493,13 +27493,13 @@
         <v>8</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C148" s="2">
         <v>0</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>11</v>
@@ -27508,10 +27508,10 @@
         <v>12</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="28.8">
@@ -27519,13 +27519,13 @@
         <v>8</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C149" s="2">
         <v>0</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>11</v>
@@ -27534,10 +27534,10 @@
         <v>12</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -27545,13 +27545,13 @@
         <v>8</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C150" s="2">
         <v>2</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>11</v>
@@ -27560,10 +27560,10 @@
         <v>12</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="129.6">
@@ -27571,13 +27571,13 @@
         <v>8</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C151" s="2">
         <v>0</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>11</v>
@@ -27586,10 +27586,10 @@
         <v>12</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
     </row>
     <row r="152" spans="1:8" ht="28.8">
@@ -27597,13 +27597,13 @@
         <v>8</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C152" s="2">
         <v>1</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>11</v>
@@ -27612,10 +27612,10 @@
         <v>12</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="153" spans="1:8" ht="28.8">
@@ -27623,13 +27623,13 @@
         <v>8</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C153" s="2">
         <v>0</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>11</v>
@@ -27638,10 +27638,10 @@
         <v>12</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="H153" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="154" spans="1:8" ht="115.2">
@@ -27649,13 +27649,13 @@
         <v>8</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C154" s="2">
         <v>1</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>11</v>
@@ -27664,10 +27664,10 @@
         <v>12</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
     </row>
     <row r="155" spans="1:8" ht="28.8">
@@ -27675,13 +27675,13 @@
         <v>8</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C155" s="2">
         <v>0</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>11</v>
@@ -27690,10 +27690,10 @@
         <v>12</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="H155" s="6" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
     </row>
     <row r="156" spans="1:8" ht="409.6">
@@ -27701,13 +27701,13 @@
         <v>8</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C156" s="2">
         <v>1</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>11</v>
@@ -27716,10 +27716,10 @@
         <v>12</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
     </row>
     <row r="157" spans="1:8" ht="43.2">
@@ -27727,13 +27727,13 @@
         <v>8</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C157" s="2">
         <v>0</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>11</v>
@@ -27742,10 +27742,10 @@
         <v>12</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H157" s="6" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="158" spans="1:8" ht="86.4">
@@ -27753,13 +27753,13 @@
         <v>8</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C158" s="2">
         <v>1</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>11</v>
@@ -27768,10 +27768,10 @@
         <v>12</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="28.8">
@@ -27779,13 +27779,13 @@
         <v>8</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C159" s="2">
         <v>0</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>11</v>
@@ -27794,10 +27794,10 @@
         <v>12</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H159" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="160" spans="1:8" ht="144">
@@ -27805,13 +27805,13 @@
         <v>8</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C160" s="2">
         <v>1</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>11</v>
@@ -27820,10 +27820,10 @@
         <v>12</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="100.8">
@@ -27831,13 +27831,13 @@
         <v>8</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C161" s="2">
         <v>0</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>11</v>
@@ -27846,10 +27846,10 @@
         <v>12</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="144">
@@ -27857,13 +27857,13 @@
         <v>8</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C162" s="2">
         <v>1</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>11</v>
@@ -27872,10 +27872,10 @@
         <v>12</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="100.8">
@@ -27883,13 +27883,13 @@
         <v>8</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C163" s="2">
         <v>0</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>11</v>
@@ -27898,10 +27898,10 @@
         <v>12</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="164" spans="1:8" ht="43.2">
@@ -27909,13 +27909,13 @@
         <v>8</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C164" s="2">
         <v>1</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>11</v>
@@ -27924,10 +27924,10 @@
         <v>12</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
     </row>
     <row r="165" spans="1:8" ht="115.2">
@@ -27935,13 +27935,13 @@
         <v>8</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C165" s="2">
         <v>0</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>11</v>
@@ -27950,10 +27950,10 @@
         <v>12</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="166" spans="1:8" ht="86.4">
@@ -27961,13 +27961,13 @@
         <v>8</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C166" s="2">
         <v>1</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>11</v>
@@ -27976,10 +27976,10 @@
         <v>12</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="86.4">
@@ -27987,13 +27987,13 @@
         <v>8</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C167" s="2">
         <v>0</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>11</v>
@@ -28002,10 +28002,10 @@
         <v>12</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H167" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="28.8">
@@ -28013,13 +28013,13 @@
         <v>8</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C168" s="2">
         <v>0</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>11</v>
@@ -28028,10 +28028,10 @@
         <v>12</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="169" spans="1:8" ht="57.6">
@@ -28039,13 +28039,13 @@
         <v>8</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C169" s="2">
         <v>1</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>11</v>
@@ -28054,10 +28054,10 @@
         <v>12</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="H169" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="170" spans="1:8">
@@ -28065,13 +28065,13 @@
         <v>8</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C170" s="2">
         <v>2</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>11</v>
@@ -28080,10 +28080,10 @@
         <v>12</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H170" s="3" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="57.6">
@@ -28091,13 +28091,13 @@
         <v>8</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C171" s="2">
         <v>0</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>11</v>
@@ -28106,10 +28106,10 @@
         <v>12</v>
       </c>
       <c r="G171" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H171" s="6" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
     <row r="172" spans="1:8" ht="28.8">
@@ -28117,13 +28117,13 @@
         <v>8</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C172" s="2">
         <v>1</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>11</v>
@@ -28132,10 +28132,10 @@
         <v>12</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="H172" s="6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="28.8">
@@ -28143,13 +28143,13 @@
         <v>8</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C173" s="2">
         <v>0</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>11</v>
@@ -28158,10 +28158,10 @@
         <v>12</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H173" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="409.6">
@@ -28169,13 +28169,13 @@
         <v>8</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C174" s="2">
         <v>1</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>11</v>
@@ -28184,10 +28184,10 @@
         <v>12</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="H174" s="3" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="28.8">
@@ -28195,13 +28195,13 @@
         <v>8</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C175" s="2">
         <v>0</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>11</v>
@@ -28210,10 +28210,10 @@
         <v>12</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H175" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="176" spans="1:8" ht="409.6">
@@ -28221,13 +28221,13 @@
         <v>8</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C176" s="2">
         <v>1</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>11</v>
@@ -28236,10 +28236,10 @@
         <v>12</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
     </row>
     <row r="177" spans="1:8" ht="201.6">
@@ -28247,13 +28247,13 @@
         <v>8</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C177" s="2">
         <v>2</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>11</v>
@@ -28262,10 +28262,10 @@
         <v>12</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H177" s="3" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="86.4">
@@ -28273,13 +28273,13 @@
         <v>8</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C178" s="2">
         <v>0</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>11</v>
@@ -28288,10 +28288,10 @@
         <v>12</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -28299,13 +28299,13 @@
         <v>8</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C179" s="2">
         <v>1</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>11</v>
@@ -28314,7 +28314,7 @@
         <v>12</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="H179" s="6" t="s">
         <v>29</v>
@@ -28325,13 +28325,13 @@
         <v>8</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C180" s="2">
         <v>0</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>11</v>
@@ -28340,10 +28340,10 @@
         <v>12</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -28351,13 +28351,13 @@
         <v>8</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C181" s="2">
         <v>0</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>11</v>
@@ -28366,10 +28366,10 @@
         <v>12</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="H181" s="6" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -28377,13 +28377,13 @@
         <v>8</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C182" s="2">
         <v>0</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>11</v>
@@ -28392,10 +28392,10 @@
         <v>12</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -28403,13 +28403,13 @@
         <v>8</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C183" s="2">
         <v>0</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>11</v>
@@ -28418,10 +28418,10 @@
         <v>12</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="H183" s="6" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -28429,13 +28429,13 @@
         <v>8</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C184" s="2">
         <v>0</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>11</v>
@@ -28444,10 +28444,10 @@
         <v>12</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="144">
@@ -28455,13 +28455,13 @@
         <v>8</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C185" s="2">
         <v>0</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>11</v>
@@ -28470,10 +28470,10 @@
         <v>12</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
     </row>
     <row r="186" spans="1:8" ht="28.8">
@@ -28481,13 +28481,13 @@
         <v>8</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C186" s="2">
         <v>14</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>11</v>
@@ -28496,10 +28496,10 @@
         <v>12</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="187" spans="1:8" ht="28.8">
@@ -28507,13 +28507,13 @@
         <v>8</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C187" s="2">
         <v>15</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>11</v>
@@ -28522,10 +28522,10 @@
         <v>12</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="H187" s="6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="188" spans="1:8" ht="57.6">
@@ -28533,13 +28533,13 @@
         <v>8</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C188" s="2">
         <v>16</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>11</v>
@@ -28548,10 +28548,10 @@
         <v>12</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H188" s="3" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="28.8">
@@ -28559,13 +28559,13 @@
         <v>8</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C189" s="2">
         <v>18</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>11</v>
@@ -28574,10 +28574,10 @@
         <v>12</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H189" s="6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="190" spans="1:8" ht="57.6">
@@ -28585,13 +28585,13 @@
         <v>8</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C190" s="2">
         <v>20</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>11</v>
@@ -28600,10 +28600,10 @@
         <v>12</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="43.2">
@@ -28611,13 +28611,13 @@
         <v>8</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C191" s="2">
         <v>21</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>11</v>
@@ -28626,10 +28626,10 @@
         <v>12</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H191" s="6" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="192" spans="1:8" ht="28.8">
@@ -28637,13 +28637,13 @@
         <v>8</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C192" s="2">
         <v>22</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>11</v>
@@ -28652,10 +28652,10 @@
         <v>12</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="H192" s="6" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="193" spans="1:8" ht="28.8">
@@ -28663,13 +28663,13 @@
         <v>8</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C193" s="2">
         <v>29</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>11</v>
@@ -28678,10 +28678,10 @@
         <v>12</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H193" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="194" spans="1:8" ht="244.8">
@@ -28689,13 +28689,13 @@
         <v>8</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C194" s="2">
         <v>30</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>11</v>
@@ -28704,10 +28704,10 @@
         <v>12</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H194" s="6" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -28715,13 +28715,13 @@
         <v>8</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C195" s="2">
         <v>31</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>11</v>
@@ -28730,7 +28730,7 @@
         <v>12</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H195" s="6" t="s">
         <v>14</v>
@@ -28741,13 +28741,13 @@
         <v>8</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C196" s="2">
         <v>0</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>11</v>
@@ -28756,10 +28756,10 @@
         <v>12</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="H196" s="6" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="197" spans="1:8" ht="28.8">
@@ -28767,13 +28767,13 @@
         <v>8</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C197" s="2">
         <v>1</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>11</v>
@@ -28782,10 +28782,10 @@
         <v>12</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="H197" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -28793,13 +28793,13 @@
         <v>8</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C198" s="2">
         <v>2</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>11</v>
@@ -28808,10 +28808,10 @@
         <v>12</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="H198" s="6" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="100.8">
@@ -28819,13 +28819,13 @@
         <v>8</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C199" s="2">
         <v>3</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>11</v>
@@ -28834,10 +28834,10 @@
         <v>12</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H199" s="3" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
     </row>
     <row r="200" spans="1:8" ht="158.4">
@@ -28845,13 +28845,13 @@
         <v>8</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C200" s="2">
         <v>4</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>11</v>
@@ -28860,10 +28860,10 @@
         <v>12</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="H200" s="3" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="201" spans="1:8" ht="43.2">
@@ -28871,13 +28871,13 @@
         <v>8</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C201" s="2">
         <v>5</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>11</v>
@@ -28886,10 +28886,10 @@
         <v>12</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
     </row>
     <row r="202" spans="1:8" ht="100.8">
@@ -28897,13 +28897,13 @@
         <v>8</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C202" s="2">
         <v>6</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>11</v>
@@ -28912,10 +28912,10 @@
         <v>12</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="H202" s="3" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
     </row>
     <row r="203" spans="1:8" ht="43.2">
@@ -28923,13 +28923,13 @@
         <v>8</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C203" s="2">
         <v>7</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>11</v>
@@ -28938,10 +28938,10 @@
         <v>12</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="H203" s="3" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="100.8">
@@ -28949,13 +28949,13 @@
         <v>8</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C204" s="2">
         <v>8</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>11</v>
@@ -28964,10 +28964,10 @@
         <v>12</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="H204" s="3" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
     </row>
     <row r="205" spans="1:8" ht="100.8">
@@ -28975,13 +28975,13 @@
         <v>8</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C205" s="2">
         <v>9</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>11</v>
@@ -28990,10 +28990,10 @@
         <v>12</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="H205" s="3" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="115.2">
@@ -29001,13 +29001,13 @@
         <v>8</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C206" s="2">
         <v>10</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>11</v>
@@ -29016,10 +29016,10 @@
         <v>12</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H206" s="3" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
     </row>
     <row r="207" spans="1:8" ht="158.4">
@@ -29027,13 +29027,13 @@
         <v>8</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C207" s="2">
         <v>11</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>11</v>
@@ -29042,10 +29042,10 @@
         <v>12</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="H207" s="3" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="172.8">
@@ -29053,13 +29053,13 @@
         <v>8</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C208" s="2">
         <v>12</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>11</v>
@@ -29068,10 +29068,10 @@
         <v>12</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H208" s="3" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
     </row>
     <row r="209" spans="1:9" ht="115.2">
@@ -29079,13 +29079,13 @@
         <v>8</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C209" s="2">
         <v>13</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>11</v>
@@ -29094,10 +29094,10 @@
         <v>12</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="H209" s="3" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
     </row>
     <row r="210" spans="1:9" ht="158.4">
@@ -29105,13 +29105,13 @@
         <v>8</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C210" s="2">
         <v>14</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>11</v>
@@ -29120,10 +29120,10 @@
         <v>12</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="H210" s="3" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
     </row>
     <row r="211" spans="1:9" ht="158.4">
@@ -29131,13 +29131,13 @@
         <v>8</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C211" s="2">
         <v>15</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>11</v>
@@ -29146,10 +29146,10 @@
         <v>12</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H211" s="3" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="212" spans="1:9" ht="100.8">
@@ -29157,13 +29157,13 @@
         <v>8</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C212" s="2">
         <v>16</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>11</v>
@@ -29172,10 +29172,10 @@
         <v>12</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H212" s="3" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
     </row>
     <row r="213" spans="1:9" ht="100.8">
@@ -29183,13 +29183,13 @@
         <v>8</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C213" s="2">
         <v>17</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>11</v>
@@ -29198,10 +29198,10 @@
         <v>12</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="H213" s="3" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
     </row>
     <row r="214" spans="1:9" ht="43.2">
@@ -29209,13 +29209,13 @@
         <v>8</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C214" s="2">
         <v>18</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>11</v>
@@ -29224,10 +29224,10 @@
         <v>12</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="H214" s="3" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
     </row>
     <row r="215" spans="1:9" ht="43.2">
@@ -29235,13 +29235,13 @@
         <v>8</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C215" s="2">
         <v>19</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>11</v>
@@ -29250,10 +29250,10 @@
         <v>12</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="H215" s="3" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="216" spans="1:9" ht="43.2">
@@ -29261,13 +29261,13 @@
         <v>8</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C216" s="2">
         <v>20</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>11</v>
@@ -29276,10 +29276,10 @@
         <v>12</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
     </row>
     <row r="217" spans="1:9" ht="409.6">
@@ -29287,13 +29287,13 @@
         <v>8</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C217" s="2">
         <v>21</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>11</v>
@@ -29302,10 +29302,10 @@
         <v>12</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="H217" s="3" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="I217" s="3"/>
     </row>
@@ -29314,13 +29314,13 @@
         <v>8</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C218" s="2">
         <v>22</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>11</v>
@@ -29329,10 +29329,10 @@
         <v>12</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="H218" s="3" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
     </row>
     <row r="219" spans="1:9" ht="43.2">
@@ -29340,13 +29340,13 @@
         <v>8</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C219" s="2">
         <v>23</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>11</v>
@@ -29355,10 +29355,10 @@
         <v>12</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="H219" s="3" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="220" spans="1:9" ht="86.4">
@@ -29366,13 +29366,13 @@
         <v>8</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C220" s="2">
         <v>24</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>11</v>
@@ -29381,10 +29381,10 @@
         <v>12</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H220" s="3" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
     </row>
     <row r="221" spans="1:9" ht="115.2">
@@ -29392,13 +29392,13 @@
         <v>8</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C221" s="2">
         <v>25</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>11</v>
@@ -29407,10 +29407,10 @@
         <v>12</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="H221" s="3" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
     </row>
     <row r="222" spans="1:9" ht="43.2">
@@ -29418,13 +29418,13 @@
         <v>8</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C222" s="2">
         <v>26</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>11</v>
@@ -29433,10 +29433,10 @@
         <v>12</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="H222" s="3" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
     </row>
     <row r="223" spans="1:9" ht="100.8">
@@ -29444,13 +29444,13 @@
         <v>8</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C223" s="2">
         <v>27</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>11</v>
@@ -29459,10 +29459,10 @@
         <v>12</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="H223" s="3" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
     </row>
     <row r="224" spans="1:9" ht="43.2">
@@ -29470,13 +29470,13 @@
         <v>8</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C224" s="2">
         <v>28</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>11</v>
@@ -29485,10 +29485,10 @@
         <v>12</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H224" s="3" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="225" spans="1:8" ht="43.2">
@@ -29496,13 +29496,13 @@
         <v>8</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C225" s="2">
         <v>29</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>11</v>
@@ -29511,10 +29511,10 @@
         <v>12</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="H225" s="3" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
     </row>
     <row r="226" spans="1:8" ht="100.8">
@@ -29522,13 +29522,13 @@
         <v>8</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C226" s="2">
         <v>30</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>11</v>
@@ -29537,10 +29537,10 @@
         <v>12</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="H226" s="3" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
     </row>
     <row r="227" spans="1:8" ht="28.8">
@@ -29548,13 +29548,13 @@
         <v>8</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C227" s="2">
         <v>0</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>11</v>
@@ -29563,10 +29563,10 @@
         <v>12</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="H227" s="6" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="228" spans="1:8" ht="28.8">
@@ -29574,13 +29574,13 @@
         <v>8</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C228" s="2">
         <v>0</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>11</v>
@@ -29589,10 +29589,10 @@
         <v>12</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="229" spans="1:8" ht="43.2">
@@ -29600,13 +29600,13 @@
         <v>8</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C229" s="2">
         <v>1</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>11</v>
@@ -29615,10 +29615,10 @@
         <v>12</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H229" s="3" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="230" spans="1:8" ht="100.8">
@@ -29626,13 +29626,13 @@
         <v>8</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C230" s="2">
         <v>2</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>11</v>
@@ -29641,10 +29641,10 @@
         <v>12</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H230" s="3" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
     </row>
     <row r="231" spans="1:8" ht="43.2">
@@ -29652,13 +29652,13 @@
         <v>8</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C231" s="2">
         <v>3</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>11</v>
@@ -29667,10 +29667,10 @@
         <v>12</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="H231" s="3" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="232" spans="1:8">
@@ -29678,13 +29678,13 @@
         <v>8</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C232" s="2">
         <v>0</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>11</v>
@@ -29693,10 +29693,10 @@
         <v>12</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="H232" s="6" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="233" spans="1:8">
@@ -29704,13 +29704,13 @@
         <v>8</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C233" s="2">
         <v>0</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>11</v>
@@ -29719,10 +29719,10 @@
         <v>12</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="H233" s="6" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="234" spans="1:8" ht="28.8">
@@ -29730,13 +29730,13 @@
         <v>8</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C234" s="2">
         <v>1</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>11</v>
@@ -29745,10 +29745,10 @@
         <v>12</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="H234" s="6" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="235" spans="1:8">
@@ -29756,13 +29756,13 @@
         <v>8</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C235" s="2">
         <v>0</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>11</v>
@@ -29771,10 +29771,10 @@
         <v>12</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H235" s="6" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="236" spans="1:8" ht="28.8">
@@ -29782,13 +29782,13 @@
         <v>8</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C236" s="2">
         <v>1</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>11</v>
@@ -29797,10 +29797,10 @@
         <v>12</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="H236" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="237" spans="1:8">
@@ -29808,13 +29808,13 @@
         <v>8</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C237" s="2">
         <v>0</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>11</v>
@@ -29823,7 +29823,7 @@
         <v>12</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="H237" s="4" t="s">
         <v>23</v>
@@ -29834,13 +29834,13 @@
         <v>8</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C238" s="2">
         <v>1</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>11</v>
@@ -29849,10 +29849,10 @@
         <v>12</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="H238" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -29860,13 +29860,13 @@
         <v>8</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C239" s="2">
         <v>0</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>11</v>
@@ -29875,24 +29875,24 @@
         <v>12</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="H239" s="4" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="240" spans="1:8">
       <c r="A240" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="B240" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C240">
         <v>1</v>
       </c>
       <c r="D240" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="E240" t="s">
         <v>11</v>
@@ -29901,10 +29901,10 @@
         <v>12</v>
       </c>
       <c r="G240" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="H240" s="4" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
     </row>
     <row r="241" spans="1:8">

--- a/docassemble/PowerOfAttorneyHealthCare/data/sources/poa_hc_es.xlsx
+++ b/docassemble/PowerOfAttorneyHealthCare/data/sources/poa_hc_es.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnewsted\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{726B4E2B-DC62-4DF1-8113-8FB901BCE7A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{393F5A6D-BE77-4124-A610-C910AC23663C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-36045" yWindow="-3345" windowWidth="30840" windowHeight="16845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-35685" yWindow="-1230" windowWidth="28485" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1681" uniqueCount="798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1695" uniqueCount="804">
   <si>
     <t>interview</t>
   </si>
@@ -210,77 +210,6 @@
     <t>next steps</t>
   </si>
   <si>
-    <t>71059466a0b5aed9f67c6fd9b1367145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Your next steps
-</t>
-  </si>
-  <si>
-    <t>Tus próximos pasos</t>
-  </si>
-  <si>
-    <t>b40adbdd8b329fa42924ae6af24679fa</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>After you download your forms, you will need to sign the form in the front of a witness. The witness will also need to sign the form. You do not need to know who the witness will be to use this program.
-After the form is signed, you will want to give copies of the power of attorney to your agent as well as your health care providers. Your forms will include instructions with more information.
-To learn more, read ILAO's article about [**Power of Attorney for Health Care basics**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://www.illinoislegalaid.org/legal-information/setting-power-attorney-healthcare</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>). 
-If you would like to know more about planning for disability or end of life care, you can review ILAO and CDEL's guide to the [**Power of Planning**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${ preview.url_for() }</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">).
-</t>
-    </r>
-  </si>
-  <si>
     <t>about power of attorney</t>
   </si>
   <si>
@@ -21349,63 +21278,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Después de descargar tus formularios, tendrás que firmar el documento frente a un testigo. El testigo también tendrá que firmar el documento. No necesitas saber quién será el testigo para usar este programa.
-Después de que el formulario esté firmado, querrás entregar copias del poder notarial a tu agente, así como a tus proveedores de atención médica. Tus formularios incluirán instrucciones con más información.
-Para obtener más información, lee el artículo de ILAO sobre los [**Conceptos Básicos del Poder Notarial para el Cuidado de la Salud**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://es.illinoislegalaid.org/legal-information/setting-power-attorney-healthcare</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>).
-Si deseas saber más sobre la planificación en caso de discapacidad o el cuidado al final de la vida, puedes revisar la guía de ILAO y CDEL [**Empodérate de tu Futuro**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${ preview_es.url_for() }</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>).</t>
-    </r>
-  </si>
-  <si>
     <t>98dc4f5f71b807757f3e798f7c664c92</t>
   </si>
   <si>
@@ -22736,7 +22608,515 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Bienvenido(a) al Formulario Guiado de Poder Notarial para el Cuidado de la Salud de Illinois Legal Aid Online.
+      <t xml:space="preserve">**Instrucciones sobre la disposición de tus restos: (En inglés)** 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if self_remains_preference != "specific":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${self_remains_preference}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${self_specific_burial_preference}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% endif</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**Instrucciones sobre la disposición de los restos de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()} (En inglés)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if other_remains_preference != "specific":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${other_remains_preference}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${other_specific_burial_preference}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% endif</t>
+    </r>
+  </si>
+  <si>
+    <t>La **capacidad legal** significa que una persona puede entender lo que está firmando y lo que esto implica para su futuro.</t>
+  </si>
+  <si>
+    <t>758dbe9f10315dbb11909fb009a7a357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**Legal capacity** means a person is mentally able to understand what they are signing and understand what it means for their future.
+</t>
+  </si>
+  <si>
+    <t>2642cdc8eb6c26981a65117ec0ee636c</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if get_language() == 'en':
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:globe:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> English | [Español](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ interview_url(new_session=1, lang="es") }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:globe:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> [English](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ interview_url(new_session=1, lang="en") }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) | Español
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+Welcome to Illinois Legal Aid Online's **Power of Attorney for Health Care** Easy Form.
+This program helps you make documents that give someone you trust power of attorney to make decisions about your health care. This means they can make choices about your health care when you cannot. You can also let them make choices about your health care earlier, if you choose.
+This program has videos with information about making a Power of Attorney for Health Care. You do not have to watch them, but you may find them helpful.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if user_path == "Shirley":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[YOUTUBE 7qy101TRdiI]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif user_path == "Frederico" or user_path == "Federico":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[YOUTUBE GR9t6ygX13g]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif user_path == "Lisa":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[YOUTUBE h2ZGl568xHo]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+To learn more, read ILAO's article about [**Power of Attorney for Health Care basics**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://www.illinoislegalaid.org/legal-information/setting-power-attorney-healthcare</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">).
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if get_language() == 'en':
+:globe: English | [Español](${ interview_url(new_session=1, lang="es") })
+% else:
+:globe: [English](${ interview_url(new_session=1, lang="en") }) | Español
+% endif
+Bienvenido(a) al Formulario Guiado de Poder Notarial para el Cuidado de la Salud de Illinois Legal Aid Online.
 Este programa te ayuda a crear documentos que le otorgan a una persona de tu confianza la autoridad legal para tomar decisiones sobre tu atención médica. Esto significa que esa persona podrá tomar decisiones sobre tu atención médica cuando no puedas hacerlo por ti mismo(a). Si así lo deseas, también puedes autorizarla para que tome decisiones sobre tu atención médica antesde que eso ocurra.
 Este programa incluye videos con información sobre cómo hacer un Poder Notarial para el Cuidado de la Salud. No tienes que verlos, pero pueden serte útiles.
 </t>
@@ -22787,145 +23167,44 @@
     </r>
   </si>
   <si>
-    <t>80b04da1b3097b769fbc55dc4f8a6d71</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Welcome to Illinois Legal Aid Online's **Power of Attorney for Health Care** Easy Form.
-This program helps you make documents that give someone you trust power of attorney to make decisions about your health care. This means they can make choices about your health care when you cannot. You can also let them make choices about your health care earlier, if you choose.
-This program has videos with information about making a Power of Attorney for Health Care. You do not have to watch them, but you may find them helpful.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if user_path == "Shirley":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[YOUTUBE 7qy101TRdiI]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif user_path == "Frederico" or user_path == "Federico":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[YOUTUBE GR9t6ygX13g]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif user_path == "Lisa":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[YOUTUBE h2ZGl568xHo]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
+    <t>0f7bfeab41a01c4696b50fcc79df32b5</t>
+  </si>
+  <si>
+    <t>Yes, I'm making a Power of Attorney for myself.</t>
+  </si>
+  <si>
+    <t>1bd6a89bcf3dbd5aceaaecb5a9682aca</t>
+  </si>
+  <si>
+    <t>No, I'm helping someone else make a Power of Attorney.</t>
+  </si>
+  <si>
+    <t>Sí, estoy haciendo este poder notarial para mí.</t>
+  </si>
+  <si>
+    <t>No, estoy ayudando a otra persona a hacer un poder notarial.</t>
+  </si>
+  <si>
+    <t>c6c95b6872cd48179fbead7dc5307882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After you download your form
+</t>
+  </si>
+  <si>
+    <t>9a614ef02faf556de8a0996528bc349f</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Once you download and print your form, you will need to sign it in front of a witness. The witness will also need to sign the form. You do not need to know who the witness will be to use this program.
+After the form is signed, you will want to give copies of the power of attorney to your agent as well as your health care providers. Your forms will include instructions with more information.
 To learn more, read ILAO's article about </t>
     </r>
     <r>
@@ -22967,224 +23246,111 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t xml:space="preserve">). 
+If you would like to know more about planning for disability or end of life care, you can review ILAO and CDEL's guide to the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[**Power of Planning**]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ preview.url_for() }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">).
 </t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**Instrucciones sobre la disposición de tus restos: (En inglés)** 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if self_remains_preference != "specific":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${self_remains_preference}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${self_specific_burial_preference}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**Instrucciones sobre la disposición de los restos de </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()} (En inglés)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if other_remains_preference != "specific":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${other_remains_preference}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${other_specific_burial_preference}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
-    </r>
-  </si>
-  <si>
-    <t>La **capacidad legal** significa que una persona puede entender lo que está firmando y lo que esto implica para su futuro.</t>
-  </si>
-  <si>
-    <t>758dbe9f10315dbb11909fb009a7a357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**Legal capacity** means a person is mentally able to understand what they are signing and understand what it means for their future.
-</t>
+    <t>Después de descargar tu formulario</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Una vez que descargues e imprimas tu formulario, tendrás que firmarlo ante un testigo. El testigo también tendrá que firmar el documento. No necesitas saber quién será el testigo para usar este programa.
+Después de que el formulario esté firmado, querrás entregar copias del poder notarial a tu agente, así como a tus proveedores de atención médica. Tus formularios incluirán instrucciones con más información.
+Para obtener más información, lee el artículo de ILAO sobre los [**Conceptos Básicos del Poder Notarial para el Cuidado de la Salud**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://es.illinoislegalaid.org/legal-information/setting-power-attorney-healthcare</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).
+Si deseas saber más sobre la planificación en caso de discapacidad o el cuidado al final de la vida, puedes revisar la guía de ILAO y CDEL [**Empodérate de tu Futuro**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ preview_es.url_for() }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -23310,7 +23476,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -23335,12 +23501,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -23655,7 +23815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I242"/>
+  <dimension ref="A1:I244"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="61.109375" customWidth="1"/>
@@ -23718,7 +23878,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="316.8">
+    <row r="3" spans="1:8" ht="403.2">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -23729,7 +23889,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>11</v>
@@ -23738,10 +23898,10 @@
         <v>12</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -23793,7 +23953,7 @@
         <v>20</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -23897,7 +24057,7 @@
         <v>31</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="28.8">
@@ -23911,7 +24071,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>11</v>
@@ -23920,7 +24080,7 @@
         <v>12</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>33</v>
@@ -23937,7 +24097,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>11</v>
@@ -23946,7 +24106,7 @@
         <v>12</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>34</v>
@@ -23963,7 +24123,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>36</v>
+        <v>798</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>11</v>
@@ -23972,10 +24132,10 @@
         <v>12</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>37</v>
+        <v>799</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>38</v>
+        <v>802</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="216">
@@ -23989,7 +24149,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>39</v>
+        <v>800</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>11</v>
@@ -23997,11 +24157,11 @@
       <c r="F13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>40</v>
+      <c r="G13" s="3" t="s">
+        <v>801</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>783</v>
+        <v>803</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="28.8">
@@ -24009,13 +24169,13 @@
         <v>8</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C14" s="2">
         <v>0</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>11</v>
@@ -24024,10 +24184,10 @@
         <v>12</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="331.2">
@@ -24035,13 +24195,13 @@
         <v>8</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C15" s="2">
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>11</v>
@@ -24050,10 +24210,10 @@
         <v>12</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="28.8">
@@ -24061,13 +24221,13 @@
         <v>8</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C16" s="2">
         <v>0</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>11</v>
@@ -24076,10 +24236,10 @@
         <v>12</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="273.60000000000002">
@@ -24087,13 +24247,13 @@
         <v>8</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C17" s="2">
         <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>11</v>
@@ -24102,24 +24262,24 @@
         <v>12</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="115.2">
       <c r="A18" s="2" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="C18" s="2">
         <v>0</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>11</v>
@@ -24128,24 +24288,24 @@
         <v>12</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="28.8">
       <c r="A19" s="2" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>11</v>
@@ -24154,10 +24314,10 @@
         <v>12</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="187.2">
@@ -24165,13 +24325,13 @@
         <v>8</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C20" s="2">
         <v>0</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>11</v>
@@ -24180,10 +24340,10 @@
         <v>12</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -24191,13 +24351,13 @@
         <v>8</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C21" s="2">
         <v>0</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>11</v>
@@ -24206,10 +24366,10 @@
         <v>12</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="43.2">
@@ -24217,13 +24377,13 @@
         <v>8</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C22" s="2">
         <v>1</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>11</v>
@@ -24232,10 +24392,10 @@
         <v>12</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="57.6">
@@ -24243,13 +24403,13 @@
         <v>8</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C23" s="2">
         <v>2</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>11</v>
@@ -24258,10 +24418,10 @@
         <v>12</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="28.8">
@@ -24269,13 +24429,13 @@
         <v>8</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C24" s="2">
         <v>3</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>11</v>
@@ -24284,10 +24444,10 @@
         <v>12</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="57.6">
@@ -24295,13 +24455,13 @@
         <v>8</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C25" s="2">
         <v>4</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>11</v>
@@ -24310,24 +24470,24 @@
         <v>12</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="28.8">
+    <row r="26" spans="1:8">
       <c r="A26" s="2" t="s">
-        <v>8</v>
+        <v>755</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="C26" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>71</v>
+        <v>792</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>11</v>
@@ -24336,24 +24496,24 @@
         <v>12</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>72</v>
+        <v>793</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>597</v>
+        <v>796</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="244.8">
+    <row r="27" spans="1:8">
       <c r="A27" s="2" t="s">
-        <v>8</v>
+        <v>755</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="C27" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>73</v>
+        <v>794</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>11</v>
@@ -24362,24 +24522,24 @@
         <v>12</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>74</v>
+        <v>795</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>598</v>
+        <v>797</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="86.4">
+    <row r="28" spans="1:8" ht="28.8">
       <c r="A28" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C28" s="2">
         <v>0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>11</v>
@@ -24388,24 +24548,24 @@
         <v>12</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>599</v>
+        <v>67</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>592</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="409.6">
+    <row r="29" spans="1:8" ht="244.8">
       <c r="A29" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C29" s="2">
         <v>1</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>777</v>
+        <v>68</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>11</v>
@@ -24414,24 +24574,24 @@
         <v>12</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>778</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>779</v>
+        <v>69</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>593</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" ht="86.4">
       <c r="A30" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C30" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>11</v>
@@ -24440,24 +24600,24 @@
         <v>12</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>600</v>
+        <v>72</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>594</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" ht="409.6">
       <c r="A31" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C31" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>80</v>
+        <v>772</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>11</v>
@@ -24466,10 +24626,10 @@
         <v>12</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>601</v>
+        <v>773</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>774</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -24477,13 +24637,13 @@
         <v>8</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C32" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>11</v>
@@ -24492,10 +24652,10 @@
         <v>12</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -24503,13 +24663,13 @@
         <v>8</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" s="2">
+        <v>3</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="C33" s="2">
-        <v>5</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>11</v>
@@ -24518,10 +24678,10 @@
         <v>12</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>774</v>
+        <v>76</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -24529,13 +24689,13 @@
         <v>8</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C34" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>11</v>
@@ -24544,10 +24704,10 @@
         <v>12</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>88</v>
+        <v>78</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -24555,13 +24715,13 @@
         <v>8</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C35" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>11</v>
@@ -24570,24 +24730,24 @@
         <v>12</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>603</v>
+        <v>80</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>769</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="100.8">
+    <row r="36" spans="1:8">
       <c r="A36" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="C36" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>11</v>
@@ -24596,24 +24756,24 @@
         <v>12</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>604</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="28.8">
+    <row r="37" spans="1:8">
       <c r="A37" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="C37" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>11</v>
@@ -24622,24 +24782,24 @@
         <v>12</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="86.4">
+    <row r="38" spans="1:8" ht="100.8">
       <c r="A38" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C38" s="2">
         <v>0</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>11</v>
@@ -24648,10 +24808,10 @@
         <v>12</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>606</v>
+        <v>88</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="28.8">
@@ -24659,13 +24819,13 @@
         <v>8</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="C39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>11</v>
@@ -24674,24 +24834,24 @@
         <v>12</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="144">
+    <row r="40" spans="1:8" ht="86.4">
       <c r="A40" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>11</v>
@@ -24700,24 +24860,24 @@
         <v>12</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="86.4">
+    <row r="41" spans="1:8" ht="28.8">
       <c r="A41" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C41" s="2">
         <v>0</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>11</v>
@@ -24726,24 +24886,24 @@
         <v>12</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>107</v>
+        <v>96</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>602</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="86.4">
+    <row r="42" spans="1:8" ht="144">
       <c r="A42" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="C42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>11</v>
@@ -24752,24 +24912,24 @@
         <v>12</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="374.4">
+    <row r="43" spans="1:8" ht="86.4">
       <c r="A43" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="C43" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>11</v>
@@ -24778,10 +24938,10 @@
         <v>12</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>610</v>
+        <v>102</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="86.4">
@@ -24789,13 +24949,13 @@
         <v>8</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="C44" s="2">
         <v>0</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>11</v>
@@ -24804,24 +24964,24 @@
         <v>12</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>611</v>
+        <v>105</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>604</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="28.8">
+    <row r="45" spans="1:8" ht="374.4">
       <c r="A45" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="C45" s="2">
         <v>1</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>11</v>
@@ -24830,24 +24990,24 @@
         <v>12</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H45" s="6" t="s">
-        <v>612</v>
+        <v>107</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>605</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="28.8">
+    <row r="46" spans="1:8" ht="86.4">
       <c r="A46" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="C46" s="2">
         <v>0</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>11</v>
@@ -24856,24 +25016,24 @@
         <v>12</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>714</v>
+        <v>110</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>606</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" ht="28.8">
       <c r="A47" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="C47" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>11</v>
@@ -24882,24 +25042,24 @@
         <v>12</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>613</v>
+        <v>112</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>607</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="43.2">
+    <row r="48" spans="1:8" ht="28.8">
       <c r="A48" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C48" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>11</v>
@@ -24908,10 +25068,10 @@
         <v>12</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="H48" t="s">
-        <v>614</v>
+        <v>115</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>709</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -24919,13 +25079,13 @@
         <v>8</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C49" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>11</v>
@@ -24934,24 +25094,24 @@
         <v>12</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="H49" s="6" t="s">
-        <v>615</v>
+        <v>117</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>608</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" ht="43.2">
       <c r="A50" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C50" s="2">
+        <v>3</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="C50" s="2">
-        <v>5</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>11</v>
@@ -24960,24 +25120,24 @@
         <v>12</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>616</v>
+        <v>119</v>
+      </c>
+      <c r="H50" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="129.6">
+    <row r="51" spans="1:8">
       <c r="A51" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="C51" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>11</v>
@@ -24986,24 +25146,24 @@
         <v>12</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>753</v>
+        <v>121</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>610</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="28.8">
+    <row r="52" spans="1:8">
       <c r="A52" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="C52" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>11</v>
@@ -25012,24 +25172,24 @@
         <v>12</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>744</v>
+        <v>611</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="28.8">
+    <row r="53" spans="1:8" ht="129.6">
       <c r="A53" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C53" s="2">
         <v>0</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>11</v>
@@ -25038,24 +25198,24 @@
         <v>12</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>137</v>
+        <v>748</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="100.8">
+    <row r="54" spans="1:8" ht="28.8">
       <c r="A54" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C54" s="2">
         <v>1</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>11</v>
@@ -25064,24 +25224,24 @@
         <v>12</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>617</v>
+        <v>128</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>739</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="100.8">
+    <row r="55" spans="1:8" ht="28.8">
       <c r="A55" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="C55" s="2">
         <v>0</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>11</v>
@@ -25090,24 +25250,24 @@
         <v>12</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>780</v>
+        <v>132</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="288">
+    <row r="56" spans="1:8" ht="100.8">
       <c r="A56" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="C56" s="2">
         <v>1</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>11</v>
@@ -25116,24 +25276,24 @@
         <v>12</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>715</v>
+        <v>612</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="28.8">
+    <row r="57" spans="1:8" ht="100.8">
       <c r="A57" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C57" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>11</v>
@@ -25142,24 +25302,24 @@
         <v>12</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="H57" s="6" t="s">
-        <v>618</v>
+        <v>137</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>775</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" ht="288">
       <c r="A58" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="C58" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>11</v>
@@ -25168,10 +25328,10 @@
         <v>12</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>151</v>
+        <v>139</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>710</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="28.8">
@@ -25179,13 +25339,13 @@
         <v>8</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C59" s="2">
         <v>1</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>11</v>
@@ -25194,24 +25354,24 @@
         <v>12</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="28.8">
+    <row r="60" spans="1:8">
       <c r="A60" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C60" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>11</v>
@@ -25220,24 +25380,24 @@
         <v>12</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>620</v>
+        <v>145</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>146</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="144">
+    <row r="61" spans="1:8" ht="28.8">
       <c r="A61" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C61" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>11</v>
@@ -25246,24 +25406,24 @@
         <v>12</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>621</v>
+        <v>148</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>614</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" ht="28.8">
       <c r="A62" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C62" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>11</v>
@@ -25272,24 +25432,24 @@
         <v>12</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="H62" s="5" t="s">
-        <v>160</v>
+        <v>150</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>615</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="28.8">
+    <row r="63" spans="1:8" ht="144">
       <c r="A63" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C63" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>11</v>
@@ -25298,10 +25458,10 @@
         <v>12</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H63" s="6" t="s">
-        <v>163</v>
+        <v>152</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -25309,13 +25469,13 @@
         <v>8</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C64" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>11</v>
@@ -25324,24 +25484,24 @@
         <v>12</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>622</v>
+        <v>154</v>
+      </c>
+      <c r="H64" s="5" t="s">
+        <v>155</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="43.2">
+    <row r="65" spans="1:8" ht="28.8">
       <c r="A65" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C65" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>11</v>
@@ -25350,24 +25510,24 @@
         <v>12</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>623</v>
+        <v>158</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="57.6">
+    <row r="66" spans="1:8">
       <c r="A66" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C66" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>11</v>
@@ -25376,24 +25536,24 @@
         <v>12</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" ht="43.2">
       <c r="A67" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C67" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>11</v>
@@ -25402,24 +25562,24 @@
         <v>12</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>172</v>
+        <v>618</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="28.8">
+    <row r="68" spans="1:8" ht="57.6">
       <c r="A68" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="C68" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>11</v>
@@ -25428,24 +25588,24 @@
         <v>12</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>625</v>
+        <v>164</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>619</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="172.8">
+    <row r="69" spans="1:8">
       <c r="A69" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="C69" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>11</v>
@@ -25454,10 +25614,10 @@
         <v>12</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>716</v>
+        <v>166</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="28.8">
@@ -25465,13 +25625,13 @@
         <v>8</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C70" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>11</v>
@@ -25480,24 +25640,24 @@
         <v>12</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H70" s="9" t="s">
-        <v>717</v>
+        <v>170</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>620</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" ht="172.8">
       <c r="A71" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C71" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>11</v>
@@ -25506,24 +25666,24 @@
         <v>12</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>626</v>
+        <v>711</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="43.2">
+    <row r="72" spans="1:8" ht="28.8">
       <c r="A72" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B72" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C72" s="2">
+        <v>2</v>
+      </c>
+      <c r="D72" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C72" s="2">
-        <v>4</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>11</v>
@@ -25532,24 +25692,24 @@
         <v>12</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>627</v>
+        <v>174</v>
+      </c>
+      <c r="H72" s="9" t="s">
+        <v>712</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="57.6">
+    <row r="73" spans="1:8">
       <c r="A73" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C73" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>11</v>
@@ -25558,24 +25718,24 @@
         <v>12</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="H73" s="6" t="s">
-        <v>719</v>
+        <v>176</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>621</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" ht="43.2">
       <c r="A74" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C74" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>11</v>
@@ -25584,24 +25744,24 @@
         <v>12</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="28.8">
+    <row r="75" spans="1:8" ht="57.6">
       <c r="A75" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="C75" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>11</v>
@@ -25610,24 +25770,24 @@
         <v>12</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>191</v>
+        <v>714</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="144">
+    <row r="76" spans="1:8">
       <c r="A76" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="C76" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>11</v>
@@ -25636,24 +25796,24 @@
         <v>12</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>718</v>
+        <v>623</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="115.2">
+    <row r="77" spans="1:8" ht="28.8">
       <c r="A77" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="C77" s="2">
         <v>0</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>11</v>
@@ -25662,24 +25822,24 @@
         <v>12</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>630</v>
+        <v>185</v>
+      </c>
+      <c r="H77" s="6" t="s">
+        <v>186</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="360">
+    <row r="78" spans="1:8" ht="144">
       <c r="A78" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>11</v>
@@ -25688,24 +25848,24 @@
         <v>12</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="28.8">
+    <row r="79" spans="1:8" ht="115.2">
       <c r="A79" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C79" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>11</v>
@@ -25714,24 +25874,24 @@
         <v>12</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="H79" s="6" t="s">
-        <v>631</v>
+        <v>191</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>625</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="28.8">
+    <row r="80" spans="1:8" ht="360">
       <c r="A80" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="C80" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>11</v>
@@ -25740,24 +25900,24 @@
         <v>12</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>775</v>
+        <v>193</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>632</v>
+        <v>715</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="72">
+    <row r="81" spans="1:8" ht="28.8">
       <c r="A81" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C81" s="2">
         <v>1</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>11</v>
@@ -25766,24 +25926,24 @@
         <v>12</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>633</v>
+        <v>196</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>626</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="72">
+    <row r="82" spans="1:8" ht="28.8">
       <c r="A82" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C82" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>11</v>
@@ -25792,24 +25952,24 @@
         <v>12</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>207</v>
+        <v>770</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>721</v>
+        <v>627</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" ht="72">
       <c r="A83" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C83" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>11</v>
@@ -25818,24 +25978,24 @@
         <v>12</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="H83" s="6" t="s">
-        <v>210</v>
+        <v>200</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>628</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="43.2">
+    <row r="84" spans="1:8" ht="72">
       <c r="A84" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C84" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>11</v>
@@ -25844,10 +26004,10 @@
         <v>12</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>634</v>
+        <v>716</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -25855,13 +26015,13 @@
         <v>8</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C85" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>11</v>
@@ -25870,24 +26030,24 @@
         <v>12</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>635</v>
+        <v>205</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" ht="43.2">
       <c r="A86" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C86" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>11</v>
@@ -25896,24 +26056,24 @@
         <v>12</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>217</v>
+        <v>207</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>629</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="172.8">
+    <row r="87" spans="1:8">
       <c r="A87" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="C87" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>11</v>
@@ -25922,24 +26082,24 @@
         <v>12</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>722</v>
+        <v>630</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="43.2">
+    <row r="88" spans="1:8">
       <c r="A88" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="C88" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>11</v>
@@ -25948,24 +26108,24 @@
         <v>12</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>636</v>
+        <v>212</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="43.2">
+    <row r="89" spans="1:8" ht="172.8">
       <c r="A89" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C89" s="2">
         <v>0</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>11</v>
@@ -25974,24 +26134,24 @@
         <v>12</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>637</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>723</v>
+        <v>215</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>717</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="72">
+    <row r="90" spans="1:8" ht="43.2">
       <c r="A90" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C90" s="2">
         <v>1</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>11</v>
@@ -26000,24 +26160,24 @@
         <v>12</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>638</v>
+        <v>217</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>631</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="72">
+    <row r="91" spans="1:8" ht="43.2">
       <c r="A91" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C91" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>11</v>
@@ -26026,24 +26186,24 @@
         <v>12</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>228</v>
+        <v>632</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" ht="72">
       <c r="A92" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C92" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>11</v>
@@ -26052,24 +26212,24 @@
         <v>12</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>231</v>
+        <v>221</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>633</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="57.6">
+    <row r="93" spans="1:8" ht="72">
       <c r="A93" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C93" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>11</v>
@@ -26078,10 +26238,10 @@
         <v>12</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>639</v>
+        <v>719</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -26089,13 +26249,13 @@
         <v>8</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C94" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>11</v>
@@ -26104,24 +26264,24 @@
         <v>12</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>640</v>
+        <v>226</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" ht="57.6">
       <c r="A95" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C95" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>11</v>
@@ -26130,24 +26290,24 @@
         <v>12</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="H95" s="6" t="s">
-        <v>641</v>
+        <v>228</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>634</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="201.6">
+    <row r="96" spans="1:8">
       <c r="A96" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="C96" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>11</v>
@@ -26156,24 +26316,24 @@
         <v>12</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>642</v>
+        <v>230</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>635</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="28.8">
+    <row r="97" spans="1:8">
       <c r="A97" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="C97" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>11</v>
@@ -26182,24 +26342,24 @@
         <v>12</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>725</v>
+        <v>636</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="129.6">
+    <row r="98" spans="1:8" ht="201.6">
       <c r="A98" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C98" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>11</v>
@@ -26208,24 +26368,24 @@
         <v>12</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>781</v>
+        <v>637</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="86.4">
+    <row r="99" spans="1:8" ht="28.8">
       <c r="A99" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C99" s="2">
         <v>0</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>11</v>
@@ -26234,24 +26394,24 @@
         <v>12</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>643</v>
+        <v>238</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>720</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="302.39999999999998">
+    <row r="100" spans="1:8" ht="129.6">
       <c r="A100" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C100" s="2">
         <v>1</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>11</v>
@@ -26260,24 +26420,24 @@
         <v>12</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>745</v>
+        <v>776</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="28.8">
+    <row r="101" spans="1:8" ht="86.4">
       <c r="A101" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C101" s="2">
         <v>0</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>11</v>
@@ -26286,24 +26446,24 @@
         <v>12</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="86.4">
+    <row r="102" spans="1:8" ht="302.39999999999998">
       <c r="A102" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C102" s="2">
         <v>1</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>11</v>
@@ -26312,24 +26472,24 @@
         <v>12</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>645</v>
+        <v>740</v>
       </c>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:8" ht="28.8">
       <c r="A103" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C103" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>11</v>
@@ -26338,24 +26498,24 @@
         <v>12</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="H103" s="6" t="s">
-        <v>258</v>
+        <v>248</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>639</v>
       </c>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:8" ht="86.4">
       <c r="A104" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C104" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>11</v>
@@ -26364,10 +26524,10 @@
         <v>12</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>646</v>
+        <v>250</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>640</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -26375,13 +26535,13 @@
         <v>8</v>
       </c>
       <c r="B105" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C105" s="2">
+        <v>2</v>
+      </c>
+      <c r="D105" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="C105" s="2">
-        <v>4</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>261</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>11</v>
@@ -26390,10 +26550,10 @@
         <v>12</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -26401,13 +26561,13 @@
         <v>8</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C106" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>11</v>
@@ -26416,10 +26576,10 @@
         <v>12</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>661</v>
+        <v>641</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -26427,13 +26587,13 @@
         <v>8</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C107" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>11</v>
@@ -26442,10 +26602,10 @@
         <v>12</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -26453,13 +26613,13 @@
         <v>8</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C108" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>11</v>
@@ -26468,10 +26628,10 @@
         <v>12</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>271</v>
+        <v>656</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -26479,13 +26639,13 @@
         <v>8</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C109" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>11</v>
@@ -26494,24 +26654,24 @@
         <v>12</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>647</v>
+        <v>263</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="43.2">
+    <row r="110" spans="1:8">
       <c r="A110" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>274</v>
+        <v>246</v>
       </c>
       <c r="C110" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>11</v>
@@ -26520,24 +26680,24 @@
         <v>12</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="H110" s="3" t="s">
-        <v>648</v>
+        <v>265</v>
+      </c>
+      <c r="H110" s="6" t="s">
+        <v>266</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="86.4">
+    <row r="111" spans="1:8">
       <c r="A111" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>274</v>
+        <v>246</v>
       </c>
       <c r="C111" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>11</v>
@@ -26545,25 +26705,25 @@
       <c r="F111" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G111" s="8" t="s">
-        <v>739</v>
-      </c>
-      <c r="H111" s="3" t="s">
-        <v>649</v>
+      <c r="G111" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="H111" s="6" t="s">
+        <v>642</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:8" ht="43.2">
       <c r="A112" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C112" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>11</v>
@@ -26572,24 +26732,24 @@
         <v>12</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="H112" t="s">
-        <v>650</v>
+        <v>271</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>643</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" ht="86.4">
       <c r="A113" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C113" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>11</v>
@@ -26597,11 +26757,11 @@
       <c r="F113" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G113" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="H113" t="s">
-        <v>651</v>
+      <c r="G113" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -26609,13 +26769,13 @@
         <v>8</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C114" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>11</v>
@@ -26624,10 +26784,10 @@
         <v>12</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="H114" t="s">
-        <v>662</v>
+        <v>645</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -26635,13 +26795,13 @@
         <v>8</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C115" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>11</v>
@@ -26650,24 +26810,24 @@
         <v>12</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="H115" s="6" t="s">
-        <v>652</v>
+        <v>276</v>
+      </c>
+      <c r="H115" t="s">
+        <v>646</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="43.2">
+    <row r="116" spans="1:8">
       <c r="A116" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C116" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>11</v>
@@ -26676,24 +26836,24 @@
         <v>12</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>653</v>
+        <v>278</v>
+      </c>
+      <c r="H116" t="s">
+        <v>657</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="28.8">
+    <row r="117" spans="1:8">
       <c r="A117" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="C117" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>11</v>
@@ -26702,24 +26862,24 @@
         <v>12</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="H117" s="6" t="s">
-        <v>291</v>
+        <v>647</v>
       </c>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:8" ht="43.2">
       <c r="A118" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="C118" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>11</v>
@@ -26728,24 +26888,24 @@
         <v>12</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>293</v>
+        <v>648</v>
       </c>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" ht="28.8">
       <c r="A119" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="C119" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>11</v>
@@ -26754,24 +26914,24 @@
         <v>12</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="H119" s="6" t="s">
-        <v>654</v>
+        <v>286</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="28.8">
+    <row r="120" spans="1:8">
       <c r="A120" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="C120" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>11</v>
@@ -26780,10 +26940,10 @@
         <v>12</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="H120" s="3" t="s">
-        <v>655</v>
+        <v>288</v>
+      </c>
+      <c r="H120" s="6" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -26791,13 +26951,13 @@
         <v>8</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="C121" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>11</v>
@@ -26806,24 +26966,24 @@
         <v>12</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="H121" t="s">
-        <v>656</v>
+        <v>290</v>
+      </c>
+      <c r="H121" s="6" t="s">
+        <v>649</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="86.4">
+    <row r="122" spans="1:8" ht="28.8">
       <c r="A122" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="C122" s="2">
         <v>0</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>11</v>
@@ -26832,24 +26992,24 @@
         <v>12</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="28.8">
+    <row r="123" spans="1:8">
       <c r="A123" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="C123" s="2">
         <v>1</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>11</v>
@@ -26858,24 +27018,24 @@
         <v>12</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="H123" s="6" t="s">
-        <v>658</v>
+        <v>295</v>
+      </c>
+      <c r="H123" t="s">
+        <v>651</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="28.8">
+    <row r="124" spans="1:8" ht="86.4">
       <c r="A124" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C124" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>11</v>
@@ -26884,10 +27044,10 @@
         <v>12</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="H124" s="8" t="s">
-        <v>727</v>
+        <v>298</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>652</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="28.8">
@@ -26895,13 +27055,13 @@
         <v>8</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C125" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>11</v>
@@ -26910,10 +27070,10 @@
         <v>12</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="H125" s="8" t="s">
-        <v>740</v>
+        <v>300</v>
+      </c>
+      <c r="H125" s="6" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="28.8">
@@ -26921,13 +27081,13 @@
         <v>8</v>
       </c>
       <c r="B126" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C126" s="2">
+        <v>2</v>
+      </c>
+      <c r="D126" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="C126" s="2">
-        <v>4</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>310</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>11</v>
@@ -26936,24 +27096,24 @@
         <v>12</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="H126" s="8" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:8" ht="28.8">
       <c r="A127" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C127" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>11</v>
@@ -26962,24 +27122,24 @@
         <v>12</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="H127" s="8" t="s">
-        <v>663</v>
+        <v>735</v>
       </c>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:8" ht="28.8">
       <c r="A128" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C128" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>11</v>
@@ -26988,10 +27148,10 @@
         <v>12</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>316</v>
+        <v>306</v>
+      </c>
+      <c r="H128" s="8" t="s">
+        <v>723</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -26999,13 +27159,13 @@
         <v>8</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C129" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>11</v>
@@ -27014,10 +27174,10 @@
         <v>12</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="H129" s="3" t="s">
-        <v>726</v>
+        <v>308</v>
+      </c>
+      <c r="H129" s="8" t="s">
+        <v>658</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -27025,13 +27185,13 @@
         <v>8</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C130" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>11</v>
@@ -27040,24 +27200,24 @@
         <v>12</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="H130" s="3" t="s">
-        <v>659</v>
+        <v>310</v>
+      </c>
+      <c r="H130" s="6" t="s">
+        <v>311</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="28.8">
+    <row r="131" spans="1:8">
       <c r="A131" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="C131" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>11</v>
@@ -27066,24 +27226,24 @@
         <v>12</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="H131" s="6" t="s">
-        <v>660</v>
+        <v>313</v>
+      </c>
+      <c r="H131" s="3" t="s">
+        <v>721</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="403.2">
+    <row r="132" spans="1:8">
       <c r="A132" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="C132" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>11</v>
@@ -27092,24 +27252,24 @@
         <v>12</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>754</v>
+        <v>654</v>
       </c>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:8" ht="28.8">
       <c r="A133" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="C133" s="2">
         <v>0</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>11</v>
@@ -27118,50 +27278,50 @@
         <v>12</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="H133" s="6" t="s">
-        <v>664</v>
+        <v>655</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="43.2">
+    <row r="134" spans="1:8" ht="403.2">
       <c r="A134" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="C134" s="10">
+        <v>316</v>
+      </c>
+      <c r="C134" s="2">
         <v>1</v>
       </c>
-      <c r="D134" s="10" t="s">
-        <v>796</v>
-      </c>
-      <c r="E134" s="10" t="s">
+      <c r="D134" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E134" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F134" s="10" t="s">
+      <c r="F134" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G134" s="11" t="s">
-        <v>797</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>795</v>
+      <c r="G134" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="H134" s="3" t="s">
+        <v>749</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="100.8">
+    <row r="135" spans="1:8">
       <c r="A135" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="C135" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>750</v>
+        <v>322</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>11</v>
@@ -27170,24 +27330,24 @@
         <v>12</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="H135" s="3" t="s">
-        <v>729</v>
+        <v>323</v>
+      </c>
+      <c r="H135" s="6" t="s">
+        <v>659</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="115.2">
+    <row r="136" spans="1:8" ht="43.2">
       <c r="A136" s="2" t="s">
-        <v>760</v>
+        <v>8</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>770</v>
+        <v>321</v>
       </c>
       <c r="C136" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>771</v>
+        <v>787</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>11</v>
@@ -27196,24 +27356,24 @@
         <v>12</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="H136" s="3" t="s">
-        <v>773</v>
+        <v>788</v>
+      </c>
+      <c r="H136" s="6" t="s">
+        <v>786</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="409.6">
+    <row r="137" spans="1:8" ht="100.8">
       <c r="A137" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="C137" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>329</v>
+        <v>745</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>11</v>
@@ -27222,24 +27382,24 @@
         <v>12</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>330</v>
+        <v>746</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>782</v>
+        <v>724</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="28.8">
+    <row r="138" spans="1:8" ht="115.2">
       <c r="A138" s="2" t="s">
-        <v>8</v>
+        <v>755</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>331</v>
+        <v>765</v>
       </c>
       <c r="C138" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>332</v>
+        <v>766</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>11</v>
@@ -27248,24 +27408,24 @@
         <v>12</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>665</v>
+        <v>767</v>
+      </c>
+      <c r="H138" s="3" t="s">
+        <v>768</v>
       </c>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" spans="1:8" ht="409.6">
       <c r="A139" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="C139" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>11</v>
@@ -27274,24 +27434,24 @@
         <v>12</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="H139" s="6" t="s">
-        <v>666</v>
+        <v>325</v>
+      </c>
+      <c r="H139" s="3" t="s">
+        <v>777</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="57.6">
+    <row r="140" spans="1:8" ht="28.8">
       <c r="A140" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="C140" s="2">
         <v>1</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>11</v>
@@ -27300,10 +27460,10 @@
         <v>12</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -27311,13 +27471,13 @@
         <v>8</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="C141" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>11</v>
@@ -27326,24 +27486,24 @@
         <v>12</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="H141" s="6" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="43.2">
+    <row r="142" spans="1:8" ht="57.6">
       <c r="A142" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="C142" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>11</v>
@@ -27352,24 +27512,24 @@
         <v>12</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="86.4">
+    <row r="143" spans="1:8">
       <c r="A143" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B143" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C143" s="2">
+        <v>2</v>
+      </c>
+      <c r="D143" s="2" t="s">
         <v>334</v>
-      </c>
-      <c r="C143" s="2">
-        <v>4</v>
-      </c>
-      <c r="D143" s="2" t="s">
-        <v>343</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>11</v>
@@ -27378,24 +27538,24 @@
         <v>12</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="H143" s="3" t="s">
-        <v>670</v>
+        <v>335</v>
+      </c>
+      <c r="H143" s="6" t="s">
+        <v>663</v>
       </c>
     </row>
-    <row r="144" spans="1:8" ht="216">
+    <row r="144" spans="1:8" ht="43.2">
       <c r="A144" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="C144" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>11</v>
@@ -27404,10 +27564,10 @@
         <v>12</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="H144" s="3" t="s">
-        <v>671</v>
+        <v>337</v>
+      </c>
+      <c r="H144" s="6" t="s">
+        <v>664</v>
       </c>
     </row>
     <row r="145" spans="1:8" ht="86.4">
@@ -27415,13 +27575,13 @@
         <v>8</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="C145" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>11</v>
@@ -27430,24 +27590,24 @@
         <v>12</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>350</v>
+        <v>665</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="86.4">
+    <row r="146" spans="1:8" ht="216">
       <c r="A146" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="C146" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>11</v>
@@ -27456,24 +27616,24 @@
         <v>12</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>776</v>
+        <v>666</v>
       </c>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:8" ht="86.4">
       <c r="A147" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C147" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>11</v>
@@ -27482,10 +27642,10 @@
         <v>12</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="H147" s="6" t="s">
-        <v>355</v>
+        <v>344</v>
+      </c>
+      <c r="H147" s="3" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="148" spans="1:8" ht="86.4">
@@ -27493,13 +27653,13 @@
         <v>8</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="C148" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>11</v>
@@ -27508,24 +27668,24 @@
         <v>12</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>672</v>
+        <v>771</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="28.8">
+    <row r="149" spans="1:8">
       <c r="A149" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="C149" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>11</v>
@@ -27534,24 +27694,24 @@
         <v>12</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="H149" s="3" t="s">
-        <v>673</v>
+        <v>349</v>
+      </c>
+      <c r="H149" s="6" t="s">
+        <v>350</v>
       </c>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" spans="1:8" ht="86.4">
       <c r="A150" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="C150" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>11</v>
@@ -27560,24 +27720,24 @@
         <v>12</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="129.6">
+    <row r="151" spans="1:8" ht="28.8">
       <c r="A151" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="C151" s="2">
         <v>0</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>11</v>
@@ -27586,24 +27746,24 @@
         <v>12</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>755</v>
+        <v>668</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="28.8">
+    <row r="152" spans="1:8">
       <c r="A152" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="C152" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>11</v>
@@ -27612,24 +27772,24 @@
         <v>12</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="H152" s="6" t="s">
-        <v>369</v>
+        <v>358</v>
+      </c>
+      <c r="H152" s="3" t="s">
+        <v>669</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="28.8">
+    <row r="153" spans="1:8" ht="129.6">
       <c r="A153" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="C153" s="2">
         <v>0</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>11</v>
@@ -27638,24 +27798,24 @@
         <v>12</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="H153" s="3" t="s">
-        <v>373</v>
+        <v>750</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="115.2">
+    <row r="154" spans="1:8" ht="28.8">
       <c r="A154" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="C154" s="2">
         <v>1</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>11</v>
@@ -27664,10 +27824,10 @@
         <v>12</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="H154" s="3" t="s">
-        <v>675</v>
+        <v>363</v>
+      </c>
+      <c r="H154" s="6" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="155" spans="1:8" ht="28.8">
@@ -27675,13 +27835,13 @@
         <v>8</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="C155" s="2">
         <v>0</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>11</v>
@@ -27690,24 +27850,24 @@
         <v>12</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="H155" s="6" t="s">
-        <v>676</v>
+        <v>367</v>
+      </c>
+      <c r="H155" s="3" t="s">
+        <v>368</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="409.6">
+    <row r="156" spans="1:8" ht="115.2">
       <c r="A156" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="C156" s="2">
         <v>1</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>11</v>
@@ -27716,24 +27876,24 @@
         <v>12</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>730</v>
+        <v>670</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="43.2">
+    <row r="157" spans="1:8" ht="28.8">
       <c r="A157" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="C157" s="2">
         <v>0</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>11</v>
@@ -27742,24 +27902,24 @@
         <v>12</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="H157" s="6" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="86.4">
+    <row r="158" spans="1:8" ht="409.6">
       <c r="A158" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="C158" s="2">
         <v>1</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>11</v>
@@ -27768,24 +27928,24 @@
         <v>12</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>386</v>
+        <v>725</v>
       </c>
     </row>
-    <row r="159" spans="1:8" ht="28.8">
+    <row r="159" spans="1:8" ht="43.2">
       <c r="A159" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="C159" s="2">
         <v>0</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>11</v>
@@ -27794,24 +27954,24 @@
         <v>12</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="H159" s="6" t="s">
-        <v>390</v>
+        <v>672</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="144">
+    <row r="160" spans="1:8" ht="86.4">
       <c r="A160" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="C160" s="2">
         <v>1</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>11</v>
@@ -27820,24 +27980,24 @@
         <v>12</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="H160" s="6" t="s">
-        <v>731</v>
+        <v>380</v>
+      </c>
+      <c r="H160" s="3" t="s">
+        <v>381</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="100.8">
+    <row r="161" spans="1:8" ht="28.8">
       <c r="A161" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="C161" s="2">
         <v>0</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>11</v>
@@ -27846,10 +28006,10 @@
         <v>12</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="H161" s="3" t="s">
-        <v>678</v>
+        <v>384</v>
+      </c>
+      <c r="H161" s="6" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="144">
@@ -27857,13 +28017,13 @@
         <v>8</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="C162" s="2">
         <v>1</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>11</v>
@@ -27872,10 +28032,10 @@
         <v>12</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="H162" s="3" t="s">
-        <v>732</v>
+        <v>387</v>
+      </c>
+      <c r="H162" s="6" t="s">
+        <v>726</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="100.8">
@@ -27883,13 +28043,13 @@
         <v>8</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="C163" s="2">
         <v>0</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>11</v>
@@ -27898,24 +28058,24 @@
         <v>12</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="43.2">
+    <row r="164" spans="1:8" ht="144">
       <c r="A164" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="C164" s="2">
         <v>1</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>11</v>
@@ -27924,24 +28084,24 @@
         <v>12</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="H164" s="6" t="s">
-        <v>680</v>
+        <v>392</v>
+      </c>
+      <c r="H164" s="3" t="s">
+        <v>727</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="115.2">
+    <row r="165" spans="1:8" ht="100.8">
       <c r="A165" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="C165" s="2">
         <v>0</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>11</v>
@@ -27950,24 +28110,24 @@
         <v>12</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="86.4">
+    <row r="166" spans="1:8" ht="43.2">
       <c r="A166" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="C166" s="2">
         <v>1</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>11</v>
@@ -27976,24 +28136,24 @@
         <v>12</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="H166" s="3" t="s">
-        <v>408</v>
+        <v>397</v>
+      </c>
+      <c r="H166" s="6" t="s">
+        <v>675</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="86.4">
+    <row r="167" spans="1:8" ht="115.2">
       <c r="A167" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="C167" s="2">
         <v>0</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>11</v>
@@ -28002,24 +28162,24 @@
         <v>12</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="H167" s="3" t="s">
-        <v>412</v>
+        <v>676</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="28.8">
+    <row r="168" spans="1:8" ht="86.4">
       <c r="A168" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="C168" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>11</v>
@@ -28028,24 +28188,24 @@
         <v>12</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>733</v>
+        <v>403</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="57.6">
+    <row r="169" spans="1:8" ht="86.4">
       <c r="A169" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="C169" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>11</v>
@@ -28054,24 +28214,24 @@
         <v>12</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="H169" s="3" t="s">
-        <v>418</v>
+        <v>407</v>
       </c>
     </row>
-    <row r="170" spans="1:8">
+    <row r="170" spans="1:8" ht="28.8">
       <c r="A170" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C170" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>11</v>
@@ -28080,10 +28240,10 @@
         <v>12</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="H170" s="3" t="s">
-        <v>691</v>
+        <v>728</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="57.6">
@@ -28091,13 +28251,13 @@
         <v>8</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="C171" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>11</v>
@@ -28106,24 +28266,24 @@
         <v>12</v>
       </c>
       <c r="G171" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="H171" s="6" t="s">
-        <v>692</v>
+        <v>412</v>
+      </c>
+      <c r="H171" s="3" t="s">
+        <v>413</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="28.8">
+    <row r="172" spans="1:8">
       <c r="A172" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="C172" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>11</v>
@@ -28132,24 +28292,24 @@
         <v>12</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="H172" s="6" t="s">
-        <v>426</v>
+        <v>415</v>
+      </c>
+      <c r="H172" s="3" t="s">
+        <v>686</v>
       </c>
     </row>
-    <row r="173" spans="1:8" ht="28.8">
+    <row r="173" spans="1:8" ht="57.6">
       <c r="A173" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="C173" s="2">
         <v>0</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>11</v>
@@ -28158,24 +28318,24 @@
         <v>12</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="H173" s="6" t="s">
-        <v>430</v>
+        <v>687</v>
       </c>
     </row>
-    <row r="174" spans="1:8" ht="409.6">
+    <row r="174" spans="1:8" ht="28.8">
       <c r="A174" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="C174" s="2">
         <v>1</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>11</v>
@@ -28184,10 +28344,10 @@
         <v>12</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>693</v>
-      </c>
-      <c r="H174" s="3" t="s">
-        <v>734</v>
+        <v>420</v>
+      </c>
+      <c r="H174" s="6" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="28.8">
@@ -28195,13 +28355,13 @@
         <v>8</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="C175" s="2">
         <v>0</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>11</v>
@@ -28210,10 +28370,10 @@
         <v>12</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="H175" s="6" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
     </row>
     <row r="176" spans="1:8" ht="409.6">
@@ -28221,13 +28381,13 @@
         <v>8</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="C176" s="2">
         <v>1</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>787</v>
+        <v>426</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>11</v>
@@ -28236,24 +28396,24 @@
         <v>12</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>788</v>
+        <v>688</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>789</v>
+        <v>729</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="201.6">
+    <row r="177" spans="1:8" ht="28.8">
       <c r="A177" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="C177" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>11</v>
@@ -28262,24 +28422,24 @@
         <v>12</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="H177" s="3" t="s">
-        <v>764</v>
+        <v>429</v>
+      </c>
+      <c r="H177" s="6" t="s">
+        <v>430</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="86.4">
+    <row r="178" spans="1:8" ht="409.6">
       <c r="A178" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="C178" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>439</v>
+        <v>781</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>11</v>
@@ -28288,24 +28448,24 @@
         <v>12</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>440</v>
+        <v>782</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>756</v>
+        <v>783</v>
       </c>
     </row>
-    <row r="179" spans="1:8">
+    <row r="179" spans="1:8" ht="201.6">
       <c r="A179" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>441</v>
+        <v>427</v>
       </c>
       <c r="C179" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>11</v>
@@ -28314,24 +28474,24 @@
         <v>12</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="H179" s="6" t="s">
-        <v>29</v>
+        <v>432</v>
+      </c>
+      <c r="H179" s="3" t="s">
+        <v>759</v>
       </c>
     </row>
-    <row r="180" spans="1:8">
+    <row r="180" spans="1:8" ht="86.4">
       <c r="A180" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="C180" s="2">
         <v>0</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>11</v>
@@ -28340,10 +28500,10 @@
         <v>12</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="H180" s="6" t="s">
-        <v>697</v>
+        <v>435</v>
+      </c>
+      <c r="H180" s="3" t="s">
+        <v>751</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -28351,13 +28511,13 @@
         <v>8</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="C181" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>11</v>
@@ -28366,10 +28526,10 @@
         <v>12</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="H181" s="6" t="s">
-        <v>694</v>
+        <v>29</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -28377,13 +28537,13 @@
         <v>8</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="C182" s="2">
         <v>0</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>11</v>
@@ -28392,10 +28552,10 @@
         <v>12</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -28403,13 +28563,13 @@
         <v>8</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="C183" s="2">
         <v>0</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>11</v>
@@ -28418,10 +28578,10 @@
         <v>12</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="H183" s="6" t="s">
-        <v>698</v>
+        <v>689</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -28429,13 +28589,13 @@
         <v>8</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="C184" s="2">
         <v>0</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>11</v>
@@ -28444,24 +28604,24 @@
         <v>12</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="144">
+    <row r="185" spans="1:8">
       <c r="A185" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="C185" s="2">
         <v>0</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>11</v>
@@ -28470,24 +28630,24 @@
         <v>12</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="H185" s="3" t="s">
-        <v>699</v>
+        <v>450</v>
+      </c>
+      <c r="H185" s="6" t="s">
+        <v>693</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="28.8">
+    <row r="186" spans="1:8">
       <c r="A186" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="C186" s="2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>11</v>
@@ -28496,24 +28656,24 @@
         <v>12</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>464</v>
+        <v>691</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="28.8">
+    <row r="187" spans="1:8" ht="144">
       <c r="A187" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C187" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>11</v>
@@ -28522,24 +28682,24 @@
         <v>12</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="H187" s="6" t="s">
-        <v>467</v>
+        <v>456</v>
+      </c>
+      <c r="H187" s="3" t="s">
+        <v>694</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="57.6">
+    <row r="188" spans="1:8" ht="28.8">
       <c r="A188" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C188" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>11</v>
@@ -28548,10 +28708,10 @@
         <v>12</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="H188" s="3" t="s">
-        <v>470</v>
+        <v>458</v>
+      </c>
+      <c r="H188" s="6" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="28.8">
@@ -28559,13 +28719,13 @@
         <v>8</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C189" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>11</v>
@@ -28574,10 +28734,10 @@
         <v>12</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="H189" s="6" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
     </row>
     <row r="190" spans="1:8" ht="57.6">
@@ -28585,13 +28745,13 @@
         <v>8</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C190" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>11</v>
@@ -28600,24 +28760,24 @@
         <v>12</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
     </row>
-    <row r="191" spans="1:8" ht="43.2">
+    <row r="191" spans="1:8" ht="28.8">
       <c r="A191" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C191" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>11</v>
@@ -28626,24 +28786,24 @@
         <v>12</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="H191" s="6" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="28.8">
+    <row r="192" spans="1:8" ht="57.6">
       <c r="A192" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C192" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>11</v>
@@ -28652,24 +28812,24 @@
         <v>12</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="H192" s="6" t="s">
-        <v>482</v>
+        <v>470</v>
+      </c>
+      <c r="H192" s="3" t="s">
+        <v>471</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="28.8">
+    <row r="193" spans="1:8" ht="43.2">
       <c r="A193" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C193" s="2">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>11</v>
@@ -28678,24 +28838,24 @@
         <v>12</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="H193" s="6" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="244.8">
+    <row r="194" spans="1:8" ht="28.8">
       <c r="A194" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C194" s="2">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>486</v>
+        <v>475</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>11</v>
@@ -28704,24 +28864,24 @@
         <v>12</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="H194" s="6" t="s">
-        <v>700</v>
+        <v>477</v>
       </c>
     </row>
-    <row r="195" spans="1:8">
+    <row r="195" spans="1:8" ht="28.8">
       <c r="A195" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C195" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>11</v>
@@ -28730,24 +28890,24 @@
         <v>12</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="H195" s="6" t="s">
-        <v>14</v>
+        <v>480</v>
       </c>
     </row>
-    <row r="196" spans="1:8" ht="28.8">
+    <row r="196" spans="1:8" ht="244.8">
       <c r="A196" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>490</v>
+        <v>454</v>
       </c>
       <c r="C196" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>11</v>
@@ -28756,24 +28916,24 @@
         <v>12</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="H196" s="6" t="s">
-        <v>493</v>
+        <v>695</v>
       </c>
     </row>
-    <row r="197" spans="1:8" ht="28.8">
+    <row r="197" spans="1:8">
       <c r="A197" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>490</v>
+        <v>454</v>
       </c>
       <c r="C197" s="2">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>11</v>
@@ -28782,24 +28942,24 @@
         <v>12</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="H197" t="s">
-        <v>735</v>
+        <v>484</v>
+      </c>
+      <c r="H197" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="198" spans="1:8">
+    <row r="198" spans="1:8" ht="28.8">
       <c r="A198" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C198" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>11</v>
@@ -28808,24 +28968,24 @@
         <v>12</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="H198" s="6" t="s">
-        <v>736</v>
+        <v>488</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="100.8">
+    <row r="199" spans="1:8" ht="28.8">
       <c r="A199" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C199" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>11</v>
@@ -28834,24 +28994,24 @@
         <v>12</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="H199" s="3" t="s">
-        <v>757</v>
+        <v>490</v>
+      </c>
+      <c r="H199" t="s">
+        <v>730</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="158.4">
+    <row r="200" spans="1:8">
       <c r="A200" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C200" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>11</v>
@@ -28860,24 +29020,24 @@
         <v>12</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="H200" s="3" t="s">
-        <v>701</v>
+        <v>492</v>
+      </c>
+      <c r="H200" s="6" t="s">
+        <v>731</v>
       </c>
     </row>
-    <row r="201" spans="1:8" ht="43.2">
+    <row r="201" spans="1:8" ht="100.8">
       <c r="A201" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C201" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>11</v>
@@ -28886,24 +29046,24 @@
         <v>12</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>702</v>
+        <v>752</v>
       </c>
     </row>
-    <row r="202" spans="1:8" ht="100.8">
+    <row r="202" spans="1:8" ht="158.4">
       <c r="A202" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C202" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>11</v>
@@ -28912,10 +29072,10 @@
         <v>12</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="H202" s="3" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
     </row>
     <row r="203" spans="1:8" ht="43.2">
@@ -28923,13 +29083,13 @@
         <v>8</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C203" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>11</v>
@@ -28938,10 +29098,10 @@
         <v>12</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="H203" s="3" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="100.8">
@@ -28949,13 +29109,13 @@
         <v>8</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C204" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>11</v>
@@ -28964,24 +29124,24 @@
         <v>12</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="H204" s="3" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
     </row>
-    <row r="205" spans="1:8" ht="100.8">
+    <row r="205" spans="1:8" ht="43.2">
       <c r="A205" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C205" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>11</v>
@@ -28990,24 +29150,24 @@
         <v>12</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="H205" s="3" t="s">
-        <v>737</v>
+        <v>699</v>
       </c>
     </row>
-    <row r="206" spans="1:8" ht="115.2">
+    <row r="206" spans="1:8" ht="100.8">
       <c r="A206" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C206" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>11</v>
@@ -29016,24 +29176,24 @@
         <v>12</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="H206" s="3" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
     </row>
-    <row r="207" spans="1:8" ht="158.4">
+    <row r="207" spans="1:8" ht="100.8">
       <c r="A207" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C207" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>11</v>
@@ -29042,24 +29202,24 @@
         <v>12</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="H207" s="3" t="s">
-        <v>707</v>
+        <v>732</v>
       </c>
     </row>
-    <row r="208" spans="1:8" ht="172.8">
+    <row r="208" spans="1:8" ht="115.2">
       <c r="A208" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C208" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>11</v>
@@ -29068,24 +29228,24 @@
         <v>12</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="H208" s="3" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="115.2">
+    <row r="209" spans="1:9" ht="158.4">
       <c r="A209" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C209" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>11</v>
@@ -29094,24 +29254,24 @@
         <v>12</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="H209" s="3" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="158.4">
+    <row r="210" spans="1:9" ht="172.8">
       <c r="A210" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C210" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>11</v>
@@ -29120,24 +29280,24 @@
         <v>12</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>758</v>
+        <v>512</v>
       </c>
       <c r="H210" s="3" t="s">
-        <v>759</v>
+        <v>703</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="158.4">
+    <row r="211" spans="1:9" ht="115.2">
       <c r="A211" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C211" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>11</v>
@@ -29146,24 +29306,24 @@
         <v>12</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="H211" s="3" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="100.8">
+    <row r="212" spans="1:9" ht="158.4">
       <c r="A212" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C212" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>11</v>
@@ -29172,24 +29332,24 @@
         <v>12</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>524</v>
+        <v>753</v>
       </c>
       <c r="H212" s="3" t="s">
-        <v>793</v>
+        <v>754</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="100.8">
+    <row r="213" spans="1:9" ht="158.4">
       <c r="A213" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C213" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>11</v>
@@ -29198,24 +29358,24 @@
         <v>12</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="H213" s="3" t="s">
-        <v>794</v>
+        <v>705</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="43.2">
+    <row r="214" spans="1:9" ht="100.8">
       <c r="A214" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C214" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>11</v>
@@ -29224,24 +29384,24 @@
         <v>12</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="H214" s="3" t="s">
-        <v>711</v>
+        <v>784</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="43.2">
+    <row r="215" spans="1:9" ht="100.8">
       <c r="A215" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C215" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>11</v>
@@ -29250,10 +29410,10 @@
         <v>12</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="H215" s="3" t="s">
-        <v>531</v>
+        <v>785</v>
       </c>
     </row>
     <row r="216" spans="1:9" ht="43.2">
@@ -29261,13 +29421,13 @@
         <v>8</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C216" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>11</v>
@@ -29276,24 +29436,24 @@
         <v>12</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="409.6">
+    <row r="217" spans="1:9" ht="43.2">
       <c r="A217" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C217" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>784</v>
+        <v>524</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>11</v>
@@ -29302,25 +29462,24 @@
         <v>12</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>785</v>
+        <v>525</v>
       </c>
       <c r="H217" s="3" t="s">
-        <v>786</v>
-      </c>
-      <c r="I217" s="3"/>
+        <v>526</v>
+      </c>
     </row>
-    <row r="218" spans="1:9" ht="115.2">
+    <row r="218" spans="1:9" ht="43.2">
       <c r="A218" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C218" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>11</v>
@@ -29329,24 +29488,24 @@
         <v>12</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="H218" s="3" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="43.2">
+    <row r="219" spans="1:9" ht="409.6">
       <c r="A219" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C219" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>536</v>
+        <v>778</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>11</v>
@@ -29355,24 +29514,25 @@
         <v>12</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>537</v>
+        <v>779</v>
       </c>
       <c r="H219" s="3" t="s">
-        <v>538</v>
-      </c>
+        <v>780</v>
+      </c>
+      <c r="I219" s="3"/>
     </row>
-    <row r="220" spans="1:9" ht="86.4">
+    <row r="220" spans="1:9" ht="115.2">
       <c r="A220" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C220" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>11</v>
@@ -29381,24 +29541,24 @@
         <v>12</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="H220" s="3" t="s">
-        <v>682</v>
+        <v>708</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="115.2">
+    <row r="221" spans="1:9" ht="43.2">
       <c r="A221" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C221" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>11</v>
@@ -29407,24 +29567,24 @@
         <v>12</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="H221" s="3" t="s">
-        <v>683</v>
+        <v>533</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="43.2">
+    <row r="222" spans="1:9" ht="86.4">
       <c r="A222" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C222" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>11</v>
@@ -29433,24 +29593,24 @@
         <v>12</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="H222" s="3" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="100.8">
+    <row r="223" spans="1:9" ht="115.2">
       <c r="A223" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C223" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>11</v>
@@ -29459,10 +29619,10 @@
         <v>12</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="H223" s="3" t="s">
-        <v>738</v>
+        <v>678</v>
       </c>
     </row>
     <row r="224" spans="1:9" ht="43.2">
@@ -29470,13 +29630,13 @@
         <v>8</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C224" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>11</v>
@@ -29485,24 +29645,24 @@
         <v>12</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="H224" s="3" t="s">
-        <v>549</v>
+        <v>679</v>
       </c>
     </row>
-    <row r="225" spans="1:8" ht="43.2">
+    <row r="225" spans="1:8" ht="100.8">
       <c r="A225" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C225" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>11</v>
@@ -29511,24 +29671,24 @@
         <v>12</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="H225" s="3" t="s">
-        <v>685</v>
+        <v>733</v>
       </c>
     </row>
-    <row r="226" spans="1:8" ht="100.8">
+    <row r="226" spans="1:8" ht="43.2">
       <c r="A226" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C226" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>11</v>
@@ -29537,24 +29697,24 @@
         <v>12</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
       <c r="H226" s="3" t="s">
-        <v>686</v>
+        <v>544</v>
       </c>
     </row>
-    <row r="227" spans="1:8" ht="28.8">
+    <row r="227" spans="1:8" ht="43.2">
       <c r="A227" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>554</v>
+        <v>485</v>
       </c>
       <c r="C227" s="2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>11</v>
@@ -29563,24 +29723,24 @@
         <v>12</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>556</v>
-      </c>
-      <c r="H227" s="6" t="s">
-        <v>687</v>
+        <v>546</v>
+      </c>
+      <c r="H227" s="3" t="s">
+        <v>680</v>
       </c>
     </row>
-    <row r="228" spans="1:8" ht="28.8">
+    <row r="228" spans="1:8" ht="100.8">
       <c r="A228" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>557</v>
+        <v>485</v>
       </c>
       <c r="C228" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>558</v>
+        <v>547</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>11</v>
@@ -29589,24 +29749,24 @@
         <v>12</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>560</v>
+        <v>681</v>
       </c>
     </row>
-    <row r="229" spans="1:8" ht="43.2">
+    <row r="229" spans="1:8" ht="28.8">
       <c r="A229" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="C229" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>11</v>
@@ -29615,24 +29775,24 @@
         <v>12</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="H229" s="3" t="s">
-        <v>688</v>
+        <v>551</v>
+      </c>
+      <c r="H229" s="6" t="s">
+        <v>682</v>
       </c>
     </row>
-    <row r="230" spans="1:8" ht="100.8">
+    <row r="230" spans="1:8" ht="28.8">
       <c r="A230" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="C230" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>11</v>
@@ -29641,10 +29801,10 @@
         <v>12</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="H230" s="3" t="s">
-        <v>689</v>
+        <v>555</v>
       </c>
     </row>
     <row r="231" spans="1:8" ht="43.2">
@@ -29652,13 +29812,13 @@
         <v>8</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="C231" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>11</v>
@@ -29667,24 +29827,24 @@
         <v>12</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="H231" s="3" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
     </row>
-    <row r="232" spans="1:8">
+    <row r="232" spans="1:8" ht="100.8">
       <c r="A232" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>567</v>
+        <v>552</v>
       </c>
       <c r="C232" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>11</v>
@@ -29693,24 +29853,24 @@
         <v>12</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="H232" s="6" t="s">
-        <v>570</v>
+        <v>559</v>
+      </c>
+      <c r="H232" s="3" t="s">
+        <v>684</v>
       </c>
     </row>
-    <row r="233" spans="1:8">
+    <row r="233" spans="1:8" ht="43.2">
       <c r="A233" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>571</v>
+        <v>552</v>
       </c>
       <c r="C233" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>11</v>
@@ -29719,24 +29879,24 @@
         <v>12</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="H233" s="6" t="s">
-        <v>593</v>
+        <v>561</v>
+      </c>
+      <c r="H233" s="3" t="s">
+        <v>685</v>
       </c>
     </row>
-    <row r="234" spans="1:8" ht="28.8">
+    <row r="234" spans="1:8">
       <c r="A234" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="C234" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>11</v>
@@ -29745,10 +29905,10 @@
         <v>12</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="H234" s="6" t="s">
-        <v>629</v>
+        <v>565</v>
       </c>
     </row>
     <row r="235" spans="1:8">
@@ -29756,13 +29916,13 @@
         <v>8</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="C235" s="2">
         <v>0</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>11</v>
@@ -29771,10 +29931,10 @@
         <v>12</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="H235" s="6" t="s">
-        <v>579</v>
+        <v>588</v>
       </c>
     </row>
     <row r="236" spans="1:8" ht="28.8">
@@ -29782,13 +29942,13 @@
         <v>8</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="C236" s="2">
         <v>1</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>580</v>
+        <v>569</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>11</v>
@@ -29797,10 +29957,10 @@
         <v>12</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="H236" s="4" t="s">
-        <v>582</v>
+        <v>570</v>
+      </c>
+      <c r="H236" s="6" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="237" spans="1:8">
@@ -29808,13 +29968,13 @@
         <v>8</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>554</v>
+        <v>571</v>
       </c>
       <c r="C237" s="2">
         <v>0</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>583</v>
+        <v>572</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>11</v>
@@ -29823,10 +29983,10 @@
         <v>12</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>584</v>
-      </c>
-      <c r="H237" s="4" t="s">
-        <v>23</v>
+        <v>573</v>
+      </c>
+      <c r="H237" s="6" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="238" spans="1:8" ht="28.8">
@@ -29834,13 +29994,13 @@
         <v>8</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>554</v>
+        <v>571</v>
       </c>
       <c r="C238" s="2">
         <v>1</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>11</v>
@@ -29849,10 +30009,10 @@
         <v>12</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="H238" s="4" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -29860,13 +30020,13 @@
         <v>8</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>588</v>
+        <v>549</v>
       </c>
       <c r="C239" s="2">
         <v>0</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>11</v>
@@ -29875,57 +30035,109 @@
         <v>12</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="H239" s="4" t="s">
-        <v>591</v>
+        <v>23</v>
       </c>
     </row>
-    <row r="240" spans="1:8">
-      <c r="A240" t="s">
-        <v>760</v>
-      </c>
-      <c r="B240" t="s">
-        <v>588</v>
-      </c>
-      <c r="C240">
+    <row r="240" spans="1:8" ht="28.8">
+      <c r="A240" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C240" s="2">
         <v>1</v>
       </c>
-      <c r="D240" t="s">
-        <v>761</v>
-      </c>
-      <c r="E240" t="s">
+      <c r="D240" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="E240" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F240" t="s">
+      <c r="F240" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G240" t="s">
-        <v>762</v>
+      <c r="G240" s="3" t="s">
+        <v>581</v>
       </c>
       <c r="H240" s="4" t="s">
-        <v>763</v>
+        <v>582</v>
       </c>
     </row>
     <row r="241" spans="1:8">
-      <c r="A241" s="2"/>
-      <c r="B241" s="2"/>
-      <c r="C241" s="2"/>
-      <c r="D241" s="2"/>
-      <c r="E241" s="2"/>
-      <c r="F241" s="2"/>
-      <c r="G241" s="3"/>
-      <c r="H241" s="3"/>
+      <c r="A241" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="C241" s="2">
+        <v>0</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="E241" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F241" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G241" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="H241" s="4" t="s">
+        <v>586</v>
+      </c>
     </row>
     <row r="242" spans="1:8">
-      <c r="A242" s="2"/>
-      <c r="B242" s="2"/>
-      <c r="C242" s="2"/>
-      <c r="D242" s="2"/>
-      <c r="E242" s="2"/>
-      <c r="F242" s="2"/>
-      <c r="G242" s="3"/>
-      <c r="H242" s="3"/>
+      <c r="A242" t="s">
+        <v>755</v>
+      </c>
+      <c r="B242" t="s">
+        <v>583</v>
+      </c>
+      <c r="C242">
+        <v>1</v>
+      </c>
+      <c r="D242" t="s">
+        <v>756</v>
+      </c>
+      <c r="E242" t="s">
+        <v>11</v>
+      </c>
+      <c r="F242" t="s">
+        <v>12</v>
+      </c>
+      <c r="G242" t="s">
+        <v>757</v>
+      </c>
+      <c r="H242" s="4" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8">
+      <c r="A243" s="2"/>
+      <c r="B243" s="2"/>
+      <c r="C243" s="2"/>
+      <c r="D243" s="2"/>
+      <c r="E243" s="2"/>
+      <c r="F243" s="2"/>
+      <c r="G243" s="3"/>
+      <c r="H243" s="3"/>
+    </row>
+    <row r="244" spans="1:8">
+      <c r="A244" s="2"/>
+      <c r="B244" s="2"/>
+      <c r="C244" s="2"/>
+      <c r="D244" s="2"/>
+      <c r="E244" s="2"/>
+      <c r="F244" s="2"/>
+      <c r="G244" s="3"/>
+      <c r="H244" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docassemble/PowerOfAttorneyHealthCare/data/sources/poa_hc_es.xlsx
+++ b/docassemble/PowerOfAttorneyHealthCare/data/sources/poa_hc_es.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnewsted\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{393F5A6D-BE77-4124-A610-C910AC23663C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A473E20-9C94-4332-A243-5B783B93F23A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35685" yWindow="-1230" windowWidth="28485" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-36045" yWindow="-2865" windowWidth="28485" windowHeight="16530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1472,64 +1472,6 @@
     <t>Question_406</t>
   </si>
   <si>
-    <t>aa69e6ef818d219600cc5918861b65c3</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">No. You are able to list someone outside of the United States as the agent. The agent does not need to be a United States citizen. However, there may issues if a bank or financial organization is unable to reach them. You may want to ask a lawyer for advice. Use </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[**Get Legal Help**]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://www.illinoislegalaid.org/get-legal-help</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">) to find free or low-cost legal services in your area.
-For international addresses, there will be space for two lines to enter the address. You should enter the international address using the English alphabet.
-</t>
-    </r>
-  </si>
-  <si>
     <t>75c0d30daac521ef94043d6de7ba7491</t>
   </si>
   <si>
@@ -19304,40 +19246,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>No. Puedes nombrar como agente a alguien que vive fuera de los Estados Unidos. El agente no necesita ser ciudadano de los Estados Unidos. Sin embargo, pueden haber problemas si un banco u otra institución financiera no puede comunicarse con esa persona. Es posible que desees consultar a un abogado para obtener asesoramiento. Usa [**Obtener ayuda legal**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://es.illinoislegalaid.org/get-legal-help</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>) para encontrar servicios legales gratuitos o de bajo costo en tu área.
-Para direcciones internacionales, habrá espacio para ingresar la dirección en dos líneas. Debes escribir la dirección internacional usando el alfabeto inglés.</t>
     </r>
   </si>
   <si>
@@ -23350,6 +23258,98 @@
         <scheme val="minor"/>
       </rPr>
       <t>).</t>
+    </r>
+  </si>
+  <si>
+    <t>a2d0ae67d469eb448125476c4fd086c7</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">No. You are able to list someone outside of the United States as the agent. The agent does not need to be a United States citizen. However, there may be issues if a doctor or health care provider is unable to reach them. You may want to ask a lawyer for advice. Use </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[**Get Legal Help**]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://www.illinoislegalaid.org/get-legal-help</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) to find free or low-cost legal services in your area.
+For international addresses, there will be space for two lines to enter the address. You should enter the international address using the English alphabet.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>No. Puedes nombrar como agente a alguien que vive fuera de los Estados Unidos. El agente no necesita ser ciudadano de los Estados Unidos. Sin embargo, puede haber problemas si un médico o un proveedor de atención médica no puede comunicarse con esa persona. Es posible que desees consultar a un abogado para obtener asesoramiento. Usa [**Obtener ayuda legal**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://es.illinoislegalaid.org/get-legal-help</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) para encontrar servicios legales gratuitos o de bajo costo en tu área.
+Para direcciones internacionales, habrá espacio para ingresar la dirección en dos líneas. Debes escribir la dirección internacional usando el alfabeto inglés.</t>
     </r>
   </si>
 </sst>
@@ -23889,7 +23889,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>11</v>
@@ -23898,10 +23898,10 @@
         <v>12</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -23953,7 +23953,7 @@
         <v>20</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -24057,7 +24057,7 @@
         <v>31</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="28.8">
@@ -24071,7 +24071,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>11</v>
@@ -24080,7 +24080,7 @@
         <v>12</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>33</v>
@@ -24097,7 +24097,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>11</v>
@@ -24106,7 +24106,7 @@
         <v>12</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>34</v>
@@ -24123,7 +24123,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>11</v>
@@ -24132,10 +24132,10 @@
         <v>12</v>
       </c>
       <c r="G12" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>799</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="216">
@@ -24149,7 +24149,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>11</v>
@@ -24158,10 +24158,10 @@
         <v>12</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="28.8">
@@ -24213,7 +24213,7 @@
         <v>41</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="28.8">
@@ -24265,21 +24265,21 @@
         <v>47</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="115.2">
       <c r="A18" s="2" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="C18" s="2">
         <v>0</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>11</v>
@@ -24288,18 +24288,18 @@
         <v>12</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="28.8">
       <c r="A19" s="2" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
@@ -24343,7 +24343,7 @@
         <v>53</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -24369,7 +24369,7 @@
         <v>56</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="43.2">
@@ -24395,7 +24395,7 @@
         <v>58</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="57.6">
@@ -24421,7 +24421,7 @@
         <v>60</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="28.8">
@@ -24447,7 +24447,7 @@
         <v>62</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="57.6">
@@ -24473,12 +24473,12 @@
         <v>64</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="2" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>54</v>
@@ -24487,7 +24487,7 @@
         <v>5</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>11</v>
@@ -24496,15 +24496,15 @@
         <v>12</v>
       </c>
       <c r="G26" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="H26" s="4" t="s">
         <v>793</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="2" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>54</v>
@@ -24513,7 +24513,7 @@
         <v>6</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>11</v>
@@ -24522,10 +24522,10 @@
         <v>12</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="28.8">
@@ -24551,7 +24551,7 @@
         <v>67</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="244.8">
@@ -24577,7 +24577,7 @@
         <v>69</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="86.4">
@@ -24603,7 +24603,7 @@
         <v>72</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="409.6">
@@ -24617,7 +24617,7 @@
         <v>1</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>11</v>
@@ -24626,10 +24626,10 @@
         <v>12</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -24655,7 +24655,7 @@
         <v>74</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -24681,7 +24681,7 @@
         <v>76</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -24707,7 +24707,7 @@
         <v>78</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -24733,7 +24733,7 @@
         <v>80</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -24785,7 +24785,7 @@
         <v>85</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="100.8">
@@ -24811,7 +24811,7 @@
         <v>88</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="28.8">
@@ -24837,7 +24837,7 @@
         <v>90</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="86.4">
@@ -24863,7 +24863,7 @@
         <v>93</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="28.8">
@@ -24889,7 +24889,7 @@
         <v>96</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="144">
@@ -24915,7 +24915,7 @@
         <v>98</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="86.4">
@@ -24967,7 +24967,7 @@
         <v>105</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="374.4">
@@ -24993,7 +24993,7 @@
         <v>107</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="86.4">
@@ -25019,7 +25019,7 @@
         <v>110</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="28.8">
@@ -25045,7 +25045,7 @@
         <v>112</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="28.8">
@@ -25071,7 +25071,7 @@
         <v>115</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -25097,7 +25097,7 @@
         <v>117</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="43.2">
@@ -25123,7 +25123,7 @@
         <v>119</v>
       </c>
       <c r="H50" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -25149,7 +25149,7 @@
         <v>121</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -25175,7 +25175,7 @@
         <v>123</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="129.6">
@@ -25189,7 +25189,7 @@
         <v>0</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>125</v>
+        <v>801</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>11</v>
@@ -25198,10 +25198,10 @@
         <v>12</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>126</v>
+        <v>802</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>748</v>
+        <v>803</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="28.8">
@@ -25215,7 +25215,7 @@
         <v>1</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>11</v>
@@ -25224,10 +25224,10 @@
         <v>12</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="28.8">
@@ -25235,13 +25235,13 @@
         <v>8</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C55" s="2">
         <v>0</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>11</v>
@@ -25250,10 +25250,10 @@
         <v>12</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="100.8">
@@ -25261,13 +25261,13 @@
         <v>8</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C56" s="2">
         <v>1</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>11</v>
@@ -25276,10 +25276,10 @@
         <v>12</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="100.8">
@@ -25287,13 +25287,13 @@
         <v>8</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C57" s="2">
         <v>0</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>11</v>
@@ -25302,10 +25302,10 @@
         <v>12</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="288">
@@ -25313,13 +25313,13 @@
         <v>8</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C58" s="2">
         <v>1</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>11</v>
@@ -25328,10 +25328,10 @@
         <v>12</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="28.8">
@@ -25339,13 +25339,13 @@
         <v>8</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C59" s="2">
         <v>1</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>11</v>
@@ -25354,10 +25354,10 @@
         <v>12</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -25365,13 +25365,13 @@
         <v>8</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C60" s="2">
         <v>0</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>11</v>
@@ -25380,10 +25380,10 @@
         <v>12</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="28.8">
@@ -25391,13 +25391,13 @@
         <v>8</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C61" s="2">
         <v>1</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>11</v>
@@ -25406,10 +25406,10 @@
         <v>12</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="28.8">
@@ -25417,13 +25417,13 @@
         <v>8</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C62" s="2">
         <v>2</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>11</v>
@@ -25432,10 +25432,10 @@
         <v>12</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="144">
@@ -25443,13 +25443,13 @@
         <v>8</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C63" s="2">
         <v>3</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>11</v>
@@ -25458,10 +25458,10 @@
         <v>12</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -25469,13 +25469,13 @@
         <v>8</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C64" s="2">
         <v>4</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>11</v>
@@ -25484,10 +25484,10 @@
         <v>12</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="28.8">
@@ -25495,13 +25495,13 @@
         <v>8</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C65" s="2">
         <v>5</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>11</v>
@@ -25510,10 +25510,10 @@
         <v>12</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -25521,13 +25521,13 @@
         <v>8</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C66" s="2">
         <v>6</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>11</v>
@@ -25536,10 +25536,10 @@
         <v>12</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="43.2">
@@ -25547,13 +25547,13 @@
         <v>8</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C67" s="2">
         <v>7</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>11</v>
@@ -25562,10 +25562,10 @@
         <v>12</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="57.6">
@@ -25573,13 +25573,13 @@
         <v>8</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C68" s="2">
         <v>8</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>11</v>
@@ -25588,10 +25588,10 @@
         <v>12</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -25599,13 +25599,13 @@
         <v>8</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C69" s="2">
         <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>11</v>
@@ -25614,10 +25614,10 @@
         <v>12</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="28.8">
@@ -25625,13 +25625,13 @@
         <v>8</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C70" s="2">
         <v>0</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>11</v>
@@ -25640,10 +25640,10 @@
         <v>12</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="172.8">
@@ -25651,13 +25651,13 @@
         <v>8</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C71" s="2">
         <v>1</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>11</v>
@@ -25666,10 +25666,10 @@
         <v>12</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="28.8">
@@ -25677,13 +25677,13 @@
         <v>8</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C72" s="2">
         <v>2</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>11</v>
@@ -25692,10 +25692,10 @@
         <v>12</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -25703,13 +25703,13 @@
         <v>8</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C73" s="2">
         <v>3</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>11</v>
@@ -25718,10 +25718,10 @@
         <v>12</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="43.2">
@@ -25729,13 +25729,13 @@
         <v>8</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C74" s="2">
         <v>4</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>11</v>
@@ -25744,10 +25744,10 @@
         <v>12</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="57.6">
@@ -25755,13 +25755,13 @@
         <v>8</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C75" s="2">
         <v>5</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>11</v>
@@ -25770,10 +25770,10 @@
         <v>12</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -25781,13 +25781,13 @@
         <v>8</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C76" s="2">
         <v>6</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>11</v>
@@ -25796,10 +25796,10 @@
         <v>12</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="28.8">
@@ -25807,13 +25807,13 @@
         <v>8</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C77" s="2">
         <v>0</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>11</v>
@@ -25822,10 +25822,10 @@
         <v>12</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="144">
@@ -25833,13 +25833,13 @@
         <v>8</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>11</v>
@@ -25848,10 +25848,10 @@
         <v>12</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="115.2">
@@ -25859,13 +25859,13 @@
         <v>8</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C79" s="2">
         <v>0</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>11</v>
@@ -25874,10 +25874,10 @@
         <v>12</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="360">
@@ -25885,13 +25885,13 @@
         <v>8</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C80" s="2">
         <v>1</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>11</v>
@@ -25900,10 +25900,10 @@
         <v>12</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="28.8">
@@ -25911,13 +25911,13 @@
         <v>8</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C81" s="2">
         <v>1</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>11</v>
@@ -25926,10 +25926,10 @@
         <v>12</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="28.8">
@@ -25937,13 +25937,13 @@
         <v>8</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C82" s="2">
         <v>0</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>11</v>
@@ -25952,10 +25952,10 @@
         <v>12</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="72">
@@ -25963,13 +25963,13 @@
         <v>8</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C83" s="2">
         <v>1</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>11</v>
@@ -25978,10 +25978,10 @@
         <v>12</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="72">
@@ -25989,13 +25989,13 @@
         <v>8</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C84" s="2">
         <v>2</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>11</v>
@@ -26004,10 +26004,10 @@
         <v>12</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -26015,13 +26015,13 @@
         <v>8</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C85" s="2">
         <v>3</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>11</v>
@@ -26030,10 +26030,10 @@
         <v>12</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="43.2">
@@ -26041,13 +26041,13 @@
         <v>8</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C86" s="2">
         <v>4</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>11</v>
@@ -26056,10 +26056,10 @@
         <v>12</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -26067,13 +26067,13 @@
         <v>8</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C87" s="2">
         <v>5</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>11</v>
@@ -26082,10 +26082,10 @@
         <v>12</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -26093,13 +26093,13 @@
         <v>8</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C88" s="2">
         <v>6</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>11</v>
@@ -26108,10 +26108,10 @@
         <v>12</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="172.8">
@@ -26119,13 +26119,13 @@
         <v>8</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C89" s="2">
         <v>0</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>11</v>
@@ -26134,10 +26134,10 @@
         <v>12</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="43.2">
@@ -26145,13 +26145,13 @@
         <v>8</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C90" s="2">
         <v>1</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>11</v>
@@ -26160,10 +26160,10 @@
         <v>12</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="43.2">
@@ -26171,13 +26171,13 @@
         <v>8</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C91" s="2">
         <v>0</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>11</v>
@@ -26186,10 +26186,10 @@
         <v>12</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="72">
@@ -26197,13 +26197,13 @@
         <v>8</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C92" s="2">
         <v>1</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>11</v>
@@ -26212,10 +26212,10 @@
         <v>12</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="72">
@@ -26223,13 +26223,13 @@
         <v>8</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C93" s="2">
         <v>2</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>11</v>
@@ -26238,10 +26238,10 @@
         <v>12</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -26249,13 +26249,13 @@
         <v>8</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C94" s="2">
         <v>3</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>11</v>
@@ -26264,10 +26264,10 @@
         <v>12</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="57.6">
@@ -26275,13 +26275,13 @@
         <v>8</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C95" s="2">
         <v>4</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>11</v>
@@ -26290,10 +26290,10 @@
         <v>12</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -26301,13 +26301,13 @@
         <v>8</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C96" s="2">
         <v>5</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>11</v>
@@ -26316,10 +26316,10 @@
         <v>12</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -26327,13 +26327,13 @@
         <v>8</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C97" s="2">
         <v>6</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>11</v>
@@ -26342,10 +26342,10 @@
         <v>12</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="201.6">
@@ -26353,13 +26353,13 @@
         <v>8</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C98" s="2">
         <v>0</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>11</v>
@@ -26368,10 +26368,10 @@
         <v>12</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="28.8">
@@ -26379,13 +26379,13 @@
         <v>8</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C99" s="2">
         <v>0</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>11</v>
@@ -26394,10 +26394,10 @@
         <v>12</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="129.6">
@@ -26405,13 +26405,13 @@
         <v>8</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C100" s="2">
         <v>1</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>11</v>
@@ -26420,10 +26420,10 @@
         <v>12</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="86.4">
@@ -26431,13 +26431,13 @@
         <v>8</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C101" s="2">
         <v>0</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>11</v>
@@ -26446,10 +26446,10 @@
         <v>12</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="102" spans="1:8" ht="302.39999999999998">
@@ -26457,13 +26457,13 @@
         <v>8</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C102" s="2">
         <v>1</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>11</v>
@@ -26472,10 +26472,10 @@
         <v>12</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
     <row r="103" spans="1:8" ht="28.8">
@@ -26483,13 +26483,13 @@
         <v>8</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C103" s="2">
         <v>0</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>11</v>
@@ -26498,10 +26498,10 @@
         <v>12</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="104" spans="1:8" ht="86.4">
@@ -26509,13 +26509,13 @@
         <v>8</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C104" s="2">
         <v>1</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>11</v>
@@ -26524,10 +26524,10 @@
         <v>12</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -26535,13 +26535,13 @@
         <v>8</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C105" s="2">
         <v>2</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>11</v>
@@ -26550,10 +26550,10 @@
         <v>12</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -26561,13 +26561,13 @@
         <v>8</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C106" s="2">
         <v>3</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>11</v>
@@ -26576,10 +26576,10 @@
         <v>12</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -26587,13 +26587,13 @@
         <v>8</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C107" s="2">
         <v>4</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>11</v>
@@ -26602,10 +26602,10 @@
         <v>12</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -26613,13 +26613,13 @@
         <v>8</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C108" s="2">
         <v>5</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>11</v>
@@ -26628,10 +26628,10 @@
         <v>12</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -26639,13 +26639,13 @@
         <v>8</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C109" s="2">
         <v>6</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>11</v>
@@ -26654,10 +26654,10 @@
         <v>12</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -26665,13 +26665,13 @@
         <v>8</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C110" s="2">
         <v>7</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>11</v>
@@ -26680,10 +26680,10 @@
         <v>12</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -26691,13 +26691,13 @@
         <v>8</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C111" s="2">
         <v>8</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>11</v>
@@ -26706,10 +26706,10 @@
         <v>12</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="43.2">
@@ -26717,13 +26717,13 @@
         <v>8</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C112" s="2">
         <v>0</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>11</v>
@@ -26732,10 +26732,10 @@
         <v>12</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="113" spans="1:8" ht="86.4">
@@ -26743,13 +26743,13 @@
         <v>8</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C113" s="2">
         <v>1</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>11</v>
@@ -26758,10 +26758,10 @@
         <v>12</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -26769,13 +26769,13 @@
         <v>8</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C114" s="2">
         <v>2</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>11</v>
@@ -26784,10 +26784,10 @@
         <v>12</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="H114" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -26795,13 +26795,13 @@
         <v>8</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C115" s="2">
         <v>3</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>11</v>
@@ -26810,10 +26810,10 @@
         <v>12</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H115" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -26821,13 +26821,13 @@
         <v>8</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C116" s="2">
         <v>4</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>11</v>
@@ -26836,10 +26836,10 @@
         <v>12</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H116" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -26847,13 +26847,13 @@
         <v>8</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C117" s="2">
         <v>5</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>11</v>
@@ -26862,10 +26862,10 @@
         <v>12</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H117" s="6" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="118" spans="1:8" ht="43.2">
@@ -26873,13 +26873,13 @@
         <v>8</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C118" s="2">
         <v>6</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>11</v>
@@ -26888,10 +26888,10 @@
         <v>12</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="28.8">
@@ -26899,13 +26899,13 @@
         <v>8</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C119" s="2">
         <v>0</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>11</v>
@@ -26914,10 +26914,10 @@
         <v>12</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H119" s="6" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -26925,13 +26925,13 @@
         <v>8</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C120" s="2">
         <v>1</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>11</v>
@@ -26940,10 +26940,10 @@
         <v>12</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -26951,13 +26951,13 @@
         <v>8</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C121" s="2">
         <v>2</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>11</v>
@@ -26966,10 +26966,10 @@
         <v>12</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H121" s="6" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="28.8">
@@ -26977,13 +26977,13 @@
         <v>8</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C122" s="2">
         <v>0</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>11</v>
@@ -26992,10 +26992,10 @@
         <v>12</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -27003,13 +27003,13 @@
         <v>8</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C123" s="2">
         <v>1</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>11</v>
@@ -27018,10 +27018,10 @@
         <v>12</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H123" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="86.4">
@@ -27029,13 +27029,13 @@
         <v>8</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C124" s="2">
         <v>0</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>11</v>
@@ -27044,10 +27044,10 @@
         <v>12</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="28.8">
@@ -27055,13 +27055,13 @@
         <v>8</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C125" s="2">
         <v>1</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>11</v>
@@ -27070,10 +27070,10 @@
         <v>12</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H125" s="6" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="28.8">
@@ -27081,13 +27081,13 @@
         <v>8</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C126" s="2">
         <v>2</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>11</v>
@@ -27096,10 +27096,10 @@
         <v>12</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H126" s="8" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="28.8">
@@ -27107,13 +27107,13 @@
         <v>8</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C127" s="2">
         <v>3</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>11</v>
@@ -27122,10 +27122,10 @@
         <v>12</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H127" s="8" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
     <row r="128" spans="1:8" ht="28.8">
@@ -27133,13 +27133,13 @@
         <v>8</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C128" s="2">
         <v>4</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>11</v>
@@ -27148,10 +27148,10 @@
         <v>12</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H128" s="8" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -27159,13 +27159,13 @@
         <v>8</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C129" s="2">
         <v>5</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>11</v>
@@ -27174,10 +27174,10 @@
         <v>12</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="H129" s="8" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -27185,13 +27185,13 @@
         <v>8</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C130" s="2">
         <v>6</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>11</v>
@@ -27200,10 +27200,10 @@
         <v>12</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -27211,13 +27211,13 @@
         <v>8</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C131" s="2">
         <v>7</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>11</v>
@@ -27226,10 +27226,10 @@
         <v>12</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -27237,13 +27237,13 @@
         <v>8</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C132" s="2">
         <v>8</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>11</v>
@@ -27252,10 +27252,10 @@
         <v>12</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="133" spans="1:8" ht="28.8">
@@ -27263,13 +27263,13 @@
         <v>8</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C133" s="2">
         <v>0</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>11</v>
@@ -27278,10 +27278,10 @@
         <v>12</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H133" s="6" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="134" spans="1:8" ht="403.2">
@@ -27289,13 +27289,13 @@
         <v>8</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C134" s="2">
         <v>1</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>11</v>
@@ -27304,10 +27304,10 @@
         <v>12</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -27315,13 +27315,13 @@
         <v>8</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C135" s="2">
         <v>0</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>11</v>
@@ -27330,10 +27330,10 @@
         <v>12</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="H135" s="6" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="136" spans="1:8" ht="43.2">
@@ -27341,13 +27341,13 @@
         <v>8</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C136" s="2">
         <v>1</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>11</v>
@@ -27356,10 +27356,10 @@
         <v>12</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
     </row>
     <row r="137" spans="1:8" ht="100.8">
@@ -27367,13 +27367,13 @@
         <v>8</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C137" s="2">
         <v>2</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>11</v>
@@ -27382,24 +27382,24 @@
         <v>12</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="115.2">
       <c r="A138" s="2" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="C138" s="2">
         <v>0</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>11</v>
@@ -27408,10 +27408,10 @@
         <v>12</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
     </row>
     <row r="139" spans="1:8" ht="409.6">
@@ -27419,13 +27419,13 @@
         <v>8</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C139" s="2">
         <v>3</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>11</v>
@@ -27434,10 +27434,10 @@
         <v>12</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
     </row>
     <row r="140" spans="1:8" ht="28.8">
@@ -27445,13 +27445,13 @@
         <v>8</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C140" s="2">
         <v>1</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>11</v>
@@ -27460,10 +27460,10 @@
         <v>12</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -27471,13 +27471,13 @@
         <v>8</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C141" s="2">
         <v>0</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>11</v>
@@ -27486,10 +27486,10 @@
         <v>12</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="H141" s="6" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="142" spans="1:8" ht="57.6">
@@ -27497,13 +27497,13 @@
         <v>8</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C142" s="2">
         <v>1</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>11</v>
@@ -27512,10 +27512,10 @@
         <v>12</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -27523,13 +27523,13 @@
         <v>8</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C143" s="2">
         <v>2</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>11</v>
@@ -27538,10 +27538,10 @@
         <v>12</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H143" s="6" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="144" spans="1:8" ht="43.2">
@@ -27549,13 +27549,13 @@
         <v>8</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C144" s="2">
         <v>3</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>11</v>
@@ -27564,10 +27564,10 @@
         <v>12</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="145" spans="1:8" ht="86.4">
@@ -27575,13 +27575,13 @@
         <v>8</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C145" s="2">
         <v>4</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>11</v>
@@ -27590,10 +27590,10 @@
         <v>12</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="146" spans="1:8" ht="216">
@@ -27601,13 +27601,13 @@
         <v>8</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C146" s="2">
         <v>5</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>11</v>
@@ -27616,10 +27616,10 @@
         <v>12</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="147" spans="1:8" ht="86.4">
@@ -27627,13 +27627,13 @@
         <v>8</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C147" s="2">
         <v>0</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>11</v>
@@ -27642,10 +27642,10 @@
         <v>12</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="148" spans="1:8" ht="86.4">
@@ -27653,13 +27653,13 @@
         <v>8</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C148" s="2">
         <v>1</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>11</v>
@@ -27668,10 +27668,10 @@
         <v>12</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -27679,13 +27679,13 @@
         <v>8</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C149" s="2">
         <v>2</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>11</v>
@@ -27694,10 +27694,10 @@
         <v>12</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H149" s="6" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="150" spans="1:8" ht="86.4">
@@ -27705,13 +27705,13 @@
         <v>8</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C150" s="2">
         <v>0</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>11</v>
@@ -27720,10 +27720,10 @@
         <v>12</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="28.8">
@@ -27731,13 +27731,13 @@
         <v>8</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C151" s="2">
         <v>0</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>11</v>
@@ -27746,10 +27746,10 @@
         <v>12</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -27757,13 +27757,13 @@
         <v>8</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C152" s="2">
         <v>2</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>11</v>
@@ -27772,10 +27772,10 @@
         <v>12</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H152" s="3" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="153" spans="1:8" ht="129.6">
@@ -27783,13 +27783,13 @@
         <v>8</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C153" s="2">
         <v>0</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>11</v>
@@ -27798,10 +27798,10 @@
         <v>12</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="H153" s="3" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="154" spans="1:8" ht="28.8">
@@ -27809,13 +27809,13 @@
         <v>8</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C154" s="2">
         <v>1</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>11</v>
@@ -27824,10 +27824,10 @@
         <v>12</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="155" spans="1:8" ht="28.8">
@@ -27835,13 +27835,13 @@
         <v>8</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C155" s="2">
         <v>0</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>11</v>
@@ -27850,10 +27850,10 @@
         <v>12</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="H155" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="156" spans="1:8" ht="115.2">
@@ -27861,13 +27861,13 @@
         <v>8</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C156" s="2">
         <v>1</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>11</v>
@@ -27876,10 +27876,10 @@
         <v>12</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="157" spans="1:8" ht="28.8">
@@ -27887,13 +27887,13 @@
         <v>8</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C157" s="2">
         <v>0</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>11</v>
@@ -27902,10 +27902,10 @@
         <v>12</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="H157" s="6" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="158" spans="1:8" ht="409.6">
@@ -27913,13 +27913,13 @@
         <v>8</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C158" s="2">
         <v>1</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>11</v>
@@ -27928,10 +27928,10 @@
         <v>12</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="43.2">
@@ -27939,13 +27939,13 @@
         <v>8</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C159" s="2">
         <v>0</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>11</v>
@@ -27954,10 +27954,10 @@
         <v>12</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H159" s="6" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="160" spans="1:8" ht="86.4">
@@ -27965,13 +27965,13 @@
         <v>8</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C160" s="2">
         <v>1</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>11</v>
@@ -27980,10 +27980,10 @@
         <v>12</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="H160" s="3" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="28.8">
@@ -27991,13 +27991,13 @@
         <v>8</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C161" s="2">
         <v>0</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>11</v>
@@ -28006,10 +28006,10 @@
         <v>12</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="H161" s="6" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="144">
@@ -28017,13 +28017,13 @@
         <v>8</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C162" s="2">
         <v>1</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>11</v>
@@ -28032,10 +28032,10 @@
         <v>12</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="100.8">
@@ -28043,13 +28043,13 @@
         <v>8</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C163" s="2">
         <v>0</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>11</v>
@@ -28058,10 +28058,10 @@
         <v>12</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="164" spans="1:8" ht="144">
@@ -28069,13 +28069,13 @@
         <v>8</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C164" s="2">
         <v>1</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>11</v>
@@ -28084,10 +28084,10 @@
         <v>12</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
     </row>
     <row r="165" spans="1:8" ht="100.8">
@@ -28095,13 +28095,13 @@
         <v>8</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C165" s="2">
         <v>0</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>11</v>
@@ -28110,10 +28110,10 @@
         <v>12</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="166" spans="1:8" ht="43.2">
@@ -28121,13 +28121,13 @@
         <v>8</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C166" s="2">
         <v>1</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>11</v>
@@ -28136,10 +28136,10 @@
         <v>12</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H166" s="6" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="115.2">
@@ -28147,13 +28147,13 @@
         <v>8</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C167" s="2">
         <v>0</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>11</v>
@@ -28162,10 +28162,10 @@
         <v>12</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H167" s="3" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="86.4">
@@ -28173,13 +28173,13 @@
         <v>8</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C168" s="2">
         <v>1</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>11</v>
@@ -28188,10 +28188,10 @@
         <v>12</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="169" spans="1:8" ht="86.4">
@@ -28199,13 +28199,13 @@
         <v>8</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C169" s="2">
         <v>0</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>11</v>
@@ -28214,10 +28214,10 @@
         <v>12</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H169" s="3" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="28.8">
@@ -28225,13 +28225,13 @@
         <v>8</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C170" s="2">
         <v>0</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>11</v>
@@ -28240,10 +28240,10 @@
         <v>12</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H170" s="3" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="57.6">
@@ -28251,13 +28251,13 @@
         <v>8</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C171" s="2">
         <v>1</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>11</v>
@@ -28266,10 +28266,10 @@
         <v>12</v>
       </c>
       <c r="G171" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="H171" s="3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -28277,13 +28277,13 @@
         <v>8</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C172" s="2">
         <v>2</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>11</v>
@@ -28292,10 +28292,10 @@
         <v>12</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H172" s="3" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="57.6">
@@ -28303,13 +28303,13 @@
         <v>8</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C173" s="2">
         <v>0</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>11</v>
@@ -28318,10 +28318,10 @@
         <v>12</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="H173" s="6" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="28.8">
@@ -28329,13 +28329,13 @@
         <v>8</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C174" s="2">
         <v>1</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>11</v>
@@ -28344,10 +28344,10 @@
         <v>12</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H174" s="6" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="28.8">
@@ -28355,13 +28355,13 @@
         <v>8</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C175" s="2">
         <v>0</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>11</v>
@@ -28370,10 +28370,10 @@
         <v>12</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H175" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="176" spans="1:8" ht="409.6">
@@ -28381,13 +28381,13 @@
         <v>8</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C176" s="2">
         <v>1</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>11</v>
@@ -28396,10 +28396,10 @@
         <v>12</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
     </row>
     <row r="177" spans="1:8" ht="28.8">
@@ -28407,13 +28407,13 @@
         <v>8</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C177" s="2">
         <v>0</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>11</v>
@@ -28422,10 +28422,10 @@
         <v>12</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H177" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="409.6">
@@ -28433,13 +28433,13 @@
         <v>8</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C178" s="2">
         <v>1</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>11</v>
@@ -28448,10 +28448,10 @@
         <v>12</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="201.6">
@@ -28459,13 +28459,13 @@
         <v>8</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C179" s="2">
         <v>2</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>11</v>
@@ -28474,10 +28474,10 @@
         <v>12</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="H179" s="3" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
     </row>
     <row r="180" spans="1:8" ht="86.4">
@@ -28485,13 +28485,13 @@
         <v>8</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C180" s="2">
         <v>0</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>11</v>
@@ -28500,10 +28500,10 @@
         <v>12</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H180" s="3" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -28511,13 +28511,13 @@
         <v>8</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C181" s="2">
         <v>1</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>11</v>
@@ -28526,7 +28526,7 @@
         <v>12</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="H181" s="6" t="s">
         <v>29</v>
@@ -28537,13 +28537,13 @@
         <v>8</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C182" s="2">
         <v>0</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>11</v>
@@ -28552,10 +28552,10 @@
         <v>12</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -28563,13 +28563,13 @@
         <v>8</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C183" s="2">
         <v>0</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>11</v>
@@ -28578,10 +28578,10 @@
         <v>12</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H183" s="6" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -28589,13 +28589,13 @@
         <v>8</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C184" s="2">
         <v>0</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>11</v>
@@ -28604,10 +28604,10 @@
         <v>12</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -28615,13 +28615,13 @@
         <v>8</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C185" s="2">
         <v>0</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>11</v>
@@ -28630,10 +28630,10 @@
         <v>12</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="H185" s="6" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -28641,13 +28641,13 @@
         <v>8</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C186" s="2">
         <v>0</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>11</v>
@@ -28656,10 +28656,10 @@
         <v>12</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="187" spans="1:8" ht="144">
@@ -28667,13 +28667,13 @@
         <v>8</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C187" s="2">
         <v>0</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>11</v>
@@ -28682,10 +28682,10 @@
         <v>12</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="H187" s="3" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="188" spans="1:8" ht="28.8">
@@ -28693,13 +28693,13 @@
         <v>8</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C188" s="2">
         <v>14</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>11</v>
@@ -28708,10 +28708,10 @@
         <v>12</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="H188" s="6" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="28.8">
@@ -28719,13 +28719,13 @@
         <v>8</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C189" s="2">
         <v>15</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>11</v>
@@ -28734,10 +28734,10 @@
         <v>12</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H189" s="6" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="190" spans="1:8" ht="57.6">
@@ -28745,13 +28745,13 @@
         <v>8</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C190" s="2">
         <v>16</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>11</v>
@@ -28760,10 +28760,10 @@
         <v>12</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="28.8">
@@ -28771,13 +28771,13 @@
         <v>8</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C191" s="2">
         <v>18</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>11</v>
@@ -28786,10 +28786,10 @@
         <v>12</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H191" s="6" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="192" spans="1:8" ht="57.6">
@@ -28797,13 +28797,13 @@
         <v>8</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C192" s="2">
         <v>20</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>11</v>
@@ -28812,10 +28812,10 @@
         <v>12</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H192" s="3" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="193" spans="1:8" ht="43.2">
@@ -28823,13 +28823,13 @@
         <v>8</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C193" s="2">
         <v>21</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>11</v>
@@ -28838,10 +28838,10 @@
         <v>12</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="H193" s="6" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="194" spans="1:8" ht="28.8">
@@ -28849,13 +28849,13 @@
         <v>8</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C194" s="2">
         <v>22</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>11</v>
@@ -28864,10 +28864,10 @@
         <v>12</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="H194" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="195" spans="1:8" ht="28.8">
@@ -28875,13 +28875,13 @@
         <v>8</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C195" s="2">
         <v>29</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>11</v>
@@ -28890,10 +28890,10 @@
         <v>12</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="H195" s="6" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="196" spans="1:8" ht="244.8">
@@ -28901,13 +28901,13 @@
         <v>8</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C196" s="2">
         <v>30</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>11</v>
@@ -28916,10 +28916,10 @@
         <v>12</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="H196" s="6" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="197" spans="1:8">
@@ -28927,13 +28927,13 @@
         <v>8</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C197" s="2">
         <v>31</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>11</v>
@@ -28942,7 +28942,7 @@
         <v>12</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="H197" s="6" t="s">
         <v>14</v>
@@ -28953,13 +28953,13 @@
         <v>8</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C198" s="2">
         <v>0</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>11</v>
@@ -28968,10 +28968,10 @@
         <v>12</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="H198" s="6" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="28.8">
@@ -28979,13 +28979,13 @@
         <v>8</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C199" s="2">
         <v>1</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>11</v>
@@ -28994,10 +28994,10 @@
         <v>12</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="H199" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="200" spans="1:8">
@@ -29005,13 +29005,13 @@
         <v>8</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C200" s="2">
         <v>2</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>11</v>
@@ -29020,10 +29020,10 @@
         <v>12</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="H200" s="6" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
     <row r="201" spans="1:8" ht="100.8">
@@ -29031,13 +29031,13 @@
         <v>8</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C201" s="2">
         <v>3</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>11</v>
@@ -29046,10 +29046,10 @@
         <v>12</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
     </row>
     <row r="202" spans="1:8" ht="158.4">
@@ -29057,13 +29057,13 @@
         <v>8</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C202" s="2">
         <v>4</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>11</v>
@@ -29072,10 +29072,10 @@
         <v>12</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="H202" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="203" spans="1:8" ht="43.2">
@@ -29083,13 +29083,13 @@
         <v>8</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C203" s="2">
         <v>5</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>11</v>
@@ -29098,10 +29098,10 @@
         <v>12</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="H203" s="3" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="100.8">
@@ -29109,13 +29109,13 @@
         <v>8</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C204" s="2">
         <v>6</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>11</v>
@@ -29124,10 +29124,10 @@
         <v>12</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="H204" s="3" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="205" spans="1:8" ht="43.2">
@@ -29135,13 +29135,13 @@
         <v>8</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C205" s="2">
         <v>7</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>11</v>
@@ -29150,10 +29150,10 @@
         <v>12</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="H205" s="3" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="100.8">
@@ -29161,13 +29161,13 @@
         <v>8</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C206" s="2">
         <v>8</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>11</v>
@@ -29176,10 +29176,10 @@
         <v>12</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="H206" s="3" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="207" spans="1:8" ht="100.8">
@@ -29187,13 +29187,13 @@
         <v>8</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C207" s="2">
         <v>9</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>11</v>
@@ -29202,10 +29202,10 @@
         <v>12</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="H207" s="3" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="115.2">
@@ -29213,13 +29213,13 @@
         <v>8</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C208" s="2">
         <v>10</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>11</v>
@@ -29228,10 +29228,10 @@
         <v>12</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="H208" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="209" spans="1:9" ht="158.4">
@@ -29239,13 +29239,13 @@
         <v>8</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C209" s="2">
         <v>11</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>11</v>
@@ -29254,10 +29254,10 @@
         <v>12</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="H209" s="3" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="210" spans="1:9" ht="172.8">
@@ -29265,13 +29265,13 @@
         <v>8</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C210" s="2">
         <v>12</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>11</v>
@@ -29280,10 +29280,10 @@
         <v>12</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="H210" s="3" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
     <row r="211" spans="1:9" ht="115.2">
@@ -29291,13 +29291,13 @@
         <v>8</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C211" s="2">
         <v>13</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>11</v>
@@ -29306,10 +29306,10 @@
         <v>12</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="H211" s="3" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="212" spans="1:9" ht="158.4">
@@ -29317,13 +29317,13 @@
         <v>8</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C212" s="2">
         <v>14</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>11</v>
@@ -29332,10 +29332,10 @@
         <v>12</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="H212" s="3" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
     </row>
     <row r="213" spans="1:9" ht="158.4">
@@ -29343,13 +29343,13 @@
         <v>8</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C213" s="2">
         <v>15</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>11</v>
@@ -29358,10 +29358,10 @@
         <v>12</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="H213" s="3" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="214" spans="1:9" ht="100.8">
@@ -29369,13 +29369,13 @@
         <v>8</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C214" s="2">
         <v>16</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>11</v>
@@ -29384,10 +29384,10 @@
         <v>12</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H214" s="3" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
     </row>
     <row r="215" spans="1:9" ht="100.8">
@@ -29395,13 +29395,13 @@
         <v>8</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C215" s="2">
         <v>17</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>11</v>
@@ -29410,10 +29410,10 @@
         <v>12</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="H215" s="3" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
     </row>
     <row r="216" spans="1:9" ht="43.2">
@@ -29421,13 +29421,13 @@
         <v>8</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C216" s="2">
         <v>18</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>11</v>
@@ -29436,10 +29436,10 @@
         <v>12</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="217" spans="1:9" ht="43.2">
@@ -29447,13 +29447,13 @@
         <v>8</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C217" s="2">
         <v>19</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>11</v>
@@ -29462,10 +29462,10 @@
         <v>12</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H217" s="3" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="218" spans="1:9" ht="43.2">
@@ -29473,13 +29473,13 @@
         <v>8</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C218" s="2">
         <v>20</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>11</v>
@@ -29488,10 +29488,10 @@
         <v>12</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="H218" s="3" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="219" spans="1:9" ht="409.6">
@@ -29499,13 +29499,13 @@
         <v>8</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C219" s="2">
         <v>21</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>11</v>
@@ -29514,10 +29514,10 @@
         <v>12</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="H219" s="3" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="I219" s="3"/>
     </row>
@@ -29526,13 +29526,13 @@
         <v>8</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C220" s="2">
         <v>22</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>11</v>
@@ -29541,10 +29541,10 @@
         <v>12</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="H220" s="3" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="221" spans="1:9" ht="43.2">
@@ -29552,13 +29552,13 @@
         <v>8</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C221" s="2">
         <v>23</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>11</v>
@@ -29567,10 +29567,10 @@
         <v>12</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="H221" s="3" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="222" spans="1:9" ht="86.4">
@@ -29578,13 +29578,13 @@
         <v>8</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C222" s="2">
         <v>24</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>11</v>
@@ -29593,10 +29593,10 @@
         <v>12</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H222" s="3" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="223" spans="1:9" ht="115.2">
@@ -29604,13 +29604,13 @@
         <v>8</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C223" s="2">
         <v>25</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>11</v>
@@ -29619,10 +29619,10 @@
         <v>12</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="H223" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="224" spans="1:9" ht="43.2">
@@ -29630,13 +29630,13 @@
         <v>8</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C224" s="2">
         <v>26</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>11</v>
@@ -29645,10 +29645,10 @@
         <v>12</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="H224" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="225" spans="1:8" ht="100.8">
@@ -29656,13 +29656,13 @@
         <v>8</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C225" s="2">
         <v>27</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>11</v>
@@ -29671,10 +29671,10 @@
         <v>12</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="H225" s="3" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
     </row>
     <row r="226" spans="1:8" ht="43.2">
@@ -29682,13 +29682,13 @@
         <v>8</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C226" s="2">
         <v>28</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>11</v>
@@ -29697,10 +29697,10 @@
         <v>12</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="H226" s="3" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="227" spans="1:8" ht="43.2">
@@ -29708,13 +29708,13 @@
         <v>8</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C227" s="2">
         <v>29</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>11</v>
@@ -29723,10 +29723,10 @@
         <v>12</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="H227" s="3" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="228" spans="1:8" ht="100.8">
@@ -29734,13 +29734,13 @@
         <v>8</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C228" s="2">
         <v>30</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>11</v>
@@ -29749,10 +29749,10 @@
         <v>12</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
     </row>
     <row r="229" spans="1:8" ht="28.8">
@@ -29760,13 +29760,13 @@
         <v>8</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C229" s="2">
         <v>0</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>11</v>
@@ -29775,10 +29775,10 @@
         <v>12</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="H229" s="6" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="230" spans="1:8" ht="28.8">
@@ -29786,13 +29786,13 @@
         <v>8</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C230" s="2">
         <v>0</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>11</v>
@@ -29801,10 +29801,10 @@
         <v>12</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H230" s="3" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="231" spans="1:8" ht="43.2">
@@ -29812,13 +29812,13 @@
         <v>8</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C231" s="2">
         <v>1</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>11</v>
@@ -29827,10 +29827,10 @@
         <v>12</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="H231" s="3" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="232" spans="1:8" ht="100.8">
@@ -29838,13 +29838,13 @@
         <v>8</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C232" s="2">
         <v>2</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>11</v>
@@ -29853,10 +29853,10 @@
         <v>12</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="H232" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="233" spans="1:8" ht="43.2">
@@ -29864,13 +29864,13 @@
         <v>8</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C233" s="2">
         <v>3</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>11</v>
@@ -29879,10 +29879,10 @@
         <v>12</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="H233" s="3" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="234" spans="1:8">
@@ -29890,13 +29890,13 @@
         <v>8</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C234" s="2">
         <v>0</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>11</v>
@@ -29905,10 +29905,10 @@
         <v>12</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H234" s="6" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="235" spans="1:8">
@@ -29916,13 +29916,13 @@
         <v>8</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C235" s="2">
         <v>0</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>11</v>
@@ -29931,10 +29931,10 @@
         <v>12</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="H235" s="6" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="236" spans="1:8" ht="28.8">
@@ -29942,13 +29942,13 @@
         <v>8</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C236" s="2">
         <v>1</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>11</v>
@@ -29957,10 +29957,10 @@
         <v>12</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="H236" s="6" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="237" spans="1:8">
@@ -29968,13 +29968,13 @@
         <v>8</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C237" s="2">
         <v>0</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>11</v>
@@ -29983,10 +29983,10 @@
         <v>12</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H237" s="6" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="238" spans="1:8" ht="28.8">
@@ -29994,13 +29994,13 @@
         <v>8</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C238" s="2">
         <v>1</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>11</v>
@@ -30009,10 +30009,10 @@
         <v>12</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="H238" s="4" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -30020,13 +30020,13 @@
         <v>8</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C239" s="2">
         <v>0</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>11</v>
@@ -30035,7 +30035,7 @@
         <v>12</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H239" s="4" t="s">
         <v>23</v>
@@ -30046,13 +30046,13 @@
         <v>8</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C240" s="2">
         <v>1</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>11</v>
@@ -30061,10 +30061,10 @@
         <v>12</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H240" s="4" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="241" spans="1:8">
@@ -30072,13 +30072,13 @@
         <v>8</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C241" s="2">
         <v>0</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>11</v>
@@ -30087,24 +30087,24 @@
         <v>12</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="H241" s="4" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="242" spans="1:8">
       <c r="A242" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B242" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C242">
         <v>1</v>
       </c>
       <c r="D242" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="E242" t="s">
         <v>11</v>
@@ -30113,10 +30113,10 @@
         <v>12</v>
       </c>
       <c r="G242" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="H242" s="4" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
     </row>
     <row r="243" spans="1:8">

--- a/docassemble/PowerOfAttorneyHealthCare/data/sources/poa_hc_es.xlsx
+++ b/docassemble/PowerOfAttorneyHealthCare/data/sources/poa_hc_es.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnewsted\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A473E20-9C94-4332-A243-5B783B93F23A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702F067C-3D08-41ED-868D-E66DFCC589C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-36045" yWindow="-2865" windowWidth="28485" windowHeight="16530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-34770" yWindow="-4050" windowWidth="32145" windowHeight="17925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1695" uniqueCount="804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1702" uniqueCount="807">
   <si>
     <t>interview</t>
   </si>
@@ -9836,361 +9836,6 @@
     </r>
   </si>
   <si>
-    <t>f2e5234888400378d931fe3723a15fc9</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**Your disposition of remains instructions:**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if self_remains_preference != "specific":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${self_remains_preference}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${self_specific_burial_preference}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-  </si>
-  <si>
-    <t>610f4d316b71903bcb4b12bd192286d0</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>**</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">'s disposition of remains instructions:**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if other_remains_preference != "specific":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${other_remains_preference}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${other_specific_burial_preference}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-  </si>
-  <si>
-    <t>4b38fa91082a93045d1774e44ffe256e</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**Would you like to donate your organs?**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${self_organ_donor}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
-    <t>5eb63675cc1df0b911334cfe5c33a105</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**Would </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> like to donate their organs?**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${other_organ_donor}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**¿Quisiera </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> donar sus órganos?**  
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${other_organ_donor}</t>
-    </r>
-  </si>
-  <si>
     <t>46596387ba6a257c63d7cacaf2679952</t>
   </si>
   <si>
@@ -16352,30 +15997,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">**¿Quisieras donar tus órganos?**  
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${self_organ_donor}</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">**¿La autoridad de </t>
     </r>
     <r>
@@ -22505,211 +22126,6 @@
       <t xml:space="preserve">
 **Nota:** El Poder Notarial debe firmarse frente a al menos un testigo para que sea válido.
 ¡Gracias por usar los Formularios Guiados de ILAO!</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**Instrucciones sobre la disposición de tus restos: (En inglés)** 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if self_remains_preference != "specific":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${self_remains_preference}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${self_specific_burial_preference}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**Instrucciones sobre la disposición de los restos de </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()} (En inglés)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if other_remains_preference != "specific":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${other_remains_preference}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${other_specific_burial_preference}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
     </r>
   </si>
   <si>
@@ -23350,6 +22766,870 @@
       </rPr>
       <t>) para encontrar servicios legales gratuitos o de bajo costo en tu área.
 Para direcciones internacionales, habrá espacio para ingresar la dirección en dos líneas. Debes escribir la dirección internacional usando el alfabeto inglés.</t>
+    </r>
+  </si>
+  <si>
+    <t>b1de226d3a94dae7311aa4d010edf401</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Enter </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">'s address below.
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Ingrese la dirección de ${agent.name_full()} a continuación.</t>
+  </si>
+  <si>
+    <t>9aa7634ed326cf05a8e3f53a8f59fc2b</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**Would you like to donate your organs?**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if self_organ_donor == "I would like my agent to decide this.":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">I would like my agent to decide this.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${self_organ_donor}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+  </si>
+  <si>
+    <t>d253affb5ee2ddbc896f171a10a681af</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**Would </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> like to donate their organs?**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if other_organ_donor == "They would like their agent to decide this.":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">They would like their agent to decide this.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${other_organ_donor}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">**¿Quisieras donar tus órganos?**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if self_organ_donor == "I would like my agent to decide this.":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Quiero que mi agente decida esto.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${self_organ_donor}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">**¿Quisiera ${principal.name_full()} donar sus órganos?**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if other_organ_donor == "They would like their agent to decide this.":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Prefiere que su agente decida esto.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${other_organ_donor}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+  </si>
+  <si>
+    <t>f59afd349b753b7eb1cbb757a20d28bc</t>
+  </si>
+  <si>
+    <t>3c0c7296e37f91716c4610531e14ddd1</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">**Your disposition of remains instructions:**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if self_remains_preference != "specific":
+% if self_remains_preference == "I would prefer a burial for my remains.":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">I would prefer a burial for my remains.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif self_remains_preference == "I would prefer my remains be cremated.":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">I would prefer my remains be cremated.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">I do not have a preference.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${self_specific_burial_preference}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**Instrucciones sobre la disposición de tus restos:** 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if self_remains_preference != "specific":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% if self_remains_preference == "I would prefer a burial for my remains.":
+Prefiero que mis restos sean enterrados.
+% elif self_remains_preference == "I would prefer my remains be cremated.":
+Prefiero que mis restos sean cremados.
+% else:
+No tengo una preferencia.
+% endif</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(En inglés) ${self_specific_burial_preference}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% endif</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">'s disposition of remains instructions:**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if other_remains_preference != "specific":
+% if other_remains_preference == "They would prefer a burial for their remains.":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">They would prefer a burial for their remains.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif other_remains_preference == "They would prefer their remains be cremated.":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">They would prefer their remains be cremated.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">They do not have a preference.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${other_specific_burial_preference}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**Instrucciones sobre la disposición de los restos de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% if other_remains_preference != "specific":</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+% if other_remains_preference == "They would prefer a burial for their remains.":
+Preferiría que sus restos fueran enterrados.
+% elif other_remains_preference == "They would prefer their remains be cremated.":
+Preferiría que sus restos fueran cremados.
+% else:
+No tiene una preferencia.
+% endif</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(En inglés) ${other_specific_burial_preference}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% endif</t>
     </r>
   </si>
 </sst>
@@ -23815,7 +24095,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I244"/>
+  <dimension ref="A1:I245"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="61.109375" customWidth="1"/>
@@ -23889,7 +24169,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>786</v>
+        <v>774</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>11</v>
@@ -23898,10 +24178,10 @@
         <v>12</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>787</v>
+        <v>775</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>788</v>
+        <v>776</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -23953,7 +24233,7 @@
         <v>20</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -24057,7 +24337,7 @@
         <v>31</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>734</v>
+        <v>724</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="28.8">
@@ -24071,7 +24351,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>739</v>
+        <v>729</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>11</v>
@@ -24080,7 +24360,7 @@
         <v>12</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>742</v>
+        <v>732</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>33</v>
@@ -24097,7 +24377,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>740</v>
+        <v>730</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>11</v>
@@ -24106,7 +24386,7 @@
         <v>12</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>741</v>
+        <v>731</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>34</v>
@@ -24123,7 +24403,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>795</v>
+        <v>783</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>11</v>
@@ -24132,10 +24412,10 @@
         <v>12</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>796</v>
+        <v>784</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>799</v>
+        <v>787</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="216">
@@ -24149,7 +24429,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>797</v>
+        <v>785</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>11</v>
@@ -24158,10 +24438,10 @@
         <v>12</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>800</v>
+        <v>788</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="28.8">
@@ -24213,7 +24493,7 @@
         <v>41</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>757</v>
+        <v>747</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="28.8">
@@ -24265,21 +24545,21 @@
         <v>47</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="115.2">
       <c r="A18" s="2" t="s">
-        <v>752</v>
+        <v>742</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>758</v>
+        <v>748</v>
       </c>
       <c r="C18" s="2">
         <v>0</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>759</v>
+        <v>749</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>11</v>
@@ -24288,18 +24568,18 @@
         <v>12</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>760</v>
+        <v>750</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>761</v>
+        <v>751</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="28.8">
       <c r="A19" s="2" t="s">
-        <v>752</v>
+        <v>742</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>758</v>
+        <v>748</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
@@ -24343,7 +24623,7 @@
         <v>53</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -24369,7 +24649,7 @@
         <v>56</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="43.2">
@@ -24395,7 +24675,7 @@
         <v>58</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>735</v>
+        <v>725</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="57.6">
@@ -24421,7 +24701,7 @@
         <v>60</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>736</v>
+        <v>726</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="28.8">
@@ -24447,7 +24727,7 @@
         <v>62</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="57.6">
@@ -24473,12 +24753,12 @@
         <v>64</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="2" t="s">
-        <v>752</v>
+        <v>742</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>54</v>
@@ -24487,7 +24767,7 @@
         <v>5</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>789</v>
+        <v>777</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>11</v>
@@ -24496,15 +24776,15 @@
         <v>12</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>790</v>
+        <v>778</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>793</v>
+        <v>781</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="2" t="s">
-        <v>752</v>
+        <v>742</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>54</v>
@@ -24513,7 +24793,7 @@
         <v>6</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>791</v>
+        <v>779</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>11</v>
@@ -24522,10 +24802,10 @@
         <v>12</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>792</v>
+        <v>780</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>794</v>
+        <v>782</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="28.8">
@@ -24551,7 +24831,7 @@
         <v>67</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="244.8">
@@ -24577,7 +24857,7 @@
         <v>69</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="86.4">
@@ -24603,7 +24883,7 @@
         <v>72</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="409.6">
@@ -24617,7 +24897,7 @@
         <v>1</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>769</v>
+        <v>759</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>11</v>
@@ -24626,10 +24906,10 @@
         <v>12</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>770</v>
+        <v>760</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>771</v>
+        <v>761</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -24655,7 +24935,7 @@
         <v>74</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -24681,7 +24961,7 @@
         <v>76</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -24707,7 +24987,7 @@
         <v>78</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -24733,7 +25013,7 @@
         <v>80</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>766</v>
+        <v>756</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -24785,7 +25065,7 @@
         <v>85</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="100.8">
@@ -24811,7 +25091,7 @@
         <v>88</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="28.8">
@@ -24837,7 +25117,7 @@
         <v>90</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="86.4">
@@ -24863,7 +25143,7 @@
         <v>93</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="28.8">
@@ -24889,7 +25169,7 @@
         <v>96</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="144">
@@ -24915,7 +25195,7 @@
         <v>98</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="86.4">
@@ -24967,7 +25247,7 @@
         <v>105</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="374.4">
@@ -24993,7 +25273,7 @@
         <v>107</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="86.4">
@@ -25019,7 +25299,7 @@
         <v>110</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="28.8">
@@ -25045,7 +25325,7 @@
         <v>112</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="28.8">
@@ -25071,7 +25351,7 @@
         <v>115</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -25097,7 +25377,7 @@
         <v>117</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="43.2">
@@ -25123,12 +25403,12 @@
         <v>119</v>
       </c>
       <c r="H50" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" ht="28.8">
       <c r="A51" s="2" t="s">
-        <v>8</v>
+        <v>742</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>113</v>
@@ -25137,7 +25417,7 @@
         <v>4</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>120</v>
+        <v>792</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>11</v>
@@ -25146,10 +25426,10 @@
         <v>12</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>608</v>
+        <v>793</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>794</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -25160,10 +25440,10 @@
         <v>113</v>
       </c>
       <c r="C52" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>11</v>
@@ -25172,24 +25452,24 @@
         <v>12</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="129.6">
+    <row r="53" spans="1:8">
       <c r="A53" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="C53" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>801</v>
+        <v>122</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>11</v>
@@ -25198,13 +25478,13 @@
         <v>12</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>802</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>803</v>
+        <v>123</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>600</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="28.8">
+    <row r="54" spans="1:8" ht="129.6">
       <c r="A54" s="2" t="s">
         <v>8</v>
       </c>
@@ -25212,10 +25492,10 @@
         <v>124</v>
       </c>
       <c r="C54" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>125</v>
+        <v>789</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>11</v>
@@ -25224,10 +25504,10 @@
         <v>12</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>737</v>
+        <v>790</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>791</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="28.8">
@@ -25235,13 +25515,13 @@
         <v>8</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C55" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>11</v>
@@ -25250,13 +25530,13 @@
         <v>12</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>727</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="100.8">
+    <row r="56" spans="1:8" ht="28.8">
       <c r="A56" s="2" t="s">
         <v>8</v>
       </c>
@@ -25264,10 +25544,10 @@
         <v>127</v>
       </c>
       <c r="C56" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>11</v>
@@ -25276,10 +25556,10 @@
         <v>12</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>610</v>
+        <v>130</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="100.8">
@@ -25287,13 +25567,13 @@
         <v>8</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C57" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>11</v>
@@ -25302,13 +25582,13 @@
         <v>12</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>772</v>
+        <v>601</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="288">
+    <row r="58" spans="1:8" ht="100.8">
       <c r="A58" s="2" t="s">
         <v>8</v>
       </c>
@@ -25316,10 +25596,10 @@
         <v>133</v>
       </c>
       <c r="C58" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>11</v>
@@ -25328,24 +25608,24 @@
         <v>12</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>708</v>
+        <v>762</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="28.8">
+    <row r="59" spans="1:8" ht="288">
       <c r="A59" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C59" s="2">
         <v>1</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>11</v>
@@ -25354,24 +25634,24 @@
         <v>12</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="H59" s="6" t="s">
-        <v>611</v>
+        <v>137</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>698</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" ht="28.8">
       <c r="A60" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C60" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>11</v>
@@ -25380,13 +25660,13 @@
         <v>12</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>144</v>
+        <v>602</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="28.8">
+    <row r="61" spans="1:8">
       <c r="A61" s="2" t="s">
         <v>8</v>
       </c>
@@ -25394,10 +25674,10 @@
         <v>141</v>
       </c>
       <c r="C61" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>11</v>
@@ -25406,10 +25686,10 @@
         <v>12</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>612</v>
+        <v>144</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="28.8">
@@ -25420,10 +25700,10 @@
         <v>141</v>
       </c>
       <c r="C62" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>11</v>
@@ -25432,13 +25712,13 @@
         <v>12</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>613</v>
+        <v>146</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>603</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="144">
+    <row r="63" spans="1:8" ht="28.8">
       <c r="A63" s="2" t="s">
         <v>8</v>
       </c>
@@ -25446,10 +25726,10 @@
         <v>141</v>
       </c>
       <c r="C63" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>11</v>
@@ -25458,13 +25738,13 @@
         <v>12</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>614</v>
+        <v>604</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" ht="144">
       <c r="A64" s="2" t="s">
         <v>8</v>
       </c>
@@ -25472,10 +25752,10 @@
         <v>141</v>
       </c>
       <c r="C64" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>11</v>
@@ -25484,13 +25764,13 @@
         <v>12</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="H64" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>605</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="28.8">
+    <row r="65" spans="1:8">
       <c r="A65" s="2" t="s">
         <v>8</v>
       </c>
@@ -25498,10 +25778,10 @@
         <v>141</v>
       </c>
       <c r="C65" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>11</v>
@@ -25510,13 +25790,13 @@
         <v>12</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H65" s="6" t="s">
-        <v>156</v>
+        <v>152</v>
+      </c>
+      <c r="H65" s="5" t="s">
+        <v>153</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" ht="28.8">
       <c r="A66" s="2" t="s">
         <v>8</v>
       </c>
@@ -25524,10 +25804,10 @@
         <v>141</v>
       </c>
       <c r="C66" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>11</v>
@@ -25536,13 +25816,13 @@
         <v>12</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>615</v>
+        <v>156</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="43.2">
+    <row r="67" spans="1:8">
       <c r="A67" s="2" t="s">
         <v>8</v>
       </c>
@@ -25550,10 +25830,10 @@
         <v>141</v>
       </c>
       <c r="C67" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>11</v>
@@ -25562,13 +25842,13 @@
         <v>12</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="57.6">
+    <row r="68" spans="1:8" ht="43.2">
       <c r="A68" s="2" t="s">
         <v>8</v>
       </c>
@@ -25576,10 +25856,10 @@
         <v>141</v>
       </c>
       <c r="C68" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>11</v>
@@ -25588,13 +25868,13 @@
         <v>12</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>617</v>
+        <v>607</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" ht="57.6">
       <c r="A69" s="2" t="s">
         <v>8</v>
       </c>
@@ -25602,10 +25882,10 @@
         <v>141</v>
       </c>
       <c r="C69" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>11</v>
@@ -25614,24 +25894,24 @@
         <v>12</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>165</v>
+        <v>608</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="28.8">
+    <row r="70" spans="1:8">
       <c r="A70" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="C70" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>11</v>
@@ -25640,13 +25920,13 @@
         <v>12</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>618</v>
+        <v>164</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>165</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="172.8">
+    <row r="71" spans="1:8" ht="28.8">
       <c r="A71" s="2" t="s">
         <v>8</v>
       </c>
@@ -25654,10 +25934,10 @@
         <v>166</v>
       </c>
       <c r="C71" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>11</v>
@@ -25666,13 +25946,13 @@
         <v>12</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>709</v>
+        <v>609</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="28.8">
+    <row r="72" spans="1:8" ht="172.8">
       <c r="A72" s="2" t="s">
         <v>8</v>
       </c>
@@ -25680,10 +25960,10 @@
         <v>166</v>
       </c>
       <c r="C72" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>11</v>
@@ -25692,13 +25972,13 @@
         <v>12</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H72" s="9" t="s">
-        <v>710</v>
+        <v>170</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>699</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" ht="28.8">
       <c r="A73" s="2" t="s">
         <v>8</v>
       </c>
@@ -25706,10 +25986,10 @@
         <v>166</v>
       </c>
       <c r="C73" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>11</v>
@@ -25718,13 +25998,13 @@
         <v>12</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>619</v>
+        <v>172</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>700</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="43.2">
+    <row r="74" spans="1:8">
       <c r="A74" s="2" t="s">
         <v>8</v>
       </c>
@@ -25732,10 +26012,10 @@
         <v>166</v>
       </c>
       <c r="C74" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>11</v>
@@ -25744,13 +26024,13 @@
         <v>12</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="57.6">
+    <row r="75" spans="1:8" ht="43.2">
       <c r="A75" s="2" t="s">
         <v>8</v>
       </c>
@@ -25758,10 +26038,10 @@
         <v>166</v>
       </c>
       <c r="C75" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>11</v>
@@ -25770,13 +26050,13 @@
         <v>12</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H75" s="6" t="s">
-        <v>712</v>
+        <v>176</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>611</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" ht="57.6">
       <c r="A76" s="2" t="s">
         <v>8</v>
       </c>
@@ -25784,10 +26064,10 @@
         <v>166</v>
       </c>
       <c r="C76" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>11</v>
@@ -25796,24 +26076,24 @@
         <v>12</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>621</v>
+        <v>178</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>702</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="28.8">
+    <row r="77" spans="1:8">
       <c r="A77" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="C77" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>11</v>
@@ -25822,13 +26102,13 @@
         <v>12</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H77" s="6" t="s">
-        <v>184</v>
+        <v>180</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>612</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="144">
+    <row r="78" spans="1:8" ht="28.8">
       <c r="A78" s="2" t="s">
         <v>8</v>
       </c>
@@ -25836,10 +26116,10 @@
         <v>181</v>
       </c>
       <c r="C78" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>11</v>
@@ -25848,24 +26128,24 @@
         <v>12</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>711</v>
+        <v>183</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>184</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="115.2">
+    <row r="79" spans="1:8" ht="144">
       <c r="A79" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C79" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>11</v>
@@ -25874,13 +26154,13 @@
         <v>12</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>623</v>
+        <v>701</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="360">
+    <row r="80" spans="1:8" ht="115.2">
       <c r="A80" s="2" t="s">
         <v>8</v>
       </c>
@@ -25888,10 +26168,10 @@
         <v>187</v>
       </c>
       <c r="C80" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>11</v>
@@ -25900,24 +26180,24 @@
         <v>12</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>713</v>
+        <v>614</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="28.8">
+    <row r="81" spans="1:8" ht="360">
       <c r="A81" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C81" s="2">
         <v>1</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>11</v>
@@ -25926,10 +26206,10 @@
         <v>12</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="H81" s="6" t="s">
-        <v>624</v>
+        <v>191</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>703</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="28.8">
@@ -25937,13 +26217,13 @@
         <v>8</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C82" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>11</v>
@@ -25952,13 +26232,13 @@
         <v>12</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>767</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>625</v>
+        <v>194</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>615</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="72">
+    <row r="83" spans="1:8" ht="28.8">
       <c r="A83" s="2" t="s">
         <v>8</v>
       </c>
@@ -25966,10 +26246,10 @@
         <v>195</v>
       </c>
       <c r="C83" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>11</v>
@@ -25978,10 +26258,10 @@
         <v>12</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>198</v>
+        <v>757</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="72">
@@ -25992,10 +26272,10 @@
         <v>195</v>
       </c>
       <c r="C84" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>11</v>
@@ -26004,13 +26284,13 @@
         <v>12</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>714</v>
+        <v>617</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" ht="72">
       <c r="A85" s="2" t="s">
         <v>8</v>
       </c>
@@ -26018,10 +26298,10 @@
         <v>195</v>
       </c>
       <c r="C85" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>11</v>
@@ -26030,13 +26310,13 @@
         <v>12</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="H85" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>704</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="43.2">
+    <row r="86" spans="1:8">
       <c r="A86" s="2" t="s">
         <v>8</v>
       </c>
@@ -26044,10 +26324,10 @@
         <v>195</v>
       </c>
       <c r="C86" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>11</v>
@@ -26056,13 +26336,13 @@
         <v>12</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>627</v>
+        <v>202</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>203</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" ht="43.2">
       <c r="A87" s="2" t="s">
         <v>8</v>
       </c>
@@ -26070,10 +26350,10 @@
         <v>195</v>
       </c>
       <c r="C87" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>11</v>
@@ -26082,10 +26362,10 @@
         <v>12</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="H87" s="6" t="s">
-        <v>628</v>
+        <v>205</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -26096,10 +26376,10 @@
         <v>195</v>
       </c>
       <c r="C88" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>11</v>
@@ -26108,24 +26388,24 @@
         <v>12</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>210</v>
+        <v>619</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="172.8">
+    <row r="89" spans="1:8">
       <c r="A89" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="C89" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>11</v>
@@ -26134,13 +26414,13 @@
         <v>12</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>715</v>
+        <v>210</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="43.2">
+    <row r="90" spans="1:8" ht="172.8">
       <c r="A90" s="2" t="s">
         <v>8</v>
       </c>
@@ -26148,10 +26428,10 @@
         <v>211</v>
       </c>
       <c r="C90" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>11</v>
@@ -26160,10 +26440,10 @@
         <v>12</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>629</v>
+        <v>705</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="43.2">
@@ -26171,13 +26451,13 @@
         <v>8</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C91" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>11</v>
@@ -26186,13 +26466,13 @@
         <v>12</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>630</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>716</v>
+        <v>215</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>620</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="72">
+    <row r="92" spans="1:8" ht="43.2">
       <c r="A92" s="2" t="s">
         <v>8</v>
       </c>
@@ -26200,10 +26480,10 @@
         <v>216</v>
       </c>
       <c r="C92" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>11</v>
@@ -26212,10 +26492,10 @@
         <v>12</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>219</v>
+        <v>621</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>631</v>
+        <v>706</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="72">
@@ -26226,10 +26506,10 @@
         <v>216</v>
       </c>
       <c r="C93" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>11</v>
@@ -26238,13 +26518,13 @@
         <v>12</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>717</v>
+        <v>622</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" ht="72">
       <c r="A94" s="2" t="s">
         <v>8</v>
       </c>
@@ -26252,10 +26532,10 @@
         <v>216</v>
       </c>
       <c r="C94" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>11</v>
@@ -26264,13 +26544,13 @@
         <v>12</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>707</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="57.6">
+    <row r="95" spans="1:8">
       <c r="A95" s="2" t="s">
         <v>8</v>
       </c>
@@ -26278,10 +26558,10 @@
         <v>216</v>
       </c>
       <c r="C95" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>11</v>
@@ -26290,13 +26570,13 @@
         <v>12</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="H95" s="3" t="s">
-        <v>632</v>
+        <v>223</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>224</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" ht="57.6">
       <c r="A96" s="2" t="s">
         <v>8</v>
       </c>
@@ -26304,10 +26584,10 @@
         <v>216</v>
       </c>
       <c r="C96" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>11</v>
@@ -26316,10 +26596,10 @@
         <v>12</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>633</v>
+        <v>226</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>623</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -26330,10 +26610,10 @@
         <v>216</v>
       </c>
       <c r="C97" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>11</v>
@@ -26342,24 +26622,24 @@
         <v>12</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>634</v>
+        <v>624</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="201.6">
+    <row r="98" spans="1:8">
       <c r="A98" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="C98" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>11</v>
@@ -26368,24 +26648,24 @@
         <v>12</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>635</v>
+        <v>230</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>625</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="28.8">
+    <row r="99" spans="1:8" ht="201.6">
       <c r="A99" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C99" s="2">
         <v>0</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>11</v>
@@ -26394,13 +26674,13 @@
         <v>12</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="H99" s="6" t="s">
-        <v>718</v>
+        <v>233</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>626</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="129.6">
+    <row r="100" spans="1:8" ht="28.8">
       <c r="A100" s="2" t="s">
         <v>8</v>
       </c>
@@ -26408,10 +26688,10 @@
         <v>234</v>
       </c>
       <c r="C100" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>11</v>
@@ -26420,24 +26700,24 @@
         <v>12</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>773</v>
+        <v>236</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>708</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="86.4">
+    <row r="101" spans="1:8" ht="129.6">
       <c r="A101" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C101" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>11</v>
@@ -26446,13 +26726,13 @@
         <v>12</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>636</v>
+        <v>763</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="302.39999999999998">
+    <row r="102" spans="1:8" ht="86.4">
       <c r="A102" s="2" t="s">
         <v>8</v>
       </c>
@@ -26460,10 +26740,10 @@
         <v>239</v>
       </c>
       <c r="C102" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>11</v>
@@ -26472,24 +26752,24 @@
         <v>12</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>738</v>
+        <v>627</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="28.8">
+    <row r="103" spans="1:8" ht="302.39999999999998">
       <c r="A103" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C103" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>11</v>
@@ -26498,13 +26778,13 @@
         <v>12</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>637</v>
+        <v>728</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="86.4">
+    <row r="104" spans="1:8" ht="28.8">
       <c r="A104" s="2" t="s">
         <v>8</v>
       </c>
@@ -26512,10 +26792,10 @@
         <v>244</v>
       </c>
       <c r="C104" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>11</v>
@@ -26524,13 +26804,13 @@
         <v>12</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:8" ht="86.4">
       <c r="A105" s="2" t="s">
         <v>8</v>
       </c>
@@ -26538,10 +26818,10 @@
         <v>244</v>
       </c>
       <c r="C105" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>11</v>
@@ -26550,10 +26830,10 @@
         <v>12</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="H105" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -26564,10 +26844,10 @@
         <v>244</v>
       </c>
       <c r="C106" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>11</v>
@@ -26576,10 +26856,10 @@
         <v>12</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>639</v>
+        <v>251</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -26590,10 +26870,10 @@
         <v>244</v>
       </c>
       <c r="C107" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>11</v>
@@ -26602,10 +26882,10 @@
         <v>12</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>256</v>
+        <v>630</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -26616,10 +26896,10 @@
         <v>244</v>
       </c>
       <c r="C108" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>11</v>
@@ -26628,10 +26908,10 @@
         <v>12</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>654</v>
+        <v>256</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -26642,10 +26922,10 @@
         <v>244</v>
       </c>
       <c r="C109" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>11</v>
@@ -26654,10 +26934,10 @@
         <v>12</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>261</v>
+        <v>645</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -26668,10 +26948,10 @@
         <v>244</v>
       </c>
       <c r="C110" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>11</v>
@@ -26680,10 +26960,10 @@
         <v>12</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -26694,10 +26974,10 @@
         <v>244</v>
       </c>
       <c r="C111" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>11</v>
@@ -26706,24 +26986,24 @@
         <v>12</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>640</v>
+        <v>264</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="43.2">
+    <row r="112" spans="1:8">
       <c r="A112" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="C112" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>11</v>
@@ -26732,13 +27012,13 @@
         <v>12</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="H112" s="3" t="s">
-        <v>641</v>
+        <v>266</v>
+      </c>
+      <c r="H112" s="6" t="s">
+        <v>631</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="86.4">
+    <row r="113" spans="1:8" ht="43.2">
       <c r="A113" s="2" t="s">
         <v>8</v>
       </c>
@@ -26746,10 +27026,10 @@
         <v>267</v>
       </c>
       <c r="C113" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>11</v>
@@ -26757,14 +27037,14 @@
       <c r="F113" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G113" s="8" t="s">
-        <v>732</v>
+      <c r="G113" s="3" t="s">
+        <v>269</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" ht="86.4">
       <c r="A114" s="2" t="s">
         <v>8</v>
       </c>
@@ -26772,10 +27052,10 @@
         <v>267</v>
       </c>
       <c r="C114" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>11</v>
@@ -26783,11 +27063,11 @@
       <c r="F114" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G114" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="H114" t="s">
-        <v>643</v>
+      <c r="G114" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>633</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -26798,10 +27078,10 @@
         <v>267</v>
       </c>
       <c r="C115" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>11</v>
@@ -26810,10 +27090,10 @@
         <v>12</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="H115" t="s">
-        <v>644</v>
+        <v>634</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -26824,10 +27104,10 @@
         <v>267</v>
       </c>
       <c r="C116" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>11</v>
@@ -26836,10 +27116,10 @@
         <v>12</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H116" t="s">
-        <v>655</v>
+        <v>635</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -26850,10 +27130,10 @@
         <v>267</v>
       </c>
       <c r="C117" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>11</v>
@@ -26862,13 +27142,13 @@
         <v>12</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="H117" s="6" t="s">
-        <v>645</v>
+        <v>276</v>
+      </c>
+      <c r="H117" t="s">
+        <v>646</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="43.2">
+    <row r="118" spans="1:8">
       <c r="A118" s="2" t="s">
         <v>8</v>
       </c>
@@ -26876,10 +27156,10 @@
         <v>267</v>
       </c>
       <c r="C118" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>11</v>
@@ -26888,24 +27168,24 @@
         <v>12</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="28.8">
+    <row r="119" spans="1:8" ht="43.2">
       <c r="A119" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="C119" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>11</v>
@@ -26914,13 +27194,13 @@
         <v>12</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="H119" s="6" t="s">
-        <v>284</v>
+        <v>637</v>
       </c>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" ht="28.8">
       <c r="A120" s="2" t="s">
         <v>8</v>
       </c>
@@ -26928,10 +27208,10 @@
         <v>281</v>
       </c>
       <c r="C120" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>11</v>
@@ -26940,10 +27220,10 @@
         <v>12</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -26954,10 +27234,10 @@
         <v>281</v>
       </c>
       <c r="C121" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>11</v>
@@ -26966,24 +27246,24 @@
         <v>12</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H121" s="6" t="s">
-        <v>647</v>
+        <v>286</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="28.8">
+    <row r="122" spans="1:8">
       <c r="A122" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="C122" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>11</v>
@@ -26992,13 +27272,13 @@
         <v>12</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="H122" s="3" t="s">
-        <v>648</v>
+        <v>288</v>
+      </c>
+      <c r="H122" s="6" t="s">
+        <v>638</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:8" ht="28.8">
       <c r="A123" s="2" t="s">
         <v>8</v>
       </c>
@@ -27006,10 +27286,10 @@
         <v>289</v>
       </c>
       <c r="C123" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>11</v>
@@ -27018,24 +27298,24 @@
         <v>12</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="H123" t="s">
-        <v>649</v>
+        <v>291</v>
+      </c>
+      <c r="H123" s="3" t="s">
+        <v>639</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="86.4">
+    <row r="124" spans="1:8">
       <c r="A124" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C124" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>11</v>
@@ -27044,13 +27324,13 @@
         <v>12</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="H124" s="3" t="s">
-        <v>650</v>
+        <v>293</v>
+      </c>
+      <c r="H124" t="s">
+        <v>640</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="28.8">
+    <row r="125" spans="1:8" ht="86.4">
       <c r="A125" s="2" t="s">
         <v>8</v>
       </c>
@@ -27058,10 +27338,10 @@
         <v>294</v>
       </c>
       <c r="C125" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>11</v>
@@ -27070,10 +27350,10 @@
         <v>12</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="H125" s="6" t="s">
-        <v>651</v>
+        <v>296</v>
+      </c>
+      <c r="H125" s="3" t="s">
+        <v>641</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="28.8">
@@ -27084,10 +27364,10 @@
         <v>294</v>
       </c>
       <c r="C126" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>11</v>
@@ -27096,10 +27376,10 @@
         <v>12</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="H126" s="8" t="s">
-        <v>720</v>
+        <v>298</v>
+      </c>
+      <c r="H126" s="6" t="s">
+        <v>642</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="28.8">
@@ -27110,10 +27390,10 @@
         <v>294</v>
       </c>
       <c r="C127" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>11</v>
@@ -27122,10 +27402,10 @@
         <v>12</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H127" s="8" t="s">
-        <v>733</v>
+        <v>710</v>
       </c>
     </row>
     <row r="128" spans="1:8" ht="28.8">
@@ -27136,10 +27416,10 @@
         <v>294</v>
       </c>
       <c r="C128" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>11</v>
@@ -27148,13 +27428,13 @@
         <v>12</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H128" s="8" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:8" ht="28.8">
       <c r="A129" s="2" t="s">
         <v>8</v>
       </c>
@@ -27162,10 +27442,10 @@
         <v>294</v>
       </c>
       <c r="C129" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>11</v>
@@ -27174,10 +27454,10 @@
         <v>12</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H129" s="8" t="s">
-        <v>656</v>
+        <v>711</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -27188,10 +27468,10 @@
         <v>294</v>
       </c>
       <c r="C130" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>11</v>
@@ -27200,10 +27480,10 @@
         <v>12</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>309</v>
+        <v>306</v>
+      </c>
+      <c r="H130" s="8" t="s">
+        <v>647</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -27214,10 +27494,10 @@
         <v>294</v>
       </c>
       <c r="C131" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>11</v>
@@ -27226,10 +27506,10 @@
         <v>12</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="H131" s="3" t="s">
-        <v>719</v>
+        <v>308</v>
+      </c>
+      <c r="H131" s="6" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -27240,10 +27520,10 @@
         <v>294</v>
       </c>
       <c r="C132" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>11</v>
@@ -27252,24 +27532,24 @@
         <v>12</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>652</v>
+        <v>709</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="28.8">
+    <row r="133" spans="1:8">
       <c r="A133" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="C133" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>11</v>
@@ -27278,13 +27558,13 @@
         <v>12</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="H133" s="6" t="s">
-        <v>653</v>
+        <v>313</v>
+      </c>
+      <c r="H133" s="3" t="s">
+        <v>643</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="403.2">
+    <row r="134" spans="1:8" ht="28.8">
       <c r="A134" s="2" t="s">
         <v>8</v>
       </c>
@@ -27292,10 +27572,10 @@
         <v>314</v>
       </c>
       <c r="C134" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>11</v>
@@ -27304,24 +27584,24 @@
         <v>12</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="H134" s="3" t="s">
-        <v>746</v>
+        <v>316</v>
+      </c>
+      <c r="H134" s="6" t="s">
+        <v>644</v>
       </c>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:8" ht="403.2">
       <c r="A135" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="C135" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>11</v>
@@ -27330,13 +27610,13 @@
         <v>12</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="H135" s="6" t="s">
-        <v>657</v>
+        <v>318</v>
+      </c>
+      <c r="H135" s="3" t="s">
+        <v>736</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="43.2">
+    <row r="136" spans="1:8">
       <c r="A136" s="2" t="s">
         <v>8</v>
       </c>
@@ -27344,10 +27624,10 @@
         <v>319</v>
       </c>
       <c r="C136" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>784</v>
+        <v>320</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>11</v>
@@ -27356,13 +27636,13 @@
         <v>12</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>785</v>
+        <v>321</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>783</v>
+        <v>648</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="100.8">
+    <row r="137" spans="1:8" ht="43.2">
       <c r="A137" s="2" t="s">
         <v>8</v>
       </c>
@@ -27370,10 +27650,10 @@
         <v>319</v>
       </c>
       <c r="C137" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>743</v>
+        <v>772</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>11</v>
@@ -27382,24 +27662,24 @@
         <v>12</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>744</v>
-      </c>
-      <c r="H137" s="3" t="s">
-        <v>722</v>
+        <v>773</v>
+      </c>
+      <c r="H137" s="6" t="s">
+        <v>771</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="115.2">
+    <row r="138" spans="1:8" ht="100.8">
       <c r="A138" s="2" t="s">
-        <v>752</v>
+        <v>8</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>762</v>
+        <v>319</v>
       </c>
       <c r="C138" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>763</v>
+        <v>733</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>11</v>
@@ -27408,24 +27688,24 @@
         <v>12</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>764</v>
+        <v>734</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>765</v>
+        <v>712</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="409.6">
+    <row r="139" spans="1:8" ht="115.2">
       <c r="A139" s="2" t="s">
-        <v>8</v>
+        <v>742</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>319</v>
+        <v>752</v>
       </c>
       <c r="C139" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>322</v>
+        <v>753</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>11</v>
@@ -27434,24 +27714,24 @@
         <v>12</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>323</v>
+        <v>754</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>774</v>
+        <v>755</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="28.8">
+    <row r="140" spans="1:8" ht="409.6">
       <c r="A140" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C140" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>11</v>
@@ -27460,24 +27740,24 @@
         <v>12</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>658</v>
+        <v>323</v>
+      </c>
+      <c r="H140" s="3" t="s">
+        <v>764</v>
       </c>
     </row>
-    <row r="141" spans="1:8">
+    <row r="141" spans="1:8" ht="28.8">
       <c r="A141" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C141" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>11</v>
@@ -27486,13 +27766,13 @@
         <v>12</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="H141" s="6" t="s">
-        <v>659</v>
+        <v>649</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="57.6">
+    <row r="142" spans="1:8">
       <c r="A142" s="2" t="s">
         <v>8</v>
       </c>
@@ -27500,10 +27780,10 @@
         <v>327</v>
       </c>
       <c r="C142" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>11</v>
@@ -27512,13 +27792,13 @@
         <v>12</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>660</v>
+        <v>650</v>
       </c>
     </row>
-    <row r="143" spans="1:8">
+    <row r="143" spans="1:8" ht="57.6">
       <c r="A143" s="2" t="s">
         <v>8</v>
       </c>
@@ -27526,10 +27806,10 @@
         <v>327</v>
       </c>
       <c r="C143" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>11</v>
@@ -27538,13 +27818,13 @@
         <v>12</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H143" s="6" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
     </row>
-    <row r="144" spans="1:8" ht="43.2">
+    <row r="144" spans="1:8">
       <c r="A144" s="2" t="s">
         <v>8</v>
       </c>
@@ -27552,10 +27832,10 @@
         <v>327</v>
       </c>
       <c r="C144" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>11</v>
@@ -27564,13 +27844,13 @@
         <v>12</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>662</v>
+        <v>652</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="86.4">
+    <row r="145" spans="1:8" ht="43.2">
       <c r="A145" s="2" t="s">
         <v>8</v>
       </c>
@@ -27578,10 +27858,10 @@
         <v>327</v>
       </c>
       <c r="C145" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>11</v>
@@ -27590,13 +27870,13 @@
         <v>12</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H145" s="3" t="s">
-        <v>663</v>
+        <v>335</v>
+      </c>
+      <c r="H145" s="6" t="s">
+        <v>653</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="216">
+    <row r="146" spans="1:8" ht="86.4">
       <c r="A146" s="2" t="s">
         <v>8</v>
       </c>
@@ -27604,10 +27884,10 @@
         <v>327</v>
       </c>
       <c r="C146" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>11</v>
@@ -27616,24 +27896,24 @@
         <v>12</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>664</v>
+        <v>654</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="86.4">
+    <row r="147" spans="1:8" ht="216">
       <c r="A147" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="C147" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>11</v>
@@ -27642,10 +27922,10 @@
         <v>12</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>343</v>
+        <v>655</v>
       </c>
     </row>
     <row r="148" spans="1:8" ht="86.4">
@@ -27656,10 +27936,10 @@
         <v>340</v>
       </c>
       <c r="C148" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>11</v>
@@ -27668,13 +27948,13 @@
         <v>12</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>768</v>
+        <v>343</v>
       </c>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:8" ht="86.4">
       <c r="A149" s="2" t="s">
         <v>8</v>
       </c>
@@ -27682,10 +27962,10 @@
         <v>340</v>
       </c>
       <c r="C149" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>11</v>
@@ -27694,24 +27974,24 @@
         <v>12</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="H149" s="6" t="s">
-        <v>348</v>
+        <v>345</v>
+      </c>
+      <c r="H149" s="3" t="s">
+        <v>758</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="86.4">
+    <row r="150" spans="1:8">
       <c r="A150" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="C150" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>11</v>
@@ -27720,24 +28000,24 @@
         <v>12</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="H150" s="3" t="s">
-        <v>665</v>
+        <v>347</v>
+      </c>
+      <c r="H150" s="6" t="s">
+        <v>348</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="28.8">
+    <row r="151" spans="1:8" ht="86.4">
       <c r="A151" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C151" s="2">
         <v>0</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>11</v>
@@ -27746,13 +28026,13 @@
         <v>12</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>666</v>
+        <v>656</v>
       </c>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" spans="1:8" ht="28.8">
       <c r="A152" s="2" t="s">
         <v>8</v>
       </c>
@@ -27760,10 +28040,10 @@
         <v>352</v>
       </c>
       <c r="C152" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>11</v>
@@ -27772,24 +28052,24 @@
         <v>12</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="H152" s="3" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="129.6">
+    <row r="153" spans="1:8">
       <c r="A153" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C153" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>11</v>
@@ -27798,13 +28078,13 @@
         <v>12</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="H153" s="3" t="s">
-        <v>747</v>
+        <v>658</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="28.8">
+    <row r="154" spans="1:8" ht="129.6">
       <c r="A154" s="2" t="s">
         <v>8</v>
       </c>
@@ -27812,10 +28092,10 @@
         <v>357</v>
       </c>
       <c r="C154" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>11</v>
@@ -27824,10 +28104,10 @@
         <v>12</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="H154" s="6" t="s">
-        <v>362</v>
+        <v>359</v>
+      </c>
+      <c r="H154" s="3" t="s">
+        <v>737</v>
       </c>
     </row>
     <row r="155" spans="1:8" ht="28.8">
@@ -27835,13 +28115,13 @@
         <v>8</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="C155" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>11</v>
@@ -27850,13 +28130,13 @@
         <v>12</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="H155" s="3" t="s">
-        <v>366</v>
+        <v>361</v>
+      </c>
+      <c r="H155" s="6" t="s">
+        <v>362</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="115.2">
+    <row r="156" spans="1:8" ht="28.8">
       <c r="A156" s="2" t="s">
         <v>8</v>
       </c>
@@ -27864,10 +28144,10 @@
         <v>363</v>
       </c>
       <c r="C156" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>11</v>
@@ -27876,24 +28156,24 @@
         <v>12</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>668</v>
+        <v>366</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="28.8">
+    <row r="157" spans="1:8" ht="115.2">
       <c r="A157" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="C157" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>11</v>
@@ -27902,13 +28182,13 @@
         <v>12</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="H157" s="6" t="s">
-        <v>669</v>
+        <v>368</v>
+      </c>
+      <c r="H157" s="3" t="s">
+        <v>659</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="409.6">
+    <row r="158" spans="1:8" ht="28.8">
       <c r="A158" s="2" t="s">
         <v>8</v>
       </c>
@@ -27916,10 +28196,10 @@
         <v>369</v>
       </c>
       <c r="C158" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>11</v>
@@ -27928,24 +28208,24 @@
         <v>12</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="H158" s="3" t="s">
-        <v>723</v>
+        <v>371</v>
+      </c>
+      <c r="H158" s="6" t="s">
+        <v>660</v>
       </c>
     </row>
-    <row r="159" spans="1:8" ht="43.2">
+    <row r="159" spans="1:8" ht="409.6">
       <c r="A159" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C159" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>11</v>
@@ -27954,13 +28234,13 @@
         <v>12</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="H159" s="6" t="s">
-        <v>670</v>
+        <v>373</v>
+      </c>
+      <c r="H159" s="3" t="s">
+        <v>713</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="86.4">
+    <row r="160" spans="1:8" ht="43.2">
       <c r="A160" s="2" t="s">
         <v>8</v>
       </c>
@@ -27968,10 +28248,10 @@
         <v>374</v>
       </c>
       <c r="C160" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>11</v>
@@ -27980,24 +28260,24 @@
         <v>12</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="H160" s="3" t="s">
-        <v>379</v>
+        <v>376</v>
+      </c>
+      <c r="H160" s="6" t="s">
+        <v>661</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="28.8">
+    <row r="161" spans="1:8" ht="86.4">
       <c r="A161" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="C161" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>11</v>
@@ -28006,13 +28286,13 @@
         <v>12</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="H161" s="6" t="s">
-        <v>383</v>
+        <v>378</v>
+      </c>
+      <c r="H161" s="3" t="s">
+        <v>379</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="144">
+    <row r="162" spans="1:8" ht="28.8">
       <c r="A162" s="2" t="s">
         <v>8</v>
       </c>
@@ -28020,10 +28300,10 @@
         <v>380</v>
       </c>
       <c r="C162" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>11</v>
@@ -28032,24 +28312,24 @@
         <v>12</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>724</v>
+        <v>383</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="100.8">
+    <row r="163" spans="1:8" ht="144">
       <c r="A163" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="C163" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>11</v>
@@ -28058,13 +28338,13 @@
         <v>12</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="H163" s="3" t="s">
-        <v>671</v>
+        <v>385</v>
+      </c>
+      <c r="H163" s="6" t="s">
+        <v>714</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="144">
+    <row r="164" spans="1:8" ht="100.8">
       <c r="A164" s="2" t="s">
         <v>8</v>
       </c>
@@ -28072,10 +28352,10 @@
         <v>386</v>
       </c>
       <c r="C164" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>11</v>
@@ -28084,24 +28364,24 @@
         <v>12</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>725</v>
+        <v>662</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="100.8">
+    <row r="165" spans="1:8" ht="144">
       <c r="A165" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C165" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>11</v>
@@ -28110,13 +28390,13 @@
         <v>12</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>672</v>
+        <v>715</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="43.2">
+    <row r="166" spans="1:8" ht="100.8">
       <c r="A166" s="2" t="s">
         <v>8</v>
       </c>
@@ -28124,10 +28404,10 @@
         <v>391</v>
       </c>
       <c r="C166" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>11</v>
@@ -28136,24 +28416,24 @@
         <v>12</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="H166" s="6" t="s">
-        <v>673</v>
+        <v>393</v>
+      </c>
+      <c r="H166" s="3" t="s">
+        <v>663</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="115.2">
+    <row r="167" spans="1:8" ht="43.2">
       <c r="A167" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C167" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>11</v>
@@ -28162,13 +28442,13 @@
         <v>12</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="H167" s="3" t="s">
-        <v>674</v>
+        <v>395</v>
+      </c>
+      <c r="H167" s="6" t="s">
+        <v>664</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="86.4">
+    <row r="168" spans="1:8" ht="115.2">
       <c r="A168" s="2" t="s">
         <v>8</v>
       </c>
@@ -28176,10 +28456,10 @@
         <v>396</v>
       </c>
       <c r="C168" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>11</v>
@@ -28188,10 +28468,10 @@
         <v>12</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>401</v>
+        <v>665</v>
       </c>
     </row>
     <row r="169" spans="1:8" ht="86.4">
@@ -28199,13 +28479,13 @@
         <v>8</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C169" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>11</v>
@@ -28214,24 +28494,24 @@
         <v>12</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="H169" s="3" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="28.8">
+    <row r="170" spans="1:8" ht="86.4">
       <c r="A170" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C170" s="2">
         <v>0</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>11</v>
@@ -28240,13 +28520,13 @@
         <v>12</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="H170" s="3" t="s">
-        <v>726</v>
+        <v>405</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="57.6">
+    <row r="171" spans="1:8" ht="28.8">
       <c r="A171" s="2" t="s">
         <v>8</v>
       </c>
@@ -28254,10 +28534,10 @@
         <v>406</v>
       </c>
       <c r="C171" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>11</v>
@@ -28266,13 +28546,13 @@
         <v>12</v>
       </c>
       <c r="G171" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H171" s="3" t="s">
-        <v>411</v>
+        <v>716</v>
       </c>
     </row>
-    <row r="172" spans="1:8">
+    <row r="172" spans="1:8" ht="57.6">
       <c r="A172" s="2" t="s">
         <v>8</v>
       </c>
@@ -28280,10 +28560,10 @@
         <v>406</v>
       </c>
       <c r="C172" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>11</v>
@@ -28292,24 +28572,24 @@
         <v>12</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="H172" s="3" t="s">
-        <v>684</v>
+        <v>411</v>
       </c>
     </row>
-    <row r="173" spans="1:8" ht="57.6">
+    <row r="173" spans="1:8">
       <c r="A173" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="C173" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>11</v>
@@ -28318,13 +28598,13 @@
         <v>12</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="H173" s="6" t="s">
-        <v>685</v>
+        <v>413</v>
+      </c>
+      <c r="H173" s="3" t="s">
+        <v>675</v>
       </c>
     </row>
-    <row r="174" spans="1:8" ht="28.8">
+    <row r="174" spans="1:8" ht="57.6">
       <c r="A174" s="2" t="s">
         <v>8</v>
       </c>
@@ -28332,10 +28612,10 @@
         <v>414</v>
       </c>
       <c r="C174" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>11</v>
@@ -28344,10 +28624,10 @@
         <v>12</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="H174" s="6" t="s">
-        <v>419</v>
+        <v>676</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="28.8">
@@ -28355,13 +28635,13 @@
         <v>8</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C175" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>11</v>
@@ -28370,13 +28650,13 @@
         <v>12</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="H175" s="6" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="409.6">
+    <row r="176" spans="1:8" ht="28.8">
       <c r="A176" s="2" t="s">
         <v>8</v>
       </c>
@@ -28384,10 +28664,10 @@
         <v>420</v>
       </c>
       <c r="C176" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>11</v>
@@ -28396,24 +28676,24 @@
         <v>12</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>686</v>
-      </c>
-      <c r="H176" s="3" t="s">
-        <v>727</v>
+        <v>422</v>
+      </c>
+      <c r="H176" s="6" t="s">
+        <v>423</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="28.8">
+    <row r="177" spans="1:8" ht="409.6">
       <c r="A177" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C177" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>11</v>
@@ -28422,13 +28702,13 @@
         <v>12</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="H177" s="6" t="s">
-        <v>428</v>
+        <v>677</v>
+      </c>
+      <c r="H177" s="3" t="s">
+        <v>717</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="409.6">
+    <row r="178" spans="1:8" ht="28.8">
       <c r="A178" s="2" t="s">
         <v>8</v>
       </c>
@@ -28436,10 +28716,10 @@
         <v>425</v>
       </c>
       <c r="C178" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>778</v>
+        <v>426</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>11</v>
@@ -28448,13 +28728,13 @@
         <v>12</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="H178" s="3" t="s">
-        <v>780</v>
+        <v>427</v>
+      </c>
+      <c r="H178" s="6" t="s">
+        <v>428</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="201.6">
+    <row r="179" spans="1:8" ht="409.6">
       <c r="A179" s="2" t="s">
         <v>8</v>
       </c>
@@ -28462,10 +28742,10 @@
         <v>425</v>
       </c>
       <c r="C179" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>429</v>
+        <v>768</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>11</v>
@@ -28474,24 +28754,24 @@
         <v>12</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>430</v>
+        <v>769</v>
       </c>
       <c r="H179" s="3" t="s">
-        <v>756</v>
+        <v>770</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="86.4">
+    <row r="180" spans="1:8" ht="201.6">
       <c r="A180" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="C180" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>11</v>
@@ -28500,24 +28780,24 @@
         <v>12</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H180" s="3" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
-    <row r="181" spans="1:8">
+    <row r="181" spans="1:8" ht="86.4">
       <c r="A181" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C181" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>11</v>
@@ -28526,10 +28806,10 @@
         <v>12</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="H181" s="6" t="s">
-        <v>29</v>
+        <v>433</v>
+      </c>
+      <c r="H181" s="3" t="s">
+        <v>738</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -28537,13 +28817,13 @@
         <v>8</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C182" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>11</v>
@@ -28552,10 +28832,10 @@
         <v>12</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>690</v>
+        <v>29</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -28563,13 +28843,13 @@
         <v>8</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C183" s="2">
         <v>0</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>11</v>
@@ -28578,10 +28858,10 @@
         <v>12</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="H183" s="6" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -28589,13 +28869,13 @@
         <v>8</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C184" s="2">
         <v>0</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>11</v>
@@ -28604,10 +28884,10 @@
         <v>12</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -28615,13 +28895,13 @@
         <v>8</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C185" s="2">
         <v>0</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>11</v>
@@ -28630,10 +28910,10 @@
         <v>12</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="H185" s="6" t="s">
-        <v>691</v>
+        <v>679</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -28641,13 +28921,13 @@
         <v>8</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C186" s="2">
         <v>0</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>11</v>
@@ -28656,24 +28936,24 @@
         <v>12</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="144">
+    <row r="187" spans="1:8">
       <c r="A187" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C187" s="2">
         <v>0</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>11</v>
@@ -28682,13 +28962,13 @@
         <v>12</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="H187" s="3" t="s">
-        <v>692</v>
+        <v>451</v>
+      </c>
+      <c r="H187" s="6" t="s">
+        <v>680</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="28.8">
+    <row r="188" spans="1:8" ht="144">
       <c r="A188" s="2" t="s">
         <v>8</v>
       </c>
@@ -28696,10 +28976,10 @@
         <v>452</v>
       </c>
       <c r="C188" s="2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>11</v>
@@ -28708,10 +28988,10 @@
         <v>12</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="H188" s="6" t="s">
-        <v>457</v>
+        <v>454</v>
+      </c>
+      <c r="H188" s="3" t="s">
+        <v>683</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="28.8">
@@ -28722,10 +29002,10 @@
         <v>452</v>
       </c>
       <c r="C189" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>11</v>
@@ -28734,13 +29014,13 @@
         <v>12</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="H189" s="6" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="57.6">
+    <row r="190" spans="1:8" ht="28.8">
       <c r="A190" s="2" t="s">
         <v>8</v>
       </c>
@@ -28748,10 +29028,10 @@
         <v>452</v>
       </c>
       <c r="C190" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>11</v>
@@ -28760,13 +29040,13 @@
         <v>12</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="H190" s="3" t="s">
-        <v>463</v>
+        <v>459</v>
+      </c>
+      <c r="H190" s="6" t="s">
+        <v>460</v>
       </c>
     </row>
-    <row r="191" spans="1:8" ht="28.8">
+    <row r="191" spans="1:8" ht="57.6">
       <c r="A191" s="2" t="s">
         <v>8</v>
       </c>
@@ -28774,10 +29054,10 @@
         <v>452</v>
       </c>
       <c r="C191" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>11</v>
@@ -28786,13 +29066,13 @@
         <v>12</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="H191" s="6" t="s">
-        <v>466</v>
+        <v>462</v>
+      </c>
+      <c r="H191" s="3" t="s">
+        <v>463</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="57.6">
+    <row r="192" spans="1:8" ht="28.8">
       <c r="A192" s="2" t="s">
         <v>8</v>
       </c>
@@ -28800,10 +29080,10 @@
         <v>452</v>
       </c>
       <c r="C192" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>11</v>
@@ -28812,13 +29092,13 @@
         <v>12</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="H192" s="3" t="s">
-        <v>469</v>
+        <v>465</v>
+      </c>
+      <c r="H192" s="6" t="s">
+        <v>466</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="43.2">
+    <row r="193" spans="1:8" ht="57.6">
       <c r="A193" s="2" t="s">
         <v>8</v>
       </c>
@@ -28826,10 +29106,10 @@
         <v>452</v>
       </c>
       <c r="C193" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>11</v>
@@ -28838,13 +29118,13 @@
         <v>12</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="H193" s="6" t="s">
-        <v>472</v>
+        <v>468</v>
+      </c>
+      <c r="H193" s="3" t="s">
+        <v>469</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="28.8">
+    <row r="194" spans="1:8" ht="43.2">
       <c r="A194" s="2" t="s">
         <v>8</v>
       </c>
@@ -28852,10 +29132,10 @@
         <v>452</v>
       </c>
       <c r="C194" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>11</v>
@@ -28864,10 +29144,10 @@
         <v>12</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H194" s="6" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="195" spans="1:8" ht="28.8">
@@ -28878,10 +29158,10 @@
         <v>452</v>
       </c>
       <c r="C195" s="2">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>11</v>
@@ -28890,13 +29170,13 @@
         <v>12</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="H195" s="6" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
-    <row r="196" spans="1:8" ht="244.8">
+    <row r="196" spans="1:8" ht="28.8">
       <c r="A196" s="2" t="s">
         <v>8</v>
       </c>
@@ -28904,10 +29184,10 @@
         <v>452</v>
       </c>
       <c r="C196" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>11</v>
@@ -28916,13 +29196,13 @@
         <v>12</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="H196" s="6" t="s">
-        <v>693</v>
+        <v>478</v>
       </c>
     </row>
-    <row r="197" spans="1:8">
+    <row r="197" spans="1:8" ht="244.8">
       <c r="A197" s="2" t="s">
         <v>8</v>
       </c>
@@ -28930,10 +29210,10 @@
         <v>452</v>
       </c>
       <c r="C197" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>11</v>
@@ -28942,24 +29222,24 @@
         <v>12</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="H197" s="6" t="s">
-        <v>14</v>
+        <v>684</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="28.8">
+    <row r="198" spans="1:8">
       <c r="A198" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>483</v>
+        <v>452</v>
       </c>
       <c r="C198" s="2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>11</v>
@@ -28968,10 +29248,10 @@
         <v>12</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="H198" s="6" t="s">
-        <v>486</v>
+        <v>14</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="28.8">
@@ -28982,10 +29262,10 @@
         <v>483</v>
       </c>
       <c r="C199" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>11</v>
@@ -28994,13 +29274,13 @@
         <v>12</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="H199" t="s">
-        <v>728</v>
+        <v>485</v>
+      </c>
+      <c r="H199" s="6" t="s">
+        <v>486</v>
       </c>
     </row>
-    <row r="200" spans="1:8">
+    <row r="200" spans="1:8" ht="28.8">
       <c r="A200" s="2" t="s">
         <v>8</v>
       </c>
@@ -29008,10 +29288,10 @@
         <v>483</v>
       </c>
       <c r="C200" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>11</v>
@@ -29020,13 +29300,13 @@
         <v>12</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="H200" s="6" t="s">
-        <v>729</v>
+        <v>488</v>
+      </c>
+      <c r="H200" t="s">
+        <v>718</v>
       </c>
     </row>
-    <row r="201" spans="1:8" ht="100.8">
+    <row r="201" spans="1:8">
       <c r="A201" s="2" t="s">
         <v>8</v>
       </c>
@@ -29034,10 +29314,10 @@
         <v>483</v>
       </c>
       <c r="C201" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>11</v>
@@ -29046,13 +29326,13 @@
         <v>12</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="H201" s="3" t="s">
-        <v>749</v>
+        <v>490</v>
+      </c>
+      <c r="H201" s="6" t="s">
+        <v>719</v>
       </c>
     </row>
-    <row r="202" spans="1:8" ht="158.4">
+    <row r="202" spans="1:8" ht="100.8">
       <c r="A202" s="2" t="s">
         <v>8</v>
       </c>
@@ -29060,10 +29340,10 @@
         <v>483</v>
       </c>
       <c r="C202" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>11</v>
@@ -29072,13 +29352,13 @@
         <v>12</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="H202" s="3" t="s">
-        <v>694</v>
+        <v>739</v>
       </c>
     </row>
-    <row r="203" spans="1:8" ht="43.2">
+    <row r="203" spans="1:8" ht="158.4">
       <c r="A203" s="2" t="s">
         <v>8</v>
       </c>
@@ -29086,10 +29366,10 @@
         <v>483</v>
       </c>
       <c r="C203" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>11</v>
@@ -29098,13 +29378,13 @@
         <v>12</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="H203" s="3" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
     </row>
-    <row r="204" spans="1:8" ht="100.8">
+    <row r="204" spans="1:8" ht="43.2">
       <c r="A204" s="2" t="s">
         <v>8</v>
       </c>
@@ -29112,10 +29392,10 @@
         <v>483</v>
       </c>
       <c r="C204" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>11</v>
@@ -29124,13 +29404,13 @@
         <v>12</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="H204" s="3" t="s">
-        <v>696</v>
+        <v>686</v>
       </c>
     </row>
-    <row r="205" spans="1:8" ht="43.2">
+    <row r="205" spans="1:8" ht="100.8">
       <c r="A205" s="2" t="s">
         <v>8</v>
       </c>
@@ -29138,10 +29418,10 @@
         <v>483</v>
       </c>
       <c r="C205" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>11</v>
@@ -29150,13 +29430,13 @@
         <v>12</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="H205" s="3" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
     </row>
-    <row r="206" spans="1:8" ht="100.8">
+    <row r="206" spans="1:8" ht="43.2">
       <c r="A206" s="2" t="s">
         <v>8</v>
       </c>
@@ -29164,10 +29444,10 @@
         <v>483</v>
       </c>
       <c r="C206" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>11</v>
@@ -29176,10 +29456,10 @@
         <v>12</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="H206" s="3" t="s">
-        <v>698</v>
+        <v>688</v>
       </c>
     </row>
     <row r="207" spans="1:8" ht="100.8">
@@ -29190,10 +29470,10 @@
         <v>483</v>
       </c>
       <c r="C207" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>11</v>
@@ -29202,13 +29482,13 @@
         <v>12</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="H207" s="3" t="s">
-        <v>730</v>
+        <v>689</v>
       </c>
     </row>
-    <row r="208" spans="1:8" ht="115.2">
+    <row r="208" spans="1:8" ht="100.8">
       <c r="A208" s="2" t="s">
         <v>8</v>
       </c>
@@ -29216,10 +29496,10 @@
         <v>483</v>
       </c>
       <c r="C208" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>11</v>
@@ -29228,13 +29508,13 @@
         <v>12</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="H208" s="3" t="s">
-        <v>699</v>
+        <v>720</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="158.4">
+    <row r="209" spans="1:9" ht="115.2">
       <c r="A209" s="2" t="s">
         <v>8</v>
       </c>
@@ -29242,10 +29522,10 @@
         <v>483</v>
       </c>
       <c r="C209" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>11</v>
@@ -29254,13 +29534,13 @@
         <v>12</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="H209" s="3" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="172.8">
+    <row r="210" spans="1:9" ht="158.4">
       <c r="A210" s="2" t="s">
         <v>8</v>
       </c>
@@ -29268,10 +29548,10 @@
         <v>483</v>
       </c>
       <c r="C210" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>11</v>
@@ -29280,13 +29560,13 @@
         <v>12</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="H210" s="3" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="115.2">
+    <row r="211" spans="1:9" ht="172.8">
       <c r="A211" s="2" t="s">
         <v>8</v>
       </c>
@@ -29294,10 +29574,10 @@
         <v>483</v>
       </c>
       <c r="C211" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>11</v>
@@ -29306,13 +29586,13 @@
         <v>12</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="H211" s="3" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="158.4">
+    <row r="212" spans="1:9" ht="115.2">
       <c r="A212" s="2" t="s">
         <v>8</v>
       </c>
@@ -29320,10 +29600,10 @@
         <v>483</v>
       </c>
       <c r="C212" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>11</v>
@@ -29332,10 +29612,10 @@
         <v>12</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>750</v>
+        <v>512</v>
       </c>
       <c r="H212" s="3" t="s">
-        <v>751</v>
+        <v>693</v>
       </c>
     </row>
     <row r="213" spans="1:9" ht="158.4">
@@ -29346,10 +29626,10 @@
         <v>483</v>
       </c>
       <c r="C213" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>11</v>
@@ -29358,13 +29638,13 @@
         <v>12</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>515</v>
+        <v>740</v>
       </c>
       <c r="H213" s="3" t="s">
-        <v>703</v>
+        <v>741</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="100.8">
+    <row r="214" spans="1:9" ht="158.4">
       <c r="A214" s="2" t="s">
         <v>8</v>
       </c>
@@ -29372,10 +29652,10 @@
         <v>483</v>
       </c>
       <c r="C214" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>11</v>
@@ -29384,13 +29664,13 @@
         <v>12</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="H214" s="3" t="s">
-        <v>781</v>
+        <v>694</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="100.8">
+    <row r="215" spans="1:9" ht="187.2">
       <c r="A215" s="2" t="s">
         <v>8</v>
       </c>
@@ -29398,10 +29678,10 @@
         <v>483</v>
       </c>
       <c r="C215" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>518</v>
+        <v>801</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>11</v>
@@ -29410,13 +29690,13 @@
         <v>12</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>519</v>
+        <v>803</v>
       </c>
       <c r="H215" s="3" t="s">
-        <v>782</v>
+        <v>804</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="43.2">
+    <row r="216" spans="1:9" ht="187.2">
       <c r="A216" s="2" t="s">
         <v>8</v>
       </c>
@@ -29424,10 +29704,10 @@
         <v>483</v>
       </c>
       <c r="C216" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>520</v>
+        <v>802</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>11</v>
@@ -29436,13 +29716,13 @@
         <v>12</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>521</v>
+        <v>805</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>704</v>
+        <v>806</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="43.2">
+    <row r="217" spans="1:9" ht="100.8">
       <c r="A217" s="2" t="s">
         <v>8</v>
       </c>
@@ -29450,10 +29730,10 @@
         <v>483</v>
       </c>
       <c r="C217" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>522</v>
+        <v>795</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>11</v>
@@ -29462,13 +29742,13 @@
         <v>12</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>523</v>
+        <v>796</v>
       </c>
       <c r="H217" s="3" t="s">
-        <v>524</v>
+        <v>799</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="43.2">
+    <row r="218" spans="1:9" ht="100.8">
       <c r="A218" s="2" t="s">
         <v>8</v>
       </c>
@@ -29476,10 +29756,10 @@
         <v>483</v>
       </c>
       <c r="C218" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>525</v>
+        <v>797</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>11</v>
@@ -29488,13 +29768,13 @@
         <v>12</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>526</v>
+        <v>798</v>
       </c>
       <c r="H218" s="3" t="s">
-        <v>705</v>
+        <v>800</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="409.6">
+    <row r="219" spans="1:9" ht="43.2">
       <c r="A219" s="2" t="s">
         <v>8</v>
       </c>
@@ -29502,10 +29782,10 @@
         <v>483</v>
       </c>
       <c r="C219" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>775</v>
+        <v>516</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>11</v>
@@ -29514,14 +29794,13 @@
         <v>12</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>776</v>
+        <v>517</v>
       </c>
       <c r="H219" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="I219" s="3"/>
+        <v>695</v>
+      </c>
     </row>
-    <row r="220" spans="1:9" ht="115.2">
+    <row r="220" spans="1:9" ht="409.6">
       <c r="A220" s="2" t="s">
         <v>8</v>
       </c>
@@ -29529,10 +29808,10 @@
         <v>483</v>
       </c>
       <c r="C220" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>527</v>
+        <v>765</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>11</v>
@@ -29541,13 +29820,14 @@
         <v>12</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>528</v>
+        <v>766</v>
       </c>
       <c r="H220" s="3" t="s">
-        <v>706</v>
-      </c>
+        <v>767</v>
+      </c>
+      <c r="I220" s="3"/>
     </row>
-    <row r="221" spans="1:9" ht="43.2">
+    <row r="221" spans="1:9" ht="115.2">
       <c r="A221" s="2" t="s">
         <v>8</v>
       </c>
@@ -29555,10 +29835,10 @@
         <v>483</v>
       </c>
       <c r="C221" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>11</v>
@@ -29567,13 +29847,13 @@
         <v>12</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="H221" s="3" t="s">
-        <v>531</v>
+        <v>696</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="86.4">
+    <row r="222" spans="1:9" ht="43.2">
       <c r="A222" s="2" t="s">
         <v>8</v>
       </c>
@@ -29581,10 +29861,10 @@
         <v>483</v>
       </c>
       <c r="C222" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>11</v>
@@ -29593,13 +29873,13 @@
         <v>12</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="H222" s="3" t="s">
-        <v>675</v>
+        <v>522</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="115.2">
+    <row r="223" spans="1:9" ht="86.4">
       <c r="A223" s="2" t="s">
         <v>8</v>
       </c>
@@ -29607,10 +29887,10 @@
         <v>483</v>
       </c>
       <c r="C223" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>534</v>
+        <v>523</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>11</v>
@@ -29619,13 +29899,13 @@
         <v>12</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>535</v>
+        <v>524</v>
       </c>
       <c r="H223" s="3" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="43.2">
+    <row r="224" spans="1:9" ht="115.2">
       <c r="A224" s="2" t="s">
         <v>8</v>
       </c>
@@ -29633,10 +29913,10 @@
         <v>483</v>
       </c>
       <c r="C224" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>536</v>
+        <v>525</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>11</v>
@@ -29645,13 +29925,13 @@
         <v>12</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>537</v>
+        <v>526</v>
       </c>
       <c r="H224" s="3" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
     </row>
-    <row r="225" spans="1:8" ht="100.8">
+    <row r="225" spans="1:8" ht="43.2">
       <c r="A225" s="2" t="s">
         <v>8</v>
       </c>
@@ -29659,10 +29939,10 @@
         <v>483</v>
       </c>
       <c r="C225" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>11</v>
@@ -29671,13 +29951,13 @@
         <v>12</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="H225" s="3" t="s">
-        <v>731</v>
+        <v>668</v>
       </c>
     </row>
-    <row r="226" spans="1:8" ht="43.2">
+    <row r="226" spans="1:8" ht="100.8">
       <c r="A226" s="2" t="s">
         <v>8</v>
       </c>
@@ -29685,10 +29965,10 @@
         <v>483</v>
       </c>
       <c r="C226" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>11</v>
@@ -29697,10 +29977,10 @@
         <v>12</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="H226" s="3" t="s">
-        <v>542</v>
+        <v>721</v>
       </c>
     </row>
     <row r="227" spans="1:8" ht="43.2">
@@ -29711,10 +29991,10 @@
         <v>483</v>
       </c>
       <c r="C227" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>11</v>
@@ -29723,13 +30003,13 @@
         <v>12</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="H227" s="3" t="s">
-        <v>678</v>
+        <v>533</v>
       </c>
     </row>
-    <row r="228" spans="1:8" ht="100.8">
+    <row r="228" spans="1:8" ht="43.2">
       <c r="A228" s="2" t="s">
         <v>8</v>
       </c>
@@ -29737,10 +30017,10 @@
         <v>483</v>
       </c>
       <c r="C228" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>11</v>
@@ -29749,24 +30029,24 @@
         <v>12</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>546</v>
+        <v>535</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
     </row>
-    <row r="229" spans="1:8" ht="28.8">
+    <row r="229" spans="1:8" ht="100.8">
       <c r="A229" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>547</v>
+        <v>483</v>
       </c>
       <c r="C229" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>11</v>
@@ -29775,10 +30055,10 @@
         <v>12</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="H229" s="6" t="s">
-        <v>680</v>
+        <v>537</v>
+      </c>
+      <c r="H229" s="3" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="230" spans="1:8" ht="28.8">
@@ -29786,13 +30066,13 @@
         <v>8</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="C230" s="2">
         <v>0</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>11</v>
@@ -29801,24 +30081,24 @@
         <v>12</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>552</v>
-      </c>
-      <c r="H230" s="3" t="s">
-        <v>553</v>
+        <v>540</v>
+      </c>
+      <c r="H230" s="6" t="s">
+        <v>671</v>
       </c>
     </row>
-    <row r="231" spans="1:8" ht="43.2">
+    <row r="231" spans="1:8" ht="28.8">
       <c r="A231" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="C231" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>11</v>
@@ -29827,24 +30107,24 @@
         <v>12</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="H231" s="3" t="s">
-        <v>681</v>
+        <v>544</v>
       </c>
     </row>
-    <row r="232" spans="1:8" ht="100.8">
+    <row r="232" spans="1:8" ht="43.2">
       <c r="A232" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="C232" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>556</v>
+        <v>545</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>11</v>
@@ -29853,24 +30133,24 @@
         <v>12</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>557</v>
+        <v>546</v>
       </c>
       <c r="H232" s="3" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
     </row>
-    <row r="233" spans="1:8" ht="43.2">
+    <row r="233" spans="1:8" ht="100.8">
       <c r="A233" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="C233" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>558</v>
+        <v>547</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>11</v>
@@ -29879,24 +30159,24 @@
         <v>12</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="H233" s="3" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
     </row>
-    <row r="234" spans="1:8">
+    <row r="234" spans="1:8" ht="43.2">
       <c r="A234" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>560</v>
+        <v>541</v>
       </c>
       <c r="C234" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>11</v>
@@ -29905,10 +30185,10 @@
         <v>12</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="H234" s="6" t="s">
-        <v>563</v>
+        <v>550</v>
+      </c>
+      <c r="H234" s="3" t="s">
+        <v>674</v>
       </c>
     </row>
     <row r="235" spans="1:8">
@@ -29916,13 +30196,13 @@
         <v>8</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>564</v>
+        <v>551</v>
       </c>
       <c r="C235" s="2">
         <v>0</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>11</v>
@@ -29931,24 +30211,24 @@
         <v>12</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="H235" s="6" t="s">
-        <v>586</v>
+        <v>554</v>
       </c>
     </row>
-    <row r="236" spans="1:8" ht="28.8">
+    <row r="236" spans="1:8">
       <c r="A236" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="C236" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>567</v>
+        <v>556</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>11</v>
@@ -29957,24 +30237,24 @@
         <v>12</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>568</v>
+        <v>557</v>
       </c>
       <c r="H236" s="6" t="s">
-        <v>622</v>
+        <v>577</v>
       </c>
     </row>
-    <row r="237" spans="1:8">
+    <row r="237" spans="1:8" ht="28.8">
       <c r="A237" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>569</v>
+        <v>555</v>
       </c>
       <c r="C237" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>11</v>
@@ -29983,24 +30263,24 @@
         <v>12</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="H237" s="6" t="s">
-        <v>572</v>
+        <v>613</v>
       </c>
     </row>
-    <row r="238" spans="1:8" ht="28.8">
+    <row r="238" spans="1:8">
       <c r="A238" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="C238" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>11</v>
@@ -30009,24 +30289,24 @@
         <v>12</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="H238" s="4" t="s">
-        <v>575</v>
+        <v>562</v>
+      </c>
+      <c r="H238" s="6" t="s">
+        <v>563</v>
       </c>
     </row>
-    <row r="239" spans="1:8">
+    <row r="239" spans="1:8" ht="28.8">
       <c r="A239" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>547</v>
+        <v>560</v>
       </c>
       <c r="C239" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>11</v>
@@ -30035,24 +30315,24 @@
         <v>12</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="H239" s="4" t="s">
-        <v>23</v>
+        <v>566</v>
       </c>
     </row>
-    <row r="240" spans="1:8" ht="28.8">
+    <row r="240" spans="1:8">
       <c r="A240" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="C240" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>11</v>
@@ -30061,24 +30341,24 @@
         <v>12</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>579</v>
+        <v>568</v>
       </c>
       <c r="H240" s="4" t="s">
-        <v>580</v>
+        <v>23</v>
       </c>
     </row>
-    <row r="241" spans="1:8">
+    <row r="241" spans="1:8" ht="28.8">
       <c r="A241" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>581</v>
+        <v>538</v>
       </c>
       <c r="C241" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>582</v>
+        <v>569</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>11</v>
@@ -30087,47 +30367,63 @@
         <v>12</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>583</v>
+        <v>570</v>
       </c>
       <c r="H241" s="4" t="s">
-        <v>584</v>
+        <v>571</v>
       </c>
     </row>
     <row r="242" spans="1:8">
-      <c r="A242" t="s">
-        <v>752</v>
-      </c>
-      <c r="B242" t="s">
-        <v>581</v>
-      </c>
-      <c r="C242">
-        <v>1</v>
-      </c>
-      <c r="D242" t="s">
-        <v>753</v>
-      </c>
-      <c r="E242" t="s">
+      <c r="A242" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="C242" s="2">
+        <v>0</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E242" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F242" t="s">
+      <c r="F242" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G242" t="s">
-        <v>754</v>
+      <c r="G242" s="3" t="s">
+        <v>574</v>
       </c>
       <c r="H242" s="4" t="s">
-        <v>755</v>
+        <v>575</v>
       </c>
     </row>
     <row r="243" spans="1:8">
-      <c r="A243" s="2"/>
-      <c r="B243" s="2"/>
-      <c r="C243" s="2"/>
-      <c r="D243" s="2"/>
-      <c r="E243" s="2"/>
-      <c r="F243" s="2"/>
-      <c r="G243" s="3"/>
-      <c r="H243" s="3"/>
+      <c r="A243" t="s">
+        <v>742</v>
+      </c>
+      <c r="B243" t="s">
+        <v>572</v>
+      </c>
+      <c r="C243">
+        <v>1</v>
+      </c>
+      <c r="D243" t="s">
+        <v>743</v>
+      </c>
+      <c r="E243" t="s">
+        <v>11</v>
+      </c>
+      <c r="F243" t="s">
+        <v>12</v>
+      </c>
+      <c r="G243" t="s">
+        <v>744</v>
+      </c>
+      <c r="H243" s="4" t="s">
+        <v>745</v>
+      </c>
     </row>
     <row r="244" spans="1:8">
       <c r="A244" s="2"/>
@@ -30139,6 +30435,16 @@
       <c r="G244" s="3"/>
       <c r="H244" s="3"/>
     </row>
+    <row r="245" spans="1:8">
+      <c r="A245" s="2"/>
+      <c r="B245" s="2"/>
+      <c r="C245" s="2"/>
+      <c r="D245" s="2"/>
+      <c r="E245" s="2"/>
+      <c r="F245" s="2"/>
+      <c r="G245" s="3"/>
+      <c r="H245" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
